--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,462 +436,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1111-05-32</t>
+          <t>1282_1_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1111-05-32/001.jpg,https://oleks-netizen.github.io/product-images/1111-05-32/003.jpg,https://oleks-netizen.github.io/product-images/1111-05-32/004.jpg,https://oleks-netizen.github.io/product-images/1111-05-32/005.jpg,https://oleks-netizen.github.io/product-images/1111-05-32/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1282_1_1/001.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1313-05-38</t>
+          <t>1282_1_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1313-05-38/001.jpg,https://oleks-netizen.github.io/product-images/1313-05-38/002.jpg,https://oleks-netizen.github.io/product-images/1313-05-38/003.jpg,https://oleks-netizen.github.io/product-images/1313-05-38/004.jpg,https://oleks-netizen.github.io/product-images/1313-05-38/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1282_1_2/001.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1313-18-38</t>
+          <t>1282_1_4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1313-18-38/001.jpg,https://oleks-netizen.github.io/product-images/1313-18-38/002.jpg,https://oleks-netizen.github.io/product-images/1313-18-38/003.jpg,https://oleks-netizen.github.io/product-images/1313-18-38/005.jpg,https://oleks-netizen.github.io/product-images/1313-18-38/006.jpg,https://oleks-netizen.github.io/product-images/1313-18-38/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1282_1_4/001.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1314-05-38</t>
+          <t>1282_1_5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1314-05-38/001.jpg,https://oleks-netizen.github.io/product-images/1314-05-38/002.jpg,https://oleks-netizen.github.io/product-images/1314-05-38/004.jpg,https://oleks-netizen.github.io/product-images/1314-05-38/005.jpg,https://oleks-netizen.github.io/product-images/1314-05-38/006.jpg,https://oleks-netizen.github.io/product-images/1314-05-38/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1282_1_5/001.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1314-06-38</t>
+          <t>1793_1_100</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1314-06-38/001.jpg,https://oleks-netizen.github.io/product-images/1314-06-38/002.jpg,https://oleks-netizen.github.io/product-images/1314-06-38/004.jpg,https://oleks-netizen.github.io/product-images/1314-06-38/005.jpg,https://oleks-netizen.github.io/product-images/1314-06-38/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1793_1_100/001.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1665-09-32</t>
+          <t>1892_1_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1665-09-32/001.jpg,https://oleks-netizen.github.io/product-images/1665-09-32/002.jpg,https://oleks-netizen.github.io/product-images/1665-09-32/003.jpg,https://oleks-netizen.github.io/product-images/1665-09-32/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1892_1_2/001.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2210-05-31</t>
+          <t>2212-05-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2210-05-31/001.jpg,https://oleks-netizen.github.io/product-images/2210-05-31/002.jpg,https://oleks-netizen.github.io/product-images/2210-05-31/003.jpg,https://oleks-netizen.github.io/product-images/2210-05-31/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2212-05-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/005.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2210-45-31</t>
+          <t>2212-45-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2210-45-31/001.jpg,https://oleks-netizen.github.io/product-images/2210-45-31/002.jpg,https://oleks-netizen.github.io/product-images/2210-45-31/004.jpg,https://oleks-netizen.github.io/product-images/2210-45-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2212-45-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/005.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2210-56-31</t>
+          <t>2212-56-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2210-56-31/001.jpg,https://oleks-netizen.github.io/product-images/2210-56-31/002.jpg,https://oleks-netizen.github.io/product-images/2210-56-31/004.jpg,https://oleks-netizen.github.io/product-images/2210-56-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2212-56-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/005.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2213-06-31</t>
+          <t>5192301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2213-06-31/001.jpg,https://oleks-netizen.github.io/product-images/2213-06-31/002.jpg,https://oleks-netizen.github.io/product-images/2213-06-31/003.jpg,https://oleks-netizen.github.io/product-images/2213-06-31/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5192301/001.jpg,https://oleks-netizen.github.io/product-images/5192301/002.jpg,https://oleks-netizen.github.io/product-images/5192301/003.jpg,https://oleks-netizen.github.io/product-images/5192301/005.jpg,https://oleks-netizen.github.io/product-images/5192301/006.jpg,https://oleks-netizen.github.io/product-images/5192301/007.jpg,https://oleks-netizen.github.io/product-images/5192301/008.jpg,https://oleks-netizen.github.io/product-images/5192301/009.jpg,https://oleks-netizen.github.io/product-images/5192301/010.jpg,https://oleks-netizen.github.io/product-images/5192301/011.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2213-56-32</t>
+          <t>5215901</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2213-56-32/001.jpg,https://oleks-netizen.github.io/product-images/2213-56-32/002.jpg,https://oleks-netizen.github.io/product-images/2213-56-32/003.jpg,https://oleks-netizen.github.io/product-images/2213-56-32/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5215901/001.jpg,https://oleks-netizen.github.io/product-images/5215901/002.jpg,https://oleks-netizen.github.io/product-images/5215901/003.jpg,https://oleks-netizen.github.io/product-images/5215901/004.jpg,https://oleks-netizen.github.io/product-images/5215901/005.jpg,https://oleks-netizen.github.io/product-images/5215901/006.jpg,https://oleks-netizen.github.io/product-images/5215901/007.jpg,https://oleks-netizen.github.io/product-images/5215901/008.jpg,https://oleks-netizen.github.io/product-images/5215901/009.jpg,https://oleks-netizen.github.io/product-images/5215901/010.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2222-06-31</t>
+          <t>5218401</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2222-06-31/001.jpg,https://oleks-netizen.github.io/product-images/2222-06-31/002.jpg,https://oleks-netizen.github.io/product-images/2222-06-31/003.jpg,https://oleks-netizen.github.io/product-images/2222-06-31/004.jpg,https://oleks-netizen.github.io/product-images/2222-06-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5218401/001.jpg,https://oleks-netizen.github.io/product-images/5218401/003.jpg,https://oleks-netizen.github.io/product-images/5218401/004.jpg,https://oleks-netizen.github.io/product-images/5218401/005.jpg,https://oleks-netizen.github.io/product-images/5218401/006.jpg,https://oleks-netizen.github.io/product-images/5218401/007.jpg,https://oleks-netizen.github.io/product-images/5218401/008.jpg,https://oleks-netizen.github.io/product-images/5218401/009.jpg,https://oleks-netizen.github.io/product-images/5218401/010.jpg,https://oleks-netizen.github.io/product-images/5218401/011.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2222-56-31</t>
+          <t>5231601</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2222-56-31/001.jpg,https://oleks-netizen.github.io/product-images/2222-56-31/002.jpg,https://oleks-netizen.github.io/product-images/2222-56-31/003.jpg,https://oleks-netizen.github.io/product-images/2222-56-31/004.jpg,https://oleks-netizen.github.io/product-images/2222-56-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5231601/001.jpg,https://oleks-netizen.github.io/product-images/5231601/002.jpg,https://oleks-netizen.github.io/product-images/5231601/003.jpg,https://oleks-netizen.github.io/product-images/5231601/005.jpg,https://oleks-netizen.github.io/product-images/5231601/006.jpg,https://oleks-netizen.github.io/product-images/5231601/007.jpg,https://oleks-netizen.github.io/product-images/5231601/008.jpg,https://oleks-netizen.github.io/product-images/5231601/009.jpg,https://oleks-netizen.github.io/product-images/5231601/010.jpg,https://oleks-netizen.github.io/product-images/5231601/011.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>53100020</t>
+          <t>5231701</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100020/001.jpg,https://oleks-netizen.github.io/product-images/53100020/002.jpg,https://oleks-netizen.github.io/product-images/53100020/003.jpg,https://oleks-netizen.github.io/product-images/53100020/004.jpg,https://oleks-netizen.github.io/product-images/53100020/005.jpg,https://oleks-netizen.github.io/product-images/53100020/006.jpg,https://oleks-netizen.github.io/product-images/53100020/007.jpg,https://oleks-netizen.github.io/product-images/53100020/009.jpg,https://oleks-netizen.github.io/product-images/53100020/010.jpg,https://oleks-netizen.github.io/product-images/53100020/011.jpg,https://oleks-netizen.github.io/product-images/53100020/012.jpg,https://oleks-netizen.github.io/product-images/53100020/013.jpg,https://oleks-netizen.github.io/product-images/53100020/014.jpg,https://oleks-netizen.github.io/product-images/53100020/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5231701/001.jpg,https://oleks-netizen.github.io/product-images/5231701/002.jpg,https://oleks-netizen.github.io/product-images/5231701/003.jpg,https://oleks-netizen.github.io/product-images/5231701/004.jpg,https://oleks-netizen.github.io/product-images/5231701/005.jpg,https://oleks-netizen.github.io/product-images/5231701/006.jpg,https://oleks-netizen.github.io/product-images/5231701/007.jpg,https://oleks-netizen.github.io/product-images/5231701/009.jpg,https://oleks-netizen.github.io/product-images/5231701/010.jpg,https://oleks-netizen.github.io/product-images/5231701/011.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>53100067</t>
+          <t>5240601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100067/001.jpg,https://oleks-netizen.github.io/product-images/53100067/002.jpg,https://oleks-netizen.github.io/product-images/53100067/003.jpg,https://oleks-netizen.github.io/product-images/53100067/004.jpg,https://oleks-netizen.github.io/product-images/53100067/005.jpg,https://oleks-netizen.github.io/product-images/53100067/006.jpg,https://oleks-netizen.github.io/product-images/53100067/007.jpg,https://oleks-netizen.github.io/product-images/53100067/008.jpg,https://oleks-netizen.github.io/product-images/53100067/009.jpg,https://oleks-netizen.github.io/product-images/53100067/010.jpg,https://oleks-netizen.github.io/product-images/53100067/012.jpg,https://oleks-netizen.github.io/product-images/53100067/013.jpg,https://oleks-netizen.github.io/product-images/53100067/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5240601/001.jpg,https://oleks-netizen.github.io/product-images/5240601/002.jpg,https://oleks-netizen.github.io/product-images/5240601/003.jpg,https://oleks-netizen.github.io/product-images/5240601/004.jpg,https://oleks-netizen.github.io/product-images/5240601/005.jpg,https://oleks-netizen.github.io/product-images/5240601/006.jpg,https://oleks-netizen.github.io/product-images/5240601/007.jpg,https://oleks-netizen.github.io/product-images/5240601/008.jpg,https://oleks-netizen.github.io/product-images/5240601/009.jpg,https://oleks-netizen.github.io/product-images/5240601/010.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>53100068</t>
+          <t>5240801</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100068/001.jpg,https://oleks-netizen.github.io/product-images/53100068/002.jpg,https://oleks-netizen.github.io/product-images/53100068/003.jpg,https://oleks-netizen.github.io/product-images/53100068/004.jpg,https://oleks-netizen.github.io/product-images/53100068/005.jpg,https://oleks-netizen.github.io/product-images/53100068/007.jpg,https://oleks-netizen.github.io/product-images/53100068/008.jpg,https://oleks-netizen.github.io/product-images/53100068/009.jpg,https://oleks-netizen.github.io/product-images/53100068/010.jpg,https://oleks-netizen.github.io/product-images/53100068/011.jpg,https://oleks-netizen.github.io/product-images/53100068/012.jpg,https://oleks-netizen.github.io/product-images/53100068/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5240801/001.jpg,https://oleks-netizen.github.io/product-images/5240801/002.jpg,https://oleks-netizen.github.io/product-images/5240801/003.jpg,https://oleks-netizen.github.io/product-images/5240801/004.jpg,https://oleks-netizen.github.io/product-images/5240801/005.jpg,https://oleks-netizen.github.io/product-images/5240801/006.jpg,https://oleks-netizen.github.io/product-images/5240801/007.jpg,https://oleks-netizen.github.io/product-images/5240801/008.jpg,https://oleks-netizen.github.io/product-images/5240801/009.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>53200013</t>
+          <t>5246601W</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53200013/001.jpg,https://oleks-netizen.github.io/product-images/53200013/002.jpg,https://oleks-netizen.github.io/product-images/53200013/003.jpg,https://oleks-netizen.github.io/product-images/53200013/004.jpg,https://oleks-netizen.github.io/product-images/53200013/005.jpg,https://oleks-netizen.github.io/product-images/53200013/006.jpg,https://oleks-netizen.github.io/product-images/53200013/007.jpg,https://oleks-netizen.github.io/product-images/53200013/008.jpg,https://oleks-netizen.github.io/product-images/53200013/009.jpg,https://oleks-netizen.github.io/product-images/53200013/010.jpg,https://oleks-netizen.github.io/product-images/53200013/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5246601W/001.jpg,https://oleks-netizen.github.io/product-images/5246601W/002.jpg,https://oleks-netizen.github.io/product-images/5246601W/003.jpg,https://oleks-netizen.github.io/product-images/5246601W/005.jpg,https://oleks-netizen.github.io/product-images/5246601W/006.jpg,https://oleks-netizen.github.io/product-images/5246601W/007.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>53300061</t>
+          <t>5246701W</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53300061/001.jpg,https://oleks-netizen.github.io/product-images/53300061/002.jpg,https://oleks-netizen.github.io/product-images/53300061/003.jpg,https://oleks-netizen.github.io/product-images/53300061/004.jpg,https://oleks-netizen.github.io/product-images/53300061/005.jpg,https://oleks-netizen.github.io/product-images/53300061/006.jpg,https://oleks-netizen.github.io/product-images/53300061/008.jpg,https://oleks-netizen.github.io/product-images/53300061/009.jpg,https://oleks-netizen.github.io/product-images/53300061/010.jpg,https://oleks-netizen.github.io/product-images/53300061/011.jpg,https://oleks-netizen.github.io/product-images/53300061/012.jpg,https://oleks-netizen.github.io/product-images/53300061/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5246701W/001.jpg,https://oleks-netizen.github.io/product-images/5246701W/002.jpg,https://oleks-netizen.github.io/product-images/5246701W/003.jpg,https://oleks-netizen.github.io/product-images/5246701W/005.jpg,https://oleks-netizen.github.io/product-images/5246701W/006.jpg,https://oleks-netizen.github.io/product-images/5246701W/007.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>53300070</t>
+          <t>BN-BV-1-choko</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53300070/001.jpg,https://oleks-netizen.github.io/product-images/53300070/002.jpg,https://oleks-netizen.github.io/product-images/53300070/003.jpg,https://oleks-netizen.github.io/product-images/53300070/004.jpg,https://oleks-netizen.github.io/product-images/53300070/005.jpg,https://oleks-netizen.github.io/product-images/53300070/006.jpg,https://oleks-netizen.github.io/product-images/53300070/007.jpg,https://oleks-netizen.github.io/product-images/53300070/008.jpg,https://oleks-netizen.github.io/product-images/53300070/009.jpg,https://oleks-netizen.github.io/product-images/53300070/010.jpg,https://oleks-netizen.github.io/product-images/53300070/012.jpg,https://oleks-netizen.github.io/product-images/53300070/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-choko/006.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>53300519</t>
+          <t>BN-BV-1-g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53300519/001.jpg,https://oleks-netizen.github.io/product-images/53300519/002.jpg,https://oleks-netizen.github.io/product-images/53300519/003.jpg,https://oleks-netizen.github.io/product-images/53300519/004.jpg,https://oleks-netizen.github.io/product-images/53300519/005.jpg,https://oleks-netizen.github.io/product-images/53300519/006.jpg,https://oleks-netizen.github.io/product-images/53300519/008.jpg,https://oleks-netizen.github.io/product-images/53300519/009.jpg,https://oleks-netizen.github.io/product-images/53300519/010.jpg,https://oleks-netizen.github.io/product-images/53300519/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/007.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>53330506</t>
+          <t>BN-BV-1-g-kr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330506/001.jpg,https://oleks-netizen.github.io/product-images/53330506/002.jpg,https://oleks-netizen.github.io/product-images/53330506/003.jpg,https://oleks-netizen.github.io/product-images/53330506/005.jpg,https://oleks-netizen.github.io/product-images/53330506/006.jpg,https://oleks-netizen.github.io/product-images/53330506/007.jpg,https://oleks-netizen.github.io/product-images/53330506/008.jpg,https://oleks-netizen.github.io/product-images/53330506/009.jpg,https://oleks-netizen.github.io/product-images/53330506/010.jpg,https://oleks-netizen.github.io/product-images/53330506/011.jpg,https://oleks-netizen.github.io/product-images/53330506/012.jpg,https://oleks-netizen.github.io/product-images/53330506/013.jpg,https://oleks-netizen.github.io/product-images/53330506/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g-kr/002.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>80411003</t>
+          <t>BN-BV-1-iz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411003/001.jpg,https://oleks-netizen.github.io/product-images/80411003/002.jpg,https://oleks-netizen.github.io/product-images/80411003/003.jpg,https://oleks-netizen.github.io/product-images/80411003/004.jpg,https://oleks-netizen.github.io/product-images/80411003/005.jpg,https://oleks-netizen.github.io/product-images/80411003/006.jpg,https://oleks-netizen.github.io/product-images/80411003/007.jpg,https://oleks-netizen.github.io/product-images/80411003/009.jpg,https://oleks-netizen.github.io/product-images/80411003/010.jpg,https://oleks-netizen.github.io/product-images/80411003/011.jpg,https://oleks-netizen.github.io/product-images/80411003/012.jpg,https://oleks-netizen.github.io/product-images/80411003/013.jpg,https://oleks-netizen.github.io/product-images/80411003/014.jpg,https://oleks-netizen.github.io/product-images/80411003/015.jpg,https://oleks-netizen.github.io/product-images/80411003/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/007.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>80411506</t>
+          <t>BN-BV-1-k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411506/001.jpg,https://oleks-netizen.github.io/product-images/80411506/002.jpg,https://oleks-netizen.github.io/product-images/80411506/003.jpg,https://oleks-netizen.github.io/product-images/80411506/004.jpg,https://oleks-netizen.github.io/product-images/80411506/005.jpg,https://oleks-netizen.github.io/product-images/80411506/006.jpg,https://oleks-netizen.github.io/product-images/80411506/007.jpg,https://oleks-netizen.github.io/product-images/80411506/008.jpg,https://oleks-netizen.github.io/product-images/80411506/009.jpg,https://oleks-netizen.github.io/product-images/80411506/010.jpg,https://oleks-netizen.github.io/product-images/80411506/011.jpg,https://oleks-netizen.github.io/product-images/80411506/012.jpg,https://oleks-netizen.github.io/product-images/80411506/014.jpg,https://oleks-netizen.github.io/product-images/80411506/015.jpg,https://oleks-netizen.github.io/product-images/80411506/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/005.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80411514</t>
+          <t>BN-BV-1-k-kr</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411514/001.jpg,https://oleks-netizen.github.io/product-images/80411514/002.jpg,https://oleks-netizen.github.io/product-images/80411514/003.jpg,https://oleks-netizen.github.io/product-images/80411514/004.jpg,https://oleks-netizen.github.io/product-images/80411514/005.jpg,https://oleks-netizen.github.io/product-images/80411514/006.jpg,https://oleks-netizen.github.io/product-images/80411514/007.jpg,https://oleks-netizen.github.io/product-images/80411514/008.jpg,https://oleks-netizen.github.io/product-images/80411514/009.jpg,https://oleks-netizen.github.io/product-images/80411514/010.jpg,https://oleks-netizen.github.io/product-images/80411514/011.jpg,https://oleks-netizen.github.io/product-images/80411514/012.jpg,https://oleks-netizen.github.io/product-images/80411514/013.jpg,https://oleks-netizen.github.io/product-images/80411514/015.jpg,https://oleks-netizen.github.io/product-images/80411514/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/005.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>80411515</t>
+          <t>BN-BV-1-navy-blue</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411515/001.jpg,https://oleks-netizen.github.io/product-images/80411515/002.jpg,https://oleks-netizen.github.io/product-images/80411515/003.jpg,https://oleks-netizen.github.io/product-images/80411515/004.jpg,https://oleks-netizen.github.io/product-images/80411515/005.jpg,https://oleks-netizen.github.io/product-images/80411515/006.jpg,https://oleks-netizen.github.io/product-images/80411515/007.jpg,https://oleks-netizen.github.io/product-images/80411515/008.jpg,https://oleks-netizen.github.io/product-images/80411515/010.jpg,https://oleks-netizen.github.io/product-images/80411515/011.jpg,https://oleks-netizen.github.io/product-images/80411515/012.jpg,https://oleks-netizen.github.io/product-images/80411515/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/006.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>80460061</t>
+          <t>BN-BV-1-nn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460061/001.jpg,https://oleks-netizen.github.io/product-images/80460061/002.jpg,https://oleks-netizen.github.io/product-images/80460061/003.jpg,https://oleks-netizen.github.io/product-images/80460061/004.jpg,https://oleks-netizen.github.io/product-images/80460061/005.jpg,https://oleks-netizen.github.io/product-images/80460061/006.jpg,https://oleks-netizen.github.io/product-images/80460061/007.jpg,https://oleks-netizen.github.io/product-images/80460061/008.jpg,https://oleks-netizen.github.io/product-images/80460061/010.jpg,https://oleks-netizen.github.io/product-images/80460061/011.jpg,https://oleks-netizen.github.io/product-images/80460061/012.jpg,https://oleks-netizen.github.io/product-images/80460061/013.jpg,https://oleks-netizen.github.io/product-images/80460061/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/006.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>80460101</t>
+          <t>BN-BV-1-o</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460101/001.jpg,https://oleks-netizen.github.io/product-images/80460101/002.jpg,https://oleks-netizen.github.io/product-images/80460101/003.jpg,https://oleks-netizen.github.io/product-images/80460101/004.jpg,https://oleks-netizen.github.io/product-images/80460101/005.jpg,https://oleks-netizen.github.io/product-images/80460101/007.jpg,https://oleks-netizen.github.io/product-images/80460101/008.jpg,https://oleks-netizen.github.io/product-images/80460101/009.jpg,https://oleks-netizen.github.io/product-images/80460101/010.jpg,https://oleks-netizen.github.io/product-images/80460101/011.jpg,https://oleks-netizen.github.io/product-images/80460101/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/007.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>85515006</t>
+          <t>BN-BV-1-vin</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85515006/001.jpg,https://oleks-netizen.github.io/product-images/85515006/002.jpg,https://oleks-netizen.github.io/product-images/85515006/004.jpg,https://oleks-netizen.github.io/product-images/85515006/005.jpg,https://oleks-netizen.github.io/product-images/85515006/006.jpg,https://oleks-netizen.github.io/product-images/85515006/007.jpg,https://oleks-netizen.github.io/product-images/85515006/008.jpg,https://oleks-netizen.github.io/product-images/85515006/009.jpg,https://oleks-netizen.github.io/product-images/85515006/010.jpg,https://oleks-netizen.github.io/product-images/85515006/011.jpg,https://oleks-netizen.github.io/product-images/85515006/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/005.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>85515106</t>
+          <t>BN-BV-1-vin-kr</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85515106/001.jpg,https://oleks-netizen.github.io/product-images/85515106/002.jpg,https://oleks-netizen.github.io/product-images/85515106/003.jpg,https://oleks-netizen.github.io/product-images/85515106/004.jpg,https://oleks-netizen.github.io/product-images/85515106/005.jpg,https://oleks-netizen.github.io/product-images/85515106/006.jpg,https://oleks-netizen.github.io/product-images/85515106/008.jpg,https://oleks-netizen.github.io/product-images/85515106/009.jpg,https://oleks-netizen.github.io/product-images/85515106/010.jpg,https://oleks-netizen.github.io/product-images/85515106/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/005.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>93220021</t>
+          <t>BN-CB-4-choko</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/93220021/001.jpg,https://oleks-netizen.github.io/product-images/93220021/002.jpg,https://oleks-netizen.github.io/product-images/93220021/003.jpg,https://oleks-netizen.github.io/product-images/93220021/004.jpg,https://oleks-netizen.github.io/product-images/93220021/005.jpg,https://oleks-netizen.github.io/product-images/93220021/007.jpg,https://oleks-netizen.github.io/product-images/93220021/008.jpg,https://oleks-netizen.github.io/product-images/93220021/009.jpg,https://oleks-netizen.github.io/product-images/93220021/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/007.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fz379334_chok</t>
+          <t>BN-CB-4-g</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/fz379334_chok/001.jpg,https://oleks-netizen.github.io/product-images/fz379334_chok/002.jpg,https://oleks-netizen.github.io/product-images/fz379334_chok/003.jpg,https://oleks-netizen.github.io/product-images/fz379334_chok/004.jpg,https://oleks-netizen.github.io/product-images/fz379334_chok/006.jpg,https://oleks-netizen.github.io/product-images/fz379334_chok/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/007.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -901,12 +901,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GA-1304-4lx</t>
+          <t>BN-CB-4-g-kr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GA-1304-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-1304-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/008.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -916,46 +916,781 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RA-wall-005</t>
+          <t>BN-CB-4-iz</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-wall-005/001.jpg,https://oleks-netizen.github.io/product-images/RA-wall-005/002.jpg,https://oleks-netizen.github.io/product-images/RA-wall-005/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/008.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RY-6002-3md</t>
+          <t>BN-CB-4-k-kr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RY-6002-3md/001.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/002.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/003.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/004.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/005.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/006.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/008.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/009.jpg,https://oleks-netizen.github.io/product-images/RY-6002-3md/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/008.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VC02807ltaup</t>
+          <t>BN-CB-4-navy-blue</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/VC02807ltaup/001.jpg,https://oleks-netizen.github.io/product-images/VC02807ltaup/002.jpg,https://oleks-netizen.github.io/product-images/VC02807ltaup/003.jpg,https://oleks-netizen.github.io/product-images/VC02807ltaup/004.jpg,https://oleks-netizen.github.io/product-images/VC02807ltaup/005.jpg,https://oleks-netizen.github.io/product-images/VC02807ltaup/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/008.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BN-CB-4-nn</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/007.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BN-CB-4-o</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/008.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BN-CB-4-vin</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/005.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BN-GC-23-beige-kr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/008.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/009.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BN-GC-23-choko</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/004.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BN-GC-23-g</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/004.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BN-GC-23-g-kr</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/005.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BN-GC-23-iz</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/005.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BN-GC-23-k</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/006.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BN-GC-23-k-kr</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/006.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BN-GC-23-malachite</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/006.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BN-GC-23-navy-blue</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/006.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BN-GC-23-nn</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/005.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BN-GC-23-o</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/006.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BN-GC-23-red</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/006.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BN-GC-24-1-g-kr</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/011.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BN-GC-24-1-iz</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/011.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BN-GC-24-1-k-kr</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/011.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BN-GC-24-1-o</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/011.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BN-GC-24-1-vin-kr</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/011.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BN-GC-24-choko</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/006.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BN-GC-24-g</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/005.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BN-GC-24-g-kr</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/005.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BN-GC-24-iz</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/005.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BN-GC-24-k</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/005.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BN-GC-24-k-kr</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/005.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BN-GC-24-malachite</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/005.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BN-GC-24-navy-blue</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/005.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BN-GC-24-nn</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/005.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BN-GC-24-o</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/005.jpg</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BN-GC-24-red</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/005.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BV38416-160</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38416-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/003.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/008.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/009.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BV38416-2924</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38416-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/008.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/009.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BV38525-2802</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38525-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/008.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BV38525-446</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38525-446/001.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/002.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/004.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/005.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/006.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/007.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/008.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BV38601-2802</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38601-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/008.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BV38648-2807</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38648-2807/001.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/002.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/004.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/005.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/006.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/007.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/008.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BV38648-306</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38648-306/001.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/002.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/003.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/005.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/006.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/007.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BV38655-2802</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38655-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/008.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/009.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BV38753-2924</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38753-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/008.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BV38755-160</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38755-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/009.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BV38755-191</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38755-191/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/009.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BV38755-2802</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38755-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/009.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BV38792-1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38792-1/001.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/002.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/004.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/005.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/006.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/007.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/008.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BV38792-160</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38792-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/004.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/008.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BV38800-2924</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38800-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/008.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/009.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/010.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/011.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Y4309 CATCB 1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/001.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/002.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/003.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/005.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/006.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BN-BV-1-malachite</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-malachite/006.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BV38792-160 (1)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BV38792-160 (1)/004.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,102 +436,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1282_1_1</t>
+          <t>BN-KL-6-choko</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1282_1_1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-KL-6-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/007.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/008.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1282_1_2</t>
+          <t>BN-OP-33-beige</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1282_1_2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/008.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1282_1_4</t>
+          <t>BN-OP-33-choko</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1282_1_4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/007.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1282_1_5</t>
+          <t>BN-OP-33-malachite</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1282_1_5/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/007.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1793_1_100</t>
+          <t>BN-OP-33-navy-blue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1793_1_100/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/007.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1892_1_2</t>
+          <t>BN-OP-33-vin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1892_1_2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/007.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2212-05-31</t>
+          <t>BN-OP-34-g</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2212-05-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-05-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-34-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/005.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,237 +541,237 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2212-45-31</t>
+          <t>BN-OP-35-k</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2212-45-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-45-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/004.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2212-56-31</t>
+          <t>BN-OP-35-light</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2212-56-31/001.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/002.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/003.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/004.jpg,https://oleks-netizen.github.io/product-images/2212-56-31/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-light/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/004.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5192301</t>
+          <t>BN-OP-35-light-beige</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5192301/001.jpg,https://oleks-netizen.github.io/product-images/5192301/002.jpg,https://oleks-netizen.github.io/product-images/5192301/003.jpg,https://oleks-netizen.github.io/product-images/5192301/005.jpg,https://oleks-netizen.github.io/product-images/5192301/006.jpg,https://oleks-netizen.github.io/product-images/5192301/007.jpg,https://oleks-netizen.github.io/product-images/5192301/008.jpg,https://oleks-netizen.github.io/product-images/5192301/009.jpg,https://oleks-netizen.github.io/product-images/5192301/010.jpg,https://oleks-netizen.github.io/product-images/5192301/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/004.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5215901</t>
+          <t>BN-OP-35-malachite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5215901/001.jpg,https://oleks-netizen.github.io/product-images/5215901/002.jpg,https://oleks-netizen.github.io/product-images/5215901/003.jpg,https://oleks-netizen.github.io/product-images/5215901/004.jpg,https://oleks-netizen.github.io/product-images/5215901/005.jpg,https://oleks-netizen.github.io/product-images/5215901/006.jpg,https://oleks-netizen.github.io/product-images/5215901/007.jpg,https://oleks-netizen.github.io/product-images/5215901/008.jpg,https://oleks-netizen.github.io/product-images/5215901/009.jpg,https://oleks-netizen.github.io/product-images/5215901/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/004.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5218401</t>
+          <t>BN-OP-35-navy-blue</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5218401/001.jpg,https://oleks-netizen.github.io/product-images/5218401/003.jpg,https://oleks-netizen.github.io/product-images/5218401/004.jpg,https://oleks-netizen.github.io/product-images/5218401/005.jpg,https://oleks-netizen.github.io/product-images/5218401/006.jpg,https://oleks-netizen.github.io/product-images/5218401/007.jpg,https://oleks-netizen.github.io/product-images/5218401/008.jpg,https://oleks-netizen.github.io/product-images/5218401/009.jpg,https://oleks-netizen.github.io/product-images/5218401/010.jpg,https://oleks-netizen.github.io/product-images/5218401/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/004.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5231601</t>
+          <t>BN-OP-35-pink-peach</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5231601/001.jpg,https://oleks-netizen.github.io/product-images/5231601/002.jpg,https://oleks-netizen.github.io/product-images/5231601/003.jpg,https://oleks-netizen.github.io/product-images/5231601/005.jpg,https://oleks-netizen.github.io/product-images/5231601/006.jpg,https://oleks-netizen.github.io/product-images/5231601/007.jpg,https://oleks-netizen.github.io/product-images/5231601/008.jpg,https://oleks-netizen.github.io/product-images/5231601/009.jpg,https://oleks-netizen.github.io/product-images/5231601/010.jpg,https://oleks-netizen.github.io/product-images/5231601/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/004.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5231701</t>
+          <t>BN-OP-35-tiffany</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5231701/001.jpg,https://oleks-netizen.github.io/product-images/5231701/002.jpg,https://oleks-netizen.github.io/product-images/5231701/003.jpg,https://oleks-netizen.github.io/product-images/5231701/004.jpg,https://oleks-netizen.github.io/product-images/5231701/005.jpg,https://oleks-netizen.github.io/product-images/5231701/006.jpg,https://oleks-netizen.github.io/product-images/5231701/007.jpg,https://oleks-netizen.github.io/product-images/5231701/009.jpg,https://oleks-netizen.github.io/product-images/5231701/010.jpg,https://oleks-netizen.github.io/product-images/5231701/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/004.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5240601</t>
+          <t>BN-SB-16-1-choko</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5240601/001.jpg,https://oleks-netizen.github.io/product-images/5240601/002.jpg,https://oleks-netizen.github.io/product-images/5240601/003.jpg,https://oleks-netizen.github.io/product-images/5240601/004.jpg,https://oleks-netizen.github.io/product-images/5240601/005.jpg,https://oleks-netizen.github.io/product-images/5240601/006.jpg,https://oleks-netizen.github.io/product-images/5240601/007.jpg,https://oleks-netizen.github.io/product-images/5240601/008.jpg,https://oleks-netizen.github.io/product-images/5240601/009.jpg,https://oleks-netizen.github.io/product-images/5240601/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/004.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5240801</t>
+          <t>BN-SB-16-1-g</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5240801/001.jpg,https://oleks-netizen.github.io/product-images/5240801/002.jpg,https://oleks-netizen.github.io/product-images/5240801/003.jpg,https://oleks-netizen.github.io/product-images/5240801/004.jpg,https://oleks-netizen.github.io/product-images/5240801/005.jpg,https://oleks-netizen.github.io/product-images/5240801/006.jpg,https://oleks-netizen.github.io/product-images/5240801/007.jpg,https://oleks-netizen.github.io/product-images/5240801/008.jpg,https://oleks-netizen.github.io/product-images/5240801/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/004.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5246601W</t>
+          <t>BN-SB-16-1-k</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5246601W/001.jpg,https://oleks-netizen.github.io/product-images/5246601W/002.jpg,https://oleks-netizen.github.io/product-images/5246601W/003.jpg,https://oleks-netizen.github.io/product-images/5246601W/005.jpg,https://oleks-netizen.github.io/product-images/5246601W/006.jpg,https://oleks-netizen.github.io/product-images/5246601W/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/003.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5246701W</t>
+          <t>BN-SB-16-1-k-kr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5246701W/001.jpg,https://oleks-netizen.github.io/product-images/5246701W/002.jpg,https://oleks-netizen.github.io/product-images/5246701W/003.jpg,https://oleks-netizen.github.io/product-images/5246701W/005.jpg,https://oleks-netizen.github.io/product-images/5246701W/006.jpg,https://oleks-netizen.github.io/product-images/5246701W/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/004.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BN-BV-1-choko</t>
+          <t>BN-SB-16-1-navy-blue</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-choko/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/005.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BN-BV-1-g</t>
+          <t>BN-SB-16-1-o</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/005.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BN-BV-1-g-kr</t>
+          <t>BN-SB-16-choko</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-g-kr/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/005.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BN-BV-1-iz</t>
+          <t>BN-SB-16-g</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-iz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/004.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BN-BV-1-k</t>
+          <t>BN-SB-16-k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/004.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -781,12 +781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BN-BV-1-k-kr</t>
+          <t>BN-SB-16-k-kr</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-k-kr/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/004.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,42 +796,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BN-BV-1-navy-blue</t>
+          <t>BN-SB-16-navy-blue</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-navy-blue/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/004.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BN-BV-1-nn</t>
+          <t>BN-SB-16-o</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-nn/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/004.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BN-BV-1-o</t>
+          <t>GC-8086-3md</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-o/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GC-8086-3md/001.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/002.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/003.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/004.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/006.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/007.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -841,72 +841,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BN-BV-1-vin</t>
+          <t>RA-3025-3md-</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RA-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/006.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BN-BV-1-vin-kr</t>
+          <t>RB112 BERRY M</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-vin-kr/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 BERRY M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/008.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BN-CB-4-choko</t>
+          <t>RB112 BLK_RHUMBA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-choko/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/003.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/005.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/008.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BN-CB-4-g</t>
+          <t>RB112 BLUE M</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 BLUE M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/003.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/008.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BN-CB-4-g-kr</t>
+          <t>RB112 LIME M</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-g-kr/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 LIME M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/008.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -916,12 +916,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BN-CB-4-iz</t>
+          <t>RB112 PLUM M</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-iz/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 PLUM M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/008.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -931,12 +931,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BN-CB-4-k-kr</t>
+          <t>RB112 RED M</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-k-kr/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RB112 RED M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/008.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -946,751 +946,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BN-CB-4-navy-blue</t>
+          <t>RE-3025-3md-</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-navy-blue/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/006.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BN-CB-4-nn</t>
+          <t>RK-3025-3md-</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-nn/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RK-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/006.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BN-CB-4-o</t>
+          <t>S5 BLUE M</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/007.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-o/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/S5 BLUE M/001.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/002.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/004.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/005.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/006.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/007.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/008.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/009.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BN-CB-4-vin</t>
+          <t>S5 OIL TAN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-4-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-4-vin/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/S5 OIL TAN/001.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/002.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/004.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/005.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/006.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/007.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/008.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/009.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/010.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/011.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/012.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BN-GC-23-beige-kr</t>
+          <t>TW-Camilla-brown-zam</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/008.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-beige-kr/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/001.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/002.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/003.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/005.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/006.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/007.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BN-GC-23-choko</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-choko/004.jpg</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BN-GC-23-g</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g/004.jpg</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BN-GC-23-g-kr</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-g-kr/005.jpg</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BN-GC-23-iz</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-iz/005.jpg</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BN-GC-23-k</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k/006.jpg</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BN-GC-23-k-kr</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-k-kr/006.jpg</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BN-GC-23-malachite</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-malachite/006.jpg</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BN-GC-23-navy-blue</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-navy-blue/006.jpg</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BN-GC-23-nn</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-nn/005.jpg</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BN-GC-23-o</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-o/006.jpg</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BN-GC-23-red</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-23-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-23-red/006.jpg</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BN-GC-24-1-g-kr</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-g-kr/011.jpg</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BN-GC-24-1-iz</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-iz/011.jpg</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BN-GC-24-1-k-kr</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-k-kr/011.jpg</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>BN-GC-24-1-o</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-o/011.jpg</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BN-GC-24-1-vin-kr</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/009.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/010.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-1-vin-kr/011.jpg</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BN-GC-24-choko</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-choko/006.jpg</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BN-GC-24-g</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g/005.jpg</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BN-GC-24-g-kr</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-g-kr/005.jpg</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BN-GC-24-iz</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-iz/005.jpg</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BN-GC-24-k</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k/005.jpg</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BN-GC-24-k-kr</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-k-kr/005.jpg</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BN-GC-24-malachite</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-malachite/005.jpg</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BN-GC-24-navy-blue</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-navy-blue/005.jpg</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BN-GC-24-nn</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-nn/005.jpg</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>BN-GC-24-o</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-o/005.jpg</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BN-GC-24-red</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-24-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-24-red/005.jpg</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BV38416-160</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38416-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/003.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/008.jpg,https://oleks-netizen.github.io/product-images/BV38416-160/009.jpg</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BV38416-2924</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38416-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/008.jpg,https://oleks-netizen.github.io/product-images/BV38416-2924/009.jpg</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BV38525-2802</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38525-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38525-2802/008.jpg</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BV38525-446</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38525-446/001.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/002.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/004.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/005.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/006.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/007.jpg,https://oleks-netizen.github.io/product-images/BV38525-446/008.jpg</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BV38601-2802</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38601-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38601-2802/008.jpg</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BV38648-2807</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38648-2807/001.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/002.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/004.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/005.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/006.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/007.jpg,https://oleks-netizen.github.io/product-images/BV38648-2807/008.jpg</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BV38648-306</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38648-306/001.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/002.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/003.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/005.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/006.jpg,https://oleks-netizen.github.io/product-images/BV38648-306/007.jpg</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BV38655-2802</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38655-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/008.jpg,https://oleks-netizen.github.io/product-images/BV38655-2802/009.jpg</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BV38753-2924</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38753-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38753-2924/008.jpg</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BV38755-160</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38755-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-160/009.jpg</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BV38755-191</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38755-191/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-191/009.jpg</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>BV38755-2802</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38755-2802/001.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/002.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/004.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/005.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/006.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/007.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/008.jpg,https://oleks-netizen.github.io/product-images/BV38755-2802/009.jpg</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BV38792-1</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38792-1/001.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/002.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/004.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/005.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/006.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/007.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/008.jpg,https://oleks-netizen.github.io/product-images/BV38792-1/009.jpg</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BV38792-160</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38792-160/001.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/002.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/004.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/005.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/006.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/007.jpg,https://oleks-netizen.github.io/product-images/BV38792-160/008.jpg</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BV38800-2924</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38800-2924/001.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/002.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/004.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/005.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/006.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/007.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/008.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/009.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/010.jpg,https://oleks-netizen.github.io/product-images/BV38800-2924/011.jpg</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Y4309 CATCB 1</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/001.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/002.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/003.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/005.jpg,https://oleks-netizen.github.io/product-images/Y4309 CATCB 1/006.jpg</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BN-BV-1-malachite</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BV-1-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-BV-1-malachite/006.jpg</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>BV38792-160 (1)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38792-160 (1)/004.jpg</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,507 +436,507 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BN-KL-6-choko</t>
+          <t>18228066</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-KL-6-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/007.jpg,https://oleks-netizen.github.io/product-images/BN-KL-6-choko/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/18228066/001.jpg,https://oleks-netizen.github.io/product-images/18228066/002.jpg,https://oleks-netizen.github.io/product-images/18228066/003.jpg,https://oleks-netizen.github.io/product-images/18228066/004.jpg,https://oleks-netizen.github.io/product-images/18228066/005.jpg,https://oleks-netizen.github.io/product-images/18228066/006.jpg,https://oleks-netizen.github.io/product-images/18228066/007.jpg,https://oleks-netizen.github.io/product-images/18228066/008.jpg,https://oleks-netizen.github.io/product-images/18228066/009.jpg,https://oleks-netizen.github.io/product-images/18228066/011.jpg,https://oleks-netizen.github.io/product-images/18228066/012.jpg,https://oleks-netizen.github.io/product-images/18228066/013.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BN-OP-33-beige</t>
+          <t>18228067</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-beige/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/18228067/001.jpg,https://oleks-netizen.github.io/product-images/18228067/002.jpg,https://oleks-netizen.github.io/product-images/18228067/003.jpg,https://oleks-netizen.github.io/product-images/18228067/005.jpg,https://oleks-netizen.github.io/product-images/18228067/006.jpg,https://oleks-netizen.github.io/product-images/18228067/007.jpg,https://oleks-netizen.github.io/product-images/18228067/008.jpg,https://oleks-netizen.github.io/product-images/18228067/009.jpg,https://oleks-netizen.github.io/product-images/18228067/010.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BN-OP-33-choko</t>
+          <t>18228068</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-choko/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/18228068/001.jpg,https://oleks-netizen.github.io/product-images/18228068/002.jpg,https://oleks-netizen.github.io/product-images/18228068/003.jpg,https://oleks-netizen.github.io/product-images/18228068/004.jpg,https://oleks-netizen.github.io/product-images/18228068/005.jpg,https://oleks-netizen.github.io/product-images/18228068/007.jpg,https://oleks-netizen.github.io/product-images/18228068/008.jpg,https://oleks-netizen.github.io/product-images/18228068/009.jpg,https://oleks-netizen.github.io/product-images/18228068/010.jpg,https://oleks-netizen.github.io/product-images/18228068/011.jpg,https://oleks-netizen.github.io/product-images/18228068/012.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BN-OP-33-malachite</t>
+          <t>25000506</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-malachite/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000506/001.jpg,https://oleks-netizen.github.io/product-images/25000506/002.jpg,https://oleks-netizen.github.io/product-images/25000506/003.jpg,https://oleks-netizen.github.io/product-images/25000506/004.jpg,https://oleks-netizen.github.io/product-images/25000506/005.jpg,https://oleks-netizen.github.io/product-images/25000506/006.jpg,https://oleks-netizen.github.io/product-images/25000506/007.jpg,https://oleks-netizen.github.io/product-images/25000506/009.jpg,https://oleks-netizen.github.io/product-images/25000506/010.jpg,https://oleks-netizen.github.io/product-images/25000506/011.jpg,https://oleks-netizen.github.io/product-images/25000506/012.jpg,https://oleks-netizen.github.io/product-images/25000506/013.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BN-OP-33-navy-blue</t>
+          <t>25000514</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-navy-blue/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000514/001.jpg,https://oleks-netizen.github.io/product-images/25000514/002.jpg,https://oleks-netizen.github.io/product-images/25000514/003.jpg,https://oleks-netizen.github.io/product-images/25000514/004.jpg,https://oleks-netizen.github.io/product-images/25000514/005.jpg,https://oleks-netizen.github.io/product-images/25000514/006.jpg,https://oleks-netizen.github.io/product-images/25000514/007.jpg,https://oleks-netizen.github.io/product-images/25000514/008.jpg,https://oleks-netizen.github.io/product-images/25000514/009.jpg,https://oleks-netizen.github.io/product-images/25000514/011.jpg,https://oleks-netizen.github.io/product-images/25000514/012.jpg,https://oleks-netizen.github.io/product-images/25000514/013.jpg,https://oleks-netizen.github.io/product-images/25000514/014.jpg,https://oleks-netizen.github.io/product-images/25000514/015.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BN-OP-33-vin</t>
+          <t>25000514m</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-33-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-33-vin/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000514m/001.jpg,https://oleks-netizen.github.io/product-images/25000514m/002.jpg,https://oleks-netizen.github.io/product-images/25000514m/004.jpg,https://oleks-netizen.github.io/product-images/25000514m/005.jpg,https://oleks-netizen.github.io/product-images/25000514m/006.jpg,https://oleks-netizen.github.io/product-images/25000514m/007.jpg,https://oleks-netizen.github.io/product-images/25000514m/008.jpg,https://oleks-netizen.github.io/product-images/25000514m/009.jpg,https://oleks-netizen.github.io/product-images/25000514m/010.jpg,https://oleks-netizen.github.io/product-images/25000514m/011.jpg,https://oleks-netizen.github.io/product-images/25000514m/012.jpg,https://oleks-netizen.github.io/product-images/25000514m/013.jpg,https://oleks-netizen.github.io/product-images/25000514m/014.jpg,https://oleks-netizen.github.io/product-images/25000514m/015.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BN-OP-34-g</t>
+          <t>25000515</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-34-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-34-g/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000515/001.jpg,https://oleks-netizen.github.io/product-images/25000515/002.jpg,https://oleks-netizen.github.io/product-images/25000515/003.jpg,https://oleks-netizen.github.io/product-images/25000515/005.jpg,https://oleks-netizen.github.io/product-images/25000515/006.jpg,https://oleks-netizen.github.io/product-images/25000515/007.jpg,https://oleks-netizen.github.io/product-images/25000515/008.jpg,https://oleks-netizen.github.io/product-images/25000515/009.jpg,https://oleks-netizen.github.io/product-images/25000515/010.jpg,https://oleks-netizen.github.io/product-images/25000515/011.jpg,https://oleks-netizen.github.io/product-images/25000515/012.jpg,https://oleks-netizen.github.io/product-images/25000515/013.jpg,https://oleks-netizen.github.io/product-images/25000515/014.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BN-OP-35-k</t>
+          <t>25000515m</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-k/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000515m/001.jpg,https://oleks-netizen.github.io/product-images/25000515m/002.jpg,https://oleks-netizen.github.io/product-images/25000515m/003.jpg,https://oleks-netizen.github.io/product-images/25000515m/004.jpg,https://oleks-netizen.github.io/product-images/25000515m/005.jpg,https://oleks-netizen.github.io/product-images/25000515m/007.jpg,https://oleks-netizen.github.io/product-images/25000515m/008.jpg,https://oleks-netizen.github.io/product-images/25000515m/009.jpg,https://oleks-netizen.github.io/product-images/25000515m/010.jpg,https://oleks-netizen.github.io/product-images/25000515m/011.jpg,https://oleks-netizen.github.io/product-images/25000515m/012.jpg,https://oleks-netizen.github.io/product-images/25000515m/013.jpg,https://oleks-netizen.github.io/product-images/25000515m/014.jpg,https://oleks-netizen.github.io/product-images/25000515m/015.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BN-OP-35-light</t>
+          <t>51311506</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-light/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311506/001.jpg,https://oleks-netizen.github.io/product-images/51311506/002.jpg,https://oleks-netizen.github.io/product-images/51311506/003.jpg,https://oleks-netizen.github.io/product-images/51311506/004.jpg,https://oleks-netizen.github.io/product-images/51311506/005.jpg,https://oleks-netizen.github.io/product-images/51311506/006.jpg,https://oleks-netizen.github.io/product-images/51311506/008.jpg,https://oleks-netizen.github.io/product-images/51311506/009.jpg,https://oleks-netizen.github.io/product-images/51311506/010.jpg,https://oleks-netizen.github.io/product-images/51311506/011.jpg,https://oleks-netizen.github.io/product-images/51311506/012.jpg,https://oleks-netizen.github.io/product-images/51311506/013.jpg,https://oleks-netizen.github.io/product-images/51311506/014.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BN-OP-35-light-beige</t>
+          <t>51411006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-light-beige/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411006/001.jpg,https://oleks-netizen.github.io/product-images/51411006/002.jpg,https://oleks-netizen.github.io/product-images/51411006/003.jpg,https://oleks-netizen.github.io/product-images/51411006/004.jpg,https://oleks-netizen.github.io/product-images/51411006/005.jpg,https://oleks-netizen.github.io/product-images/51411006/006.jpg,https://oleks-netizen.github.io/product-images/51411006/008.jpg,https://oleks-netizen.github.io/product-images/51411006/009.jpg,https://oleks-netizen.github.io/product-images/51411006/010.jpg,https://oleks-netizen.github.io/product-images/51411006/011.jpg,https://oleks-netizen.github.io/product-images/51411006/012.jpg,https://oleks-netizen.github.io/product-images/51411006/013.jpg,https://oleks-netizen.github.io/product-images/51411006/014.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BN-OP-35-malachite</t>
+          <t>51411506</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-malachite/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411506/001.jpg,https://oleks-netizen.github.io/product-images/51411506/002.jpg,https://oleks-netizen.github.io/product-images/51411506/003.jpg,https://oleks-netizen.github.io/product-images/51411506/004.jpg,https://oleks-netizen.github.io/product-images/51411506/005.jpg,https://oleks-netizen.github.io/product-images/51411506/006.jpg,https://oleks-netizen.github.io/product-images/51411506/007.jpg,https://oleks-netizen.github.io/product-images/51411506/009.jpg,https://oleks-netizen.github.io/product-images/51411506/010.jpg,https://oleks-netizen.github.io/product-images/51411506/011.jpg,https://oleks-netizen.github.io/product-images/51411506/012.jpg,https://oleks-netizen.github.io/product-images/51411506/013.jpg,https://oleks-netizen.github.io/product-images/51411506/014.jpg,https://oleks-netizen.github.io/product-images/51411506/015.jpg,https://oleks-netizen.github.io/product-images/51411506/016.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BN-OP-35-navy-blue</t>
+          <t>53100066</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-navy-blue/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53100066/001.jpg,https://oleks-netizen.github.io/product-images/53100066/002.jpg,https://oleks-netizen.github.io/product-images/53100066/003.jpg,https://oleks-netizen.github.io/product-images/53100066/004.jpg,https://oleks-netizen.github.io/product-images/53100066/005.jpg,https://oleks-netizen.github.io/product-images/53100066/006.jpg,https://oleks-netizen.github.io/product-images/53100066/007.jpg,https://oleks-netizen.github.io/product-images/53100066/009.jpg,https://oleks-netizen.github.io/product-images/53100066/010.jpg,https://oleks-netizen.github.io/product-images/53100066/011.jpg,https://oleks-netizen.github.io/product-images/53100066/012.jpg,https://oleks-netizen.github.io/product-images/53100066/013.jpg,https://oleks-netizen.github.io/product-images/53100066/014.jpg,https://oleks-netizen.github.io/product-images/53100066/015.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BN-OP-35-pink-peach</t>
+          <t>53100106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-pink-peach/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53100106/001.jpg,https://oleks-netizen.github.io/product-images/53100106/002.jpg,https://oleks-netizen.github.io/product-images/53100106/003.jpg,https://oleks-netizen.github.io/product-images/53100106/004.jpg,https://oleks-netizen.github.io/product-images/53100106/005.jpg,https://oleks-netizen.github.io/product-images/53100106/007.jpg,https://oleks-netizen.github.io/product-images/53100106/008.jpg,https://oleks-netizen.github.io/product-images/53100106/009.jpg,https://oleks-netizen.github.io/product-images/53100106/010.jpg,https://oleks-netizen.github.io/product-images/53100106/011.jpg,https://oleks-netizen.github.io/product-images/53100106/012.jpg,https://oleks-netizen.github.io/product-images/53100106/013.jpg,https://oleks-netizen.github.io/product-images/53100106/014.jpg,https://oleks-netizen.github.io/product-images/53100106/015.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BN-OP-35-tiffany</t>
+          <t>53300066</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-35-tiffany/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53300066/001.jpg,https://oleks-netizen.github.io/product-images/53300066/002.jpg,https://oleks-netizen.github.io/product-images/53300066/003.jpg,https://oleks-netizen.github.io/product-images/53300066/004.jpg,https://oleks-netizen.github.io/product-images/53300066/005.jpg,https://oleks-netizen.github.io/product-images/53300066/006.jpg,https://oleks-netizen.github.io/product-images/53300066/007.jpg,https://oleks-netizen.github.io/product-images/53300066/009.jpg,https://oleks-netizen.github.io/product-images/53300066/010.jpg,https://oleks-netizen.github.io/product-images/53300066/011.jpg,https://oleks-netizen.github.io/product-images/53300066/012.jpg,https://oleks-netizen.github.io/product-images/53300066/013.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-choko</t>
+          <t>53330029</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-choko/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330029/001.jpg,https://oleks-netizen.github.io/product-images/53330029/002.jpg,https://oleks-netizen.github.io/product-images/53330029/003.jpg,https://oleks-netizen.github.io/product-images/53330029/004.jpg,https://oleks-netizen.github.io/product-images/53330029/005.jpg,https://oleks-netizen.github.io/product-images/53330029/006.jpg,https://oleks-netizen.github.io/product-images/53330029/008.jpg,https://oleks-netizen.github.io/product-images/53330029/009.jpg,https://oleks-netizen.github.io/product-images/53330029/010.jpg,https://oleks-netizen.github.io/product-images/53330029/011.jpg,https://oleks-netizen.github.io/product-images/53330029/012.jpg,https://oleks-netizen.github.io/product-images/53330029/013.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-g</t>
+          <t>53330029m</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-g/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330029m/001.jpg,https://oleks-netizen.github.io/product-images/53330029m/002.jpg,https://oleks-netizen.github.io/product-images/53330029m/003.jpg,https://oleks-netizen.github.io/product-images/53330029m/004.jpg,https://oleks-netizen.github.io/product-images/53330029m/005.jpg,https://oleks-netizen.github.io/product-images/53330029m/006.jpg,https://oleks-netizen.github.io/product-images/53330029m/008.jpg,https://oleks-netizen.github.io/product-images/53330029m/009.jpg,https://oleks-netizen.github.io/product-images/53330029m/010.jpg,https://oleks-netizen.github.io/product-images/53330029m/011.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-k</t>
+          <t>53330064</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330064/001.jpg,https://oleks-netizen.github.io/product-images/53330064/002.jpg,https://oleks-netizen.github.io/product-images/53330064/003.jpg,https://oleks-netizen.github.io/product-images/53330064/004.jpg,https://oleks-netizen.github.io/product-images/53330064/005.jpg,https://oleks-netizen.github.io/product-images/53330064/006.jpg,https://oleks-netizen.github.io/product-images/53330064/007.jpg,https://oleks-netizen.github.io/product-images/53330064/008.jpg,https://oleks-netizen.github.io/product-images/53330064/009.jpg,https://oleks-netizen.github.io/product-images/53330064/010.jpg,https://oleks-netizen.github.io/product-images/53330064/011.jpg,https://oleks-netizen.github.io/product-images/53330064/013.jpg,https://oleks-netizen.github.io/product-images/53330064/014.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-k-kr</t>
+          <t>53330064m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-k-kr/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330064m/001.jpg,https://oleks-netizen.github.io/product-images/53330064m/002.jpg,https://oleks-netizen.github.io/product-images/53330064m/003.jpg,https://oleks-netizen.github.io/product-images/53330064m/004.jpg,https://oleks-netizen.github.io/product-images/53330064m/006.jpg,https://oleks-netizen.github.io/product-images/53330064m/007.jpg,https://oleks-netizen.github.io/product-images/53330064m/008.jpg,https://oleks-netizen.github.io/product-images/53330064m/009.jpg,https://oleks-netizen.github.io/product-images/53330064m/010.jpg,https://oleks-netizen.github.io/product-images/53330064m/011.jpg,https://oleks-netizen.github.io/product-images/53330064m/012.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-navy-blue</t>
+          <t>53330066</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-navy-blue/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330066/001.jpg,https://oleks-netizen.github.io/product-images/53330066/002.jpg,https://oleks-netizen.github.io/product-images/53330066/003.jpg,https://oleks-netizen.github.io/product-images/53330066/004.jpg,https://oleks-netizen.github.io/product-images/53330066/005.jpg,https://oleks-netizen.github.io/product-images/53330066/007.jpg,https://oleks-netizen.github.io/product-images/53330066/008.jpg,https://oleks-netizen.github.io/product-images/53330066/009.jpg,https://oleks-netizen.github.io/product-images/53330066/010.jpg,https://oleks-netizen.github.io/product-images/53330066/011.jpg,https://oleks-netizen.github.io/product-images/53330066/012.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BN-SB-16-1-o</t>
+          <t>53330068</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-1-o/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330068/001.jpg,https://oleks-netizen.github.io/product-images/53330068/002.jpg,https://oleks-netizen.github.io/product-images/53330068/003.jpg,https://oleks-netizen.github.io/product-images/53330068/004.jpg,https://oleks-netizen.github.io/product-images/53330068/005.jpg,https://oleks-netizen.github.io/product-images/53330068/006.jpg,https://oleks-netizen.github.io/product-images/53330068/007.jpg,https://oleks-netizen.github.io/product-images/53330068/009.jpg,https://oleks-netizen.github.io/product-images/53330068/010.jpg,https://oleks-netizen.github.io/product-images/53330068/011.jpg,https://oleks-netizen.github.io/product-images/53330068/012.jpg,https://oleks-netizen.github.io/product-images/53330068/013.jpg,https://oleks-netizen.github.io/product-images/53330068/014.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BN-SB-16-choko</t>
+          <t>53330514</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-choko/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330514/001.jpg,https://oleks-netizen.github.io/product-images/53330514/002.jpg,https://oleks-netizen.github.io/product-images/53330514/003.jpg,https://oleks-netizen.github.io/product-images/53330514/004.jpg,https://oleks-netizen.github.io/product-images/53330514/005.jpg,https://oleks-netizen.github.io/product-images/53330514/006.jpg,https://oleks-netizen.github.io/product-images/53330514/008.jpg,https://oleks-netizen.github.io/product-images/53330514/009.jpg,https://oleks-netizen.github.io/product-images/53330514/010.jpg,https://oleks-netizen.github.io/product-images/53330514/011.jpg,https://oleks-netizen.github.io/product-images/53330514/012.jpg,https://oleks-netizen.github.io/product-images/53330514/013.jpg,https://oleks-netizen.github.io/product-images/53330514/014.jpg,https://oleks-netizen.github.io/product-images/53330514/015.jpg,https://oleks-netizen.github.io/product-images/53330514/016.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BN-SB-16-g</t>
+          <t>53330514m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-g/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330514m/001.jpg,https://oleks-netizen.github.io/product-images/53330514m/002.jpg,https://oleks-netizen.github.io/product-images/53330514m/003.jpg,https://oleks-netizen.github.io/product-images/53330514m/004.jpg,https://oleks-netizen.github.io/product-images/53330514m/005.jpg,https://oleks-netizen.github.io/product-images/53330514m/006.jpg,https://oleks-netizen.github.io/product-images/53330514m/007.jpg,https://oleks-netizen.github.io/product-images/53330514m/008.jpg,https://oleks-netizen.github.io/product-images/53330514m/010.jpg,https://oleks-netizen.github.io/product-images/53330514m/011.jpg,https://oleks-netizen.github.io/product-images/53330514m/012.jpg,https://oleks-netizen.github.io/product-images/53330514m/013.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BN-SB-16-k</t>
+          <t>53330530</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330530/001.jpg,https://oleks-netizen.github.io/product-images/53330530/002.jpg,https://oleks-netizen.github.io/product-images/53330530/003.jpg,https://oleks-netizen.github.io/product-images/53330530/004.jpg,https://oleks-netizen.github.io/product-images/53330530/005.jpg,https://oleks-netizen.github.io/product-images/53330530/006.jpg,https://oleks-netizen.github.io/product-images/53330530/007.jpg,https://oleks-netizen.github.io/product-images/53330530/008.jpg,https://oleks-netizen.github.io/product-images/53330530/009.jpg,https://oleks-netizen.github.io/product-images/53330530/010.jpg,https://oleks-netizen.github.io/product-images/53330530/011.jpg,https://oleks-netizen.github.io/product-images/53330530/013.jpg,https://oleks-netizen.github.io/product-images/53330530/014.jpg,https://oleks-netizen.github.io/product-images/53330530/015.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BN-SB-16-k-kr</t>
+          <t>53330530m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-k-kr/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53330530m/001.jpg,https://oleks-netizen.github.io/product-images/53330530m/002.jpg,https://oleks-netizen.github.io/product-images/53330530m/003.jpg,https://oleks-netizen.github.io/product-images/53330530m/004.jpg,https://oleks-netizen.github.io/product-images/53330530m/005.jpg,https://oleks-netizen.github.io/product-images/53330530m/006.jpg,https://oleks-netizen.github.io/product-images/53330530m/008.jpg,https://oleks-netizen.github.io/product-images/53330530m/009.jpg,https://oleks-netizen.github.io/product-images/53330530m/010.jpg,https://oleks-netizen.github.io/product-images/53330530m/011.jpg,https://oleks-netizen.github.io/product-images/53330530m/012.jpg,https://oleks-netizen.github.io/product-images/53330530m/013.jpg,https://oleks-netizen.github.io/product-images/53330530m/014.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BN-SB-16-navy-blue</t>
+          <t>53400506</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-navy-blue/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400506/001.jpg,https://oleks-netizen.github.io/product-images/53400506/002.jpg,https://oleks-netizen.github.io/product-images/53400506/003.jpg,https://oleks-netizen.github.io/product-images/53400506/004.jpg,https://oleks-netizen.github.io/product-images/53400506/005.jpg,https://oleks-netizen.github.io/product-images/53400506/006.jpg,https://oleks-netizen.github.io/product-images/53400506/007.jpg,https://oleks-netizen.github.io/product-images/53400506/008.jpg,https://oleks-netizen.github.io/product-images/53400506/009.jpg,https://oleks-netizen.github.io/product-images/53400506/010.jpg,https://oleks-netizen.github.io/product-images/53400506/012.jpg,https://oleks-netizen.github.io/product-images/53400506/013.jpg,https://oleks-netizen.github.io/product-images/53400506/014.jpg,https://oleks-netizen.github.io/product-images/53400506/015.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BN-SB-16-o</t>
+          <t>53400514</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-16-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-16-o/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400514/001.jpg,https://oleks-netizen.github.io/product-images/53400514/002.jpg,https://oleks-netizen.github.io/product-images/53400514/003.jpg,https://oleks-netizen.github.io/product-images/53400514/005.jpg,https://oleks-netizen.github.io/product-images/53400514/006.jpg,https://oleks-netizen.github.io/product-images/53400514/007.jpg,https://oleks-netizen.github.io/product-images/53400514/008.jpg,https://oleks-netizen.github.io/product-images/53400514/009.jpg,https://oleks-netizen.github.io/product-images/53400514/010.jpg,https://oleks-netizen.github.io/product-images/53400514/011.jpg,https://oleks-netizen.github.io/product-images/53400514/012.jpg,https://oleks-netizen.github.io/product-images/53400514/013.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GC-8086-3md</t>
+          <t>53400514m</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-8086-3md/001.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/002.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/003.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/004.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/006.jpg,https://oleks-netizen.github.io/product-images/GC-8086-3md/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400514m/001.jpg,https://oleks-netizen.github.io/product-images/53400514m/002.jpg,https://oleks-netizen.github.io/product-images/53400514m/003.jpg,https://oleks-netizen.github.io/product-images/53400514m/004.jpg,https://oleks-netizen.github.io/product-images/53400514m/005.jpg,https://oleks-netizen.github.io/product-images/53400514m/006.jpg,https://oleks-netizen.github.io/product-images/53400514m/007.jpg,https://oleks-netizen.github.io/product-images/53400514m/009.jpg,https://oleks-netizen.github.io/product-images/53400514m/010.jpg,https://oleks-netizen.github.io/product-images/53400514m/011.jpg,https://oleks-netizen.github.io/product-images/53400514m/012.jpg,https://oleks-netizen.github.io/product-images/53400514m/013.jpg,https://oleks-netizen.github.io/product-images/53400514m/014.jpg,https://oleks-netizen.github.io/product-images/53400514m/015.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RA-3025-3md-</t>
+          <t>6936686411318</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RA-3025-3md-/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6936686411318/001.jpg,https://oleks-netizen.github.io/product-images/6936686411318/002.jpg,https://oleks-netizen.github.io/product-images/6936686411318/003.jpg,https://oleks-netizen.github.io/product-images/6936686411318/004.jpg,https://oleks-netizen.github.io/product-images/6936686411318/005.jpg,https://oleks-netizen.github.io/product-images/6936686411318/006.jpg,https://oleks-netizen.github.io/product-images/6936686411318/007.jpg,https://oleks-netizen.github.io/product-images/6936686411318/008.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RB112 BERRY M</t>
+          <t>6976195091748</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 BERRY M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BERRY M/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195091748/001.jpg,https://oleks-netizen.github.io/product-images/6976195091748/002.jpg,https://oleks-netizen.github.io/product-images/6976195091748/003.jpg,https://oleks-netizen.github.io/product-images/6976195091748/004.jpg,https://oleks-netizen.github.io/product-images/6976195091748/005.jpg,https://oleks-netizen.github.io/product-images/6976195091748/007.jpg,https://oleks-netizen.github.io/product-images/6976195091748/008.jpg,https://oleks-netizen.github.io/product-images/6976195091748/009.jpg,https://oleks-netizen.github.io/product-images/6976195091748/010.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RB112 BLK_RHUMBA</t>
+          <t>6976195091755</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/003.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/005.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BLK_RHUMBA/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195091755/001.jpg,https://oleks-netizen.github.io/product-images/6976195091755/002.jpg,https://oleks-netizen.github.io/product-images/6976195091755/003.jpg,https://oleks-netizen.github.io/product-images/6976195091755/004.jpg,https://oleks-netizen.github.io/product-images/6976195091755/005.jpg,https://oleks-netizen.github.io/product-images/6976195091755/007.jpg,https://oleks-netizen.github.io/product-images/6976195091755/008.jpg,https://oleks-netizen.github.io/product-images/6976195091755/009.jpg,https://oleks-netizen.github.io/product-images/6976195091755/010.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RB112 BLUE M</t>
+          <t>6976195091779</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 BLUE M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/003.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 BLUE M/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195091779/001.jpg,https://oleks-netizen.github.io/product-images/6976195091779/002.jpg,https://oleks-netizen.github.io/product-images/6976195091779/003.jpg,https://oleks-netizen.github.io/product-images/6976195091779/004.jpg,https://oleks-netizen.github.io/product-images/6976195091779/005.jpg,https://oleks-netizen.github.io/product-images/6976195091779/007.jpg,https://oleks-netizen.github.io/product-images/6976195091779/008.jpg,https://oleks-netizen.github.io/product-images/6976195091779/009.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RB112 LIME M</t>
+          <t>6976195091786</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 LIME M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 LIME M/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195091786/001.jpg,https://oleks-netizen.github.io/product-images/6976195091786/002.jpg,https://oleks-netizen.github.io/product-images/6976195091786/003.jpg,https://oleks-netizen.github.io/product-images/6976195091786/004.jpg,https://oleks-netizen.github.io/product-images/6976195091786/006.jpg,https://oleks-netizen.github.io/product-images/6976195091786/007.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RB112 PLUM M</t>
+          <t>6976195091793</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 PLUM M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 PLUM M/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195091793/001.jpg,https://oleks-netizen.github.io/product-images/6976195091793/002.jpg,https://oleks-netizen.github.io/product-images/6976195091793/004.jpg,https://oleks-netizen.github.io/product-images/6976195091793/005.jpg,https://oleks-netizen.github.io/product-images/6976195091793/006.jpg,https://oleks-netizen.github.io/product-images/6976195091793/007.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RB112 RED M</t>
+          <t>6976195094718</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB112 RED M/001.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/002.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/004.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/005.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/006.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/007.jpg,https://oleks-netizen.github.io/product-images/RB112 RED M/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195094718/001.jpg,https://oleks-netizen.github.io/product-images/6976195094718/002.jpg,https://oleks-netizen.github.io/product-images/6976195094718/003.jpg,https://oleks-netizen.github.io/product-images/6976195094718/004.jpg,https://oleks-netizen.github.io/product-images/6976195094718/005.jpg,https://oleks-netizen.github.io/product-images/6976195094718/006.jpg,https://oleks-netizen.github.io/product-images/6976195094718/008.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -946,76 +946,886 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RE-3025-3md-</t>
+          <t>6976195095838</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RE-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RE-3025-3md-/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195095838/001.jpg,https://oleks-netizen.github.io/product-images/6976195095838/002.jpg,https://oleks-netizen.github.io/product-images/6976195095838/004.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RK-3025-3md-</t>
+          <t>6976195095845</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RK-3025-3md-/001.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/002.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/004.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/005.jpg,https://oleks-netizen.github.io/product-images/RK-3025-3md-/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195095845/001.jpg,https://oleks-netizen.github.io/product-images/6976195095845/002.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S5 BLUE M</t>
+          <t>6976195096064</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S5 BLUE M/001.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/002.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/004.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/005.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/006.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/007.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/008.jpg,https://oleks-netizen.github.io/product-images/S5 BLUE M/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195096064/001.jpg,https://oleks-netizen.github.io/product-images/6976195096064/002.jpg,https://oleks-netizen.github.io/product-images/6976195096064/004.jpg,https://oleks-netizen.github.io/product-images/6976195096064/005.jpg,https://oleks-netizen.github.io/product-images/6976195096064/006.jpg,https://oleks-netizen.github.io/product-images/6976195096064/007.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S5 OIL TAN</t>
+          <t>6976195096989</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S5 OIL TAN/001.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/002.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/004.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/005.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/006.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/007.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/008.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/009.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/010.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/011.jpg,https://oleks-netizen.github.io/product-images/S5 OIL TAN/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976195096989/001.jpg,https://oleks-netizen.github.io/product-images/6976195096989/002.jpg,https://oleks-netizen.github.io/product-images/6976195096989/003.jpg,https://oleks-netizen.github.io/product-images/6976195096989/004.jpg,https://oleks-netizen.github.io/product-images/6976195096989/006.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TW-Camilla-brown-zam</t>
+          <t>6976975615294</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/001.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/002.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/003.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/005.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/006.jpg,https://oleks-netizen.github.io/product-images/TW-Camilla-brown-zam/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/6976975615294/001.jpg,https://oleks-netizen.github.io/product-images/6976975615294/002.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6976975615324</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/6976975615324/001.jpg,https://oleks-netizen.github.io/product-images/6976975615324/003.jpg,https://oleks-netizen.github.io/product-images/6976975615324/004.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6977703651690</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/6977703651690/001.jpg,https://oleks-netizen.github.io/product-images/6977703651690/002.jpg,https://oleks-netizen.github.io/product-images/6977703651690/003.jpg,https://oleks-netizen.github.io/product-images/6977703651690/005.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6977703651713</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/6977703651713/001.jpg,https://oleks-netizen.github.io/product-images/6977703651713/002.jpg,https://oleks-netizen.github.io/product-images/6977703651713/003.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>80411514m</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80411514m/001.jpg,https://oleks-netizen.github.io/product-images/80411514m/002.jpg,https://oleks-netizen.github.io/product-images/80411514m/004.jpg,https://oleks-netizen.github.io/product-images/80411514m/005.jpg,https://oleks-netizen.github.io/product-images/80411514m/006.jpg,https://oleks-netizen.github.io/product-images/80411514m/007.jpg,https://oleks-netizen.github.io/product-images/80411514m/008.jpg,https://oleks-netizen.github.io/product-images/80411514m/009.jpg,https://oleks-netizen.github.io/product-images/80411514m/010.jpg,https://oleks-netizen.github.io/product-images/80411514m/011.jpg,https://oleks-netizen.github.io/product-images/80411514m/012.jpg,https://oleks-netizen.github.io/product-images/80411514m/013.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>80411515m</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80411515m/001.jpg,https://oleks-netizen.github.io/product-images/80411515m/002.jpg,https://oleks-netizen.github.io/product-images/80411515m/003.jpg,https://oleks-netizen.github.io/product-images/80411515m/005.jpg,https://oleks-netizen.github.io/product-images/80411515m/006.jpg,https://oleks-netizen.github.io/product-images/80411515m/007.jpg,https://oleks-netizen.github.io/product-images/80411515m/008.jpg,https://oleks-netizen.github.io/product-images/80411515m/009.jpg,https://oleks-netizen.github.io/product-images/80411515m/010.jpg,https://oleks-netizen.github.io/product-images/80411515m/011.jpg,https://oleks-netizen.github.io/product-images/80411515m/012.jpg,https://oleks-netizen.github.io/product-images/80411515m/013.jpg,https://oleks-netizen.github.io/product-images/80411515m/014.jpg,https://oleks-netizen.github.io/product-images/80411515m/015.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>80411530m</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80411530m/001.jpg,https://oleks-netizen.github.io/product-images/80411530m/002.jpg,https://oleks-netizen.github.io/product-images/80411530m/003.jpg,https://oleks-netizen.github.io/product-images/80411530m/004.jpg,https://oleks-netizen.github.io/product-images/80411530m/005.jpg,https://oleks-netizen.github.io/product-images/80411530m/006.jpg,https://oleks-netizen.github.io/product-images/80411530m/007.jpg,https://oleks-netizen.github.io/product-images/80411530m/009.jpg,https://oleks-netizen.github.io/product-images/80411530m/010.jpg,https://oleks-netizen.github.io/product-images/80411530m/011.jpg,https://oleks-netizen.github.io/product-images/80411530m/012.jpg,https://oleks-netizen.github.io/product-images/80411530m/013.jpg,https://oleks-netizen.github.io/product-images/80411530m/014.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>80411714</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80411714/001.jpg,https://oleks-netizen.github.io/product-images/80411714/002.jpg,https://oleks-netizen.github.io/product-images/80411714/003.jpg,https://oleks-netizen.github.io/product-images/80411714/004.jpg,https://oleks-netizen.github.io/product-images/80411714/006.jpg,https://oleks-netizen.github.io/product-images/80411714/007.jpg,https://oleks-netizen.github.io/product-images/80411714/008.jpg,https://oleks-netizen.github.io/product-images/80411714/009.jpg,https://oleks-netizen.github.io/product-images/80411714/010.jpg,https://oleks-netizen.github.io/product-images/80411714/011.jpg,https://oleks-netizen.github.io/product-images/80411714/012.jpg,https://oleks-netizen.github.io/product-images/80411714/013.jpg,https://oleks-netizen.github.io/product-images/80411714/014.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>804600410</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/804600410/001.jpg,https://oleks-netizen.github.io/product-images/804600410/002.jpg,https://oleks-netizen.github.io/product-images/804600410/003.jpg,https://oleks-netizen.github.io/product-images/804600410/005.jpg,https://oleks-netizen.github.io/product-images/804600410/006.jpg,https://oleks-netizen.github.io/product-images/804600410/007.jpg,https://oleks-netizen.github.io/product-images/804600410/008.jpg,https://oleks-netizen.github.io/product-images/804600410/009.jpg,https://oleks-netizen.github.io/product-images/804600410/010.jpg,https://oleks-netizen.github.io/product-images/804600410/011.jpg,https://oleks-netizen.github.io/product-images/804600410/012.jpg,https://oleks-netizen.github.io/product-images/804600410/013.jpg,https://oleks-netizen.github.io/product-images/804600410/014.jpg,https://oleks-netizen.github.io/product-images/804600410/015.jpg,https://oleks-netizen.github.io/product-images/804600410/016.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>80460060</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460060/001.jpg,https://oleks-netizen.github.io/product-images/80460060/002.jpg,https://oleks-netizen.github.io/product-images/80460060/003.jpg,https://oleks-netizen.github.io/product-images/80460060/005.jpg,https://oleks-netizen.github.io/product-images/80460060/006.jpg,https://oleks-netizen.github.io/product-images/80460060/007.jpg,https://oleks-netizen.github.io/product-images/80460060/008.jpg,https://oleks-netizen.github.io/product-images/80460060/009.jpg,https://oleks-netizen.github.io/product-images/80460060/010.jpg,https://oleks-netizen.github.io/product-images/80460060/011.jpg,https://oleks-netizen.github.io/product-images/80460060/012.jpg,https://oleks-netizen.github.io/product-images/80460060/013.jpg,https://oleks-netizen.github.io/product-images/80460060/014.jpg,https://oleks-netizen.github.io/product-images/80460060/015.jpg,https://oleks-netizen.github.io/product-images/80460060/016.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>80460401</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460401/001.jpg,https://oleks-netizen.github.io/product-images/80460401/002.jpg,https://oleks-netizen.github.io/product-images/80460401/003.jpg,https://oleks-netizen.github.io/product-images/80460401/005.jpg,https://oleks-netizen.github.io/product-images/80460401/006.jpg,https://oleks-netizen.github.io/product-images/80460401/007.jpg,https://oleks-netizen.github.io/product-images/80460401/008.jpg,https://oleks-netizen.github.io/product-images/80460401/009.jpg,https://oleks-netizen.github.io/product-images/80460401/010.jpg,https://oleks-netizen.github.io/product-images/80460401/011.jpg,https://oleks-netizen.github.io/product-images/80460401/012.jpg,https://oleks-netizen.github.io/product-images/80460401/013.jpg,https://oleks-netizen.github.io/product-images/80460401/014.jpg,https://oleks-netizen.github.io/product-images/80460401/015.jpg,https://oleks-netizen.github.io/product-images/80460401/016.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>85151020</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/85151020/001.jpg,https://oleks-netizen.github.io/product-images/85151020/002.jpg,https://oleks-netizen.github.io/product-images/85151020/003.jpg,https://oleks-netizen.github.io/product-images/85151020/004.jpg,https://oleks-netizen.github.io/product-images/85151020/005.jpg,https://oleks-netizen.github.io/product-images/85151020/006.jpg,https://oleks-netizen.github.io/product-images/85151020/007.jpg,https://oleks-netizen.github.io/product-images/85151020/009.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>85451064</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/85451064/001.jpg,https://oleks-netizen.github.io/product-images/85451064/002.jpg,https://oleks-netizen.github.io/product-images/85451064/004.jpg,https://oleks-netizen.github.io/product-images/85451064/005.jpg,https://oleks-netizen.github.io/product-images/85451064/006.jpg,https://oleks-netizen.github.io/product-images/85451064/007.jpg,https://oleks-netizen.github.io/product-images/85451064/008.jpg,https://oleks-netizen.github.io/product-images/85451064/009.jpg,https://oleks-netizen.github.io/product-images/85451064/010.jpg,https://oleks-netizen.github.io/product-images/85451064/011.jpg,https://oleks-netizen.github.io/product-images/85451064/012.jpg,https://oleks-netizen.github.io/product-images/85451064/013.jpg,https://oleks-netizen.github.io/product-images/85451064/014.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>85451064m</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/85451064m/001.jpg,https://oleks-netizen.github.io/product-images/85451064m/002.jpg,https://oleks-netizen.github.io/product-images/85451064m/003.jpg,https://oleks-netizen.github.io/product-images/85451064m/004.jpg,https://oleks-netizen.github.io/product-images/85451064m/005.jpg,https://oleks-netizen.github.io/product-images/85451064m/006.jpg,https://oleks-netizen.github.io/product-images/85451064m/007.jpg,https://oleks-netizen.github.io/product-images/85451064m/009.jpg,https://oleks-netizen.github.io/product-images/85451064m/010.jpg,https://oleks-netizen.github.io/product-images/85451064m/011.jpg,https://oleks-netizen.github.io/product-images/85451064m/012.jpg,https://oleks-netizen.github.io/product-images/85451064m/013.jpg,https://oleks-netizen.github.io/product-images/85451064m/014.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>85451506</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/85451506/001.jpg,https://oleks-netizen.github.io/product-images/85451506/002.jpg,https://oleks-netizen.github.io/product-images/85451506/003.jpg,https://oleks-netizen.github.io/product-images/85451506/004.jpg,https://oleks-netizen.github.io/product-images/85451506/005.jpg,https://oleks-netizen.github.io/product-images/85451506/007.jpg,https://oleks-netizen.github.io/product-images/85451506/008.jpg,https://oleks-netizen.github.io/product-images/85451506/009.jpg,https://oleks-netizen.github.io/product-images/85451506/010.jpg,https://oleks-netizen.github.io/product-images/85451506/011.jpg,https://oleks-netizen.github.io/product-images/85451506/012.jpg,https://oleks-netizen.github.io/product-images/85451506/013.jpg,https://oleks-netizen.github.io/product-images/85451506/014.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B085</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/B085/001.jpg,https://oleks-netizen.github.io/product-images/B085/002.jpg,https://oleks-netizen.github.io/product-images/B085/004.jpg,https://oleks-netizen.github.io/product-images/B085/005.jpg,https://oleks-netizen.github.io/product-images/B085/006.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B158</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/B158/001.jpg,https://oleks-netizen.github.io/product-images/B158/002.jpg,https://oleks-netizen.github.io/product-images/B158/003.jpg,https://oleks-netizen.github.io/product-images/B158/004.jpg,https://oleks-netizen.github.io/product-images/B158/005.jpg,https://oleks-netizen.github.io/product-images/B158/006.jpg,https://oleks-netizen.github.io/product-images/B158/007.jpg,https://oleks-netizen.github.io/product-images/B158/009.jpg,https://oleks-netizen.github.io/product-images/B158/010.jpg,https://oleks-netizen.github.io/product-images/B158/011.jpg,https://oleks-netizen.github.io/product-images/B158/012.jpg,https://oleks-netizen.github.io/product-images/B158/013.jpg,https://oleks-netizen.github.io/product-images/B158/014.jpg,https://oleks-netizen.github.io/product-images/B158/015.jpg,https://oleks-netizen.github.io/product-images/B158/016.jpg,https://oleks-netizen.github.io/product-images/B158/017.jpg,https://oleks-netizen.github.io/product-images/B158/018.jpg,https://oleks-netizen.github.io/product-images/B158/019.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BN-BAG-62-g</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/007.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/008.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BN-DC-7-k-kr</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/008.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CC602_SN_BLK</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/CC602_SN_BLK/001.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/002.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/003.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/005.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/006.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/007.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L21360-010</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21360-010/001.jpg,https://oleks-netizen.github.io/product-images/L21360-010/002.jpg,https://oleks-netizen.github.io/product-images/L21360-010/004.jpg,https://oleks-netizen.github.io/product-images/L21360-010/005.jpg,https://oleks-netizen.github.io/product-images/L21360-010/006.jpg,https://oleks-netizen.github.io/product-images/L21360-010/007.jpg,https://oleks-netizen.github.io/product-images/L21360-010/008.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L21360-021</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21360-021/001.jpg,https://oleks-netizen.github.io/product-images/L21360-021/002.jpg,https://oleks-netizen.github.io/product-images/L21360-021/004.jpg,https://oleks-netizen.github.io/product-images/L21360-021/005.jpg,https://oleks-netizen.github.io/product-images/L21360-021/006.jpg,https://oleks-netizen.github.io/product-images/L21360-021/007.jpg,https://oleks-netizen.github.io/product-images/L21360-021/008.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L21360-025</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21360-025/001.jpg,https://oleks-netizen.github.io/product-images/L21360-025/002.jpg,https://oleks-netizen.github.io/product-images/L21360-025/003.jpg,https://oleks-netizen.github.io/product-images/L21360-025/005.jpg,https://oleks-netizen.github.io/product-images/L21360-025/006.jpg,https://oleks-netizen.github.io/product-images/L21360-025/007.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L21563-010</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21563-010/001.jpg,https://oleks-netizen.github.io/product-images/L21563-010/002.jpg,https://oleks-netizen.github.io/product-images/L21563-010/003.jpg,https://oleks-netizen.github.io/product-images/L21563-010/005.jpg,https://oleks-netizen.github.io/product-images/L21563-010/006.jpg,https://oleks-netizen.github.io/product-images/L21563-010/007.jpg,https://oleks-netizen.github.io/product-images/L21563-010/008.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L21563-038</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21563-038/001.jpg,https://oleks-netizen.github.io/product-images/L21563-038/002.jpg,https://oleks-netizen.github.io/product-images/L21563-038/003.jpg,https://oleks-netizen.github.io/product-images/L21563-038/005.jpg,https://oleks-netizen.github.io/product-images/L21563-038/006.jpg,https://oleks-netizen.github.io/product-images/L21563-038/007.jpg,https://oleks-netizen.github.io/product-images/L21563-038/008.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L21563-045</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21563-045/001.jpg,https://oleks-netizen.github.io/product-images/L21563-045/002.jpg,https://oleks-netizen.github.io/product-images/L21563-045/003.jpg,https://oleks-netizen.github.io/product-images/L21563-045/005.jpg,https://oleks-netizen.github.io/product-images/L21563-045/006.jpg,https://oleks-netizen.github.io/product-images/L21563-045/007.jpg,https://oleks-netizen.github.io/product-images/L21563-045/008.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L21564-010</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21564-010/001.jpg,https://oleks-netizen.github.io/product-images/L21564-010/002.jpg,https://oleks-netizen.github.io/product-images/L21564-010/003.jpg,https://oleks-netizen.github.io/product-images/L21564-010/005.jpg,https://oleks-netizen.github.io/product-images/L21564-010/006.jpg,https://oleks-netizen.github.io/product-images/L21564-010/007.jpg,https://oleks-netizen.github.io/product-images/L21564-010/008.jpg</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L21564-025</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21564-025/001.jpg,https://oleks-netizen.github.io/product-images/L21564-025/002.jpg,https://oleks-netizen.github.io/product-images/L21564-025/003.jpg,https://oleks-netizen.github.io/product-images/L21564-025/005.jpg,https://oleks-netizen.github.io/product-images/L21564-025/006.jpg,https://oleks-netizen.github.io/product-images/L21564-025/007.jpg,https://oleks-netizen.github.io/product-images/L21564-025/008.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L21564-066</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21564-066/001.jpg,https://oleks-netizen.github.io/product-images/L21564-066/002.jpg,https://oleks-netizen.github.io/product-images/L21564-066/003.jpg,https://oleks-netizen.github.io/product-images/L21564-066/005.jpg,https://oleks-netizen.github.io/product-images/L21564-066/006.jpg,https://oleks-netizen.github.io/product-images/L21564-066/007.jpg,https://oleks-netizen.github.io/product-images/L21564-066/008.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L21580-1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21580-1/001.jpg,https://oleks-netizen.github.io/product-images/L21580-1/002.jpg,https://oleks-netizen.github.io/product-images/L21580-1/003.jpg,https://oleks-netizen.github.io/product-images/L21580-1/005.jpg,https://oleks-netizen.github.io/product-images/L21580-1/006.jpg,https://oleks-netizen.github.io/product-images/L21580-1/007.jpg,https://oleks-netizen.github.io/product-images/L21580-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L21580-175</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21580-175/001.jpg,https://oleks-netizen.github.io/product-images/L21580-175/002.jpg,https://oleks-netizen.github.io/product-images/L21580-175/003.jpg,https://oleks-netizen.github.io/product-images/L21580-175/005.jpg,https://oleks-netizen.github.io/product-images/L21580-175/006.jpg,https://oleks-netizen.github.io/product-images/L21580-175/007.jpg,https://oleks-netizen.github.io/product-images/L21580-175/008.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L21580-49</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L21580-49/001.jpg,https://oleks-netizen.github.io/product-images/L21580-49/002.jpg,https://oleks-netizen.github.io/product-images/L21580-49/003.jpg,https://oleks-netizen.github.io/product-images/L21580-49/005.jpg,https://oleks-netizen.github.io/product-images/L21580-49/006.jpg,https://oleks-netizen.github.io/product-images/L21580-49/007.jpg,https://oleks-netizen.github.io/product-images/L21580-49/008.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L87025-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87025-01/001.jpg,https://oleks-netizen.github.io/product-images/L87025-01/002.jpg,https://oleks-netizen.github.io/product-images/L87025-01/003.jpg,https://oleks-netizen.github.io/product-images/L87025-01/005.jpg,https://oleks-netizen.github.io/product-images/L87025-01/006.jpg,https://oleks-netizen.github.io/product-images/L87025-01/007.jpg,https://oleks-netizen.github.io/product-images/L87025-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L87025-13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87025-13/001.jpg,https://oleks-netizen.github.io/product-images/L87025-13/002.jpg,https://oleks-netizen.github.io/product-images/L87025-13/003.jpg,https://oleks-netizen.github.io/product-images/L87025-13/005.jpg,https://oleks-netizen.github.io/product-images/L87025-13/006.jpg,https://oleks-netizen.github.io/product-images/L87025-13/007.jpg,https://oleks-netizen.github.io/product-images/L87025-13/008.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L87025-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87025-23/001.jpg,https://oleks-netizen.github.io/product-images/L87025-23/002.jpg,https://oleks-netizen.github.io/product-images/L87025-23/003.jpg,https://oleks-netizen.github.io/product-images/L87025-23/005.jpg,https://oleks-netizen.github.io/product-images/L87025-23/006.jpg,https://oleks-netizen.github.io/product-images/L87025-23/007.jpg,https://oleks-netizen.github.io/product-images/L87025-23/008.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L87025-26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87025-26/001.jpg,https://oleks-netizen.github.io/product-images/L87025-26/002.jpg,https://oleks-netizen.github.io/product-images/L87025-26/003.jpg,https://oleks-netizen.github.io/product-images/L87025-26/005.jpg,https://oleks-netizen.github.io/product-images/L87025-26/006.jpg,https://oleks-netizen.github.io/product-images/L87025-26/007.jpg,https://oleks-netizen.github.io/product-images/L87025-26/008.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L87093-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87093-01/001.jpg,https://oleks-netizen.github.io/product-images/L87093-01/002.jpg,https://oleks-netizen.github.io/product-images/L87093-01/004.jpg,https://oleks-netizen.github.io/product-images/L87093-01/005.jpg,https://oleks-netizen.github.io/product-images/L87093-01/006.jpg,https://oleks-netizen.github.io/product-images/L87093-01/007.jpg,https://oleks-netizen.github.io/product-images/L87093-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L87093-108</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87093-108/001.jpg,https://oleks-netizen.github.io/product-images/L87093-108/003.jpg,https://oleks-netizen.github.io/product-images/L87093-108/004.jpg,https://oleks-netizen.github.io/product-images/L87093-108/005.jpg,https://oleks-netizen.github.io/product-images/L87093-108/006.jpg,https://oleks-netizen.github.io/product-images/L87093-108/007.jpg,https://oleks-netizen.github.io/product-images/L87093-108/008.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L87093-245</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87093-245/001.jpg,https://oleks-netizen.github.io/product-images/L87093-245/003.jpg,https://oleks-netizen.github.io/product-images/L87093-245/004.jpg,https://oleks-netizen.github.io/product-images/L87093-245/005.jpg,https://oleks-netizen.github.io/product-images/L87093-245/006.jpg,https://oleks-netizen.github.io/product-images/L87093-245/007.jpg,https://oleks-netizen.github.io/product-images/L87093-245/008.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L87093-246</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87093-246/001.jpg,https://oleks-netizen.github.io/product-images/L87093-246/002.jpg,https://oleks-netizen.github.io/product-images/L87093-246/004.jpg,https://oleks-netizen.github.io/product-images/L87093-246/005.jpg,https://oleks-netizen.github.io/product-images/L87093-246/006.jpg,https://oleks-netizen.github.io/product-images/L87093-246/007.jpg,https://oleks-netizen.github.io/product-images/L87093-246/008.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L87114-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87114-01/001.jpg,https://oleks-netizen.github.io/product-images/L87114-01/002.jpg,https://oleks-netizen.github.io/product-images/L87114-01/003.jpg,https://oleks-netizen.github.io/product-images/L87114-01/005.jpg,https://oleks-netizen.github.io/product-images/L87114-01/006.jpg,https://oleks-netizen.github.io/product-images/L87114-01/007.jpg,https://oleks-netizen.github.io/product-images/L87114-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L87114-108</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87114-108/001.jpg,https://oleks-netizen.github.io/product-images/L87114-108/002.jpg,https://oleks-netizen.github.io/product-images/L87114-108/003.jpg,https://oleks-netizen.github.io/product-images/L87114-108/005.jpg,https://oleks-netizen.github.io/product-images/L87114-108/006.jpg,https://oleks-netizen.github.io/product-images/L87114-108/007.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L87114-246</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87114-246/001.jpg,https://oleks-netizen.github.io/product-images/L87114-246/002.jpg,https://oleks-netizen.github.io/product-images/L87114-246/003.jpg,https://oleks-netizen.github.io/product-images/L87114-246/005.jpg,https://oleks-netizen.github.io/product-images/L87114-246/006.jpg,https://oleks-netizen.github.io/product-images/L87114-246/007.jpg,https://oleks-netizen.github.io/product-images/L87114-246/008.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L87169-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87169-01/001.jpg,https://oleks-netizen.github.io/product-images/L87169-01/002.jpg,https://oleks-netizen.github.io/product-images/L87169-01/003.jpg,https://oleks-netizen.github.io/product-images/L87169-01/005.jpg,https://oleks-netizen.github.io/product-images/L87169-01/006.jpg,https://oleks-netizen.github.io/product-images/L87169-01/007.jpg,https://oleks-netizen.github.io/product-images/L87169-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L87169-113</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87169-113/001.jpg,https://oleks-netizen.github.io/product-images/L87169-113/002.jpg,https://oleks-netizen.github.io/product-images/L87169-113/003.jpg,https://oleks-netizen.github.io/product-images/L87169-113/005.jpg,https://oleks-netizen.github.io/product-images/L87169-113/006.jpg,https://oleks-netizen.github.io/product-images/L87169-113/007.jpg,https://oleks-netizen.github.io/product-images/L87169-113/008.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L87169-175</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87169-175/001.jpg,https://oleks-netizen.github.io/product-images/L87169-175/002.jpg,https://oleks-netizen.github.io/product-images/L87169-175/003.jpg,https://oleks-netizen.github.io/product-images/L87169-175/005.jpg,https://oleks-netizen.github.io/product-images/L87169-175/006.jpg,https://oleks-netizen.github.io/product-images/L87169-175/007.jpg,https://oleks-netizen.github.io/product-images/L87169-175/008.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L87169-81</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87169-81/001.jpg,https://oleks-netizen.github.io/product-images/L87169-81/002.jpg,https://oleks-netizen.github.io/product-images/L87169-81/003.jpg,https://oleks-netizen.github.io/product-images/L87169-81/005.jpg,https://oleks-netizen.github.io/product-images/L87169-81/006.jpg,https://oleks-netizen.github.io/product-images/L87169-81/007.jpg,https://oleks-netizen.github.io/product-images/L87169-81/008.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L87518-01</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87518-01/001.jpg,https://oleks-netizen.github.io/product-images/L87518-01/002.jpg,https://oleks-netizen.github.io/product-images/L87518-01/003.jpg,https://oleks-netizen.github.io/product-images/L87518-01/005.jpg,https://oleks-netizen.github.io/product-images/L87518-01/006.jpg,https://oleks-netizen.github.io/product-images/L87518-01/007.jpg,https://oleks-netizen.github.io/product-images/L87518-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L87518-56</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87518-56/001.jpg,https://oleks-netizen.github.io/product-images/L87518-56/002.jpg,https://oleks-netizen.github.io/product-images/L87518-56/004.jpg,https://oleks-netizen.github.io/product-images/L87518-56/005.jpg,https://oleks-netizen.github.io/product-images/L87518-56/006.jpg,https://oleks-netizen.github.io/product-images/L87518-56/007.jpg,https://oleks-netizen.github.io/product-images/L87518-56/008.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L87518-79</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87518-79/001.jpg,https://oleks-netizen.github.io/product-images/L87518-79/002.jpg,https://oleks-netizen.github.io/product-images/L87518-79/004.jpg,https://oleks-netizen.github.io/product-images/L87518-79/005.jpg,https://oleks-netizen.github.io/product-images/L87518-79/006.jpg,https://oleks-netizen.github.io/product-images/L87518-79/007.jpg,https://oleks-netizen.github.io/product-images/L87518-79/008.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L87713-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87713-01/001.jpg,https://oleks-netizen.github.io/product-images/L87713-01/002.jpg,https://oleks-netizen.github.io/product-images/L87713-01/003.jpg,https://oleks-netizen.github.io/product-images/L87713-01/005.jpg,https://oleks-netizen.github.io/product-images/L87713-01/006.jpg,https://oleks-netizen.github.io/product-images/L87713-01/007.jpg,https://oleks-netizen.github.io/product-images/L87713-01/008.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L87713-107</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87713-107/001.jpg,https://oleks-netizen.github.io/product-images/L87713-107/002.jpg,https://oleks-netizen.github.io/product-images/L87713-107/003.jpg,https://oleks-netizen.github.io/product-images/L87713-107/005.jpg,https://oleks-netizen.github.io/product-images/L87713-107/006.jpg,https://oleks-netizen.github.io/product-images/L87713-107/007.jpg,https://oleks-netizen.github.io/product-images/L87713-107/008.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L87713-221</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87713-221/001.jpg,https://oleks-netizen.github.io/product-images/L87713-221/002.jpg,https://oleks-netizen.github.io/product-images/L87713-221/003.jpg,https://oleks-netizen.github.io/product-images/L87713-221/005.jpg,https://oleks-netizen.github.io/product-images/L87713-221/006.jpg,https://oleks-netizen.github.io/product-images/L87713-221/007.jpg,https://oleks-netizen.github.io/product-images/L87713-221/008.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L87713-97</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87713-97/001.jpg,https://oleks-netizen.github.io/product-images/L87713-97/002.jpg,https://oleks-netizen.github.io/product-images/L87713-97/003.jpg,https://oleks-netizen.github.io/product-images/L87713-97/005.jpg,https://oleks-netizen.github.io/product-images/L87713-97/006.jpg,https://oleks-netizen.github.io/product-images/L87713-97/007.jpg,https://oleks-netizen.github.io/product-images/L87713-97/008.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TW-Vivian-mokko</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/004.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/006.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,252 +436,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18228066</t>
+          <t>1733_1_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18228066/001.jpg,https://oleks-netizen.github.io/product-images/18228066/002.jpg,https://oleks-netizen.github.io/product-images/18228066/003.jpg,https://oleks-netizen.github.io/product-images/18228066/004.jpg,https://oleks-netizen.github.io/product-images/18228066/005.jpg,https://oleks-netizen.github.io/product-images/18228066/006.jpg,https://oleks-netizen.github.io/product-images/18228066/007.jpg,https://oleks-netizen.github.io/product-images/18228066/008.jpg,https://oleks-netizen.github.io/product-images/18228066/009.jpg,https://oleks-netizen.github.io/product-images/18228066/011.jpg,https://oleks-netizen.github.io/product-images/18228066/012.jpg,https://oleks-netizen.github.io/product-images/18228066/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1733_1_1/001.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18228067</t>
+          <t>206120</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18228067/001.jpg,https://oleks-netizen.github.io/product-images/18228067/002.jpg,https://oleks-netizen.github.io/product-images/18228067/003.jpg,https://oleks-netizen.github.io/product-images/18228067/005.jpg,https://oleks-netizen.github.io/product-images/18228067/006.jpg,https://oleks-netizen.github.io/product-images/18228067/007.jpg,https://oleks-netizen.github.io/product-images/18228067/008.jpg,https://oleks-netizen.github.io/product-images/18228067/009.jpg,https://oleks-netizen.github.io/product-images/18228067/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/206120/001.jpg,https://oleks-netizen.github.io/product-images/206120/002.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18228068</t>
+          <t>20906_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18228068/001.jpg,https://oleks-netizen.github.io/product-images/18228068/002.jpg,https://oleks-netizen.github.io/product-images/18228068/003.jpg,https://oleks-netizen.github.io/product-images/18228068/004.jpg,https://oleks-netizen.github.io/product-images/18228068/005.jpg,https://oleks-netizen.github.io/product-images/18228068/007.jpg,https://oleks-netizen.github.io/product-images/18228068/008.jpg,https://oleks-netizen.github.io/product-images/18228068/009.jpg,https://oleks-netizen.github.io/product-images/18228068/010.jpg,https://oleks-netizen.github.io/product-images/18228068/011.jpg,https://oleks-netizen.github.io/product-images/18228068/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/20906_1/001.jpg,https://oleks-netizen.github.io/product-images/20906_1/003.jpg,https://oleks-netizen.github.io/product-images/20906_1/004.jpg,https://oleks-netizen.github.io/product-images/20906_1/005.jpg,https://oleks-netizen.github.io/product-images/20906_1/007.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25000506</t>
+          <t>2140_1_1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000506/001.jpg,https://oleks-netizen.github.io/product-images/25000506/002.jpg,https://oleks-netizen.github.io/product-images/25000506/003.jpg,https://oleks-netizen.github.io/product-images/25000506/004.jpg,https://oleks-netizen.github.io/product-images/25000506/005.jpg,https://oleks-netizen.github.io/product-images/25000506/006.jpg,https://oleks-netizen.github.io/product-images/25000506/007.jpg,https://oleks-netizen.github.io/product-images/25000506/009.jpg,https://oleks-netizen.github.io/product-images/25000506/010.jpg,https://oleks-netizen.github.io/product-images/25000506/011.jpg,https://oleks-netizen.github.io/product-images/25000506/012.jpg,https://oleks-netizen.github.io/product-images/25000506/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2140_1_1/001.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25000514</t>
+          <t>224420</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000514/001.jpg,https://oleks-netizen.github.io/product-images/25000514/002.jpg,https://oleks-netizen.github.io/product-images/25000514/003.jpg,https://oleks-netizen.github.io/product-images/25000514/004.jpg,https://oleks-netizen.github.io/product-images/25000514/005.jpg,https://oleks-netizen.github.io/product-images/25000514/006.jpg,https://oleks-netizen.github.io/product-images/25000514/007.jpg,https://oleks-netizen.github.io/product-images/25000514/008.jpg,https://oleks-netizen.github.io/product-images/25000514/009.jpg,https://oleks-netizen.github.io/product-images/25000514/011.jpg,https://oleks-netizen.github.io/product-images/25000514/012.jpg,https://oleks-netizen.github.io/product-images/25000514/013.jpg,https://oleks-netizen.github.io/product-images/25000514/014.jpg,https://oleks-netizen.github.io/product-images/25000514/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/224420/001.jpg,https://oleks-netizen.github.io/product-images/224420/002.jpg,https://oleks-netizen.github.io/product-images/224420/003.jpg,https://oleks-netizen.github.io/product-images/224420/004.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25000514m</t>
+          <t>2338_1_5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000514m/001.jpg,https://oleks-netizen.github.io/product-images/25000514m/002.jpg,https://oleks-netizen.github.io/product-images/25000514m/004.jpg,https://oleks-netizen.github.io/product-images/25000514m/005.jpg,https://oleks-netizen.github.io/product-images/25000514m/006.jpg,https://oleks-netizen.github.io/product-images/25000514m/007.jpg,https://oleks-netizen.github.io/product-images/25000514m/008.jpg,https://oleks-netizen.github.io/product-images/25000514m/009.jpg,https://oleks-netizen.github.io/product-images/25000514m/010.jpg,https://oleks-netizen.github.io/product-images/25000514m/011.jpg,https://oleks-netizen.github.io/product-images/25000514m/012.jpg,https://oleks-netizen.github.io/product-images/25000514m/013.jpg,https://oleks-netizen.github.io/product-images/25000514m/014.jpg,https://oleks-netizen.github.io/product-images/25000514m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2338_1_5/001.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25000515</t>
+          <t>2421_1_2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000515/001.jpg,https://oleks-netizen.github.io/product-images/25000515/002.jpg,https://oleks-netizen.github.io/product-images/25000515/003.jpg,https://oleks-netizen.github.io/product-images/25000515/005.jpg,https://oleks-netizen.github.io/product-images/25000515/006.jpg,https://oleks-netizen.github.io/product-images/25000515/007.jpg,https://oleks-netizen.github.io/product-images/25000515/008.jpg,https://oleks-netizen.github.io/product-images/25000515/009.jpg,https://oleks-netizen.github.io/product-images/25000515/010.jpg,https://oleks-netizen.github.io/product-images/25000515/011.jpg,https://oleks-netizen.github.io/product-images/25000515/012.jpg,https://oleks-netizen.github.io/product-images/25000515/013.jpg,https://oleks-netizen.github.io/product-images/25000515/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2421_1_2/001.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25000515m</t>
+          <t>2423_1_100</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000515m/001.jpg,https://oleks-netizen.github.io/product-images/25000515m/002.jpg,https://oleks-netizen.github.io/product-images/25000515m/003.jpg,https://oleks-netizen.github.io/product-images/25000515m/004.jpg,https://oleks-netizen.github.io/product-images/25000515m/005.jpg,https://oleks-netizen.github.io/product-images/25000515m/007.jpg,https://oleks-netizen.github.io/product-images/25000515m/008.jpg,https://oleks-netizen.github.io/product-images/25000515m/009.jpg,https://oleks-netizen.github.io/product-images/25000515m/010.jpg,https://oleks-netizen.github.io/product-images/25000515m/011.jpg,https://oleks-netizen.github.io/product-images/25000515m/012.jpg,https://oleks-netizen.github.io/product-images/25000515m/013.jpg,https://oleks-netizen.github.io/product-images/25000515m/014.jpg,https://oleks-netizen.github.io/product-images/25000515m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2423_1_100/001.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51311506</t>
+          <t>2459_1_6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51311506/001.jpg,https://oleks-netizen.github.io/product-images/51311506/002.jpg,https://oleks-netizen.github.io/product-images/51311506/003.jpg,https://oleks-netizen.github.io/product-images/51311506/004.jpg,https://oleks-netizen.github.io/product-images/51311506/005.jpg,https://oleks-netizen.github.io/product-images/51311506/006.jpg,https://oleks-netizen.github.io/product-images/51311506/008.jpg,https://oleks-netizen.github.io/product-images/51311506/009.jpg,https://oleks-netizen.github.io/product-images/51311506/010.jpg,https://oleks-netizen.github.io/product-images/51311506/011.jpg,https://oleks-netizen.github.io/product-images/51311506/012.jpg,https://oleks-netizen.github.io/product-images/51311506/013.jpg,https://oleks-netizen.github.io/product-images/51311506/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2459_1_6/001.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51411006</t>
+          <t>25000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411006/001.jpg,https://oleks-netizen.github.io/product-images/51411006/002.jpg,https://oleks-netizen.github.io/product-images/51411006/003.jpg,https://oleks-netizen.github.io/product-images/51411006/004.jpg,https://oleks-netizen.github.io/product-images/51411006/005.jpg,https://oleks-netizen.github.io/product-images/51411006/006.jpg,https://oleks-netizen.github.io/product-images/51411006/008.jpg,https://oleks-netizen.github.io/product-images/51411006/009.jpg,https://oleks-netizen.github.io/product-images/51411006/010.jpg,https://oleks-netizen.github.io/product-images/51411006/011.jpg,https://oleks-netizen.github.io/product-images/51411006/012.jpg,https://oleks-netizen.github.io/product-images/51411006/013.jpg,https://oleks-netizen.github.io/product-images/51411006/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000010/001.jpg,https://oleks-netizen.github.io/product-images/25000010/002.jpg,https://oleks-netizen.github.io/product-images/25000010/003.jpg,https://oleks-netizen.github.io/product-images/25000010/005.jpg,https://oleks-netizen.github.io/product-images/25000010/006.jpg,https://oleks-netizen.github.io/product-images/25000010/007.jpg,https://oleks-netizen.github.io/product-images/25000010/008.jpg,https://oleks-netizen.github.io/product-images/25000010/009.jpg,https://oleks-netizen.github.io/product-images/25000010/010.jpg,https://oleks-netizen.github.io/product-images/25000010/011.jpg,https://oleks-netizen.github.io/product-images/25000010/012.jpg,https://oleks-netizen.github.io/product-images/25000010/013.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51411506</t>
+          <t>25000010m</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411506/001.jpg,https://oleks-netizen.github.io/product-images/51411506/002.jpg,https://oleks-netizen.github.io/product-images/51411506/003.jpg,https://oleks-netizen.github.io/product-images/51411506/004.jpg,https://oleks-netizen.github.io/product-images/51411506/005.jpg,https://oleks-netizen.github.io/product-images/51411506/006.jpg,https://oleks-netizen.github.io/product-images/51411506/007.jpg,https://oleks-netizen.github.io/product-images/51411506/009.jpg,https://oleks-netizen.github.io/product-images/51411506/010.jpg,https://oleks-netizen.github.io/product-images/51411506/011.jpg,https://oleks-netizen.github.io/product-images/51411506/012.jpg,https://oleks-netizen.github.io/product-images/51411506/013.jpg,https://oleks-netizen.github.io/product-images/51411506/014.jpg,https://oleks-netizen.github.io/product-images/51411506/015.jpg,https://oleks-netizen.github.io/product-images/51411506/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000010m/001.jpg,https://oleks-netizen.github.io/product-images/25000010m/002.jpg,https://oleks-netizen.github.io/product-images/25000010m/004.jpg,https://oleks-netizen.github.io/product-images/25000010m/005.jpg,https://oleks-netizen.github.io/product-images/25000010m/006.jpg,https://oleks-netizen.github.io/product-images/25000010m/007.jpg,https://oleks-netizen.github.io/product-images/25000010m/008.jpg,https://oleks-netizen.github.io/product-images/25000010m/009.jpg,https://oleks-netizen.github.io/product-images/25000010m/010.jpg,https://oleks-netizen.github.io/product-images/25000010m/011.jpg,https://oleks-netizen.github.io/product-images/25000010m/012.jpg,https://oleks-netizen.github.io/product-images/25000010m/013.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>53100066</t>
+          <t>25000064</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100066/001.jpg,https://oleks-netizen.github.io/product-images/53100066/002.jpg,https://oleks-netizen.github.io/product-images/53100066/003.jpg,https://oleks-netizen.github.io/product-images/53100066/004.jpg,https://oleks-netizen.github.io/product-images/53100066/005.jpg,https://oleks-netizen.github.io/product-images/53100066/006.jpg,https://oleks-netizen.github.io/product-images/53100066/007.jpg,https://oleks-netizen.github.io/product-images/53100066/009.jpg,https://oleks-netizen.github.io/product-images/53100066/010.jpg,https://oleks-netizen.github.io/product-images/53100066/011.jpg,https://oleks-netizen.github.io/product-images/53100066/012.jpg,https://oleks-netizen.github.io/product-images/53100066/013.jpg,https://oleks-netizen.github.io/product-images/53100066/014.jpg,https://oleks-netizen.github.io/product-images/53100066/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000064/001.jpg,https://oleks-netizen.github.io/product-images/25000064/002.jpg,https://oleks-netizen.github.io/product-images/25000064/003.jpg,https://oleks-netizen.github.io/product-images/25000064/005.jpg,https://oleks-netizen.github.io/product-images/25000064/006.jpg,https://oleks-netizen.github.io/product-images/25000064/007.jpg,https://oleks-netizen.github.io/product-images/25000064/008.jpg,https://oleks-netizen.github.io/product-images/25000064/009.jpg,https://oleks-netizen.github.io/product-images/25000064/010.jpg,https://oleks-netizen.github.io/product-images/25000064/011.jpg,https://oleks-netizen.github.io/product-images/25000064/012.jpg,https://oleks-netizen.github.io/product-images/25000064/013.jpg,https://oleks-netizen.github.io/product-images/25000064/014.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>53100106</t>
+          <t>25000064m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100106/001.jpg,https://oleks-netizen.github.io/product-images/53100106/002.jpg,https://oleks-netizen.github.io/product-images/53100106/003.jpg,https://oleks-netizen.github.io/product-images/53100106/004.jpg,https://oleks-netizen.github.io/product-images/53100106/005.jpg,https://oleks-netizen.github.io/product-images/53100106/007.jpg,https://oleks-netizen.github.io/product-images/53100106/008.jpg,https://oleks-netizen.github.io/product-images/53100106/009.jpg,https://oleks-netizen.github.io/product-images/53100106/010.jpg,https://oleks-netizen.github.io/product-images/53100106/011.jpg,https://oleks-netizen.github.io/product-images/53100106/012.jpg,https://oleks-netizen.github.io/product-images/53100106/013.jpg,https://oleks-netizen.github.io/product-images/53100106/014.jpg,https://oleks-netizen.github.io/product-images/53100106/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000064m/001.jpg,https://oleks-netizen.github.io/product-images/25000064m/003.jpg,https://oleks-netizen.github.io/product-images/25000064m/004.jpg,https://oleks-netizen.github.io/product-images/25000064m/005.jpg,https://oleks-netizen.github.io/product-images/25000064m/006.jpg,https://oleks-netizen.github.io/product-images/25000064m/007.jpg,https://oleks-netizen.github.io/product-images/25000064m/008.jpg,https://oleks-netizen.github.io/product-images/25000064m/009.jpg,https://oleks-netizen.github.io/product-images/25000064m/010.jpg,https://oleks-netizen.github.io/product-images/25000064m/011.jpg,https://oleks-netizen.github.io/product-images/25000064m/012.jpg,https://oleks-netizen.github.io/product-images/25000064m/013.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>53300066</t>
+          <t>25000264</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53300066/001.jpg,https://oleks-netizen.github.io/product-images/53300066/002.jpg,https://oleks-netizen.github.io/product-images/53300066/003.jpg,https://oleks-netizen.github.io/product-images/53300066/004.jpg,https://oleks-netizen.github.io/product-images/53300066/005.jpg,https://oleks-netizen.github.io/product-images/53300066/006.jpg,https://oleks-netizen.github.io/product-images/53300066/007.jpg,https://oleks-netizen.github.io/product-images/53300066/009.jpg,https://oleks-netizen.github.io/product-images/53300066/010.jpg,https://oleks-netizen.github.io/product-images/53300066/011.jpg,https://oleks-netizen.github.io/product-images/53300066/012.jpg,https://oleks-netizen.github.io/product-images/53300066/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000264/001.jpg,https://oleks-netizen.github.io/product-images/25000264/002.jpg,https://oleks-netizen.github.io/product-images/25000264/003.jpg,https://oleks-netizen.github.io/product-images/25000264/004.jpg,https://oleks-netizen.github.io/product-images/25000264/005.jpg,https://oleks-netizen.github.io/product-images/25000264/007.jpg,https://oleks-netizen.github.io/product-images/25000264/008.jpg,https://oleks-netizen.github.io/product-images/25000264/009.jpg,https://oleks-netizen.github.io/product-images/25000264/010.jpg,https://oleks-netizen.github.io/product-images/25000264/011.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>53330029</t>
+          <t>25000264m</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330029/001.jpg,https://oleks-netizen.github.io/product-images/53330029/002.jpg,https://oleks-netizen.github.io/product-images/53330029/003.jpg,https://oleks-netizen.github.io/product-images/53330029/004.jpg,https://oleks-netizen.github.io/product-images/53330029/005.jpg,https://oleks-netizen.github.io/product-images/53330029/006.jpg,https://oleks-netizen.github.io/product-images/53330029/008.jpg,https://oleks-netizen.github.io/product-images/53330029/009.jpg,https://oleks-netizen.github.io/product-images/53330029/010.jpg,https://oleks-netizen.github.io/product-images/53330029/011.jpg,https://oleks-netizen.github.io/product-images/53330029/012.jpg,https://oleks-netizen.github.io/product-images/53330029/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25000264m/001.jpg,https://oleks-netizen.github.io/product-images/25000264m/002.jpg,https://oleks-netizen.github.io/product-images/25000264m/003.jpg,https://oleks-netizen.github.io/product-images/25000264m/004.jpg,https://oleks-netizen.github.io/product-images/25000264m/005.jpg,https://oleks-netizen.github.io/product-images/25000264m/006.jpg,https://oleks-netizen.github.io/product-images/25000264m/007.jpg,https://oleks-netizen.github.io/product-images/25000264m/008.jpg,https://oleks-netizen.github.io/product-images/25000264m/010.jpg,https://oleks-netizen.github.io/product-images/25000264m/011.jpg,https://oleks-netizen.github.io/product-images/25000264m/012.jpg,https://oleks-netizen.github.io/product-images/25000264m/013.jpg,https://oleks-netizen.github.io/product-images/25000264m/014.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>53330029m</t>
+          <t>25428164</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330029m/001.jpg,https://oleks-netizen.github.io/product-images/53330029m/002.jpg,https://oleks-netizen.github.io/product-images/53330029m/003.jpg,https://oleks-netizen.github.io/product-images/53330029m/004.jpg,https://oleks-netizen.github.io/product-images/53330029m/005.jpg,https://oleks-netizen.github.io/product-images/53330029m/006.jpg,https://oleks-netizen.github.io/product-images/53330029m/008.jpg,https://oleks-netizen.github.io/product-images/53330029m/009.jpg,https://oleks-netizen.github.io/product-images/53330029m/010.jpg,https://oleks-netizen.github.io/product-images/53330029m/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25428164/001.jpg,https://oleks-netizen.github.io/product-images/25428164/002.jpg,https://oleks-netizen.github.io/product-images/25428164/003.jpg,https://oleks-netizen.github.io/product-images/25428164/004.jpg,https://oleks-netizen.github.io/product-images/25428164/005.jpg,https://oleks-netizen.github.io/product-images/25428164/007.jpg,https://oleks-netizen.github.io/product-images/25428164/008.jpg,https://oleks-netizen.github.io/product-images/25428164/009.jpg,https://oleks-netizen.github.io/product-images/25428164/010.jpg,https://oleks-netizen.github.io/product-images/25428164/011.jpg,https://oleks-netizen.github.io/product-images/25428164/012.jpg,https://oleks-netizen.github.io/product-images/25428164/013.jpg,https://oleks-netizen.github.io/product-images/25428164/014.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>53330064</t>
+          <t>25428164m</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330064/001.jpg,https://oleks-netizen.github.io/product-images/53330064/002.jpg,https://oleks-netizen.github.io/product-images/53330064/003.jpg,https://oleks-netizen.github.io/product-images/53330064/004.jpg,https://oleks-netizen.github.io/product-images/53330064/005.jpg,https://oleks-netizen.github.io/product-images/53330064/006.jpg,https://oleks-netizen.github.io/product-images/53330064/007.jpg,https://oleks-netizen.github.io/product-images/53330064/008.jpg,https://oleks-netizen.github.io/product-images/53330064/009.jpg,https://oleks-netizen.github.io/product-images/53330064/010.jpg,https://oleks-netizen.github.io/product-images/53330064/011.jpg,https://oleks-netizen.github.io/product-images/53330064/013.jpg,https://oleks-netizen.github.io/product-images/53330064/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25428164m/001.jpg,https://oleks-netizen.github.io/product-images/25428164m/002.jpg,https://oleks-netizen.github.io/product-images/25428164m/004.jpg,https://oleks-netizen.github.io/product-images/25428164m/005.jpg,https://oleks-netizen.github.io/product-images/25428164m/006.jpg,https://oleks-netizen.github.io/product-images/25428164m/007.jpg,https://oleks-netizen.github.io/product-images/25428164m/008.jpg,https://oleks-netizen.github.io/product-images/25428164m/009.jpg,https://oleks-netizen.github.io/product-images/25428164m/010.jpg,https://oleks-netizen.github.io/product-images/25428164m/011.jpg,https://oleks-netizen.github.io/product-images/25428164m/012.jpg,https://oleks-netizen.github.io/product-images/25428164m/013.jpg,https://oleks-netizen.github.io/product-images/25428164m/014.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,27 +691,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>53330064m</t>
+          <t>25438115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330064m/001.jpg,https://oleks-netizen.github.io/product-images/53330064m/002.jpg,https://oleks-netizen.github.io/product-images/53330064m/003.jpg,https://oleks-netizen.github.io/product-images/53330064m/004.jpg,https://oleks-netizen.github.io/product-images/53330064m/006.jpg,https://oleks-netizen.github.io/product-images/53330064m/007.jpg,https://oleks-netizen.github.io/product-images/53330064m/008.jpg,https://oleks-netizen.github.io/product-images/53330064m/009.jpg,https://oleks-netizen.github.io/product-images/53330064m/010.jpg,https://oleks-netizen.github.io/product-images/53330064m/011.jpg,https://oleks-netizen.github.io/product-images/53330064m/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25438115/001.jpg,https://oleks-netizen.github.io/product-images/25438115/002.jpg,https://oleks-netizen.github.io/product-images/25438115/003.jpg,https://oleks-netizen.github.io/product-images/25438115/004.jpg,https://oleks-netizen.github.io/product-images/25438115/006.jpg,https://oleks-netizen.github.io/product-images/25438115/007.jpg,https://oleks-netizen.github.io/product-images/25438115/008.jpg,https://oleks-netizen.github.io/product-images/25438115/009.jpg,https://oleks-netizen.github.io/product-images/25438115/010.jpg,https://oleks-netizen.github.io/product-images/25438115/011.jpg,https://oleks-netizen.github.io/product-images/25438115/012.jpg,https://oleks-netizen.github.io/product-images/25438115/013.jpg,https://oleks-netizen.github.io/product-images/25438115/014.jpg,https://oleks-netizen.github.io/product-images/25438115/015.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>53330066</t>
+          <t>25438115m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330066/001.jpg,https://oleks-netizen.github.io/product-images/53330066/002.jpg,https://oleks-netizen.github.io/product-images/53330066/003.jpg,https://oleks-netizen.github.io/product-images/53330066/004.jpg,https://oleks-netizen.github.io/product-images/53330066/005.jpg,https://oleks-netizen.github.io/product-images/53330066/007.jpg,https://oleks-netizen.github.io/product-images/53330066/008.jpg,https://oleks-netizen.github.io/product-images/53330066/009.jpg,https://oleks-netizen.github.io/product-images/53330066/010.jpg,https://oleks-netizen.github.io/product-images/53330066/011.jpg,https://oleks-netizen.github.io/product-images/53330066/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25438115m/001.jpg,https://oleks-netizen.github.io/product-images/25438115m/002.jpg,https://oleks-netizen.github.io/product-images/25438115m/004.jpg,https://oleks-netizen.github.io/product-images/25438115m/005.jpg,https://oleks-netizen.github.io/product-images/25438115m/006.jpg,https://oleks-netizen.github.io/product-images/25438115m/007.jpg,https://oleks-netizen.github.io/product-images/25438115m/008.jpg,https://oleks-netizen.github.io/product-images/25438115m/009.jpg,https://oleks-netizen.github.io/product-images/25438115m/010.jpg,https://oleks-netizen.github.io/product-images/25438115m/011.jpg,https://oleks-netizen.github.io/product-images/25438115m/012.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>53330068</t>
+          <t>25438164</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330068/001.jpg,https://oleks-netizen.github.io/product-images/53330068/002.jpg,https://oleks-netizen.github.io/product-images/53330068/003.jpg,https://oleks-netizen.github.io/product-images/53330068/004.jpg,https://oleks-netizen.github.io/product-images/53330068/005.jpg,https://oleks-netizen.github.io/product-images/53330068/006.jpg,https://oleks-netizen.github.io/product-images/53330068/007.jpg,https://oleks-netizen.github.io/product-images/53330068/009.jpg,https://oleks-netizen.github.io/product-images/53330068/010.jpg,https://oleks-netizen.github.io/product-images/53330068/011.jpg,https://oleks-netizen.github.io/product-images/53330068/012.jpg,https://oleks-netizen.github.io/product-images/53330068/013.jpg,https://oleks-netizen.github.io/product-images/53330068/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25438164/001.jpg,https://oleks-netizen.github.io/product-images/25438164/002.jpg,https://oleks-netizen.github.io/product-images/25438164/003.jpg,https://oleks-netizen.github.io/product-images/25438164/004.jpg,https://oleks-netizen.github.io/product-images/25438164/005.jpg,https://oleks-netizen.github.io/product-images/25438164/006.jpg,https://oleks-netizen.github.io/product-images/25438164/007.jpg,https://oleks-netizen.github.io/product-images/25438164/008.jpg,https://oleks-netizen.github.io/product-images/25438164/009.jpg,https://oleks-netizen.github.io/product-images/25438164/010.jpg,https://oleks-netizen.github.io/product-images/25438164/011.jpg,https://oleks-netizen.github.io/product-images/25438164/012.jpg,https://oleks-netizen.github.io/product-images/25438164/014.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,552 +736,552 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>53330514</t>
+          <t>25438164m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330514/001.jpg,https://oleks-netizen.github.io/product-images/53330514/002.jpg,https://oleks-netizen.github.io/product-images/53330514/003.jpg,https://oleks-netizen.github.io/product-images/53330514/004.jpg,https://oleks-netizen.github.io/product-images/53330514/005.jpg,https://oleks-netizen.github.io/product-images/53330514/006.jpg,https://oleks-netizen.github.io/product-images/53330514/008.jpg,https://oleks-netizen.github.io/product-images/53330514/009.jpg,https://oleks-netizen.github.io/product-images/53330514/010.jpg,https://oleks-netizen.github.io/product-images/53330514/011.jpg,https://oleks-netizen.github.io/product-images/53330514/012.jpg,https://oleks-netizen.github.io/product-images/53330514/013.jpg,https://oleks-netizen.github.io/product-images/53330514/014.jpg,https://oleks-netizen.github.io/product-images/53330514/015.jpg,https://oleks-netizen.github.io/product-images/53330514/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/25438164m/001.jpg,https://oleks-netizen.github.io/product-images/25438164m/002.jpg,https://oleks-netizen.github.io/product-images/25438164m/003.jpg,https://oleks-netizen.github.io/product-images/25438164m/004.jpg,https://oleks-netizen.github.io/product-images/25438164m/005.jpg,https://oleks-netizen.github.io/product-images/25438164m/006.jpg,https://oleks-netizen.github.io/product-images/25438164m/007.jpg,https://oleks-netizen.github.io/product-images/25438164m/008.jpg,https://oleks-netizen.github.io/product-images/25438164m/009.jpg,https://oleks-netizen.github.io/product-images/25438164m/010.jpg,https://oleks-netizen.github.io/product-images/25438164m/011.jpg,https://oleks-netizen.github.io/product-images/25438164m/012.jpg,https://oleks-netizen.github.io/product-images/25438164m/013.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>53330514m</t>
+          <t>30127445</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330514m/001.jpg,https://oleks-netizen.github.io/product-images/53330514m/002.jpg,https://oleks-netizen.github.io/product-images/53330514m/003.jpg,https://oleks-netizen.github.io/product-images/53330514m/004.jpg,https://oleks-netizen.github.io/product-images/53330514m/005.jpg,https://oleks-netizen.github.io/product-images/53330514m/006.jpg,https://oleks-netizen.github.io/product-images/53330514m/007.jpg,https://oleks-netizen.github.io/product-images/53330514m/008.jpg,https://oleks-netizen.github.io/product-images/53330514m/010.jpg,https://oleks-netizen.github.io/product-images/53330514m/011.jpg,https://oleks-netizen.github.io/product-images/53330514m/012.jpg,https://oleks-netizen.github.io/product-images/53330514m/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30127445/001.jpg,https://oleks-netizen.github.io/product-images/30127445/002.jpg,https://oleks-netizen.github.io/product-images/30127445/003.jpg,https://oleks-netizen.github.io/product-images/30127445/004.jpg,https://oleks-netizen.github.io/product-images/30127445/005.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>53330530</t>
+          <t>303660</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330530/001.jpg,https://oleks-netizen.github.io/product-images/53330530/002.jpg,https://oleks-netizen.github.io/product-images/53330530/003.jpg,https://oleks-netizen.github.io/product-images/53330530/004.jpg,https://oleks-netizen.github.io/product-images/53330530/005.jpg,https://oleks-netizen.github.io/product-images/53330530/006.jpg,https://oleks-netizen.github.io/product-images/53330530/007.jpg,https://oleks-netizen.github.io/product-images/53330530/008.jpg,https://oleks-netizen.github.io/product-images/53330530/009.jpg,https://oleks-netizen.github.io/product-images/53330530/010.jpg,https://oleks-netizen.github.io/product-images/53330530/011.jpg,https://oleks-netizen.github.io/product-images/53330530/013.jpg,https://oleks-netizen.github.io/product-images/53330530/014.jpg,https://oleks-netizen.github.io/product-images/53330530/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/303660/001.jpg,https://oleks-netizen.github.io/product-images/303660/003.jpg,https://oleks-netizen.github.io/product-images/303660/004.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53330530m</t>
+          <t>51411010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53330530m/001.jpg,https://oleks-netizen.github.io/product-images/53330530m/002.jpg,https://oleks-netizen.github.io/product-images/53330530m/003.jpg,https://oleks-netizen.github.io/product-images/53330530m/004.jpg,https://oleks-netizen.github.io/product-images/53330530m/005.jpg,https://oleks-netizen.github.io/product-images/53330530m/006.jpg,https://oleks-netizen.github.io/product-images/53330530m/008.jpg,https://oleks-netizen.github.io/product-images/53330530m/009.jpg,https://oleks-netizen.github.io/product-images/53330530m/010.jpg,https://oleks-netizen.github.io/product-images/53330530m/011.jpg,https://oleks-netizen.github.io/product-images/53330530m/012.jpg,https://oleks-netizen.github.io/product-images/53330530m/013.jpg,https://oleks-netizen.github.io/product-images/53330530m/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010/001.jpg,https://oleks-netizen.github.io/product-images/51411010/002.jpg,https://oleks-netizen.github.io/product-images/51411010/003.jpg,https://oleks-netizen.github.io/product-images/51411010/005.jpg,https://oleks-netizen.github.io/product-images/51411010/006.jpg,https://oleks-netizen.github.io/product-images/51411010/007.jpg,https://oleks-netizen.github.io/product-images/51411010/008.jpg,https://oleks-netizen.github.io/product-images/51411010/009.jpg,https://oleks-netizen.github.io/product-images/51411010/010.jpg,https://oleks-netizen.github.io/product-images/51411010/011.jpg,https://oleks-netizen.github.io/product-images/51411010/012.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>53400506</t>
+          <t>51411064</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400506/001.jpg,https://oleks-netizen.github.io/product-images/53400506/002.jpg,https://oleks-netizen.github.io/product-images/53400506/003.jpg,https://oleks-netizen.github.io/product-images/53400506/004.jpg,https://oleks-netizen.github.io/product-images/53400506/005.jpg,https://oleks-netizen.github.io/product-images/53400506/006.jpg,https://oleks-netizen.github.io/product-images/53400506/007.jpg,https://oleks-netizen.github.io/product-images/53400506/008.jpg,https://oleks-netizen.github.io/product-images/53400506/009.jpg,https://oleks-netizen.github.io/product-images/53400506/010.jpg,https://oleks-netizen.github.io/product-images/53400506/012.jpg,https://oleks-netizen.github.io/product-images/53400506/013.jpg,https://oleks-netizen.github.io/product-images/53400506/014.jpg,https://oleks-netizen.github.io/product-images/53400506/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411064/001.jpg,https://oleks-netizen.github.io/product-images/51411064/002.jpg,https://oleks-netizen.github.io/product-images/51411064/003.jpg,https://oleks-netizen.github.io/product-images/51411064/004.jpg,https://oleks-netizen.github.io/product-images/51411064/005.jpg,https://oleks-netizen.github.io/product-images/51411064/006.jpg,https://oleks-netizen.github.io/product-images/51411064/008.jpg,https://oleks-netizen.github.io/product-images/51411064/009.jpg,https://oleks-netizen.github.io/product-images/51411064/010.jpg,https://oleks-netizen.github.io/product-images/51411064/011.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>53400514</t>
+          <t>51411064m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400514/001.jpg,https://oleks-netizen.github.io/product-images/53400514/002.jpg,https://oleks-netizen.github.io/product-images/53400514/003.jpg,https://oleks-netizen.github.io/product-images/53400514/005.jpg,https://oleks-netizen.github.io/product-images/53400514/006.jpg,https://oleks-netizen.github.io/product-images/53400514/007.jpg,https://oleks-netizen.github.io/product-images/53400514/008.jpg,https://oleks-netizen.github.io/product-images/53400514/009.jpg,https://oleks-netizen.github.io/product-images/53400514/010.jpg,https://oleks-netizen.github.io/product-images/53400514/011.jpg,https://oleks-netizen.github.io/product-images/53400514/012.jpg,https://oleks-netizen.github.io/product-images/53400514/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411064m/001.jpg,https://oleks-netizen.github.io/product-images/51411064m/002.jpg,https://oleks-netizen.github.io/product-images/51411064m/003.jpg,https://oleks-netizen.github.io/product-images/51411064m/004.jpg,https://oleks-netizen.github.io/product-images/51411064m/005.jpg,https://oleks-netizen.github.io/product-images/51411064m/007.jpg,https://oleks-netizen.github.io/product-images/51411064m/008.jpg,https://oleks-netizen.github.io/product-images/51411064m/009.jpg,https://oleks-netizen.github.io/product-images/51411064m/010.jpg,https://oleks-netizen.github.io/product-images/51411064m/011.jpg,https://oleks-netizen.github.io/product-images/51411064m/012.jpg,https://oleks-netizen.github.io/product-images/51411064m/013.jpg,https://oleks-netizen.github.io/product-images/51411064m/014.jpg,https://oleks-netizen.github.io/product-images/51411064m/015.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>53400514m</t>
+          <t>51411120</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400514m/001.jpg,https://oleks-netizen.github.io/product-images/53400514m/002.jpg,https://oleks-netizen.github.io/product-images/53400514m/003.jpg,https://oleks-netizen.github.io/product-images/53400514m/004.jpg,https://oleks-netizen.github.io/product-images/53400514m/005.jpg,https://oleks-netizen.github.io/product-images/53400514m/006.jpg,https://oleks-netizen.github.io/product-images/53400514m/007.jpg,https://oleks-netizen.github.io/product-images/53400514m/009.jpg,https://oleks-netizen.github.io/product-images/53400514m/010.jpg,https://oleks-netizen.github.io/product-images/53400514m/011.jpg,https://oleks-netizen.github.io/product-images/53400514m/012.jpg,https://oleks-netizen.github.io/product-images/53400514m/013.jpg,https://oleks-netizen.github.io/product-images/53400514m/014.jpg,https://oleks-netizen.github.io/product-images/53400514m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411120/001.jpg,https://oleks-netizen.github.io/product-images/51411120/002.jpg,https://oleks-netizen.github.io/product-images/51411120/003.jpg,https://oleks-netizen.github.io/product-images/51411120/004.jpg,https://oleks-netizen.github.io/product-images/51411120/005.jpg,https://oleks-netizen.github.io/product-images/51411120/007.jpg,https://oleks-netizen.github.io/product-images/51411120/008.jpg,https://oleks-netizen.github.io/product-images/51411120/009.jpg,https://oleks-netizen.github.io/product-images/51411120/010.jpg,https://oleks-netizen.github.io/product-images/51411120/011.jpg,https://oleks-netizen.github.io/product-images/51411120/012.jpg,https://oleks-netizen.github.io/product-images/51411120/013.jpg,https://oleks-netizen.github.io/product-images/51411120/014.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6936686411318</t>
+          <t>51411129</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6936686411318/001.jpg,https://oleks-netizen.github.io/product-images/6936686411318/002.jpg,https://oleks-netizen.github.io/product-images/6936686411318/003.jpg,https://oleks-netizen.github.io/product-images/6936686411318/004.jpg,https://oleks-netizen.github.io/product-images/6936686411318/005.jpg,https://oleks-netizen.github.io/product-images/6936686411318/006.jpg,https://oleks-netizen.github.io/product-images/6936686411318/007.jpg,https://oleks-netizen.github.io/product-images/6936686411318/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411129/001.jpg,https://oleks-netizen.github.io/product-images/51411129/002.jpg,https://oleks-netizen.github.io/product-images/51411129/003.jpg,https://oleks-netizen.github.io/product-images/51411129/004.jpg,https://oleks-netizen.github.io/product-images/51411129/005.jpg,https://oleks-netizen.github.io/product-images/51411129/007.jpg,https://oleks-netizen.github.io/product-images/51411129/008.jpg,https://oleks-netizen.github.io/product-images/51411129/009.jpg,https://oleks-netizen.github.io/product-images/51411129/010.jpg,https://oleks-netizen.github.io/product-images/51411129/011.jpg,https://oleks-netizen.github.io/product-images/51411129/012.jpg,https://oleks-netizen.github.io/product-images/51411129/013.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6976195091748</t>
+          <t>51411210</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195091748/001.jpg,https://oleks-netizen.github.io/product-images/6976195091748/002.jpg,https://oleks-netizen.github.io/product-images/6976195091748/003.jpg,https://oleks-netizen.github.io/product-images/6976195091748/004.jpg,https://oleks-netizen.github.io/product-images/6976195091748/005.jpg,https://oleks-netizen.github.io/product-images/6976195091748/007.jpg,https://oleks-netizen.github.io/product-images/6976195091748/008.jpg,https://oleks-netizen.github.io/product-images/6976195091748/009.jpg,https://oleks-netizen.github.io/product-images/6976195091748/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411210/001.jpg,https://oleks-netizen.github.io/product-images/51411210/002.jpg,https://oleks-netizen.github.io/product-images/51411210/003.jpg,https://oleks-netizen.github.io/product-images/51411210/004.jpg,https://oleks-netizen.github.io/product-images/51411210/005.jpg,https://oleks-netizen.github.io/product-images/51411210/006.jpg,https://oleks-netizen.github.io/product-images/51411210/008.jpg,https://oleks-netizen.github.io/product-images/51411210/009.jpg,https://oleks-netizen.github.io/product-images/51411210/010.jpg,https://oleks-netizen.github.io/product-images/51411210/011.jpg,https://oleks-netizen.github.io/product-images/51411210/012.jpg,https://oleks-netizen.github.io/product-images/51411210/013.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6976195091755</t>
+          <t>51411210m</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195091755/001.jpg,https://oleks-netizen.github.io/product-images/6976195091755/002.jpg,https://oleks-netizen.github.io/product-images/6976195091755/003.jpg,https://oleks-netizen.github.io/product-images/6976195091755/004.jpg,https://oleks-netizen.github.io/product-images/6976195091755/005.jpg,https://oleks-netizen.github.io/product-images/6976195091755/007.jpg,https://oleks-netizen.github.io/product-images/6976195091755/008.jpg,https://oleks-netizen.github.io/product-images/6976195091755/009.jpg,https://oleks-netizen.github.io/product-images/6976195091755/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411210m/001.jpg,https://oleks-netizen.github.io/product-images/51411210m/002.jpg,https://oleks-netizen.github.io/product-images/51411210m/004.jpg,https://oleks-netizen.github.io/product-images/51411210m/005.jpg,https://oleks-netizen.github.io/product-images/51411210m/006.jpg,https://oleks-netizen.github.io/product-images/51411210m/007.jpg,https://oleks-netizen.github.io/product-images/51411210m/008.jpg,https://oleks-netizen.github.io/product-images/51411210m/009.jpg,https://oleks-netizen.github.io/product-images/51411210m/010.jpg,https://oleks-netizen.github.io/product-images/51411210m/011.jpg,https://oleks-netizen.github.io/product-images/51411210m/012.jpg,https://oleks-netizen.github.io/product-images/51411210m/013.jpg,https://oleks-netizen.github.io/product-images/51411210m/014.jpg,https://oleks-netizen.github.io/product-images/51411210m/015.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6976195091779</t>
+          <t>51411215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195091779/001.jpg,https://oleks-netizen.github.io/product-images/6976195091779/002.jpg,https://oleks-netizen.github.io/product-images/6976195091779/003.jpg,https://oleks-netizen.github.io/product-images/6976195091779/004.jpg,https://oleks-netizen.github.io/product-images/6976195091779/005.jpg,https://oleks-netizen.github.io/product-images/6976195091779/007.jpg,https://oleks-netizen.github.io/product-images/6976195091779/008.jpg,https://oleks-netizen.github.io/product-images/6976195091779/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215/001.jpg,https://oleks-netizen.github.io/product-images/51411215/002.jpg,https://oleks-netizen.github.io/product-images/51411215/003.jpg,https://oleks-netizen.github.io/product-images/51411215/004.jpg,https://oleks-netizen.github.io/product-images/51411215/005.jpg,https://oleks-netizen.github.io/product-images/51411215/006.jpg,https://oleks-netizen.github.io/product-images/51411215/008.jpg,https://oleks-netizen.github.io/product-images/51411215/009.jpg,https://oleks-netizen.github.io/product-images/51411215/010.jpg,https://oleks-netizen.github.io/product-images/51411215/011.jpg,https://oleks-netizen.github.io/product-images/51411215/012.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6976195091786</t>
+          <t>51411215m</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195091786/001.jpg,https://oleks-netizen.github.io/product-images/6976195091786/002.jpg,https://oleks-netizen.github.io/product-images/6976195091786/003.jpg,https://oleks-netizen.github.io/product-images/6976195091786/004.jpg,https://oleks-netizen.github.io/product-images/6976195091786/006.jpg,https://oleks-netizen.github.io/product-images/6976195091786/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215m/001.jpg,https://oleks-netizen.github.io/product-images/51411215m/002.jpg,https://oleks-netizen.github.io/product-images/51411215m/004.jpg,https://oleks-netizen.github.io/product-images/51411215m/005.jpg,https://oleks-netizen.github.io/product-images/51411215m/006.jpg,https://oleks-netizen.github.io/product-images/51411215m/007.jpg,https://oleks-netizen.github.io/product-images/51411215m/008.jpg,https://oleks-netizen.github.io/product-images/51411215m/009.jpg,https://oleks-netizen.github.io/product-images/51411215m/010.jpg,https://oleks-netizen.github.io/product-images/51411215m/011.jpg,https://oleks-netizen.github.io/product-images/51411215m/012.jpg,https://oleks-netizen.github.io/product-images/51411215m/013.jpg,https://oleks-netizen.github.io/product-images/51411215m/014.jpg,https://oleks-netizen.github.io/product-images/51411215m/015.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6976195091793</t>
+          <t>51411264</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195091793/001.jpg,https://oleks-netizen.github.io/product-images/6976195091793/002.jpg,https://oleks-netizen.github.io/product-images/6976195091793/004.jpg,https://oleks-netizen.github.io/product-images/6976195091793/005.jpg,https://oleks-netizen.github.io/product-images/6976195091793/006.jpg,https://oleks-netizen.github.io/product-images/6976195091793/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264/001.jpg,https://oleks-netizen.github.io/product-images/51411264/002.jpg,https://oleks-netizen.github.io/product-images/51411264/003.jpg,https://oleks-netizen.github.io/product-images/51411264/005.jpg,https://oleks-netizen.github.io/product-images/51411264/006.jpg,https://oleks-netizen.github.io/product-images/51411264/007.jpg,https://oleks-netizen.github.io/product-images/51411264/008.jpg,https://oleks-netizen.github.io/product-images/51411264/009.jpg,https://oleks-netizen.github.io/product-images/51411264/010.jpg,https://oleks-netizen.github.io/product-images/51411264/011.jpg,https://oleks-netizen.github.io/product-images/51411264/012.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6976195094718</t>
+          <t>51411264m</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195094718/001.jpg,https://oleks-netizen.github.io/product-images/6976195094718/002.jpg,https://oleks-netizen.github.io/product-images/6976195094718/003.jpg,https://oleks-netizen.github.io/product-images/6976195094718/004.jpg,https://oleks-netizen.github.io/product-images/6976195094718/005.jpg,https://oleks-netizen.github.io/product-images/6976195094718/006.jpg,https://oleks-netizen.github.io/product-images/6976195094718/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264m/001.jpg,https://oleks-netizen.github.io/product-images/51411264m/002.jpg,https://oleks-netizen.github.io/product-images/51411264m/003.jpg,https://oleks-netizen.github.io/product-images/51411264m/004.jpg,https://oleks-netizen.github.io/product-images/51411264m/005.jpg,https://oleks-netizen.github.io/product-images/51411264m/006.jpg,https://oleks-netizen.github.io/product-images/51411264m/007.jpg,https://oleks-netizen.github.io/product-images/51411264m/009.jpg,https://oleks-netizen.github.io/product-images/51411264m/010.jpg,https://oleks-netizen.github.io/product-images/51411264m/011.jpg,https://oleks-netizen.github.io/product-images/51411264m/012.jpg,https://oleks-netizen.github.io/product-images/51411264m/013.jpg,https://oleks-netizen.github.io/product-images/51411264m/014.jpg,https://oleks-netizen.github.io/product-images/51411264m/015.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6976195095838</t>
+          <t>5193401</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195095838/001.jpg,https://oleks-netizen.github.io/product-images/6976195095838/002.jpg,https://oleks-netizen.github.io/product-images/6976195095838/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5193401/001.jpg,https://oleks-netizen.github.io/product-images/5193401/002.jpg,https://oleks-netizen.github.io/product-images/5193401/003.jpg,https://oleks-netizen.github.io/product-images/5193401/004.jpg,https://oleks-netizen.github.io/product-images/5193401/005.jpg,https://oleks-netizen.github.io/product-images/5193401/006.jpg,https://oleks-netizen.github.io/product-images/5193401/007.jpg,https://oleks-netizen.github.io/product-images/5193401/009.jpg,https://oleks-netizen.github.io/product-images/5193401/010.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6976195095845</t>
+          <t>5202801</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195095845/001.jpg,https://oleks-netizen.github.io/product-images/6976195095845/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5202801/001.jpg,https://oleks-netizen.github.io/product-images/5202801/002.jpg,https://oleks-netizen.github.io/product-images/5202801/004.jpg,https://oleks-netizen.github.io/product-images/5202801/005.jpg,https://oleks-netizen.github.io/product-images/5202801/006.jpg,https://oleks-netizen.github.io/product-images/5202801/007.jpg,https://oleks-netizen.github.io/product-images/5202801/008.jpg,https://oleks-netizen.github.io/product-images/5202801/009.jpg,https://oleks-netizen.github.io/product-images/5202801/010.jpg,https://oleks-netizen.github.io/product-images/5202801/011.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6976195096064</t>
+          <t>5204101</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195096064/001.jpg,https://oleks-netizen.github.io/product-images/6976195096064/002.jpg,https://oleks-netizen.github.io/product-images/6976195096064/004.jpg,https://oleks-netizen.github.io/product-images/6976195096064/005.jpg,https://oleks-netizen.github.io/product-images/6976195096064/006.jpg,https://oleks-netizen.github.io/product-images/6976195096064/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5204101/001.jpg,https://oleks-netizen.github.io/product-images/5204101/002.jpg,https://oleks-netizen.github.io/product-images/5204101/003.jpg,https://oleks-netizen.github.io/product-images/5204101/004.jpg,https://oleks-netizen.github.io/product-images/5204101/005.jpg,https://oleks-netizen.github.io/product-images/5204101/006.jpg,https://oleks-netizen.github.io/product-images/5204101/007.jpg,https://oleks-netizen.github.io/product-images/5204101/008.jpg,https://oleks-netizen.github.io/product-images/5204101/009.jpg,https://oleks-netizen.github.io/product-images/5204101/010.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6976195096989</t>
+          <t>5205701</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976195096989/001.jpg,https://oleks-netizen.github.io/product-images/6976195096989/002.jpg,https://oleks-netizen.github.io/product-images/6976195096989/003.jpg,https://oleks-netizen.github.io/product-images/6976195096989/004.jpg,https://oleks-netizen.github.io/product-images/6976195096989/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5205701/001.jpg,https://oleks-netizen.github.io/product-images/5205701/002.jpg,https://oleks-netizen.github.io/product-images/5205701/004.jpg,https://oleks-netizen.github.io/product-images/5205701/005.jpg,https://oleks-netizen.github.io/product-images/5205701/006.jpg,https://oleks-netizen.github.io/product-images/5205701/007.jpg,https://oleks-netizen.github.io/product-images/5205701/008.jpg,https://oleks-netizen.github.io/product-images/5205701/009.jpg,https://oleks-netizen.github.io/product-images/5205701/010.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6976975615294</t>
+          <t>5205801</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976975615294/001.jpg,https://oleks-netizen.github.io/product-images/6976975615294/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5205801/001.jpg,https://oleks-netizen.github.io/product-images/5205801/002.jpg,https://oleks-netizen.github.io/product-images/5205801/004.jpg,https://oleks-netizen.github.io/product-images/5205801/005.jpg,https://oleks-netizen.github.io/product-images/5205801/006.jpg,https://oleks-netizen.github.io/product-images/5205801/007.jpg,https://oleks-netizen.github.io/product-images/5205801/008.jpg,https://oleks-netizen.github.io/product-images/5205801/009.jpg,https://oleks-netizen.github.io/product-images/5205801/010.jpg,https://oleks-netizen.github.io/product-images/5205801/011.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6976975615324</t>
+          <t>5210401</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6976975615324/001.jpg,https://oleks-netizen.github.io/product-images/6976975615324/003.jpg,https://oleks-netizen.github.io/product-images/6976975615324/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5210401/001.jpg,https://oleks-netizen.github.io/product-images/5210401/002.jpg,https://oleks-netizen.github.io/product-images/5210401/004.jpg,https://oleks-netizen.github.io/product-images/5210401/005.jpg,https://oleks-netizen.github.io/product-images/5210401/006.jpg,https://oleks-netizen.github.io/product-images/5210401/007.jpg,https://oleks-netizen.github.io/product-images/5210401/008.jpg,https://oleks-netizen.github.io/product-images/5210401/009.jpg,https://oleks-netizen.github.io/product-images/5210401/010.jpg,https://oleks-netizen.github.io/product-images/5210401/011.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6977703651690</t>
+          <t>5218101</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6977703651690/001.jpg,https://oleks-netizen.github.io/product-images/6977703651690/002.jpg,https://oleks-netizen.github.io/product-images/6977703651690/003.jpg,https://oleks-netizen.github.io/product-images/6977703651690/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5218101/001.jpg,https://oleks-netizen.github.io/product-images/5218101/002.jpg,https://oleks-netizen.github.io/product-images/5218101/003.jpg,https://oleks-netizen.github.io/product-images/5218101/004.jpg,https://oleks-netizen.github.io/product-images/5218101/005.jpg,https://oleks-netizen.github.io/product-images/5218101/006.jpg,https://oleks-netizen.github.io/product-images/5218101/007.jpg,https://oleks-netizen.github.io/product-images/5218101/008.jpg,https://oleks-netizen.github.io/product-images/5218101/009.jpg,https://oleks-netizen.github.io/product-images/5218101/010.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6977703651713</t>
+          <t>5221401</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/6977703651713/001.jpg,https://oleks-netizen.github.io/product-images/6977703651713/002.jpg,https://oleks-netizen.github.io/product-images/6977703651713/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5221401/001.jpg,https://oleks-netizen.github.io/product-images/5221401/003.jpg,https://oleks-netizen.github.io/product-images/5221401/004.jpg,https://oleks-netizen.github.io/product-images/5221401/005.jpg,https://oleks-netizen.github.io/product-images/5221401/006.jpg,https://oleks-netizen.github.io/product-images/5221401/007.jpg,https://oleks-netizen.github.io/product-images/5221401/008.jpg,https://oleks-netizen.github.io/product-images/5221401/009.jpg,https://oleks-netizen.github.io/product-images/5221401/010.jpg,https://oleks-netizen.github.io/product-images/5221401/011.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>80411514m</t>
+          <t>5225501</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411514m/001.jpg,https://oleks-netizen.github.io/product-images/80411514m/002.jpg,https://oleks-netizen.github.io/product-images/80411514m/004.jpg,https://oleks-netizen.github.io/product-images/80411514m/005.jpg,https://oleks-netizen.github.io/product-images/80411514m/006.jpg,https://oleks-netizen.github.io/product-images/80411514m/007.jpg,https://oleks-netizen.github.io/product-images/80411514m/008.jpg,https://oleks-netizen.github.io/product-images/80411514m/009.jpg,https://oleks-netizen.github.io/product-images/80411514m/010.jpg,https://oleks-netizen.github.io/product-images/80411514m/011.jpg,https://oleks-netizen.github.io/product-images/80411514m/012.jpg,https://oleks-netizen.github.io/product-images/80411514m/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5225501/001.jpg,https://oleks-netizen.github.io/product-images/5225501/003.jpg,https://oleks-netizen.github.io/product-images/5225501/004.jpg,https://oleks-netizen.github.io/product-images/5225501/005.jpg,https://oleks-netizen.github.io/product-images/5225501/006.jpg,https://oleks-netizen.github.io/product-images/5225501/007.jpg,https://oleks-netizen.github.io/product-images/5225501/008.jpg,https://oleks-netizen.github.io/product-images/5225501/009.jpg,https://oleks-netizen.github.io/product-images/5225501/010.jpg,https://oleks-netizen.github.io/product-images/5225501/011.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>80411515m</t>
+          <t>522623</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411515m/001.jpg,https://oleks-netizen.github.io/product-images/80411515m/002.jpg,https://oleks-netizen.github.io/product-images/80411515m/003.jpg,https://oleks-netizen.github.io/product-images/80411515m/005.jpg,https://oleks-netizen.github.io/product-images/80411515m/006.jpg,https://oleks-netizen.github.io/product-images/80411515m/007.jpg,https://oleks-netizen.github.io/product-images/80411515m/008.jpg,https://oleks-netizen.github.io/product-images/80411515m/009.jpg,https://oleks-netizen.github.io/product-images/80411515m/010.jpg,https://oleks-netizen.github.io/product-images/80411515m/011.jpg,https://oleks-netizen.github.io/product-images/80411515m/012.jpg,https://oleks-netizen.github.io/product-images/80411515m/013.jpg,https://oleks-netizen.github.io/product-images/80411515m/014.jpg,https://oleks-netizen.github.io/product-images/80411515m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/522623/001.jpg,https://oleks-netizen.github.io/product-images/522623/002.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>80411530m</t>
+          <t>522660</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411530m/001.jpg,https://oleks-netizen.github.io/product-images/80411530m/002.jpg,https://oleks-netizen.github.io/product-images/80411530m/003.jpg,https://oleks-netizen.github.io/product-images/80411530m/004.jpg,https://oleks-netizen.github.io/product-images/80411530m/005.jpg,https://oleks-netizen.github.io/product-images/80411530m/006.jpg,https://oleks-netizen.github.io/product-images/80411530m/007.jpg,https://oleks-netizen.github.io/product-images/80411530m/009.jpg,https://oleks-netizen.github.io/product-images/80411530m/010.jpg,https://oleks-netizen.github.io/product-images/80411530m/011.jpg,https://oleks-netizen.github.io/product-images/80411530m/012.jpg,https://oleks-netizen.github.io/product-images/80411530m/013.jpg,https://oleks-netizen.github.io/product-images/80411530m/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/522660/001.jpg,https://oleks-netizen.github.io/product-images/522660/002.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>80411714</t>
+          <t>5230401</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80411714/001.jpg,https://oleks-netizen.github.io/product-images/80411714/002.jpg,https://oleks-netizen.github.io/product-images/80411714/003.jpg,https://oleks-netizen.github.io/product-images/80411714/004.jpg,https://oleks-netizen.github.io/product-images/80411714/006.jpg,https://oleks-netizen.github.io/product-images/80411714/007.jpg,https://oleks-netizen.github.io/product-images/80411714/008.jpg,https://oleks-netizen.github.io/product-images/80411714/009.jpg,https://oleks-netizen.github.io/product-images/80411714/010.jpg,https://oleks-netizen.github.io/product-images/80411714/011.jpg,https://oleks-netizen.github.io/product-images/80411714/012.jpg,https://oleks-netizen.github.io/product-images/80411714/013.jpg,https://oleks-netizen.github.io/product-images/80411714/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5230401/001.jpg,https://oleks-netizen.github.io/product-images/5230401/002.jpg,https://oleks-netizen.github.io/product-images/5230401/003.jpg,https://oleks-netizen.github.io/product-images/5230401/005.jpg,https://oleks-netizen.github.io/product-images/5230401/006.jpg,https://oleks-netizen.github.io/product-images/5230401/007.jpg,https://oleks-netizen.github.io/product-images/5230401/008.jpg,https://oleks-netizen.github.io/product-images/5230401/009.jpg,https://oleks-netizen.github.io/product-images/5230401/010.jpg,https://oleks-netizen.github.io/product-images/5230401/011.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>804600410</t>
+          <t>5231101</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/804600410/001.jpg,https://oleks-netizen.github.io/product-images/804600410/002.jpg,https://oleks-netizen.github.io/product-images/804600410/003.jpg,https://oleks-netizen.github.io/product-images/804600410/005.jpg,https://oleks-netizen.github.io/product-images/804600410/006.jpg,https://oleks-netizen.github.io/product-images/804600410/007.jpg,https://oleks-netizen.github.io/product-images/804600410/008.jpg,https://oleks-netizen.github.io/product-images/804600410/009.jpg,https://oleks-netizen.github.io/product-images/804600410/010.jpg,https://oleks-netizen.github.io/product-images/804600410/011.jpg,https://oleks-netizen.github.io/product-images/804600410/012.jpg,https://oleks-netizen.github.io/product-images/804600410/013.jpg,https://oleks-netizen.github.io/product-images/804600410/014.jpg,https://oleks-netizen.github.io/product-images/804600410/015.jpg,https://oleks-netizen.github.io/product-images/804600410/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5231101/001.jpg,https://oleks-netizen.github.io/product-images/5231101/002.jpg,https://oleks-netizen.github.io/product-images/5231101/003.jpg,https://oleks-netizen.github.io/product-images/5231101/004.jpg,https://oleks-netizen.github.io/product-images/5231101/005.jpg,https://oleks-netizen.github.io/product-images/5231101/006.jpg,https://oleks-netizen.github.io/product-images/5231101/007.jpg,https://oleks-netizen.github.io/product-images/5231101/008.jpg,https://oleks-netizen.github.io/product-images/5231101/009.jpg,https://oleks-netizen.github.io/product-images/5231101/010.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>80460060</t>
+          <t>5233301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460060/001.jpg,https://oleks-netizen.github.io/product-images/80460060/002.jpg,https://oleks-netizen.github.io/product-images/80460060/003.jpg,https://oleks-netizen.github.io/product-images/80460060/005.jpg,https://oleks-netizen.github.io/product-images/80460060/006.jpg,https://oleks-netizen.github.io/product-images/80460060/007.jpg,https://oleks-netizen.github.io/product-images/80460060/008.jpg,https://oleks-netizen.github.io/product-images/80460060/009.jpg,https://oleks-netizen.github.io/product-images/80460060/010.jpg,https://oleks-netizen.github.io/product-images/80460060/011.jpg,https://oleks-netizen.github.io/product-images/80460060/012.jpg,https://oleks-netizen.github.io/product-images/80460060/013.jpg,https://oleks-netizen.github.io/product-images/80460060/014.jpg,https://oleks-netizen.github.io/product-images/80460060/015.jpg,https://oleks-netizen.github.io/product-images/80460060/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5233301/001.jpg,https://oleks-netizen.github.io/product-images/5233301/002.jpg,https://oleks-netizen.github.io/product-images/5233301/003.jpg,https://oleks-netizen.github.io/product-images/5233301/004.jpg,https://oleks-netizen.github.io/product-images/5233301/006.jpg,https://oleks-netizen.github.io/product-images/5233301/007.jpg,https://oleks-netizen.github.io/product-images/5233301/008.jpg,https://oleks-netizen.github.io/product-images/5233301/009.jpg,https://oleks-netizen.github.io/product-images/5233301/010.jpg,https://oleks-netizen.github.io/product-images/5233301/011.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>80460401</t>
+          <t>5241901</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460401/001.jpg,https://oleks-netizen.github.io/product-images/80460401/002.jpg,https://oleks-netizen.github.io/product-images/80460401/003.jpg,https://oleks-netizen.github.io/product-images/80460401/005.jpg,https://oleks-netizen.github.io/product-images/80460401/006.jpg,https://oleks-netizen.github.io/product-images/80460401/007.jpg,https://oleks-netizen.github.io/product-images/80460401/008.jpg,https://oleks-netizen.github.io/product-images/80460401/009.jpg,https://oleks-netizen.github.io/product-images/80460401/010.jpg,https://oleks-netizen.github.io/product-images/80460401/011.jpg,https://oleks-netizen.github.io/product-images/80460401/012.jpg,https://oleks-netizen.github.io/product-images/80460401/013.jpg,https://oleks-netizen.github.io/product-images/80460401/014.jpg,https://oleks-netizen.github.io/product-images/80460401/015.jpg,https://oleks-netizen.github.io/product-images/80460401/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5241901/001.jpg,https://oleks-netizen.github.io/product-images/5241901/002.jpg,https://oleks-netizen.github.io/product-images/5241901/004.jpg,https://oleks-netizen.github.io/product-images/5241901/005.jpg,https://oleks-netizen.github.io/product-images/5241901/006.jpg,https://oleks-netizen.github.io/product-images/5241901/007.jpg,https://oleks-netizen.github.io/product-images/5241901/008.jpg,https://oleks-netizen.github.io/product-images/5241901/009.jpg,https://oleks-netizen.github.io/product-images/5241901/010.jpg,https://oleks-netizen.github.io/product-images/5241901/011.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>85151020</t>
+          <t>5244701</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85151020/001.jpg,https://oleks-netizen.github.io/product-images/85151020/002.jpg,https://oleks-netizen.github.io/product-images/85151020/003.jpg,https://oleks-netizen.github.io/product-images/85151020/004.jpg,https://oleks-netizen.github.io/product-images/85151020/005.jpg,https://oleks-netizen.github.io/product-images/85151020/006.jpg,https://oleks-netizen.github.io/product-images/85151020/007.jpg,https://oleks-netizen.github.io/product-images/85151020/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5244701/001.jpg,https://oleks-netizen.github.io/product-images/5244701/002.jpg,https://oleks-netizen.github.io/product-images/5244701/003.jpg,https://oleks-netizen.github.io/product-images/5244701/004.jpg,https://oleks-netizen.github.io/product-images/5244701/005.jpg,https://oleks-netizen.github.io/product-images/5244701/006.jpg,https://oleks-netizen.github.io/product-images/5244701/007.jpg,https://oleks-netizen.github.io/product-images/5244701/008.jpg,https://oleks-netizen.github.io/product-images/5244701/009.jpg,https://oleks-netizen.github.io/product-images/5244701/010.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>85451064</t>
+          <t>5246401</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85451064/001.jpg,https://oleks-netizen.github.io/product-images/85451064/002.jpg,https://oleks-netizen.github.io/product-images/85451064/004.jpg,https://oleks-netizen.github.io/product-images/85451064/005.jpg,https://oleks-netizen.github.io/product-images/85451064/006.jpg,https://oleks-netizen.github.io/product-images/85451064/007.jpg,https://oleks-netizen.github.io/product-images/85451064/008.jpg,https://oleks-netizen.github.io/product-images/85451064/009.jpg,https://oleks-netizen.github.io/product-images/85451064/010.jpg,https://oleks-netizen.github.io/product-images/85451064/011.jpg,https://oleks-netizen.github.io/product-images/85451064/012.jpg,https://oleks-netizen.github.io/product-images/85451064/013.jpg,https://oleks-netizen.github.io/product-images/85451064/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5246401/001.jpg,https://oleks-netizen.github.io/product-images/5246401/002.jpg,https://oleks-netizen.github.io/product-images/5246401/003.jpg,https://oleks-netizen.github.io/product-images/5246401/004.jpg,https://oleks-netizen.github.io/product-images/5246401/005.jpg,https://oleks-netizen.github.io/product-images/5246401/006.jpg,https://oleks-netizen.github.io/product-images/5246401/007.jpg,https://oleks-netizen.github.io/product-images/5246401/008.jpg,https://oleks-netizen.github.io/product-images/5246401/009.jpg,https://oleks-netizen.github.io/product-images/5246401/010.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>85451064m</t>
+          <t>5248401</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85451064m/001.jpg,https://oleks-netizen.github.io/product-images/85451064m/002.jpg,https://oleks-netizen.github.io/product-images/85451064m/003.jpg,https://oleks-netizen.github.io/product-images/85451064m/004.jpg,https://oleks-netizen.github.io/product-images/85451064m/005.jpg,https://oleks-netizen.github.io/product-images/85451064m/006.jpg,https://oleks-netizen.github.io/product-images/85451064m/007.jpg,https://oleks-netizen.github.io/product-images/85451064m/009.jpg,https://oleks-netizen.github.io/product-images/85451064m/010.jpg,https://oleks-netizen.github.io/product-images/85451064m/011.jpg,https://oleks-netizen.github.io/product-images/85451064m/012.jpg,https://oleks-netizen.github.io/product-images/85451064m/013.jpg,https://oleks-netizen.github.io/product-images/85451064m/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5248401/001.jpg,https://oleks-netizen.github.io/product-images/5248401/002.jpg,https://oleks-netizen.github.io/product-images/5248401/003.jpg,https://oleks-netizen.github.io/product-images/5248401/004.jpg,https://oleks-netizen.github.io/product-images/5248401/005.jpg,https://oleks-netizen.github.io/product-images/5248401/006.jpg,https://oleks-netizen.github.io/product-images/5248401/007.jpg,https://oleks-netizen.github.io/product-images/5248401/008.jpg,https://oleks-netizen.github.io/product-images/5248401/009.jpg,https://oleks-netizen.github.io/product-images/5248401/010.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>85451506</t>
+          <t>53100013</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/85451506/001.jpg,https://oleks-netizen.github.io/product-images/85451506/002.jpg,https://oleks-netizen.github.io/product-images/85451506/003.jpg,https://oleks-netizen.github.io/product-images/85451506/004.jpg,https://oleks-netizen.github.io/product-images/85451506/005.jpg,https://oleks-netizen.github.io/product-images/85451506/007.jpg,https://oleks-netizen.github.io/product-images/85451506/008.jpg,https://oleks-netizen.github.io/product-images/85451506/009.jpg,https://oleks-netizen.github.io/product-images/85451506/010.jpg,https://oleks-netizen.github.io/product-images/85451506/011.jpg,https://oleks-netizen.github.io/product-images/85451506/012.jpg,https://oleks-netizen.github.io/product-images/85451506/013.jpg,https://oleks-netizen.github.io/product-images/85451506/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53100013/001.jpg,https://oleks-netizen.github.io/product-images/53100013/002.jpg,https://oleks-netizen.github.io/product-images/53100013/003.jpg,https://oleks-netizen.github.io/product-images/53100013/005.jpg,https://oleks-netizen.github.io/product-images/53100013/006.jpg,https://oleks-netizen.github.io/product-images/53100013/007.jpg,https://oleks-netizen.github.io/product-images/53100013/008.jpg,https://oleks-netizen.github.io/product-images/53100013/009.jpg,https://oleks-netizen.github.io/product-images/53100013/010.jpg,https://oleks-netizen.github.io/product-images/53100013/011.jpg,https://oleks-netizen.github.io/product-images/53100013/012.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B085</t>
+          <t>53300039</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/B085/001.jpg,https://oleks-netizen.github.io/product-images/B085/002.jpg,https://oleks-netizen.github.io/product-images/B085/004.jpg,https://oleks-netizen.github.io/product-images/B085/005.jpg,https://oleks-netizen.github.io/product-images/B085/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53300039/001.jpg,https://oleks-netizen.github.io/product-images/53300039/002.jpg,https://oleks-netizen.github.io/product-images/53300039/003.jpg,https://oleks-netizen.github.io/product-images/53300039/004.jpg,https://oleks-netizen.github.io/product-images/53300039/005.jpg,https://oleks-netizen.github.io/product-images/53300039/007.jpg,https://oleks-netizen.github.io/product-images/53300039/008.jpg,https://oleks-netizen.github.io/product-images/53300039/009.jpg,https://oleks-netizen.github.io/product-images/53300039/010.jpg,https://oleks-netizen.github.io/product-images/53300039/011.jpg,https://oleks-netizen.github.io/product-images/53300039/012.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B158</t>
+          <t>53400013</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/B158/001.jpg,https://oleks-netizen.github.io/product-images/B158/002.jpg,https://oleks-netizen.github.io/product-images/B158/003.jpg,https://oleks-netizen.github.io/product-images/B158/004.jpg,https://oleks-netizen.github.io/product-images/B158/005.jpg,https://oleks-netizen.github.io/product-images/B158/006.jpg,https://oleks-netizen.github.io/product-images/B158/007.jpg,https://oleks-netizen.github.io/product-images/B158/009.jpg,https://oleks-netizen.github.io/product-images/B158/010.jpg,https://oleks-netizen.github.io/product-images/B158/011.jpg,https://oleks-netizen.github.io/product-images/B158/012.jpg,https://oleks-netizen.github.io/product-images/B158/013.jpg,https://oleks-netizen.github.io/product-images/B158/014.jpg,https://oleks-netizen.github.io/product-images/B158/015.jpg,https://oleks-netizen.github.io/product-images/B158/016.jpg,https://oleks-netizen.github.io/product-images/B158/017.jpg,https://oleks-netizen.github.io/product-images/B158/018.jpg,https://oleks-netizen.github.io/product-images/B158/019.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400013/001.jpg,https://oleks-netizen.github.io/product-images/53400013/002.jpg,https://oleks-netizen.github.io/product-images/53400013/004.jpg,https://oleks-netizen.github.io/product-images/53400013/005.jpg,https://oleks-netizen.github.io/product-images/53400013/006.jpg,https://oleks-netizen.github.io/product-images/53400013/007.jpg,https://oleks-netizen.github.io/product-images/53400013/008.jpg,https://oleks-netizen.github.io/product-images/53400013/009.jpg,https://oleks-netizen.github.io/product-images/53400013/010.jpg,https://oleks-netizen.github.io/product-images/53400013/011.jpg,https://oleks-netizen.github.io/product-images/53400013/012.jpg,https://oleks-netizen.github.io/product-images/53400013/013.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BN-BAG-62-g</t>
+          <t>53400020</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/007.jpg,https://oleks-netizen.github.io/product-images/BN-BAG-62-g/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400020/001.jpg,https://oleks-netizen.github.io/product-images/53400020/002.jpg,https://oleks-netizen.github.io/product-images/53400020/004.jpg,https://oleks-netizen.github.io/product-images/53400020/005.jpg,https://oleks-netizen.github.io/product-images/53400020/006.jpg,https://oleks-netizen.github.io/product-images/53400020/007.jpg,https://oleks-netizen.github.io/product-images/53400020/008.jpg,https://oleks-netizen.github.io/product-images/53400020/009.jpg,https://oleks-netizen.github.io/product-images/53400020/010.jpg,https://oleks-netizen.github.io/product-images/53400020/011.jpg,https://oleks-netizen.github.io/product-images/53400020/012.jpg,https://oleks-netizen.github.io/product-images/53400020/013.jpg,https://oleks-netizen.github.io/product-images/53400020/014.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BN-DC-7-k-kr</t>
+          <t>62725</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/005.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/006.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/007.jpg,https://oleks-netizen.github.io/product-images/BN-DC-7-k-kr/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/62725/001.jpg,https://oleks-netizen.github.io/product-images/62725/002.jpg,https://oleks-netizen.github.io/product-images/62725/003.jpg,https://oleks-netizen.github.io/product-images/62725/004.jpg,https://oleks-netizen.github.io/product-images/62725/005.jpg,https://oleks-netizen.github.io/product-images/62725/006.jpg,https://oleks-netizen.github.io/product-images/62725/007.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1291,27 +1291,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CC602_SN_BLK</t>
+          <t>62726</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/CC602_SN_BLK/001.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/002.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/003.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/005.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/006.jpg,https://oleks-netizen.github.io/product-images/CC602_SN_BLK/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/62726/001.jpg,https://oleks-netizen.github.io/product-images/62726/002.jpg,https://oleks-netizen.github.io/product-images/62726/003.jpg,https://oleks-netizen.github.io/product-images/62726/004.jpg,https://oleks-netizen.github.io/product-images/62726/005.jpg,https://oleks-netizen.github.io/product-images/62726/006.jpg,https://oleks-netizen.github.io/product-images/62726/007.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L21360-010</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21360-010/001.jpg,https://oleks-netizen.github.io/product-images/L21360-010/002.jpg,https://oleks-netizen.github.io/product-images/L21360-010/004.jpg,https://oleks-netizen.github.io/product-images/L21360-010/005.jpg,https://oleks-netizen.github.io/product-images/L21360-010/006.jpg,https://oleks-netizen.github.io/product-images/L21360-010/007.jpg,https://oleks-netizen.github.io/product-images/L21360-010/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/62727/001.jpg,https://oleks-netizen.github.io/product-images/62727/002.jpg,https://oleks-netizen.github.io/product-images/62727/004.jpg,https://oleks-netizen.github.io/product-images/62727/005.jpg,https://oleks-netizen.github.io/product-images/62727/006.jpg,https://oleks-netizen.github.io/product-images/62727/007.jpg,https://oleks-netizen.github.io/product-images/62727/008.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1321,72 +1321,72 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L21360-021</t>
+          <t>701661</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21360-021/001.jpg,https://oleks-netizen.github.io/product-images/L21360-021/002.jpg,https://oleks-netizen.github.io/product-images/L21360-021/004.jpg,https://oleks-netizen.github.io/product-images/L21360-021/005.jpg,https://oleks-netizen.github.io/product-images/L21360-021/006.jpg,https://oleks-netizen.github.io/product-images/L21360-021/007.jpg,https://oleks-netizen.github.io/product-images/L21360-021/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/701661/001.jpg,https://oleks-netizen.github.io/product-images/701661/002.jpg,https://oleks-netizen.github.io/product-images/701661/003.jpg,https://oleks-netizen.github.io/product-images/701661/004.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L21360-025</t>
+          <t>746710</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21360-025/001.jpg,https://oleks-netizen.github.io/product-images/L21360-025/002.jpg,https://oleks-netizen.github.io/product-images/L21360-025/003.jpg,https://oleks-netizen.github.io/product-images/L21360-025/005.jpg,https://oleks-netizen.github.io/product-images/L21360-025/006.jpg,https://oleks-netizen.github.io/product-images/L21360-025/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/746710/001.jpg,https://oleks-netizen.github.io/product-images/746710/002.jpg,https://oleks-netizen.github.io/product-images/746710/003.jpg,https://oleks-netizen.github.io/product-images/746710/004.jpg,https://oleks-netizen.github.io/product-images/746710/005.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L21563-010</t>
+          <t>746743</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21563-010/001.jpg,https://oleks-netizen.github.io/product-images/L21563-010/002.jpg,https://oleks-netizen.github.io/product-images/L21563-010/003.jpg,https://oleks-netizen.github.io/product-images/L21563-010/005.jpg,https://oleks-netizen.github.io/product-images/L21563-010/006.jpg,https://oleks-netizen.github.io/product-images/L21563-010/007.jpg,https://oleks-netizen.github.io/product-images/L21563-010/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/746743/001.jpg,https://oleks-netizen.github.io/product-images/746743/002.jpg,https://oleks-netizen.github.io/product-images/746743/003.jpg,https://oleks-netizen.github.io/product-images/746743/004.jpg,https://oleks-netizen.github.io/product-images/746743/005.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L21563-038</t>
+          <t>75_1_1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21563-038/001.jpg,https://oleks-netizen.github.io/product-images/L21563-038/002.jpg,https://oleks-netizen.github.io/product-images/L21563-038/003.jpg,https://oleks-netizen.github.io/product-images/L21563-038/005.jpg,https://oleks-netizen.github.io/product-images/L21563-038/006.jpg,https://oleks-netizen.github.io/product-images/L21563-038/007.jpg,https://oleks-netizen.github.io/product-images/L21563-038/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/75_1_1/001.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L21563-045</t>
+          <t>77266101</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21563-045/001.jpg,https://oleks-netizen.github.io/product-images/L21563-045/002.jpg,https://oleks-netizen.github.io/product-images/L21563-045/003.jpg,https://oleks-netizen.github.io/product-images/L21563-045/005.jpg,https://oleks-netizen.github.io/product-images/L21563-045/006.jpg,https://oleks-netizen.github.io/product-images/L21563-045/007.jpg,https://oleks-netizen.github.io/product-images/L21563-045/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/77266101/001.jpg,https://oleks-netizen.github.io/product-images/77266101/002.jpg,https://oleks-netizen.github.io/product-images/77266101/003.jpg,https://oleks-netizen.github.io/product-images/77266101/004.jpg,https://oleks-netizen.github.io/product-images/77266101/005.jpg,https://oleks-netizen.github.io/product-images/77266101/006.jpg,https://oleks-netizen.github.io/product-images/77266101/007.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1396,192 +1396,192 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L21564-010</t>
+          <t>96193001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21564-010/001.jpg,https://oleks-netizen.github.io/product-images/L21564-010/002.jpg,https://oleks-netizen.github.io/product-images/L21564-010/003.jpg,https://oleks-netizen.github.io/product-images/L21564-010/005.jpg,https://oleks-netizen.github.io/product-images/L21564-010/006.jpg,https://oleks-netizen.github.io/product-images/L21564-010/007.jpg,https://oleks-netizen.github.io/product-images/L21564-010/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/96193001/001.jpg,https://oleks-netizen.github.io/product-images/96193001/002.jpg,https://oleks-netizen.github.io/product-images/96193001/003.jpg,https://oleks-netizen.github.io/product-images/96193001/004.jpg,https://oleks-netizen.github.io/product-images/96193001/005.jpg,https://oleks-netizen.github.io/product-images/96193001/007.jpg,https://oleks-netizen.github.io/product-images/96193001/008.jpg,https://oleks-netizen.github.io/product-images/96193001/009.jpg,https://oleks-netizen.github.io/product-images/96193001/010.jpg,https://oleks-netizen.github.io/product-images/96193001/011.jpg,https://oleks-netizen.github.io/product-images/96193001/012.jpg,https://oleks-netizen.github.io/product-images/96193001/013.jpg,https://oleks-netizen.github.io/product-images/96193001/014.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L21564-025</t>
+          <t>96193008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21564-025/001.jpg,https://oleks-netizen.github.io/product-images/L21564-025/002.jpg,https://oleks-netizen.github.io/product-images/L21564-025/003.jpg,https://oleks-netizen.github.io/product-images/L21564-025/005.jpg,https://oleks-netizen.github.io/product-images/L21564-025/006.jpg,https://oleks-netizen.github.io/product-images/L21564-025/007.jpg,https://oleks-netizen.github.io/product-images/L21564-025/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/96193008/001.jpg,https://oleks-netizen.github.io/product-images/96193008/002.jpg,https://oleks-netizen.github.io/product-images/96193008/003.jpg,https://oleks-netizen.github.io/product-images/96193008/004.jpg,https://oleks-netizen.github.io/product-images/96193008/006.jpg,https://oleks-netizen.github.io/product-images/96193008/007.jpg,https://oleks-netizen.github.io/product-images/96193008/008.jpg,https://oleks-netizen.github.io/product-images/96193008/009.jpg,https://oleks-netizen.github.io/product-images/96193008/010.jpg,https://oleks-netizen.github.io/product-images/96193008/011.jpg,https://oleks-netizen.github.io/product-images/96193008/012.jpg,https://oleks-netizen.github.io/product-images/96193008/013.jpg,https://oleks-netizen.github.io/product-images/96193008/014.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L21564-066</t>
+          <t>96193070</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21564-066/001.jpg,https://oleks-netizen.github.io/product-images/L21564-066/002.jpg,https://oleks-netizen.github.io/product-images/L21564-066/003.jpg,https://oleks-netizen.github.io/product-images/L21564-066/005.jpg,https://oleks-netizen.github.io/product-images/L21564-066/006.jpg,https://oleks-netizen.github.io/product-images/L21564-066/007.jpg,https://oleks-netizen.github.io/product-images/L21564-066/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/96193070/001.jpg,https://oleks-netizen.github.io/product-images/96193070/002.jpg,https://oleks-netizen.github.io/product-images/96193070/003.jpg,https://oleks-netizen.github.io/product-images/96193070/004.jpg,https://oleks-netizen.github.io/product-images/96193070/005.jpg,https://oleks-netizen.github.io/product-images/96193070/006.jpg,https://oleks-netizen.github.io/product-images/96193070/007.jpg,https://oleks-netizen.github.io/product-images/96193070/009.jpg,https://oleks-netizen.github.io/product-images/96193070/010.jpg,https://oleks-netizen.github.io/product-images/96193070/011.jpg,https://oleks-netizen.github.io/product-images/96193070/012.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L21580-1</t>
+          <t>96199170</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21580-1/001.jpg,https://oleks-netizen.github.io/product-images/L21580-1/002.jpg,https://oleks-netizen.github.io/product-images/L21580-1/003.jpg,https://oleks-netizen.github.io/product-images/L21580-1/005.jpg,https://oleks-netizen.github.io/product-images/L21580-1/006.jpg,https://oleks-netizen.github.io/product-images/L21580-1/007.jpg,https://oleks-netizen.github.io/product-images/L21580-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/96199170/001.jpg,https://oleks-netizen.github.io/product-images/96199170/002.jpg,https://oleks-netizen.github.io/product-images/96199170/003.jpg,https://oleks-netizen.github.io/product-images/96199170/004.jpg,https://oleks-netizen.github.io/product-images/96199170/005.jpg,https://oleks-netizen.github.io/product-images/96199170/006.jpg,https://oleks-netizen.github.io/product-images/96199170/007.jpg,https://oleks-netizen.github.io/product-images/96199170/008.jpg,https://oleks-netizen.github.io/product-images/96199170/009.jpg,https://oleks-netizen.github.io/product-images/96199170/010.jpg,https://oleks-netizen.github.io/product-images/96199170/011.jpg,https://oleks-netizen.github.io/product-images/96199170/013.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L21580-175</t>
+          <t>B10-434A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21580-175/001.jpg,https://oleks-netizen.github.io/product-images/L21580-175/002.jpg,https://oleks-netizen.github.io/product-images/L21580-175/003.jpg,https://oleks-netizen.github.io/product-images/L21580-175/005.jpg,https://oleks-netizen.github.io/product-images/L21580-175/006.jpg,https://oleks-netizen.github.io/product-images/L21580-175/007.jpg,https://oleks-netizen.github.io/product-images/L21580-175/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/B10-434A/001.jpg,https://oleks-netizen.github.io/product-images/B10-434A/002.jpg,https://oleks-netizen.github.io/product-images/B10-434A/003.jpg,https://oleks-netizen.github.io/product-images/B10-434A/004.jpg,https://oleks-netizen.github.io/product-images/B10-434A/005.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L21580-49</t>
+          <t>BB80701-50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L21580-49/001.jpg,https://oleks-netizen.github.io/product-images/L21580-49/002.jpg,https://oleks-netizen.github.io/product-images/L21580-49/003.jpg,https://oleks-netizen.github.io/product-images/L21580-49/005.jpg,https://oleks-netizen.github.io/product-images/L21580-49/006.jpg,https://oleks-netizen.github.io/product-images/L21580-49/007.jpg,https://oleks-netizen.github.io/product-images/L21580-49/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BB80701-50/001.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/002.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/003.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/005.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/006.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/007.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L87025-01</t>
+          <t>BB81251-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87025-01/001.jpg,https://oleks-netizen.github.io/product-images/L87025-01/002.jpg,https://oleks-netizen.github.io/product-images/L87025-01/003.jpg,https://oleks-netizen.github.io/product-images/L87025-01/005.jpg,https://oleks-netizen.github.io/product-images/L87025-01/006.jpg,https://oleks-netizen.github.io/product-images/L87025-01/007.jpg,https://oleks-netizen.github.io/product-images/L87025-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BB81251-02/001.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/002.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/003.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/005.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/006.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/007.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L87025-13</t>
+          <t>BN-KK-4-k-kr-karbon</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87025-13/001.jpg,https://oleks-netizen.github.io/product-images/L87025-13/002.jpg,https://oleks-netizen.github.io/product-images/L87025-13/003.jpg,https://oleks-netizen.github.io/product-images/L87025-13/005.jpg,https://oleks-netizen.github.io/product-images/L87025-13/006.jpg,https://oleks-netizen.github.io/product-images/L87025-13/007.jpg,https://oleks-netizen.github.io/product-images/L87025-13/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/001.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/002.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/003.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/004.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/006.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L87025-23</t>
+          <t>BN-KK-4-vin-kr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87025-23/001.jpg,https://oleks-netizen.github.io/product-images/L87025-23/002.jpg,https://oleks-netizen.github.io/product-images/L87025-23/003.jpg,https://oleks-netizen.github.io/product-images/L87025-23/005.jpg,https://oleks-netizen.github.io/product-images/L87025-23/006.jpg,https://oleks-netizen.github.io/product-images/L87025-23/007.jpg,https://oleks-netizen.github.io/product-images/L87025-23/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/003.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L87025-26</t>
+          <t>BN-SB-2-st-red</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87025-26/001.jpg,https://oleks-netizen.github.io/product-images/L87025-26/002.jpg,https://oleks-netizen.github.io/product-images/L87025-26/003.jpg,https://oleks-netizen.github.io/product-images/L87025-26/005.jpg,https://oleks-netizen.github.io/product-images/L87025-26/006.jpg,https://oleks-netizen.github.io/product-images/L87025-26/007.jpg,https://oleks-netizen.github.io/product-images/L87025-26/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/005.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L87093-01</t>
+          <t>BS70106-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87093-01/001.jpg,https://oleks-netizen.github.io/product-images/L87093-01/002.jpg,https://oleks-netizen.github.io/product-images/L87093-01/004.jpg,https://oleks-netizen.github.io/product-images/L87093-01/005.jpg,https://oleks-netizen.github.io/product-images/L87093-01/006.jpg,https://oleks-netizen.github.io/product-images/L87093-01/007.jpg,https://oleks-netizen.github.io/product-images/L87093-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BS70106-01/001.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/002.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/003.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/005.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/006.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/007.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L87093-108</t>
+          <t>BS80401-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87093-108/001.jpg,https://oleks-netizen.github.io/product-images/L87093-108/003.jpg,https://oleks-netizen.github.io/product-images/L87093-108/004.jpg,https://oleks-netizen.github.io/product-images/L87093-108/005.jpg,https://oleks-netizen.github.io/product-images/L87093-108/006.jpg,https://oleks-netizen.github.io/product-images/L87093-108/007.jpg,https://oleks-netizen.github.io/product-images/L87093-108/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BS80401-01/001.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/002.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/003.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/005.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/006.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/007.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L87093-245</t>
+          <t>BV39032-1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87093-245/001.jpg,https://oleks-netizen.github.io/product-images/L87093-245/003.jpg,https://oleks-netizen.github.io/product-images/L87093-245/004.jpg,https://oleks-netizen.github.io/product-images/L87093-245/005.jpg,https://oleks-netizen.github.io/product-images/L87093-245/006.jpg,https://oleks-netizen.github.io/product-images/L87093-245/007.jpg,https://oleks-netizen.github.io/product-images/L87093-245/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39032-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/008.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1591,12 +1591,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L87093-246</t>
+          <t>BV39032-191</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87093-246/001.jpg,https://oleks-netizen.github.io/product-images/L87093-246/002.jpg,https://oleks-netizen.github.io/product-images/L87093-246/004.jpg,https://oleks-netizen.github.io/product-images/L87093-246/005.jpg,https://oleks-netizen.github.io/product-images/L87093-246/006.jpg,https://oleks-netizen.github.io/product-images/L87093-246/007.jpg,https://oleks-netizen.github.io/product-images/L87093-246/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39032-191/001.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/002.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/003.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/004.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/005.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/006.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/007.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1606,12 +1606,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L87114-01</t>
+          <t>BV39139-1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87114-01/001.jpg,https://oleks-netizen.github.io/product-images/L87114-01/002.jpg,https://oleks-netizen.github.io/product-images/L87114-01/003.jpg,https://oleks-netizen.github.io/product-images/L87114-01/005.jpg,https://oleks-netizen.github.io/product-images/L87114-01/006.jpg,https://oleks-netizen.github.io/product-images/L87114-01/007.jpg,https://oleks-netizen.github.io/product-images/L87114-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39139-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/008.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1621,27 +1621,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L87114-108</t>
+          <t>BV39218-1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87114-108/001.jpg,https://oleks-netizen.github.io/product-images/L87114-108/002.jpg,https://oleks-netizen.github.io/product-images/L87114-108/003.jpg,https://oleks-netizen.github.io/product-images/L87114-108/005.jpg,https://oleks-netizen.github.io/product-images/L87114-108/006.jpg,https://oleks-netizen.github.io/product-images/L87114-108/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39218-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/008.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L87114-246</t>
+          <t>BV39218-153</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87114-246/001.jpg,https://oleks-netizen.github.io/product-images/L87114-246/002.jpg,https://oleks-netizen.github.io/product-images/L87114-246/003.jpg,https://oleks-netizen.github.io/product-images/L87114-246/005.jpg,https://oleks-netizen.github.io/product-images/L87114-246/006.jpg,https://oleks-netizen.github.io/product-images/L87114-246/007.jpg,https://oleks-netizen.github.io/product-images/L87114-246/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39218-153/001.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/002.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/004.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/005.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/006.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/007.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/008.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1651,12 +1651,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L87169-01</t>
+          <t>BV39223-1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87169-01/001.jpg,https://oleks-netizen.github.io/product-images/L87169-01/002.jpg,https://oleks-netizen.github.io/product-images/L87169-01/003.jpg,https://oleks-netizen.github.io/product-images/L87169-01/005.jpg,https://oleks-netizen.github.io/product-images/L87169-01/006.jpg,https://oleks-netizen.github.io/product-images/L87169-01/007.jpg,https://oleks-netizen.github.io/product-images/L87169-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39223-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/007.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1666,12 +1666,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L87169-113</t>
+          <t>BV39223-1-small</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87169-113/001.jpg,https://oleks-netizen.github.io/product-images/L87169-113/002.jpg,https://oleks-netizen.github.io/product-images/L87169-113/003.jpg,https://oleks-netizen.github.io/product-images/L87169-113/005.jpg,https://oleks-netizen.github.io/product-images/L87169-113/006.jpg,https://oleks-netizen.github.io/product-images/L87169-113/007.jpg,https://oleks-netizen.github.io/product-images/L87169-113/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39223-1-small/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/003.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/007.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1681,12 +1681,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L87169-175</t>
+          <t>BV39223-145</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87169-175/001.jpg,https://oleks-netizen.github.io/product-images/L87169-175/002.jpg,https://oleks-netizen.github.io/product-images/L87169-175/003.jpg,https://oleks-netizen.github.io/product-images/L87169-175/005.jpg,https://oleks-netizen.github.io/product-images/L87169-175/006.jpg,https://oleks-netizen.github.io/product-images/L87169-175/007.jpg,https://oleks-netizen.github.io/product-images/L87169-175/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39223-145/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/007.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/008.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1696,42 +1696,42 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L87169-81</t>
+          <t>BV39311-1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87169-81/001.jpg,https://oleks-netizen.github.io/product-images/L87169-81/002.jpg,https://oleks-netizen.github.io/product-images/L87169-81/003.jpg,https://oleks-netizen.github.io/product-images/L87169-81/005.jpg,https://oleks-netizen.github.io/product-images/L87169-81/006.jpg,https://oleks-netizen.github.io/product-images/L87169-81/007.jpg,https://oleks-netizen.github.io/product-images/L87169-81/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39311-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/008.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/009.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/010.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L87518-01</t>
+          <t>BV39311-153</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87518-01/001.jpg,https://oleks-netizen.github.io/product-images/L87518-01/002.jpg,https://oleks-netizen.github.io/product-images/L87518-01/003.jpg,https://oleks-netizen.github.io/product-images/L87518-01/005.jpg,https://oleks-netizen.github.io/product-images/L87518-01/006.jpg,https://oleks-netizen.github.io/product-images/L87518-01/007.jpg,https://oleks-netizen.github.io/product-images/L87518-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39311-153/001.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/002.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/004.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/005.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/006.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/007.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/008.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/009.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/010.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/011.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L87518-56</t>
+          <t>BV39318-1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87518-56/001.jpg,https://oleks-netizen.github.io/product-images/L87518-56/002.jpg,https://oleks-netizen.github.io/product-images/L87518-56/004.jpg,https://oleks-netizen.github.io/product-images/L87518-56/005.jpg,https://oleks-netizen.github.io/product-images/L87518-56/006.jpg,https://oleks-netizen.github.io/product-images/L87518-56/007.jpg,https://oleks-netizen.github.io/product-images/L87518-56/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39318-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/007.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1741,12 +1741,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L87518-79</t>
+          <t>BV39318-232</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87518-79/001.jpg,https://oleks-netizen.github.io/product-images/L87518-79/002.jpg,https://oleks-netizen.github.io/product-images/L87518-79/004.jpg,https://oleks-netizen.github.io/product-images/L87518-79/005.jpg,https://oleks-netizen.github.io/product-images/L87518-79/006.jpg,https://oleks-netizen.github.io/product-images/L87518-79/007.jpg,https://oleks-netizen.github.io/product-images/L87518-79/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39318-232/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/007.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1756,12 +1756,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L87713-01</t>
+          <t>BV39318-76A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87713-01/001.jpg,https://oleks-netizen.github.io/product-images/L87713-01/002.jpg,https://oleks-netizen.github.io/product-images/L87713-01/003.jpg,https://oleks-netizen.github.io/product-images/L87713-01/005.jpg,https://oleks-netizen.github.io/product-images/L87713-01/006.jpg,https://oleks-netizen.github.io/product-images/L87713-01/007.jpg,https://oleks-netizen.github.io/product-images/L87713-01/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39318-76A/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/007.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1771,12 +1771,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L87713-107</t>
+          <t>BV39351-1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87713-107/001.jpg,https://oleks-netizen.github.io/product-images/L87713-107/002.jpg,https://oleks-netizen.github.io/product-images/L87713-107/003.jpg,https://oleks-netizen.github.io/product-images/L87713-107/005.jpg,https://oleks-netizen.github.io/product-images/L87713-107/006.jpg,https://oleks-netizen.github.io/product-images/L87713-107/007.jpg,https://oleks-netizen.github.io/product-images/L87713-107/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39351-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/007.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1786,12 +1786,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L87713-221</t>
+          <t>BV39529-1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87713-221/001.jpg,https://oleks-netizen.github.io/product-images/L87713-221/002.jpg,https://oleks-netizen.github.io/product-images/L87713-221/003.jpg,https://oleks-netizen.github.io/product-images/L87713-221/005.jpg,https://oleks-netizen.github.io/product-images/L87713-221/006.jpg,https://oleks-netizen.github.io/product-images/L87713-221/007.jpg,https://oleks-netizen.github.io/product-images/L87713-221/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39529-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/007.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1801,12 +1801,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L87713-97</t>
+          <t>BV39529-145</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87713-97/001.jpg,https://oleks-netizen.github.io/product-images/L87713-97/002.jpg,https://oleks-netizen.github.io/product-images/L87713-97/003.jpg,https://oleks-netizen.github.io/product-images/L87713-97/005.jpg,https://oleks-netizen.github.io/product-images/L87713-97/006.jpg,https://oleks-netizen.github.io/product-images/L87713-97/007.jpg,https://oleks-netizen.github.io/product-images/L87713-97/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BV39529-145/001.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/002.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/004.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/005.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/006.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/007.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/008.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1816,16 +1816,3031 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TW-Vivian-mokko</t>
+          <t>bx050a</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/004.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Vivian-mokko/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/bx050a/001.jpg,https://oleks-netizen.github.io/product-images/bx050a/002.jpg,https://oleks-netizen.github.io/product-images/bx050a/003.jpg,https://oleks-netizen.github.io/product-images/bx050a/004.jpg,https://oleks-netizen.github.io/product-images/bx050a/005.jpg,https://oleks-netizen.github.io/product-images/bx050a/006.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>bx050c</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/bx050c/001.jpg,https://oleks-netizen.github.io/product-images/bx050c/002.jpg,https://oleks-netizen.github.io/product-images/bx050c/003.jpg,https://oleks-netizen.github.io/product-images/bx050c/005.jpg,https://oleks-netizen.github.io/product-images/bx050c/006.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>bx9020</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/bx9020/001.jpg,https://oleks-netizen.github.io/product-images/bx9020/002.jpg,https://oleks-netizen.github.io/product-images/bx9020/003.jpg,https://oleks-netizen.github.io/product-images/bx9020/004.jpg,https://oleks-netizen.github.io/product-images/bx9020/005.jpg,https://oleks-netizen.github.io/product-images/bx9020/006.jpg,https://oleks-netizen.github.io/product-images/bx9020/007.jpg,https://oleks-netizen.github.io/product-images/bx9020/008.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CC605_BN</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/CC605_BN/001.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/002.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/004.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/005.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/006.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/007.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CrH-1294-4lx</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/CrH-1294-4lx/001.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/002.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/003.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/005.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/006.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/007.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/008.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/009.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/010.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/011.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DRL19031-3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19031-3/001.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/002.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/004.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/005.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/006.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/007.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DRL19086-1</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19086-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DRL19101-1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19101-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DRL19158-2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19158-2/001.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/002.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/003.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/004.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/005.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/006.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DRL1925-1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL1925-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DRL19286-6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19286-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/008.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DRL19333-1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19333-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DRL19377-1</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19377-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DRL19389-6</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19389-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/008.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DRL19393-6</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19393-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/008.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DRL19429-1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19429-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DRL19460-1</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19460-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DRL19608-1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19608-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DRL19710-1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19710-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DRL19946-1</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRL19946-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Elit-2020-4lx</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Elit-2020-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/009.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/010.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/011.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Elit-2022-4lx</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Elit-2022-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/008.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/009.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Elit-2023-4lx</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Elit-2023-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/008.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FA-1501-3md</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FA-1501-3md/001.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/002.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/003.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/004.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/005.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/006.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/007.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FCream-8077-3md</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FCream-8077-3md/001.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/002.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/003.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/005.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/006.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/007.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FR7007K</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FR7007K/001.jpg,https://oleks-netizen.github.io/product-images/FR7007K/002.jpg,https://oleks-netizen.github.io/product-images/FR7007K/003.jpg,https://oleks-netizen.github.io/product-images/FR7007K/004.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FR7007O</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FR7007O/001.jpg,https://oleks-netizen.github.io/product-images/FR7007O/002.jpg,https://oleks-netizen.github.io/product-images/FR7007O/003.jpg,https://oleks-netizen.github.io/product-images/FR7007O/004.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FR7007P</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FR7007P/001.jpg,https://oleks-netizen.github.io/product-images/FR7007P/002.jpg,https://oleks-netizen.github.io/product-images/FR7007P/003.jpg,https://oleks-netizen.github.io/product-images/FR7007P/004.jpg,https://oleks-netizen.github.io/product-images/FR7007P/005.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>fz118545</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/fz118545/001.jpg,https://oleks-netizen.github.io/product-images/fz118545/002.jpg,https://oleks-netizen.github.io/product-images/fz118545/003.jpg,https://oleks-netizen.github.io/product-images/fz118545/004.jpg,https://oleks-netizen.github.io/product-images/fz118545/005.jpg,https://oleks-netizen.github.io/product-images/fz118545/006.jpg,https://oleks-netizen.github.io/product-images/fz118545/007.jpg,https://oleks-netizen.github.io/product-images/fz118545/008.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>fz189606</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/fz189606/001.jpg,https://oleks-netizen.github.io/product-images/fz189606/002.jpg,https://oleks-netizen.github.io/product-images/fz189606/003.jpg,https://oleks-netizen.github.io/product-images/fz189606/004.jpg,https://oleks-netizen.github.io/product-images/fz189606/006.jpg,https://oleks-netizen.github.io/product-images/fz189606/007.jpg,https://oleks-netizen.github.io/product-images/fz189606/008.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fz1896103</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/fz1896103/001.jpg,https://oleks-netizen.github.io/product-images/fz1896103/002.jpg,https://oleks-netizen.github.io/product-images/fz1896103/004.jpg,https://oleks-netizen.github.io/product-images/fz1896103/005.jpg,https://oleks-netizen.github.io/product-images/fz1896103/006.jpg,https://oleks-netizen.github.io/product-images/fz1896103/007.jpg,https://oleks-netizen.github.io/product-images/fz1896103/008.jpg,https://oleks-netizen.github.io/product-images/fz1896103/009.jpg,https://oleks-netizen.github.io/product-images/fz1896103/010.jpg,https://oleks-netizen.github.io/product-images/fz1896103/011.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>fz189645</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/fz189645/001.jpg,https://oleks-netizen.github.io/product-images/fz189645/002.jpg,https://oleks-netizen.github.io/product-images/fz189645/003.jpg,https://oleks-netizen.github.io/product-images/fz189645/004.jpg,https://oleks-netizen.github.io/product-images/fz189645/005.jpg,https://oleks-netizen.github.io/product-images/fz189645/006.jpg,https://oleks-netizen.github.io/product-images/fz189645/007.jpg,https://oleks-netizen.github.io/product-images/fz189645/008.jpg,https://oleks-netizen.github.io/product-images/fz189645/009.jpg,https://oleks-netizen.github.io/product-images/fz189645/010.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>GA-0307-4lx</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GA-0307-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GA-0324-4lx</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GA-0324-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/010.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/011.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GA-1402-4lx</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GA-1402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>GA-7281-3md</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GA-7281-3md/001.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/002.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/004.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/005.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/006.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/007.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/008.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>GB-7107-3md</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GB-7107-3md/001.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/002.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/004.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/005.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/006.jpg</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>GBalc-2067-4lx</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>GBord-2067-4lx</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GBord-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>GC-0060-4lx</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GC-0060-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/008.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>GC-1239-4lx</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GC-1239-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/008.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GC-1402-4lx</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GC-1402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GC-2067-4lx</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GC-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GC-8033-4lx</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GC-8033-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/006.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GYalc-5565-4lx</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/007.jpg</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HB0502</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB0502/001.jpg,https://oleks-netizen.github.io/product-images/HB0502/002.jpg,https://oleks-netizen.github.io/product-images/HB0502/003.jpg,https://oleks-netizen.github.io/product-images/HB0502/005.jpg,https://oleks-netizen.github.io/product-images/HB0502/006.jpg,https://oleks-netizen.github.io/product-images/HB0502/007.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HB0502Blu</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB0502Blu/001.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/003.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/004.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/005.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/006.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/007.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/008.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>HB19153A</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB19153A/001.jpg,https://oleks-netizen.github.io/product-images/HB19153A/002.jpg,https://oleks-netizen.github.io/product-images/HB19153A/003.jpg,https://oleks-netizen.github.io/product-images/HB19153A/004.jpg,https://oleks-netizen.github.io/product-images/HB19153A/005.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>HB3069Asmall</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB3069Asmall/001.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/002.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/003.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/005.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/006.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>HB3095</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB3095/001.jpg,https://oleks-netizen.github.io/product-images/HB3095/002.jpg,https://oleks-netizen.github.io/product-images/HB3095/003.jpg,https://oleks-netizen.github.io/product-images/HB3095/004.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>HB3193A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB3193A/001.jpg,https://oleks-netizen.github.io/product-images/HB3193A/002.jpg,https://oleks-netizen.github.io/product-images/HB3193A/004.jpg,https://oleks-netizen.github.io/product-images/HB3193A/005.jpg,https://oleks-netizen.github.io/product-images/HB3193A/006.jpg,https://oleks-netizen.github.io/product-images/HB3193A/007.jpg,https://oleks-netizen.github.io/product-images/HB3193A/008.jpg,https://oleks-netizen.github.io/product-images/HB3193A/009.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>HB3237B</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB3237B/001.jpg,https://oleks-netizen.github.io/product-images/HB3237B/002.jpg,https://oleks-netizen.github.io/product-images/HB3237B/003.jpg,https://oleks-netizen.github.io/product-images/HB3237B/004.jpg,https://oleks-netizen.github.io/product-images/HB3237B/005.jpg,https://oleks-netizen.github.io/product-images/HB3237B/006.jpg,https://oleks-netizen.github.io/product-images/HB3237B/007.jpg,https://oleks-netizen.github.io/product-images/HB3237B/008.jpg,https://oleks-netizen.github.io/product-images/HB3237B/009.jpg,https://oleks-netizen.github.io/product-images/HB3237B/010.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HB3628R</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HB3628R/001.jpg,https://oleks-netizen.github.io/product-images/HB3628R/002.jpg,https://oleks-netizen.github.io/product-images/HB3628R/004.jpg,https://oleks-netizen.github.io/product-images/HB3628R/005.jpg,https://oleks-netizen.github.io/product-images/HB3628R/006.jpg,https://oleks-netizen.github.io/product-images/HB3628R/007.jpg,https://oleks-netizen.github.io/product-images/HB3628R/008.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>HF502LN_BR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF502LN_BR/001.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/002.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/003.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/004.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/005.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/006.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>HF502_BU</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF502_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/007.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HF502_CROC-PLN_BRN</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/006.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>HF502_CROC-PLN_BU</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/007.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>HF502_GRN</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF502_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/005.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/006.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/007.jpg</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>HF577BLL</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577BLL/001.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/002.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/003.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/004.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/005.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/006.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/007.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HF577BN</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577BN/001.jpg,https://oleks-netizen.github.io/product-images/HF577BN/002.jpg,https://oleks-netizen.github.io/product-images/HF577BN/003.jpg,https://oleks-netizen.github.io/product-images/HF577BN/004.jpg,https://oleks-netizen.github.io/product-images/HF577BN/005.jpg,https://oleks-netizen.github.io/product-images/HF577BN/006.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>HF577LN_BR</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577LN_BR/001.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/002.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/003.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/004.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/005.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/006.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>HF577_CROC-PLN_BRN</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/006.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>HF577_CROC-PLN_BU</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/007.jpg</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>HF577_GRN</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF577_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/004.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/005.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/006.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/007.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>HF592BLK</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF592BLK/001.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/002.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/003.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/004.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/005.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HF592BNL</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF592BNL/001.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/002.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/003.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/004.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/005.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/006.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>HF592LNBR</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF592LNBR/001.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/002.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/003.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/004.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/005.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>HF594BL</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF594BL/001.jpg,https://oleks-netizen.github.io/product-images/HF594BL/002.jpg,https://oleks-netizen.github.io/product-images/HF594BL/003.jpg,https://oleks-netizen.github.io/product-images/HF594BL/004.jpg,https://oleks-netizen.github.io/product-images/HF594BL/005.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>HF594MH</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF594MH/001.jpg,https://oleks-netizen.github.io/product-images/HF594MH/002.jpg,https://oleks-netizen.github.io/product-images/HF594MH/003.jpg,https://oleks-netizen.github.io/product-images/HF594MH/004.jpg,https://oleks-netizen.github.io/product-images/HF594MH/005.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>HF594_BNL</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF594_BNL/001.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/002.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/003.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/004.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/005.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>HF594_GRN</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF594_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/004.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/005.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>HF595_MTN_BLK</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/001.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/002.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/003.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/004.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/005.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/006.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>HF597_LNBR</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/HF597_LNBR/001.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/002.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/003.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/004.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/005.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/006.jpg</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JD6020B</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/JD6020B/001.jpg,https://oleks-netizen.github.io/product-images/JD6020B/002.jpg,https://oleks-netizen.github.io/product-images/JD6020B/003.jpg,https://oleks-netizen.github.io/product-images/JD6020B/004.jpg,https://oleks-netizen.github.io/product-images/JD6020B/005.jpg,https://oleks-netizen.github.io/product-images/JD6020B/006.jpg,https://oleks-netizen.github.io/product-images/JD6020B/007.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JD7289A</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/JD7289A/001.jpg,https://oleks-netizen.github.io/product-images/JD7289A/002.jpg,https://oleks-netizen.github.io/product-images/JD7289A/003.jpg,https://oleks-netizen.github.io/product-images/JD7289A/005.jpg,https://oleks-netizen.github.io/product-images/JD7289A/006.jpg,https://oleks-netizen.github.io/product-images/JD7289A/007.jpg,https://oleks-netizen.github.io/product-images/JD7289A/008.jpg,https://oleks-netizen.github.io/product-images/JD7289A/009.jpg,https://oleks-netizen.github.io/product-images/JD7289A/010.jpg,https://oleks-netizen.github.io/product-images/JD7289A/011.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>K1617f-black</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/K1617f-black/001.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/002.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/004.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/005.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/006.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>L28001-1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28001-1/001.jpg,https://oleks-netizen.github.io/product-images/L28001-1/003.jpg,https://oleks-netizen.github.io/product-images/L28001-1/004.jpg,https://oleks-netizen.github.io/product-images/L28001-1/005.jpg,https://oleks-netizen.github.io/product-images/L28001-1/006.jpg,https://oleks-netizen.github.io/product-images/L28001-1/007.jpg,https://oleks-netizen.github.io/product-images/L28001-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>L28001-2</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28001-2/001.jpg,https://oleks-netizen.github.io/product-images/L28001-2/003.jpg,https://oleks-netizen.github.io/product-images/L28001-2/004.jpg,https://oleks-netizen.github.io/product-images/L28001-2/005.jpg,https://oleks-netizen.github.io/product-images/L28001-2/006.jpg,https://oleks-netizen.github.io/product-images/L28001-2/007.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>L28001-3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28001-3/001.jpg,https://oleks-netizen.github.io/product-images/L28001-3/003.jpg,https://oleks-netizen.github.io/product-images/L28001-3/004.jpg,https://oleks-netizen.github.io/product-images/L28001-3/005.jpg,https://oleks-netizen.github.io/product-images/L28001-3/006.jpg,https://oleks-netizen.github.io/product-images/L28001-3/007.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>L28001-4</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28001-4/001.jpg,https://oleks-netizen.github.io/product-images/L28001-4/003.jpg,https://oleks-netizen.github.io/product-images/L28001-4/004.jpg,https://oleks-netizen.github.io/product-images/L28001-4/005.jpg,https://oleks-netizen.github.io/product-images/L28001-4/006.jpg,https://oleks-netizen.github.io/product-images/L28001-4/007.jpg,https://oleks-netizen.github.io/product-images/L28001-4/008.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>L28028-1</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28028-1/001.jpg,https://oleks-netizen.github.io/product-images/L28028-1/003.jpg,https://oleks-netizen.github.io/product-images/L28028-1/004.jpg,https://oleks-netizen.github.io/product-images/L28028-1/005.jpg,https://oleks-netizen.github.io/product-images/L28028-1/006.jpg,https://oleks-netizen.github.io/product-images/L28028-1/007.jpg,https://oleks-netizen.github.io/product-images/L28028-1/008.jpg,https://oleks-netizen.github.io/product-images/L28028-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>L28028-2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28028-2/001.jpg,https://oleks-netizen.github.io/product-images/L28028-2/003.jpg,https://oleks-netizen.github.io/product-images/L28028-2/004.jpg,https://oleks-netizen.github.io/product-images/L28028-2/005.jpg,https://oleks-netizen.github.io/product-images/L28028-2/006.jpg,https://oleks-netizen.github.io/product-images/L28028-2/007.jpg,https://oleks-netizen.github.io/product-images/L28028-2/008.jpg,https://oleks-netizen.github.io/product-images/L28028-2/009.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>L28028-3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28028-3/001.jpg,https://oleks-netizen.github.io/product-images/L28028-3/003.jpg,https://oleks-netizen.github.io/product-images/L28028-3/004.jpg,https://oleks-netizen.github.io/product-images/L28028-3/005.jpg,https://oleks-netizen.github.io/product-images/L28028-3/006.jpg,https://oleks-netizen.github.io/product-images/L28028-3/007.jpg,https://oleks-netizen.github.io/product-images/L28028-3/008.jpg,https://oleks-netizen.github.io/product-images/L28028-3/009.jpg</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>L28029-1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28029-1/001.jpg,https://oleks-netizen.github.io/product-images/L28029-1/003.jpg,https://oleks-netizen.github.io/product-images/L28029-1/004.jpg,https://oleks-netizen.github.io/product-images/L28029-1/005.jpg,https://oleks-netizen.github.io/product-images/L28029-1/006.jpg,https://oleks-netizen.github.io/product-images/L28029-1/007.jpg,https://oleks-netizen.github.io/product-images/L28029-1/008.jpg,https://oleks-netizen.github.io/product-images/L28029-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>L28029-2</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28029-2/001.jpg,https://oleks-netizen.github.io/product-images/L28029-2/003.jpg,https://oleks-netizen.github.io/product-images/L28029-2/004.jpg,https://oleks-netizen.github.io/product-images/L28029-2/005.jpg,https://oleks-netizen.github.io/product-images/L28029-2/006.jpg,https://oleks-netizen.github.io/product-images/L28029-2/007.jpg,https://oleks-netizen.github.io/product-images/L28029-2/008.jpg,https://oleks-netizen.github.io/product-images/L28029-2/009.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>L28029-3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28029-3/001.jpg,https://oleks-netizen.github.io/product-images/L28029-3/003.jpg,https://oleks-netizen.github.io/product-images/L28029-3/004.jpg,https://oleks-netizen.github.io/product-images/L28029-3/005.jpg,https://oleks-netizen.github.io/product-images/L28029-3/006.jpg,https://oleks-netizen.github.io/product-images/L28029-3/007.jpg,https://oleks-netizen.github.io/product-images/L28029-3/008.jpg,https://oleks-netizen.github.io/product-images/L28029-3/009.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>L28029-4</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L28029-4/001.jpg,https://oleks-netizen.github.io/product-images/L28029-4/002.jpg,https://oleks-netizen.github.io/product-images/L28029-4/004.jpg,https://oleks-netizen.github.io/product-images/L28029-4/005.jpg,https://oleks-netizen.github.io/product-images/L28029-4/006.jpg,https://oleks-netizen.github.io/product-images/L28029-4/007.jpg,https://oleks-netizen.github.io/product-images/L28029-4/008.jpg,https://oleks-netizen.github.io/product-images/L28029-4/009.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>L501-041857</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L501-041857/001.jpg,https://oleks-netizen.github.io/product-images/L501-041857/002.jpg,https://oleks-netizen.github.io/product-images/L501-041857/003.jpg,https://oleks-netizen.github.io/product-images/L501-041857/004.jpg,https://oleks-netizen.github.io/product-images/L501-041857/005.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>L501-042014</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L501-042014/001.jpg,https://oleks-netizen.github.io/product-images/L501-042014/002.jpg,https://oleks-netizen.github.io/product-images/L501-042014/003.jpg,https://oleks-netizen.github.io/product-images/L501-042014/004.jpg,https://oleks-netizen.github.io/product-images/L501-042014/005.jpg,https://oleks-netizen.github.io/product-images/L501-042014/006.jpg,https://oleks-netizen.github.io/product-images/L501-042014/007.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>L501-042021</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L501-042021/001.jpg,https://oleks-netizen.github.io/product-images/L501-042021/002.jpg,https://oleks-netizen.github.io/product-images/L501-042021/003.jpg,https://oleks-netizen.github.io/product-images/L501-042021/004.jpg,https://oleks-netizen.github.io/product-images/L501-042021/005.jpg,https://oleks-netizen.github.io/product-images/L501-042021/006.jpg,https://oleks-netizen.github.io/product-images/L501-042021/007.jpg,https://oleks-netizen.github.io/product-images/L501-042021/008.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>L501-042038</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L501-042038/001.jpg,https://oleks-netizen.github.io/product-images/L501-042038/002.jpg,https://oleks-netizen.github.io/product-images/L501-042038/003.jpg,https://oleks-netizen.github.io/product-images/L501-042038/004.jpg,https://oleks-netizen.github.io/product-images/L501-042038/005.jpg,https://oleks-netizen.github.io/product-images/L501-042038/006.jpg,https://oleks-netizen.github.io/product-images/L501-042038/007.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>L87229-1</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L87229-1/001.jpg,https://oleks-netizen.github.io/product-images/L87229-1/002.jpg,https://oleks-netizen.github.io/product-images/L87229-1/003.jpg,https://oleks-netizen.github.io/product-images/L87229-1/004.jpg,https://oleks-netizen.github.io/product-images/L87229-1/005.jpg,https://oleks-netizen.github.io/product-images/L87229-1/006.jpg,https://oleks-netizen.github.io/product-images/L87229-1/007.jpg,https://oleks-netizen.github.io/product-images/L87229-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>L88003-32</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L88003-32/001.jpg,https://oleks-netizen.github.io/product-images/L88003-32/003.jpg,https://oleks-netizen.github.io/product-images/L88003-32/004.jpg,https://oleks-netizen.github.io/product-images/L88003-32/005.jpg,https://oleks-netizen.github.io/product-images/L88003-32/006.jpg,https://oleks-netizen.github.io/product-images/L88003-32/007.jpg,https://oleks-netizen.github.io/product-images/L88003-32/008.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>LC47208K-1</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47208K-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>LC47208K-1X</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47208K-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/006.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/007.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/008.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>LC47208K-92</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47208K-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/006.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>LC47210-1</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47210-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>LC47210-1X</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47210-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/006.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>LC47210-92</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47210-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>LC47240W-1</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47240W-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>LC47240W-1X</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47240W-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/006.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>LC47240W-92</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47240W-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>LC47539-1</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47539-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>LC47539-92</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47539-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>LC47632F-1</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47632F-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>LC47632F-92</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47632F-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>LC47695-1</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47695-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/007.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/008.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>LC47832-1</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47832-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>LC47832-92</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47832-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>LC47891-1</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47891-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>LC47891-92</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47891-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>LC47991-1A</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47991-1A/001.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/002.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/003.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/004.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/005.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>LC47991-92</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/LC47991-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/007.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Lim-181GA</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Lim-181GA/001.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/002.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/003.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/005.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/006.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/007.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/008.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>lim-22-115</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/lim-22-115/001.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/002.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/003.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/004.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>lim-28-115</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/lim-28-115/001.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/002.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/003.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/004.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Lim-372RC</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/Lim-372RC/001.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/002.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/003.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/005.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/006.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/007.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/008.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PH601BR</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/PH601BR/001.jpg,https://oleks-netizen.github.io/product-images/PH601BR/002.jpg,https://oleks-netizen.github.io/product-images/PH601BR/003.jpg,https://oleks-netizen.github.io/product-images/PH601BR/004.jpg,https://oleks-netizen.github.io/product-images/PH601BR/005.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PH601_BLK</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/PH601_BLK/001.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/002.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/003.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/004.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/005.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/006.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/007.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PH602TAN</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/PH602TAN/001.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/002.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/003.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/004.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/005.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/006.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/007.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PH602_CROC-PLN_BRN</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/006.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PH602_GRN</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/PH602_GRN/001.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/002.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/003.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/004.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/005.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>RA-1046-3md</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RA-1046-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/006.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/007.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/008.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>RA-1342-3md</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RA-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/005.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>RA-1403-4lx</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RA-1403-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/006.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>RA-1501-3md</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RA-1501-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/006.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/007.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>RA-7122-3md</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RA-7122-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/006.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>RAc-6690-4lx</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RAc-6690-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/008.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>RAg-1905-3md</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RAg-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/003.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/007.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/008.jpg</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>RB-2200RL-4lx</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/008.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/009.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>RB-3960-4lx</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RB-3960-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/008.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>RB-7122-3mdL</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RB-7122-3mdL/001.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/002.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/003.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/004.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/005.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/006.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/007.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/008.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/009.jpg</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>RB-7340-3md</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RB-7340-3md/001.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/002.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/003.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/004.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/006.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/007.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/008.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/009.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/010.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/011.jpg</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>RC-2200RL-4lx</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/003.jpg</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>RC-60121-3md</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-60121-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/002.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/006.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/008.jpg</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>RC-7122-3mdL</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-7122-3mdL/001.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/003.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/004.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/005.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/006.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/007.jpg</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>RC-7290-3md</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-7290-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/006.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/008.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>RC-7340-3md</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-7340-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/002.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/008.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/009.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/010.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/011.jpg</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>RCc-1905-3md</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RCc-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/007.jpg</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>RCC-3920-3md</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RCC-3920-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>RCc-6600-3md</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RCc-6600-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>RCk-3420-3md</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RCk-3420-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/008.jpg</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>RCs-1905-3md</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RCs-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/009.jpg</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>RE-1342-3md</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RE-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/005.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/006.jpg</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>RE-30272-3md</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RE-30272-3md/001.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/002.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/003.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/004.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/006.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/007.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/008.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/009.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/010.jpg</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>RK-1342-3md</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RK-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/005.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/006.jpg</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>RK-7122-3md</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RK-7122-3md/001.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/002.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/003.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/004.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/005.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/006.jpg</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>RYw-3027-4lx</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RYw-3027-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/006.jpg</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>RА-3990-3md</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RА-3990-3md/001.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/002.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/004.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/005.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/006.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/007.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/008.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/009.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/010.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>RС-1342-3md</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RС-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/003.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/005.jpg</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SB1164BRN</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/SB1164BRN/001.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/002.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/004.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/005.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/006.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/007.jpg</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>T0138А</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/T0138А/001.jpg,https://oleks-netizen.github.io/product-images/T0138А/002.jpg,https://oleks-netizen.github.io/product-images/T0138А/004.jpg</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TA-0042-4lx</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TA-0042-4lx/001.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/002.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/004.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/005.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/006.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/007.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/008.jpg</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>TA-5664-4lx</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TA-5664-4lx/001.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/002.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/003.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/004.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/005.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/006.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/007.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/008.jpg</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>TC4002 MH</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TC4002 MH/001.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/002.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/003.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/004.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/005.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/006.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/008.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/009.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/010.jpg</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>TC4003_BU</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TC4003_BU/001.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/002.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/003.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/004.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/005.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/006.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/008.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/009.jpg</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TC4004BR</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TC4004BR/001.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/002.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/003.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/004.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/005.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/006.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/007.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/009.jpg</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>TC4004_BLK</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TC4004_BLK/001.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/002.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/003.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/004.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/005.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/007.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/008.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/009.jpg</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>TC4004_BU</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TC4004_BU/001.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/002.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/003.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/004.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/005.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/006.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/007.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/009.jpg</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>tid3027</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tid3027/001.jpg,https://oleks-netizen.github.io/product-images/tid3027/002.jpg,https://oleks-netizen.github.io/product-images/tid3027/003.jpg,https://oleks-netizen.github.io/product-images/tid3027/004.jpg,https://oleks-netizen.github.io/product-images/tid3027/005.jpg</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>TR34 BLK_RED</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TR34 BLK_RED/001.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/002.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/003.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/005.jpg</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TW-Bella-black</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bella-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/005.jpg</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TW-Bella-dark-brown</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/005.jpg</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>TW-Bella-mokko</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bella-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/006.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/007.jpg</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>TW-Bella-olive</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bella-olive/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/006.jpg</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>TW-Bella-red</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bella-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/005.jpg</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>TW-Bridget-white</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Bridget-white/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/004.jpg</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>TW-Business-black</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Business-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-black/003.jpg</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>TW-Business-dark-blue</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/004.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/005.jpg</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>TW-Business-mars</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Business-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/005.jpg</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>TW-CB-8-black</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/004.jpg</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>TW-CB-8-light-beige</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/004.jpg</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>TW-CB-8-mars</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/004.jpg</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>TW-CB-8-mokko</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/004.jpg</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TW-CB-8-pink</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-pink/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/004.jpg</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TW-CB-8-red</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-red/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-red/004.jpg</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TW-Classic-mokko</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Classic-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/006.jpg</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TW-Explorer-S-mars</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Explorer-S-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Explorer-S-mars/002.jpg</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TW-Faith-mars</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Faith-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Faith-mars/002.jpg</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TW-Futsy-mars</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Futsy-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Futsy-mars/002.jpg</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TW-Holly-mars</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Holly-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/005.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/006.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/007.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/008.jpg</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TW-Jill-caramel</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Jill-caramel/001.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/002.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/003.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/004.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/006.jpg</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TW-Jill-red</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Jill-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-red/002.jpg</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TW-KL-5-mars</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-KL-5-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/005.jpg</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TW-Moment-mars</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Moment-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Moment-mars/002.jpg</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>TW-Nona-2-k</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-k/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/003.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/005.jpg</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TW-Nona-2-kon</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/003.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/005.jpg</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>TW-Nona-2-pink</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/004.jpg</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>TW-OP-1-black</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-black/003.jpg</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>TW-OP-1-dark-blue</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/003.jpg</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>TW-OP-1-mars</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-mars/003.jpg</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>TW-PM-2-mars</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-PM-2-mars/001.jpg</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>TW-PM-Classic-mars</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/004.jpg</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>TW-PM-Classic-red</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/002.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/004.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/005.jpg</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TW-Ruby-big-mars</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/005.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/006.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/007.jpg</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>TW-Style-black</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Style-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/004.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/005.jpg</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TW-Style-kon</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Style-kon/001.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/002.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/004.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/005.jpg</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>TW-Vacation-vin</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/TW-Vacation-vin/001.jpg,https://oleks-netizen.github.io/product-images/TW-Vacation-vin/002.jpg</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>vc001A-orange</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/vc001A-orange/001.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/002.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/003.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/004.jpg</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>vc001a-red</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/vc001a-red/001.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/002.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/003.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/004.jpg</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>VC2234black</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/VC2234black/001.jpg,https://oleks-netizen.github.io/product-images/VC2234black/002.jpg,https://oleks-netizen.github.io/product-images/VC2234black/004.jpg,https://oleks-netizen.github.io/product-images/VC2234black/005.jpg</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20906_1 (1)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/20906_1 (1)/006.jpg</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +471,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/20906_1/001.jpg,https://oleks-netizen.github.io/product-images/20906_1/003.jpg,https://oleks-netizen.github.io/product-images/20906_1/004.jpg,https://oleks-netizen.github.io/product-images/20906_1/005.jpg,https://oleks-netizen.github.io/product-images/20906_1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/20906_1/001.jpg,https://oleks-netizen.github.io/product-images/20906_1/003.jpg,https://oleks-netizen.github.io/product-images/20906_1/004.jpg,https://oleks-netizen.github.io/product-images/20906_1/005.jpg,https://oleks-netizen.github.io/product-images/20906_1/006.jpg,https://oleks-netizen.github.io/product-images/20906_1/007.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4826,21 +4826,6 @@
       </c>
       <c r="C294" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>20906_1 (1)</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/20906_1 (1)/006.jpg</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C294"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,3102 +436,3102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1733_1_1</t>
+          <t>0026zh-1,5kz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1733_1_1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0026zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>206120</t>
+          <t>0027zh-1,5kz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/206120/001.jpg,https://oleks-netizen.github.io/product-images/206120/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0027zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/004.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20906_1</t>
+          <t>0127zh-1kz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/20906_1/001.jpg,https://oleks-netizen.github.io/product-images/20906_1/003.jpg,https://oleks-netizen.github.io/product-images/20906_1/004.jpg,https://oleks-netizen.github.io/product-images/20906_1/005.jpg,https://oleks-netizen.github.io/product-images/20906_1/006.jpg,https://oleks-netizen.github.io/product-images/20906_1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0127zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2140_1_1</t>
+          <t>0133zh-1kz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2140_1_1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0133zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>224420</t>
+          <t>0134zh-1kz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/224420/001.jpg,https://oleks-netizen.github.io/product-images/224420/002.jpg,https://oleks-netizen.github.io/product-images/224420/003.jpg,https://oleks-netizen.github.io/product-images/224420/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0134zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0134zh-1kz/003.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2338_1_5</t>
+          <t>0135zh-1kz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2338_1_5/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0135zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/005.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421_1_2</t>
+          <t>0136zh-1kz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2421_1_2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0136zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2423_1_100</t>
+          <t>0140zh-1kz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2423_1_100/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0140zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2459_1_6</t>
+          <t>0142zh-1kz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2459_1_6/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0142zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25000010</t>
+          <t>0145zh-1kz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000010/001.jpg,https://oleks-netizen.github.io/product-images/25000010/002.jpg,https://oleks-netizen.github.io/product-images/25000010/003.jpg,https://oleks-netizen.github.io/product-images/25000010/005.jpg,https://oleks-netizen.github.io/product-images/25000010/006.jpg,https://oleks-netizen.github.io/product-images/25000010/007.jpg,https://oleks-netizen.github.io/product-images/25000010/008.jpg,https://oleks-netizen.github.io/product-images/25000010/009.jpg,https://oleks-netizen.github.io/product-images/25000010/010.jpg,https://oleks-netizen.github.io/product-images/25000010/011.jpg,https://oleks-netizen.github.io/product-images/25000010/012.jpg,https://oleks-netizen.github.io/product-images/25000010/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0145zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25000010m</t>
+          <t>0154zh-1kz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000010m/001.jpg,https://oleks-netizen.github.io/product-images/25000010m/002.jpg,https://oleks-netizen.github.io/product-images/25000010m/004.jpg,https://oleks-netizen.github.io/product-images/25000010m/005.jpg,https://oleks-netizen.github.io/product-images/25000010m/006.jpg,https://oleks-netizen.github.io/product-images/25000010m/007.jpg,https://oleks-netizen.github.io/product-images/25000010m/008.jpg,https://oleks-netizen.github.io/product-images/25000010m/009.jpg,https://oleks-netizen.github.io/product-images/25000010m/010.jpg,https://oleks-netizen.github.io/product-images/25000010m/011.jpg,https://oleks-netizen.github.io/product-images/25000010m/012.jpg,https://oleks-netizen.github.io/product-images/25000010m/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0154zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25000064</t>
+          <t>0181zh-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000064/001.jpg,https://oleks-netizen.github.io/product-images/25000064/002.jpg,https://oleks-netizen.github.io/product-images/25000064/003.jpg,https://oleks-netizen.github.io/product-images/25000064/005.jpg,https://oleks-netizen.github.io/product-images/25000064/006.jpg,https://oleks-netizen.github.io/product-images/25000064/007.jpg,https://oleks-netizen.github.io/product-images/25000064/008.jpg,https://oleks-netizen.github.io/product-images/25000064/009.jpg,https://oleks-netizen.github.io/product-images/25000064/010.jpg,https://oleks-netizen.github.io/product-images/25000064/011.jpg,https://oleks-netizen.github.io/product-images/25000064/012.jpg,https://oleks-netizen.github.io/product-images/25000064/013.jpg,https://oleks-netizen.github.io/product-images/25000064/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0181zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/004.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25000064m</t>
+          <t>0182zh-1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000064m/001.jpg,https://oleks-netizen.github.io/product-images/25000064m/003.jpg,https://oleks-netizen.github.io/product-images/25000064m/004.jpg,https://oleks-netizen.github.io/product-images/25000064m/005.jpg,https://oleks-netizen.github.io/product-images/25000064m/006.jpg,https://oleks-netizen.github.io/product-images/25000064m/007.jpg,https://oleks-netizen.github.io/product-images/25000064m/008.jpg,https://oleks-netizen.github.io/product-images/25000064m/009.jpg,https://oleks-netizen.github.io/product-images/25000064m/010.jpg,https://oleks-netizen.github.io/product-images/25000064m/011.jpg,https://oleks-netizen.github.io/product-images/25000064m/012.jpg,https://oleks-netizen.github.io/product-images/25000064m/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0182zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/003.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/005.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25000264</t>
+          <t>0253zh-1kz</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000264/001.jpg,https://oleks-netizen.github.io/product-images/25000264/002.jpg,https://oleks-netizen.github.io/product-images/25000264/003.jpg,https://oleks-netizen.github.io/product-images/25000264/004.jpg,https://oleks-netizen.github.io/product-images/25000264/005.jpg,https://oleks-netizen.github.io/product-images/25000264/007.jpg,https://oleks-netizen.github.io/product-images/25000264/008.jpg,https://oleks-netizen.github.io/product-images/25000264/009.jpg,https://oleks-netizen.github.io/product-images/25000264/010.jpg,https://oleks-netizen.github.io/product-images/25000264/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0253zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25000264m</t>
+          <t>0255zh-1kz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25000264m/001.jpg,https://oleks-netizen.github.io/product-images/25000264m/002.jpg,https://oleks-netizen.github.io/product-images/25000264m/003.jpg,https://oleks-netizen.github.io/product-images/25000264m/004.jpg,https://oleks-netizen.github.io/product-images/25000264m/005.jpg,https://oleks-netizen.github.io/product-images/25000264m/006.jpg,https://oleks-netizen.github.io/product-images/25000264m/007.jpg,https://oleks-netizen.github.io/product-images/25000264m/008.jpg,https://oleks-netizen.github.io/product-images/25000264m/010.jpg,https://oleks-netizen.github.io/product-images/25000264m/011.jpg,https://oleks-netizen.github.io/product-images/25000264m/012.jpg,https://oleks-netizen.github.io/product-images/25000264m/013.jpg,https://oleks-netizen.github.io/product-images/25000264m/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0255zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25428164</t>
+          <t>0260zh-1kz</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25428164/001.jpg,https://oleks-netizen.github.io/product-images/25428164/002.jpg,https://oleks-netizen.github.io/product-images/25428164/003.jpg,https://oleks-netizen.github.io/product-images/25428164/004.jpg,https://oleks-netizen.github.io/product-images/25428164/005.jpg,https://oleks-netizen.github.io/product-images/25428164/007.jpg,https://oleks-netizen.github.io/product-images/25428164/008.jpg,https://oleks-netizen.github.io/product-images/25428164/009.jpg,https://oleks-netizen.github.io/product-images/25428164/010.jpg,https://oleks-netizen.github.io/product-images/25428164/011.jpg,https://oleks-netizen.github.io/product-images/25428164/012.jpg,https://oleks-netizen.github.io/product-images/25428164/013.jpg,https://oleks-netizen.github.io/product-images/25428164/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0260zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25428164m</t>
+          <t>0261zh-1kz</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25428164m/001.jpg,https://oleks-netizen.github.io/product-images/25428164m/002.jpg,https://oleks-netizen.github.io/product-images/25428164m/004.jpg,https://oleks-netizen.github.io/product-images/25428164m/005.jpg,https://oleks-netizen.github.io/product-images/25428164m/006.jpg,https://oleks-netizen.github.io/product-images/25428164m/007.jpg,https://oleks-netizen.github.io/product-images/25428164m/008.jpg,https://oleks-netizen.github.io/product-images/25428164m/009.jpg,https://oleks-netizen.github.io/product-images/25428164m/010.jpg,https://oleks-netizen.github.io/product-images/25428164m/011.jpg,https://oleks-netizen.github.io/product-images/25428164m/012.jpg,https://oleks-netizen.github.io/product-images/25428164m/013.jpg,https://oleks-netizen.github.io/product-images/25428164m/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0261zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25438115</t>
+          <t>0266zh-1kz</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25438115/001.jpg,https://oleks-netizen.github.io/product-images/25438115/002.jpg,https://oleks-netizen.github.io/product-images/25438115/003.jpg,https://oleks-netizen.github.io/product-images/25438115/004.jpg,https://oleks-netizen.github.io/product-images/25438115/006.jpg,https://oleks-netizen.github.io/product-images/25438115/007.jpg,https://oleks-netizen.github.io/product-images/25438115/008.jpg,https://oleks-netizen.github.io/product-images/25438115/009.jpg,https://oleks-netizen.github.io/product-images/25438115/010.jpg,https://oleks-netizen.github.io/product-images/25438115/011.jpg,https://oleks-netizen.github.io/product-images/25438115/012.jpg,https://oleks-netizen.github.io/product-images/25438115/013.jpg,https://oleks-netizen.github.io/product-images/25438115/014.jpg,https://oleks-netizen.github.io/product-images/25438115/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0266zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25438115m</t>
+          <t>0267zh-1kz</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25438115m/001.jpg,https://oleks-netizen.github.io/product-images/25438115m/002.jpg,https://oleks-netizen.github.io/product-images/25438115m/004.jpg,https://oleks-netizen.github.io/product-images/25438115m/005.jpg,https://oleks-netizen.github.io/product-images/25438115m/006.jpg,https://oleks-netizen.github.io/product-images/25438115m/007.jpg,https://oleks-netizen.github.io/product-images/25438115m/008.jpg,https://oleks-netizen.github.io/product-images/25438115m/009.jpg,https://oleks-netizen.github.io/product-images/25438115m/010.jpg,https://oleks-netizen.github.io/product-images/25438115m/011.jpg,https://oleks-netizen.github.io/product-images/25438115m/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0267zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/005.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25438164</t>
+          <t>0421zh-1kz</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25438164/001.jpg,https://oleks-netizen.github.io/product-images/25438164/002.jpg,https://oleks-netizen.github.io/product-images/25438164/003.jpg,https://oleks-netizen.github.io/product-images/25438164/004.jpg,https://oleks-netizen.github.io/product-images/25438164/005.jpg,https://oleks-netizen.github.io/product-images/25438164/006.jpg,https://oleks-netizen.github.io/product-images/25438164/007.jpg,https://oleks-netizen.github.io/product-images/25438164/008.jpg,https://oleks-netizen.github.io/product-images/25438164/009.jpg,https://oleks-netizen.github.io/product-images/25438164/010.jpg,https://oleks-netizen.github.io/product-images/25438164/011.jpg,https://oleks-netizen.github.io/product-images/25438164/012.jpg,https://oleks-netizen.github.io/product-images/25438164/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0421zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25438164m</t>
+          <t>0422zh-1kz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/25438164m/001.jpg,https://oleks-netizen.github.io/product-images/25438164m/002.jpg,https://oleks-netizen.github.io/product-images/25438164m/003.jpg,https://oleks-netizen.github.io/product-images/25438164m/004.jpg,https://oleks-netizen.github.io/product-images/25438164m/005.jpg,https://oleks-netizen.github.io/product-images/25438164m/006.jpg,https://oleks-netizen.github.io/product-images/25438164m/007.jpg,https://oleks-netizen.github.io/product-images/25438164m/008.jpg,https://oleks-netizen.github.io/product-images/25438164m/009.jpg,https://oleks-netizen.github.io/product-images/25438164m/010.jpg,https://oleks-netizen.github.io/product-images/25438164m/011.jpg,https://oleks-netizen.github.io/product-images/25438164m/012.jpg,https://oleks-netizen.github.io/product-images/25438164m/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0422zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30127445</t>
+          <t>0426zh-1kz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30127445/001.jpg,https://oleks-netizen.github.io/product-images/30127445/002.jpg,https://oleks-netizen.github.io/product-images/30127445/003.jpg,https://oleks-netizen.github.io/product-images/30127445/004.jpg,https://oleks-netizen.github.io/product-images/30127445/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0426zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>303660</t>
+          <t>0428zh-1kz</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303660/001.jpg,https://oleks-netizen.github.io/product-images/303660/003.jpg,https://oleks-netizen.github.io/product-images/303660/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0428zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>51411010</t>
+          <t>avt-4cm-ua-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411010/001.jpg,https://oleks-netizen.github.io/product-images/51411010/002.jpg,https://oleks-netizen.github.io/product-images/51411010/003.jpg,https://oleks-netizen.github.io/product-images/51411010/005.jpg,https://oleks-netizen.github.io/product-images/51411010/006.jpg,https://oleks-netizen.github.io/product-images/51411010/007.jpg,https://oleks-netizen.github.io/product-images/51411010/008.jpg,https://oleks-netizen.github.io/product-images/51411010/009.jpg,https://oleks-netizen.github.io/product-images/51411010/010.jpg,https://oleks-netizen.github.io/product-images/51411010/011.jpg,https://oleks-netizen.github.io/product-images/51411010/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/005.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>51411064</t>
+          <t>avt-4cm-ua-002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411064/001.jpg,https://oleks-netizen.github.io/product-images/51411064/002.jpg,https://oleks-netizen.github.io/product-images/51411064/003.jpg,https://oleks-netizen.github.io/product-images/51411064/004.jpg,https://oleks-netizen.github.io/product-images/51411064/005.jpg,https://oleks-netizen.github.io/product-images/51411064/006.jpg,https://oleks-netizen.github.io/product-images/51411064/008.jpg,https://oleks-netizen.github.io/product-images/51411064/009.jpg,https://oleks-netizen.github.io/product-images/51411064/010.jpg,https://oleks-netizen.github.io/product-images/51411064/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-002/001.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>51411064m</t>
+          <t>avt-4cm-ua-003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411064m/001.jpg,https://oleks-netizen.github.io/product-images/51411064m/002.jpg,https://oleks-netizen.github.io/product-images/51411064m/003.jpg,https://oleks-netizen.github.io/product-images/51411064m/004.jpg,https://oleks-netizen.github.io/product-images/51411064m/005.jpg,https://oleks-netizen.github.io/product-images/51411064m/007.jpg,https://oleks-netizen.github.io/product-images/51411064m/008.jpg,https://oleks-netizen.github.io/product-images/51411064m/009.jpg,https://oleks-netizen.github.io/product-images/51411064m/010.jpg,https://oleks-netizen.github.io/product-images/51411064m/011.jpg,https://oleks-netizen.github.io/product-images/51411064m/012.jpg,https://oleks-netizen.github.io/product-images/51411064m/013.jpg,https://oleks-netizen.github.io/product-images/51411064m/014.jpg,https://oleks-netizen.github.io/product-images/51411064m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-003/001.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>51411120</t>
+          <t>avt-4cm-ua-004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411120/001.jpg,https://oleks-netizen.github.io/product-images/51411120/002.jpg,https://oleks-netizen.github.io/product-images/51411120/003.jpg,https://oleks-netizen.github.io/product-images/51411120/004.jpg,https://oleks-netizen.github.io/product-images/51411120/005.jpg,https://oleks-netizen.github.io/product-images/51411120/007.jpg,https://oleks-netizen.github.io/product-images/51411120/008.jpg,https://oleks-netizen.github.io/product-images/51411120/009.jpg,https://oleks-netizen.github.io/product-images/51411120/010.jpg,https://oleks-netizen.github.io/product-images/51411120/011.jpg,https://oleks-netizen.github.io/product-images/51411120/012.jpg,https://oleks-netizen.github.io/product-images/51411120/013.jpg,https://oleks-netizen.github.io/product-images/51411120/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-004/001.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>51411129</t>
+          <t>avt-4cm-ua-005</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411129/001.jpg,https://oleks-netizen.github.io/product-images/51411129/002.jpg,https://oleks-netizen.github.io/product-images/51411129/003.jpg,https://oleks-netizen.github.io/product-images/51411129/004.jpg,https://oleks-netizen.github.io/product-images/51411129/005.jpg,https://oleks-netizen.github.io/product-images/51411129/007.jpg,https://oleks-netizen.github.io/product-images/51411129/008.jpg,https://oleks-netizen.github.io/product-images/51411129/009.jpg,https://oleks-netizen.github.io/product-images/51411129/010.jpg,https://oleks-netizen.github.io/product-images/51411129/011.jpg,https://oleks-netizen.github.io/product-images/51411129/012.jpg,https://oleks-netizen.github.io/product-images/51411129/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/005.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>51411210</t>
+          <t>avt-4cm-ua-006</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411210/001.jpg,https://oleks-netizen.github.io/product-images/51411210/002.jpg,https://oleks-netizen.github.io/product-images/51411210/003.jpg,https://oleks-netizen.github.io/product-images/51411210/004.jpg,https://oleks-netizen.github.io/product-images/51411210/005.jpg,https://oleks-netizen.github.io/product-images/51411210/006.jpg,https://oleks-netizen.github.io/product-images/51411210/008.jpg,https://oleks-netizen.github.io/product-images/51411210/009.jpg,https://oleks-netizen.github.io/product-images/51411210/010.jpg,https://oleks-netizen.github.io/product-images/51411210/011.jpg,https://oleks-netizen.github.io/product-images/51411210/012.jpg,https://oleks-netizen.github.io/product-images/51411210/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-006/001.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>51411210m</t>
+          <t>avt-4cm-ua-007</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411210m/001.jpg,https://oleks-netizen.github.io/product-images/51411210m/002.jpg,https://oleks-netizen.github.io/product-images/51411210m/004.jpg,https://oleks-netizen.github.io/product-images/51411210m/005.jpg,https://oleks-netizen.github.io/product-images/51411210m/006.jpg,https://oleks-netizen.github.io/product-images/51411210m/007.jpg,https://oleks-netizen.github.io/product-images/51411210m/008.jpg,https://oleks-netizen.github.io/product-images/51411210m/009.jpg,https://oleks-netizen.github.io/product-images/51411210m/010.jpg,https://oleks-netizen.github.io/product-images/51411210m/011.jpg,https://oleks-netizen.github.io/product-images/51411210m/012.jpg,https://oleks-netizen.github.io/product-images/51411210m/013.jpg,https://oleks-netizen.github.io/product-images/51411210m/014.jpg,https://oleks-netizen.github.io/product-images/51411210m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-007/001.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>51411215</t>
+          <t>avt-4cm-ua-008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411215/001.jpg,https://oleks-netizen.github.io/product-images/51411215/002.jpg,https://oleks-netizen.github.io/product-images/51411215/003.jpg,https://oleks-netizen.github.io/product-images/51411215/004.jpg,https://oleks-netizen.github.io/product-images/51411215/005.jpg,https://oleks-netizen.github.io/product-images/51411215/006.jpg,https://oleks-netizen.github.io/product-images/51411215/008.jpg,https://oleks-netizen.github.io/product-images/51411215/009.jpg,https://oleks-netizen.github.io/product-images/51411215/010.jpg,https://oleks-netizen.github.io/product-images/51411215/011.jpg,https://oleks-netizen.github.io/product-images/51411215/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-008/001.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>51411215m</t>
+          <t>avt-4cm-ua-009</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411215m/001.jpg,https://oleks-netizen.github.io/product-images/51411215m/002.jpg,https://oleks-netizen.github.io/product-images/51411215m/004.jpg,https://oleks-netizen.github.io/product-images/51411215m/005.jpg,https://oleks-netizen.github.io/product-images/51411215m/006.jpg,https://oleks-netizen.github.io/product-images/51411215m/007.jpg,https://oleks-netizen.github.io/product-images/51411215m/008.jpg,https://oleks-netizen.github.io/product-images/51411215m/009.jpg,https://oleks-netizen.github.io/product-images/51411215m/010.jpg,https://oleks-netizen.github.io/product-images/51411215m/011.jpg,https://oleks-netizen.github.io/product-images/51411215m/012.jpg,https://oleks-netizen.github.io/product-images/51411215m/013.jpg,https://oleks-netizen.github.io/product-images/51411215m/014.jpg,https://oleks-netizen.github.io/product-images/51411215m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/005.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>51411264</t>
+          <t>avt-4cm-ua-010</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411264/001.jpg,https://oleks-netizen.github.io/product-images/51411264/002.jpg,https://oleks-netizen.github.io/product-images/51411264/003.jpg,https://oleks-netizen.github.io/product-images/51411264/005.jpg,https://oleks-netizen.github.io/product-images/51411264/006.jpg,https://oleks-netizen.github.io/product-images/51411264/007.jpg,https://oleks-netizen.github.io/product-images/51411264/008.jpg,https://oleks-netizen.github.io/product-images/51411264/009.jpg,https://oleks-netizen.github.io/product-images/51411264/010.jpg,https://oleks-netizen.github.io/product-images/51411264/011.jpg,https://oleks-netizen.github.io/product-images/51411264/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-010/001.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>51411264m</t>
+          <t>avt-4cm-ua-011</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411264m/001.jpg,https://oleks-netizen.github.io/product-images/51411264m/002.jpg,https://oleks-netizen.github.io/product-images/51411264m/003.jpg,https://oleks-netizen.github.io/product-images/51411264m/004.jpg,https://oleks-netizen.github.io/product-images/51411264m/005.jpg,https://oleks-netizen.github.io/product-images/51411264m/006.jpg,https://oleks-netizen.github.io/product-images/51411264m/007.jpg,https://oleks-netizen.github.io/product-images/51411264m/009.jpg,https://oleks-netizen.github.io/product-images/51411264m/010.jpg,https://oleks-netizen.github.io/product-images/51411264m/011.jpg,https://oleks-netizen.github.io/product-images/51411264m/012.jpg,https://oleks-netizen.github.io/product-images/51411264m/013.jpg,https://oleks-netizen.github.io/product-images/51411264m/014.jpg,https://oleks-netizen.github.io/product-images/51411264m/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-011/001.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5193401</t>
+          <t>avt-4cm-ua-012</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5193401/001.jpg,https://oleks-netizen.github.io/product-images/5193401/002.jpg,https://oleks-netizen.github.io/product-images/5193401/003.jpg,https://oleks-netizen.github.io/product-images/5193401/004.jpg,https://oleks-netizen.github.io/product-images/5193401/005.jpg,https://oleks-netizen.github.io/product-images/5193401/006.jpg,https://oleks-netizen.github.io/product-images/5193401/007.jpg,https://oleks-netizen.github.io/product-images/5193401/009.jpg,https://oleks-netizen.github.io/product-images/5193401/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-012/001.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5202801</t>
+          <t>avt-4cm-ua-013</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5202801/001.jpg,https://oleks-netizen.github.io/product-images/5202801/002.jpg,https://oleks-netizen.github.io/product-images/5202801/004.jpg,https://oleks-netizen.github.io/product-images/5202801/005.jpg,https://oleks-netizen.github.io/product-images/5202801/006.jpg,https://oleks-netizen.github.io/product-images/5202801/007.jpg,https://oleks-netizen.github.io/product-images/5202801/008.jpg,https://oleks-netizen.github.io/product-images/5202801/009.jpg,https://oleks-netizen.github.io/product-images/5202801/010.jpg,https://oleks-netizen.github.io/product-images/5202801/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/005.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5204101</t>
+          <t>avt-4cm-ua-014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5204101/001.jpg,https://oleks-netizen.github.io/product-images/5204101/002.jpg,https://oleks-netizen.github.io/product-images/5204101/003.jpg,https://oleks-netizen.github.io/product-images/5204101/004.jpg,https://oleks-netizen.github.io/product-images/5204101/005.jpg,https://oleks-netizen.github.io/product-images/5204101/006.jpg,https://oleks-netizen.github.io/product-images/5204101/007.jpg,https://oleks-netizen.github.io/product-images/5204101/008.jpg,https://oleks-netizen.github.io/product-images/5204101/009.jpg,https://oleks-netizen.github.io/product-images/5204101/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-014/001.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5205701</t>
+          <t>avt-4cm-ua-015</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5205701/001.jpg,https://oleks-netizen.github.io/product-images/5205701/002.jpg,https://oleks-netizen.github.io/product-images/5205701/004.jpg,https://oleks-netizen.github.io/product-images/5205701/005.jpg,https://oleks-netizen.github.io/product-images/5205701/006.jpg,https://oleks-netizen.github.io/product-images/5205701/007.jpg,https://oleks-netizen.github.io/product-images/5205701/008.jpg,https://oleks-netizen.github.io/product-images/5205701/009.jpg,https://oleks-netizen.github.io/product-images/5205701/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-015/001.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5205801</t>
+          <t>avt-4cm-ua-016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5205801/001.jpg,https://oleks-netizen.github.io/product-images/5205801/002.jpg,https://oleks-netizen.github.io/product-images/5205801/004.jpg,https://oleks-netizen.github.io/product-images/5205801/005.jpg,https://oleks-netizen.github.io/product-images/5205801/006.jpg,https://oleks-netizen.github.io/product-images/5205801/007.jpg,https://oleks-netizen.github.io/product-images/5205801/008.jpg,https://oleks-netizen.github.io/product-images/5205801/009.jpg,https://oleks-netizen.github.io/product-images/5205801/010.jpg,https://oleks-netizen.github.io/product-images/5205801/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-016/001.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5210401</t>
+          <t>avt-4cm-ua-017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5210401/001.jpg,https://oleks-netizen.github.io/product-images/5210401/002.jpg,https://oleks-netizen.github.io/product-images/5210401/004.jpg,https://oleks-netizen.github.io/product-images/5210401/005.jpg,https://oleks-netizen.github.io/product-images/5210401/006.jpg,https://oleks-netizen.github.io/product-images/5210401/007.jpg,https://oleks-netizen.github.io/product-images/5210401/008.jpg,https://oleks-netizen.github.io/product-images/5210401/009.jpg,https://oleks-netizen.github.io/product-images/5210401/010.jpg,https://oleks-netizen.github.io/product-images/5210401/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/005.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5218101</t>
+          <t>avt-4cm-ua-018</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5218101/001.jpg,https://oleks-netizen.github.io/product-images/5218101/002.jpg,https://oleks-netizen.github.io/product-images/5218101/003.jpg,https://oleks-netizen.github.io/product-images/5218101/004.jpg,https://oleks-netizen.github.io/product-images/5218101/005.jpg,https://oleks-netizen.github.io/product-images/5218101/006.jpg,https://oleks-netizen.github.io/product-images/5218101/007.jpg,https://oleks-netizen.github.io/product-images/5218101/008.jpg,https://oleks-netizen.github.io/product-images/5218101/009.jpg,https://oleks-netizen.github.io/product-images/5218101/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-018/001.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5221401</t>
+          <t>avt-4cm-ua-019</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5221401/001.jpg,https://oleks-netizen.github.io/product-images/5221401/003.jpg,https://oleks-netizen.github.io/product-images/5221401/004.jpg,https://oleks-netizen.github.io/product-images/5221401/005.jpg,https://oleks-netizen.github.io/product-images/5221401/006.jpg,https://oleks-netizen.github.io/product-images/5221401/007.jpg,https://oleks-netizen.github.io/product-images/5221401/008.jpg,https://oleks-netizen.github.io/product-images/5221401/009.jpg,https://oleks-netizen.github.io/product-images/5221401/010.jpg,https://oleks-netizen.github.io/product-images/5221401/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-019/001.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5225501</t>
+          <t>avt-4cm-ua-020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5225501/001.jpg,https://oleks-netizen.github.io/product-images/5225501/003.jpg,https://oleks-netizen.github.io/product-images/5225501/004.jpg,https://oleks-netizen.github.io/product-images/5225501/005.jpg,https://oleks-netizen.github.io/product-images/5225501/006.jpg,https://oleks-netizen.github.io/product-images/5225501/007.jpg,https://oleks-netizen.github.io/product-images/5225501/008.jpg,https://oleks-netizen.github.io/product-images/5225501/009.jpg,https://oleks-netizen.github.io/product-images/5225501/010.jpg,https://oleks-netizen.github.io/product-images/5225501/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-020/001.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>522623</t>
+          <t>avt-4cm-ua-021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/522623/001.jpg,https://oleks-netizen.github.io/product-images/522623/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/005.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>522660</t>
+          <t>avt-4cm-ua-022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/522660/001.jpg,https://oleks-netizen.github.io/product-images/522660/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-022/001.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5230401</t>
+          <t>avt-4cm-ua-023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5230401/001.jpg,https://oleks-netizen.github.io/product-images/5230401/002.jpg,https://oleks-netizen.github.io/product-images/5230401/003.jpg,https://oleks-netizen.github.io/product-images/5230401/005.jpg,https://oleks-netizen.github.io/product-images/5230401/006.jpg,https://oleks-netizen.github.io/product-images/5230401/007.jpg,https://oleks-netizen.github.io/product-images/5230401/008.jpg,https://oleks-netizen.github.io/product-images/5230401/009.jpg,https://oleks-netizen.github.io/product-images/5230401/010.jpg,https://oleks-netizen.github.io/product-images/5230401/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-023/001.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5231101</t>
+          <t>avt-4cm-ua-024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5231101/001.jpg,https://oleks-netizen.github.io/product-images/5231101/002.jpg,https://oleks-netizen.github.io/product-images/5231101/003.jpg,https://oleks-netizen.github.io/product-images/5231101/004.jpg,https://oleks-netizen.github.io/product-images/5231101/005.jpg,https://oleks-netizen.github.io/product-images/5231101/006.jpg,https://oleks-netizen.github.io/product-images/5231101/007.jpg,https://oleks-netizen.github.io/product-images/5231101/008.jpg,https://oleks-netizen.github.io/product-images/5231101/009.jpg,https://oleks-netizen.github.io/product-images/5231101/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-024/001.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5233301</t>
+          <t>avt-4cm-ua-025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5233301/001.jpg,https://oleks-netizen.github.io/product-images/5233301/002.jpg,https://oleks-netizen.github.io/product-images/5233301/003.jpg,https://oleks-netizen.github.io/product-images/5233301/004.jpg,https://oleks-netizen.github.io/product-images/5233301/006.jpg,https://oleks-netizen.github.io/product-images/5233301/007.jpg,https://oleks-netizen.github.io/product-images/5233301/008.jpg,https://oleks-netizen.github.io/product-images/5233301/009.jpg,https://oleks-netizen.github.io/product-images/5233301/010.jpg,https://oleks-netizen.github.io/product-images/5233301/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/005.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5241901</t>
+          <t>avt-4cm-ua-026_131000315481</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5241901/001.jpg,https://oleks-netizen.github.io/product-images/5241901/002.jpg,https://oleks-netizen.github.io/product-images/5241901/004.jpg,https://oleks-netizen.github.io/product-images/5241901/005.jpg,https://oleks-netizen.github.io/product-images/5241901/006.jpg,https://oleks-netizen.github.io/product-images/5241901/007.jpg,https://oleks-netizen.github.io/product-images/5241901/008.jpg,https://oleks-netizen.github.io/product-images/5241901/009.jpg,https://oleks-netizen.github.io/product-images/5241901/010.jpg,https://oleks-netizen.github.io/product-images/5241901/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026_131000315481/001.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5244701</t>
+          <t>avt-4cm-ua-027</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5244701/001.jpg,https://oleks-netizen.github.io/product-images/5244701/002.jpg,https://oleks-netizen.github.io/product-images/5244701/003.jpg,https://oleks-netizen.github.io/product-images/5244701/004.jpg,https://oleks-netizen.github.io/product-images/5244701/005.jpg,https://oleks-netizen.github.io/product-images/5244701/006.jpg,https://oleks-netizen.github.io/product-images/5244701/007.jpg,https://oleks-netizen.github.io/product-images/5244701/008.jpg,https://oleks-netizen.github.io/product-images/5244701/009.jpg,https://oleks-netizen.github.io/product-images/5244701/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-027/001.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5246401</t>
+          <t>avt-4cm-ua-028</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5246401/001.jpg,https://oleks-netizen.github.io/product-images/5246401/002.jpg,https://oleks-netizen.github.io/product-images/5246401/003.jpg,https://oleks-netizen.github.io/product-images/5246401/004.jpg,https://oleks-netizen.github.io/product-images/5246401/005.jpg,https://oleks-netizen.github.io/product-images/5246401/006.jpg,https://oleks-netizen.github.io/product-images/5246401/007.jpg,https://oleks-netizen.github.io/product-images/5246401/008.jpg,https://oleks-netizen.github.io/product-images/5246401/009.jpg,https://oleks-netizen.github.io/product-images/5246401/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/005.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5248401</t>
+          <t>avt-4cm-ua-029</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/5248401/001.jpg,https://oleks-netizen.github.io/product-images/5248401/002.jpg,https://oleks-netizen.github.io/product-images/5248401/003.jpg,https://oleks-netizen.github.io/product-images/5248401/004.jpg,https://oleks-netizen.github.io/product-images/5248401/005.jpg,https://oleks-netizen.github.io/product-images/5248401/006.jpg,https://oleks-netizen.github.io/product-images/5248401/007.jpg,https://oleks-netizen.github.io/product-images/5248401/008.jpg,https://oleks-netizen.github.io/product-images/5248401/009.jpg,https://oleks-netizen.github.io/product-images/5248401/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-029/001.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53100013</t>
+          <t>avt-4cm-ua-030</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53100013/001.jpg,https://oleks-netizen.github.io/product-images/53100013/002.jpg,https://oleks-netizen.github.io/product-images/53100013/003.jpg,https://oleks-netizen.github.io/product-images/53100013/005.jpg,https://oleks-netizen.github.io/product-images/53100013/006.jpg,https://oleks-netizen.github.io/product-images/53100013/007.jpg,https://oleks-netizen.github.io/product-images/53100013/008.jpg,https://oleks-netizen.github.io/product-images/53100013/009.jpg,https://oleks-netizen.github.io/product-images/53100013/010.jpg,https://oleks-netizen.github.io/product-images/53100013/011.jpg,https://oleks-netizen.github.io/product-images/53100013/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-030/001.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>53300039</t>
+          <t>avt-4cm-ua-031</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53300039/001.jpg,https://oleks-netizen.github.io/product-images/53300039/002.jpg,https://oleks-netizen.github.io/product-images/53300039/003.jpg,https://oleks-netizen.github.io/product-images/53300039/004.jpg,https://oleks-netizen.github.io/product-images/53300039/005.jpg,https://oleks-netizen.github.io/product-images/53300039/007.jpg,https://oleks-netizen.github.io/product-images/53300039/008.jpg,https://oleks-netizen.github.io/product-images/53300039/009.jpg,https://oleks-netizen.github.io/product-images/53300039/010.jpg,https://oleks-netizen.github.io/product-images/53300039/011.jpg,https://oleks-netizen.github.io/product-images/53300039/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-031/001.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>53400013</t>
+          <t>avt-4cm-ua-032</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400013/001.jpg,https://oleks-netizen.github.io/product-images/53400013/002.jpg,https://oleks-netizen.github.io/product-images/53400013/004.jpg,https://oleks-netizen.github.io/product-images/53400013/005.jpg,https://oleks-netizen.github.io/product-images/53400013/006.jpg,https://oleks-netizen.github.io/product-images/53400013/007.jpg,https://oleks-netizen.github.io/product-images/53400013/008.jpg,https://oleks-netizen.github.io/product-images/53400013/009.jpg,https://oleks-netizen.github.io/product-images/53400013/010.jpg,https://oleks-netizen.github.io/product-images/53400013/011.jpg,https://oleks-netizen.github.io/product-images/53400013/012.jpg,https://oleks-netizen.github.io/product-images/53400013/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/005.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>53400020</t>
+          <t>avt-4cm-ua-033</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400020/001.jpg,https://oleks-netizen.github.io/product-images/53400020/002.jpg,https://oleks-netizen.github.io/product-images/53400020/004.jpg,https://oleks-netizen.github.io/product-images/53400020/005.jpg,https://oleks-netizen.github.io/product-images/53400020/006.jpg,https://oleks-netizen.github.io/product-images/53400020/007.jpg,https://oleks-netizen.github.io/product-images/53400020/008.jpg,https://oleks-netizen.github.io/product-images/53400020/009.jpg,https://oleks-netizen.github.io/product-images/53400020/010.jpg,https://oleks-netizen.github.io/product-images/53400020/011.jpg,https://oleks-netizen.github.io/product-images/53400020/012.jpg,https://oleks-netizen.github.io/product-images/53400020/013.jpg,https://oleks-netizen.github.io/product-images/53400020/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-033/001.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>avt-4cm-ua-034</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/62725/001.jpg,https://oleks-netizen.github.io/product-images/62725/002.jpg,https://oleks-netizen.github.io/product-images/62725/003.jpg,https://oleks-netizen.github.io/product-images/62725/004.jpg,https://oleks-netizen.github.io/product-images/62725/005.jpg,https://oleks-netizen.github.io/product-images/62725/006.jpg,https://oleks-netizen.github.io/product-images/62725/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-034/001.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>62726</t>
+          <t>avt-4cm-ua-035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/62726/001.jpg,https://oleks-netizen.github.io/product-images/62726/002.jpg,https://oleks-netizen.github.io/product-images/62726/003.jpg,https://oleks-netizen.github.io/product-images/62726/004.jpg,https://oleks-netizen.github.io/product-images/62726/005.jpg,https://oleks-netizen.github.io/product-images/62726/006.jpg,https://oleks-netizen.github.io/product-images/62726/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-035/001.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>62727</t>
+          <t>avt-4cm-ua-036</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/62727/001.jpg,https://oleks-netizen.github.io/product-images/62727/002.jpg,https://oleks-netizen.github.io/product-images/62727/004.jpg,https://oleks-netizen.github.io/product-images/62727/005.jpg,https://oleks-netizen.github.io/product-images/62727/006.jpg,https://oleks-netizen.github.io/product-images/62727/007.jpg,https://oleks-netizen.github.io/product-images/62727/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/005.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>701661</t>
+          <t>avt-4cm-ua-037</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/701661/001.jpg,https://oleks-netizen.github.io/product-images/701661/002.jpg,https://oleks-netizen.github.io/product-images/701661/003.jpg,https://oleks-netizen.github.io/product-images/701661/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-037/001.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>746710</t>
+          <t>avt-4cm-ua-038</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/746710/001.jpg,https://oleks-netizen.github.io/product-images/746710/002.jpg,https://oleks-netizen.github.io/product-images/746710/003.jpg,https://oleks-netizen.github.io/product-images/746710/004.jpg,https://oleks-netizen.github.io/product-images/746710/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-038/001.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>746743</t>
+          <t>avt-4cm-ua-039</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/746743/001.jpg,https://oleks-netizen.github.io/product-images/746743/002.jpg,https://oleks-netizen.github.io/product-images/746743/003.jpg,https://oleks-netizen.github.io/product-images/746743/004.jpg,https://oleks-netizen.github.io/product-images/746743/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-039/001.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>75_1_1</t>
+          <t>avt-4cm-ua-040</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/75_1_1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/005.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>77266101</t>
+          <t>avt-4cm-ua-041</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/77266101/001.jpg,https://oleks-netizen.github.io/product-images/77266101/002.jpg,https://oleks-netizen.github.io/product-images/77266101/003.jpg,https://oleks-netizen.github.io/product-images/77266101/004.jpg,https://oleks-netizen.github.io/product-images/77266101/005.jpg,https://oleks-netizen.github.io/product-images/77266101/006.jpg,https://oleks-netizen.github.io/product-images/77266101/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-041/001.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>96193001</t>
+          <t>avt-4cm-ua-042</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/96193001/001.jpg,https://oleks-netizen.github.io/product-images/96193001/002.jpg,https://oleks-netizen.github.io/product-images/96193001/003.jpg,https://oleks-netizen.github.io/product-images/96193001/004.jpg,https://oleks-netizen.github.io/product-images/96193001/005.jpg,https://oleks-netizen.github.io/product-images/96193001/007.jpg,https://oleks-netizen.github.io/product-images/96193001/008.jpg,https://oleks-netizen.github.io/product-images/96193001/009.jpg,https://oleks-netizen.github.io/product-images/96193001/010.jpg,https://oleks-netizen.github.io/product-images/96193001/011.jpg,https://oleks-netizen.github.io/product-images/96193001/012.jpg,https://oleks-netizen.github.io/product-images/96193001/013.jpg,https://oleks-netizen.github.io/product-images/96193001/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-042/001.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>96193008</t>
+          <t>avt-4cm-ua-043</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/96193008/001.jpg,https://oleks-netizen.github.io/product-images/96193008/002.jpg,https://oleks-netizen.github.io/product-images/96193008/003.jpg,https://oleks-netizen.github.io/product-images/96193008/004.jpg,https://oleks-netizen.github.io/product-images/96193008/006.jpg,https://oleks-netizen.github.io/product-images/96193008/007.jpg,https://oleks-netizen.github.io/product-images/96193008/008.jpg,https://oleks-netizen.github.io/product-images/96193008/009.jpg,https://oleks-netizen.github.io/product-images/96193008/010.jpg,https://oleks-netizen.github.io/product-images/96193008/011.jpg,https://oleks-netizen.github.io/product-images/96193008/012.jpg,https://oleks-netizen.github.io/product-images/96193008/013.jpg,https://oleks-netizen.github.io/product-images/96193008/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-043/001.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>96193070</t>
+          <t>avt-4cm-ua-044</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/96193070/001.jpg,https://oleks-netizen.github.io/product-images/96193070/002.jpg,https://oleks-netizen.github.io/product-images/96193070/003.jpg,https://oleks-netizen.github.io/product-images/96193070/004.jpg,https://oleks-netizen.github.io/product-images/96193070/005.jpg,https://oleks-netizen.github.io/product-images/96193070/006.jpg,https://oleks-netizen.github.io/product-images/96193070/007.jpg,https://oleks-netizen.github.io/product-images/96193070/009.jpg,https://oleks-netizen.github.io/product-images/96193070/010.jpg,https://oleks-netizen.github.io/product-images/96193070/011.jpg,https://oleks-netizen.github.io/product-images/96193070/012.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/005.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>96199170</t>
+          <t>avt-4cm-ua-045</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/96199170/001.jpg,https://oleks-netizen.github.io/product-images/96199170/002.jpg,https://oleks-netizen.github.io/product-images/96199170/003.jpg,https://oleks-netizen.github.io/product-images/96199170/004.jpg,https://oleks-netizen.github.io/product-images/96199170/005.jpg,https://oleks-netizen.github.io/product-images/96199170/006.jpg,https://oleks-netizen.github.io/product-images/96199170/007.jpg,https://oleks-netizen.github.io/product-images/96199170/008.jpg,https://oleks-netizen.github.io/product-images/96199170/009.jpg,https://oleks-netizen.github.io/product-images/96199170/010.jpg,https://oleks-netizen.github.io/product-images/96199170/011.jpg,https://oleks-netizen.github.io/product-images/96199170/013.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-045/001.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B10-434A</t>
+          <t>avt-4cm-ua-046</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/B10-434A/001.jpg,https://oleks-netizen.github.io/product-images/B10-434A/002.jpg,https://oleks-netizen.github.io/product-images/B10-434A/003.jpg,https://oleks-netizen.github.io/product-images/B10-434A/004.jpg,https://oleks-netizen.github.io/product-images/B10-434A/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-046/001.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BB80701-50</t>
+          <t>avt-4cm-ua-047</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BB80701-50/001.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/002.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/003.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/005.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/006.jpg,https://oleks-netizen.github.io/product-images/BB80701-50/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-047/001.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BB81251-02</t>
+          <t>avt-4cm-ua-048</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BB81251-02/001.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/002.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/003.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/005.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/006.jpg,https://oleks-netizen.github.io/product-images/BB81251-02/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/005.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BN-KK-4-k-kr-karbon</t>
+          <t>avt-4cm-ua-049</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/001.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/002.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/003.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/004.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-k-kr-karbon/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-049/001.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BN-KK-4-vin-kr</t>
+          <t>avt-4cm-ua-050</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-KK-4-vin-kr/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-050/001.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BN-SB-2-st-red</t>
+          <t>avt-4cm-ua-051</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-2-st-red/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-051/001.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>avt-4cm-ua-052</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/001.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/002.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/003.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/005.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/006.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/005.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BS80401-01</t>
+          <t>avt-4cm-ua-053</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS80401-01/001.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/002.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/003.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/005.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/006.jpg,https://oleks-netizen.github.io/product-images/BS80401-01/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-053/001.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BV39032-1</t>
+          <t>avt-4cm-ua-054</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39032-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39032-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-054/001.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BV39032-191</t>
+          <t>avt-4cm-ua-055</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39032-191/001.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/002.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/003.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/004.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/005.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/006.jpg,https://oleks-netizen.github.io/product-images/BV39032-191/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-055/001.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BV39139-1</t>
+          <t>avt-4cm-ua-056</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39139-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39139-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/005.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BV39218-1</t>
+          <t>avt-4cm-ua-057</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39218-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39218-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-057/001.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BV39218-153</t>
+          <t>avt-4cm-ua-058</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39218-153/001.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/002.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/004.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/005.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/006.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/007.jpg,https://oleks-netizen.github.io/product-images/BV39218-153/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-058/001.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BV39223-1</t>
+          <t>avt-4cm-ua-059</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39223-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-059/001.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BV39223-1-small</t>
+          <t>avt-4cm-ua-060</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39223-1-small/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/003.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-1-small/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/005.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BV39223-145</t>
+          <t>avt-4cm-ua-061</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39223-145/001.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/002.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/004.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/005.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/006.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/007.jpg,https://oleks-netizen.github.io/product-images/BV39223-145/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-061/001.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BV39311-1</t>
+          <t>avt-4cm-ua-062</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39311-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/007.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/008.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/009.jpg,https://oleks-netizen.github.io/product-images/BV39311-1/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-062/001.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BV39311-153</t>
+          <t>avt-4cm-ua-063</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39311-153/001.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/002.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/004.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/005.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/006.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/007.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/008.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/009.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/010.jpg,https://oleks-netizen.github.io/product-images/BV39311-153/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-063/001.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BV39318-1</t>
+          <t>avt-4cm-ua-064</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39318-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/005.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BV39318-232</t>
+          <t>avt-4cm-ua-065</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39318-232/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-232/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-065/001.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BV39318-76A</t>
+          <t>avt-4cm-ua-066</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39318-76A/001.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/002.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/003.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/004.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/005.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/006.jpg,https://oleks-netizen.github.io/product-images/BV39318-76A/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-066/001.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BV39351-1</t>
+          <t>avt-4cm-ua-067</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39351-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39351-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-067/001.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BV39529-1</t>
+          <t>avt-4cm-ua-068</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39529-1/001.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/002.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/003.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/004.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/005.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/006.jpg,https://oleks-netizen.github.io/product-images/BV39529-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/004.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BV39529-145</t>
+          <t>avt-4cm-ua-069</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV39529-145/001.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/002.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/004.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/005.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/006.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/007.jpg,https://oleks-netizen.github.io/product-images/BV39529-145/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-069/001.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bx050a</t>
+          <t>avt-4cm-ua-070</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/bx050a/001.jpg,https://oleks-netizen.github.io/product-images/bx050a/002.jpg,https://oleks-netizen.github.io/product-images/bx050a/003.jpg,https://oleks-netizen.github.io/product-images/bx050a/004.jpg,https://oleks-netizen.github.io/product-images/bx050a/005.jpg,https://oleks-netizen.github.io/product-images/bx050a/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-070/001.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bx050c</t>
+          <t>avt-4cm-ua-071</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/bx050c/001.jpg,https://oleks-netizen.github.io/product-images/bx050c/002.jpg,https://oleks-netizen.github.io/product-images/bx050c/003.jpg,https://oleks-netizen.github.io/product-images/bx050c/005.jpg,https://oleks-netizen.github.io/product-images/bx050c/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-071/001.jpg</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bx9020</t>
+          <t>det-15k-003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/bx9020/001.jpg,https://oleks-netizen.github.io/product-images/bx9020/002.jpg,https://oleks-netizen.github.io/product-images/bx9020/003.jpg,https://oleks-netizen.github.io/product-images/bx9020/004.jpg,https://oleks-netizen.github.io/product-images/bx9020/005.jpg,https://oleks-netizen.github.io/product-images/bx9020/006.jpg,https://oleks-netizen.github.io/product-images/bx9020/007.jpg,https://oleks-netizen.github.io/product-images/bx9020/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-003/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-003/003.jpg</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CC605_BN</t>
+          <t>det-15k-007</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/CC605_BN/001.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/002.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/004.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/005.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/006.jpg,https://oleks-netizen.github.io/product-images/CC605_BN/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-007/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-007/003.jpg</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CrH-1294-4lx</t>
+          <t>det-15k-008</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/CrH-1294-4lx/001.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/002.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/003.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/005.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/006.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/007.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/008.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/009.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/010.jpg,https://oleks-netizen.github.io/product-images/CrH-1294-4lx/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-008/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-008/003.jpg</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DRL19031-3</t>
+          <t>det-15k-009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19031-3/001.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/002.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/004.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/005.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/006.jpg,https://oleks-netizen.github.io/product-images/DRL19031-3/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-009/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-009/003.jpg</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DRL19086-1</t>
+          <t>det-20k-014</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19086-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19086-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-014/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-014/003.jpg</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DRL19101-1</t>
+          <t>det-20k-015</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19101-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19101-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-015/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-015/003.jpg</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DRL19158-2</t>
+          <t>det-20k-016</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19158-2/001.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/002.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/003.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/004.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/005.jpg,https://oleks-netizen.github.io/product-images/DRL19158-2/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-016/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-016/003.jpg</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DRL1925-1</t>
+          <t>det-20k-019</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL1925-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL1925-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-019/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-019/003.jpg</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DRL19286-6</t>
+          <t>det-20k-020</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19286-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19286-6/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-020/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-020/003.jpg</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DRL19333-1</t>
+          <t>det-20k-021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19333-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19333-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-021/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-021/003.jpg</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DRL19377-1</t>
+          <t>det-20k-022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19377-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19377-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-022/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-022/003.jpg</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DRL19389-6</t>
+          <t>det-pd-013</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19389-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19389-6/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-013/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-013/003.jpg</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DRL19393-6</t>
+          <t>det-pd-015</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19393-6/001.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/002.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/004.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/005.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/006.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/007.jpg,https://oleks-netizen.github.io/product-images/DRL19393-6/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-015/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-015/003.jpg</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DRL19429-1</t>
+          <t>det-pd-020</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19429-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19429-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-020/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/004.jpg</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DRL19460-1</t>
+          <t>det-pd-022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19460-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19460-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-022/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-022/003.jpg</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DRL19608-1</t>
+          <t>det-pd-023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19608-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19608-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-023/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-023/003.jpg</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DRL19710-1</t>
+          <t>det-pd-024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19710-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19710-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-024/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-024/003.jpg</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DRL19946-1</t>
+          <t>det-pd-027</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRL19946-1/001.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/002.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/004.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/005.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/006.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/007.jpg,https://oleks-netizen.github.io/product-images/DRL19946-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-027/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-027/003.jpg</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Elit-2020-4lx</t>
+          <t>det-pd-028</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Elit-2020-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/009.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/010.jpg,https://oleks-netizen.github.io/product-images/Elit-2020-4lx/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-028/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/003.jpg</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Elit-2022-4lx</t>
+          <t>det-pd-029</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Elit-2022-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/008.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/009.jpg,https://oleks-netizen.github.io/product-images/Elit-2022-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-029/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/004.jpg</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Elit-2023-4lx</t>
+          <t>det-pd-030</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Elit-2023-4lx/001.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/002.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/003.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/004.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/005.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/006.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/007.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/008.jpg,https://oleks-netizen.github.io/product-images/Elit-2023-4lx/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-030/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/004.jpg</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FA-1501-3md</t>
+          <t>det-pd-031</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/FA-1501-3md/001.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/002.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/003.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/004.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/005.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/006.jpg,https://oleks-netizen.github.io/product-images/FA-1501-3md/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-031/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/004.jpg</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FCream-8077-3md</t>
+          <t>det-pd-032</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/FCream-8077-3md/001.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/002.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/003.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/005.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/006.jpg,https://oleks-netizen.github.io/product-images/FCream-8077-3md/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-032/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/003.jpg</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FR7007K</t>
+          <t>det-pd-033</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/FR7007K/001.jpg,https://oleks-netizen.github.io/product-images/FR7007K/002.jpg,https://oleks-netizen.github.io/product-images/FR7007K/003.jpg,https://oleks-netizen.github.io/product-images/FR7007K/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-033/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/004.jpg</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FR7007O</t>
+          <t>det-pd-034</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/FR7007O/001.jpg,https://oleks-netizen.github.io/product-images/FR7007O/002.jpg,https://oleks-netizen.github.io/product-images/FR7007O/003.jpg,https://oleks-netizen.github.io/product-images/FR7007O/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-034/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/003.jpg</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FR7007P</t>
+          <t>det-pd-035</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/FR7007P/001.jpg,https://oleks-netizen.github.io/product-images/FR7007P/002.jpg,https://oleks-netizen.github.io/product-images/FR7007P/003.jpg,https://oleks-netizen.github.io/product-images/FR7007P/004.jpg,https://oleks-netizen.github.io/product-images/FR7007P/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-035/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/003.jpg</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>fz118545</t>
+          <t>det-pd-036</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/fz118545/001.jpg,https://oleks-netizen.github.io/product-images/fz118545/002.jpg,https://oleks-netizen.github.io/product-images/fz118545/003.jpg,https://oleks-netizen.github.io/product-images/fz118545/004.jpg,https://oleks-netizen.github.io/product-images/fz118545/005.jpg,https://oleks-netizen.github.io/product-images/fz118545/006.jpg,https://oleks-netizen.github.io/product-images/fz118545/007.jpg,https://oleks-netizen.github.io/product-images/fz118545/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-036/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/004.jpg</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>fz189606</t>
+          <t>det-pd-037</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/fz189606/001.jpg,https://oleks-netizen.github.io/product-images/fz189606/002.jpg,https://oleks-netizen.github.io/product-images/fz189606/003.jpg,https://oleks-netizen.github.io/product-images/fz189606/004.jpg,https://oleks-netizen.github.io/product-images/fz189606/006.jpg,https://oleks-netizen.github.io/product-images/fz189606/007.jpg,https://oleks-netizen.github.io/product-images/fz189606/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-037/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/004.jpg</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>fz1896103</t>
+          <t>det-pd-038</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/fz1896103/001.jpg,https://oleks-netizen.github.io/product-images/fz1896103/002.jpg,https://oleks-netizen.github.io/product-images/fz1896103/004.jpg,https://oleks-netizen.github.io/product-images/fz1896103/005.jpg,https://oleks-netizen.github.io/product-images/fz1896103/006.jpg,https://oleks-netizen.github.io/product-images/fz1896103/007.jpg,https://oleks-netizen.github.io/product-images/fz1896103/008.jpg,https://oleks-netizen.github.io/product-images/fz1896103/009.jpg,https://oleks-netizen.github.io/product-images/fz1896103/010.jpg,https://oleks-netizen.github.io/product-images/fz1896103/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-038/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/004.jpg</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>fz189645</t>
+          <t>det-pd-039</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/fz189645/001.jpg,https://oleks-netizen.github.io/product-images/fz189645/002.jpg,https://oleks-netizen.github.io/product-images/fz189645/003.jpg,https://oleks-netizen.github.io/product-images/fz189645/004.jpg,https://oleks-netizen.github.io/product-images/fz189645/005.jpg,https://oleks-netizen.github.io/product-images/fz189645/006.jpg,https://oleks-netizen.github.io/product-images/fz189645/007.jpg,https://oleks-netizen.github.io/product-images/fz189645/008.jpg,https://oleks-netizen.github.io/product-images/fz189645/009.jpg,https://oleks-netizen.github.io/product-images/fz189645/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-039/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/004.jpg</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GA-0307-4lx</t>
+          <t>det-pd-040</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GA-0307-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-0307-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-040/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/004.jpg</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GA-0324-4lx</t>
+          <t>det-pd-041</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GA-0324-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/010.jpg,https://oleks-netizen.github.io/product-images/GA-0324-4lx/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-041/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/004.jpg</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GA-1402-4lx</t>
+          <t>det-pd-042</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GA-1402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-1402-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-042/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-042/003.jpg</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GA-7281-3md</t>
+          <t>det-pd-043</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GA-7281-3md/001.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/002.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/004.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/005.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/006.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/007.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/008.jpg,https://oleks-netizen.github.io/product-images/GA-7281-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-043/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-043/002.jpg</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GB-7107-3md</t>
+          <t>det-pd-044</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GB-7107-3md/001.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/002.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/004.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/005.jpg,https://oleks-netizen.github.io/product-images/GB-7107-3md/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-044/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/004.jpg</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GBalc-2067-4lx</t>
+          <t>det-pd-045</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GBalc-2067-4lx/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-045/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/004.jpg</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GBord-2067-4lx</t>
+          <t>det-pd-046</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GBord-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GBord-2067-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-046/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/004.jpg</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GC-0060-4lx</t>
+          <t>det-pd-047</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-0060-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-0060-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-047/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/004.jpg</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GC-1239-4lx</t>
+          <t>det-pd-048</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-1239-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-1239-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-048/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/004.jpg</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GC-1402-4lx</t>
+          <t>det-pd-049</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-1402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GC-1402-4lx/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-049/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/004.jpg</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GC-2067-4lx</t>
+          <t>det-pd-050</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-2067-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GC-2067-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-050/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-050/003.jpg</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GC-8033-4lx</t>
+          <t>det-pd-051</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GC-8033-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-8033-4lx/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-051/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/004.jpg</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GYalc-5565-4lx</t>
+          <t>det-pd-052</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GYalc-5565-4lx/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-052/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/004.jpg</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HB0502</t>
+          <t>det-pd-053</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB0502/001.jpg,https://oleks-netizen.github.io/product-images/HB0502/002.jpg,https://oleks-netizen.github.io/product-images/HB0502/003.jpg,https://oleks-netizen.github.io/product-images/HB0502/005.jpg,https://oleks-netizen.github.io/product-images/HB0502/006.jpg,https://oleks-netizen.github.io/product-images/HB0502/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-053/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/004.jpg</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HB0502Blu</t>
+          <t>det-pd-054</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB0502Blu/001.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/003.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/004.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/005.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/006.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/007.jpg,https://oleks-netizen.github.io/product-images/HB0502Blu/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-054/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/004.jpg</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HB19153A</t>
+          <t>det-pd-055</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB19153A/001.jpg,https://oleks-netizen.github.io/product-images/HB19153A/002.jpg,https://oleks-netizen.github.io/product-images/HB19153A/003.jpg,https://oleks-netizen.github.io/product-images/HB19153A/004.jpg,https://oleks-netizen.github.io/product-images/HB19153A/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-055/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/004.jpg</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HB3069Asmall</t>
+          <t>det-pd-056</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB3069Asmall/001.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/002.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/003.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/005.jpg,https://oleks-netizen.github.io/product-images/HB3069Asmall/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-056/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/003.jpg</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HB3095</t>
+          <t>det-pd-057</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB3095/001.jpg,https://oleks-netizen.github.io/product-images/HB3095/002.jpg,https://oleks-netizen.github.io/product-images/HB3095/003.jpg,https://oleks-netizen.github.io/product-images/HB3095/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-057/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/004.jpg</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HB3193A</t>
+          <t>det-pd-058</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB3193A/001.jpg,https://oleks-netizen.github.io/product-images/HB3193A/002.jpg,https://oleks-netizen.github.io/product-images/HB3193A/004.jpg,https://oleks-netizen.github.io/product-images/HB3193A/005.jpg,https://oleks-netizen.github.io/product-images/HB3193A/006.jpg,https://oleks-netizen.github.io/product-images/HB3193A/007.jpg,https://oleks-netizen.github.io/product-images/HB3193A/008.jpg,https://oleks-netizen.github.io/product-images/HB3193A/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-058/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/004.jpg</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HB3237B</t>
+          <t>det-pd-059</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB3237B/001.jpg,https://oleks-netizen.github.io/product-images/HB3237B/002.jpg,https://oleks-netizen.github.io/product-images/HB3237B/003.jpg,https://oleks-netizen.github.io/product-images/HB3237B/004.jpg,https://oleks-netizen.github.io/product-images/HB3237B/005.jpg,https://oleks-netizen.github.io/product-images/HB3237B/006.jpg,https://oleks-netizen.github.io/product-images/HB3237B/007.jpg,https://oleks-netizen.github.io/product-images/HB3237B/008.jpg,https://oleks-netizen.github.io/product-images/HB3237B/009.jpg,https://oleks-netizen.github.io/product-images/HB3237B/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-059/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/003.jpg</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HB3628R</t>
+          <t>dts-25rez-001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HB3628R/001.jpg,https://oleks-netizen.github.io/product-images/HB3628R/002.jpg,https://oleks-netizen.github.io/product-images/HB3628R/004.jpg,https://oleks-netizen.github.io/product-images/HB3628R/005.jpg,https://oleks-netizen.github.io/product-images/HB3628R/006.jpg,https://oleks-netizen.github.io/product-images/HB3628R/007.jpg,https://oleks-netizen.github.io/product-images/HB3628R/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dts-25rez-001/001.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/002.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/004.jpg</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HF502LN_BR</t>
+          <t>dtsk-18mm-kz-006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF502LN_BR/001.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/002.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/003.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/004.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/005.jpg,https://oleks-netizen.github.io/product-images/HF502LN_BR/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/004.jpg</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HF502_BU</t>
+          <t>dtsk-18mm-kz-007</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF502_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF502_BU/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/004.jpg</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HF502_CROC-PLN_BRN</t>
+          <t>dtsk-18mm-kz-008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BRN/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/004.jpg</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HF502_CROC-PLN_BU</t>
+          <t>dtsk-18mm-kz-009</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF502_CROC-PLN_BU/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/004.jpg</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HF502_GRN</t>
+          <t>dtsk-18mm-kz-010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF502_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/005.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/006.jpg,https://oleks-netizen.github.io/product-images/HF502_GRN/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/004.jpg</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HF577BLL</t>
+          <t>dtsk-18mm-kz-011</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577BLL/001.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/002.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/003.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/004.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/005.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/006.jpg,https://oleks-netizen.github.io/product-images/HF577BLL/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/004.jpg</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>HF577BN</t>
+          <t>dtsk-18mm-kz-012</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577BN/001.jpg,https://oleks-netizen.github.io/product-images/HF577BN/002.jpg,https://oleks-netizen.github.io/product-images/HF577BN/003.jpg,https://oleks-netizen.github.io/product-images/HF577BN/004.jpg,https://oleks-netizen.github.io/product-images/HF577BN/005.jpg,https://oleks-netizen.github.io/product-images/HF577BN/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/004.jpg</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>HF577LN_BR</t>
+          <t>dtsk-18mm-kz-013</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577LN_BR/001.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/002.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/003.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/004.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/005.jpg,https://oleks-netizen.github.io/product-images/HF577LN_BR/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/004.jpg</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HF577_CROC-PLN_BRN</t>
+          <t>dtsk-28mm-kz-001</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BRN/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/005.jpg</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HF577_CROC-PLN_BU</t>
+          <t>dtsk-28mm-kz-002</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/001.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/002.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/003.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/004.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/005.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/006.jpg,https://oleks-netizen.github.io/product-images/HF577_CROC-PLN_BU/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/005.jpg</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HF577_GRN</t>
+          <t>dtsk-28mm-kz-003</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF577_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/004.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/005.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/006.jpg,https://oleks-netizen.github.io/product-images/HF577_GRN/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/005.jpg</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HF592BLK</t>
+          <t>dtsk-28mm-kz-004</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF592BLK/001.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/002.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/003.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/004.jpg,https://oleks-netizen.github.io/product-images/HF592BLK/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/005.jpg</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HF592BNL</t>
+          <t>dtsk-28mm-kz-005</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF592BNL/001.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/002.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/003.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/004.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/005.jpg,https://oleks-netizen.github.io/product-images/HF592BNL/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/005.jpg</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HF592LNBR</t>
+          <t>dtsk-28mm-kz-006</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF592LNBR/001.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/002.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/003.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/004.jpg,https://oleks-netizen.github.io/product-images/HF592LNBR/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/005.jpg</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>HF594BL</t>
+          <t>dtsk-28mm-kz-007</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF594BL/001.jpg,https://oleks-netizen.github.io/product-images/HF594BL/002.jpg,https://oleks-netizen.github.io/product-images/HF594BL/003.jpg,https://oleks-netizen.github.io/product-images/HF594BL/004.jpg,https://oleks-netizen.github.io/product-images/HF594BL/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/004.jpg</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HF594MH</t>
+          <t>dtsk-28mm-kz-008</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF594MH/001.jpg,https://oleks-netizen.github.io/product-images/HF594MH/002.jpg,https://oleks-netizen.github.io/product-images/HF594MH/003.jpg,https://oleks-netizen.github.io/product-images/HF594MH/004.jpg,https://oleks-netizen.github.io/product-images/HF594MH/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/004.jpg</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HF594_BNL</t>
+          <t>dtsk-28mm-kz-009</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF594_BNL/001.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/002.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/003.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/004.jpg,https://oleks-netizen.github.io/product-images/HF594_BNL/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/004.jpg</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HF594_GRN</t>
+          <t>dtsk-28mm-kz-014</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF594_GRN/001.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/002.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/003.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/004.jpg,https://oleks-netizen.github.io/product-images/HF594_GRN/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/005.jpg</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HF595_MTN_BLK</t>
+          <t>dtsk-28mm-kz-015</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/001.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/002.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/003.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/004.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/005.jpg,https://oleks-netizen.github.io/product-images/HF595_MTN_BLK/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/005.jpg</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HF597_LNBR</t>
+          <t>dtsk-28mm-kz-017</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF597_LNBR/001.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/002.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/003.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/004.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/005.jpg,https://oleks-netizen.github.io/product-images/HF597_LNBR/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/005.jpg</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JD6020B</t>
+          <t>dtsk-28mm-kz-018</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/JD6020B/001.jpg,https://oleks-netizen.github.io/product-images/JD6020B/002.jpg,https://oleks-netizen.github.io/product-images/JD6020B/003.jpg,https://oleks-netizen.github.io/product-images/JD6020B/004.jpg,https://oleks-netizen.github.io/product-images/JD6020B/005.jpg,https://oleks-netizen.github.io/product-images/JD6020B/006.jpg,https://oleks-netizen.github.io/product-images/JD6020B/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/004.jpg</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JD7289A</t>
+          <t>dtsk-28mm-kz-019</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/JD7289A/001.jpg,https://oleks-netizen.github.io/product-images/JD7289A/002.jpg,https://oleks-netizen.github.io/product-images/JD7289A/003.jpg,https://oleks-netizen.github.io/product-images/JD7289A/005.jpg,https://oleks-netizen.github.io/product-images/JD7289A/006.jpg,https://oleks-netizen.github.io/product-images/JD7289A/007.jpg,https://oleks-netizen.github.io/product-images/JD7289A/008.jpg,https://oleks-netizen.github.io/product-images/JD7289A/009.jpg,https://oleks-netizen.github.io/product-images/JD7289A/010.jpg,https://oleks-netizen.github.io/product-images/JD7289A/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/005.jpg</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>K1617f-black</t>
+          <t>dtsk-28mm-kz-020</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/K1617f-black/001.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/002.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/004.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/005.jpg,https://oleks-netizen.github.io/product-images/K1617f-black/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/005.jpg</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>L28001-1</t>
+          <t>dtsk-28mm-kz-021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28001-1/001.jpg,https://oleks-netizen.github.io/product-images/L28001-1/003.jpg,https://oleks-netizen.github.io/product-images/L28001-1/004.jpg,https://oleks-netizen.github.io/product-images/L28001-1/005.jpg,https://oleks-netizen.github.io/product-images/L28001-1/006.jpg,https://oleks-netizen.github.io/product-images/L28001-1/007.jpg,https://oleks-netizen.github.io/product-images/L28001-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/005.jpg</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>L28001-2</t>
+          <t>dtsk-28mm-kz-022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28001-2/001.jpg,https://oleks-netizen.github.io/product-images/L28001-2/003.jpg,https://oleks-netizen.github.io/product-images/L28001-2/004.jpg,https://oleks-netizen.github.io/product-images/L28001-2/005.jpg,https://oleks-netizen.github.io/product-images/L28001-2/006.jpg,https://oleks-netizen.github.io/product-images/L28001-2/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/005.jpg</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>L28001-3</t>
+          <t>dtsk-28mm-kz-037</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28001-3/001.jpg,https://oleks-netizen.github.io/product-images/L28001-3/003.jpg,https://oleks-netizen.github.io/product-images/L28001-3/004.jpg,https://oleks-netizen.github.io/product-images/L28001-3/005.jpg,https://oleks-netizen.github.io/product-images/L28001-3/006.jpg,https://oleks-netizen.github.io/product-images/L28001-3/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/004.jpg</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>L28001-4</t>
+          <t>dtsk-28mm-kоzh-023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28001-4/001.jpg,https://oleks-netizen.github.io/product-images/L28001-4/003.jpg,https://oleks-netizen.github.io/product-images/L28001-4/004.jpg,https://oleks-netizen.github.io/product-images/L28001-4/005.jpg,https://oleks-netizen.github.io/product-images/L28001-4/006.jpg,https://oleks-netizen.github.io/product-images/L28001-4/007.jpg,https://oleks-netizen.github.io/product-images/L28001-4/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/004.jpg</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>L28028-1</t>
+          <t>dtsk-28mm-kоzh-024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28028-1/001.jpg,https://oleks-netizen.github.io/product-images/L28028-1/003.jpg,https://oleks-netizen.github.io/product-images/L28028-1/004.jpg,https://oleks-netizen.github.io/product-images/L28028-1/005.jpg,https://oleks-netizen.github.io/product-images/L28028-1/006.jpg,https://oleks-netizen.github.io/product-images/L28028-1/007.jpg,https://oleks-netizen.github.io/product-images/L28028-1/008.jpg,https://oleks-netizen.github.io/product-images/L28028-1/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/003.jpg</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>L28028-2</t>
+          <t>dtsk-28mm-kоzh-025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28028-2/001.jpg,https://oleks-netizen.github.io/product-images/L28028-2/003.jpg,https://oleks-netizen.github.io/product-images/L28028-2/004.jpg,https://oleks-netizen.github.io/product-images/L28028-2/005.jpg,https://oleks-netizen.github.io/product-images/L28028-2/006.jpg,https://oleks-netizen.github.io/product-images/L28028-2/007.jpg,https://oleks-netizen.github.io/product-images/L28028-2/008.jpg,https://oleks-netizen.github.io/product-images/L28028-2/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/003.jpg</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>L28028-3</t>
+          <t>dtsk-28mm-kоzh-026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28028-3/001.jpg,https://oleks-netizen.github.io/product-images/L28028-3/003.jpg,https://oleks-netizen.github.io/product-images/L28028-3/004.jpg,https://oleks-netizen.github.io/product-images/L28028-3/005.jpg,https://oleks-netizen.github.io/product-images/L28028-3/006.jpg,https://oleks-netizen.github.io/product-images/L28028-3/007.jpg,https://oleks-netizen.github.io/product-images/L28028-3/008.jpg,https://oleks-netizen.github.io/product-images/L28028-3/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/003.jpg</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>L28029-1</t>
+          <t>dtsk-28mm-kоzh-027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28029-1/001.jpg,https://oleks-netizen.github.io/product-images/L28029-1/003.jpg,https://oleks-netizen.github.io/product-images/L28029-1/004.jpg,https://oleks-netizen.github.io/product-images/L28029-1/005.jpg,https://oleks-netizen.github.io/product-images/L28029-1/006.jpg,https://oleks-netizen.github.io/product-images/L28029-1/007.jpg,https://oleks-netizen.github.io/product-images/L28029-1/008.jpg,https://oleks-netizen.github.io/product-images/L28029-1/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/004.jpg</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>L28029-2</t>
+          <t>dtsk-28mm-kоzh-028</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28029-2/001.jpg,https://oleks-netizen.github.io/product-images/L28029-2/003.jpg,https://oleks-netizen.github.io/product-images/L28029-2/004.jpg,https://oleks-netizen.github.io/product-images/L28029-2/005.jpg,https://oleks-netizen.github.io/product-images/L28029-2/006.jpg,https://oleks-netizen.github.io/product-images/L28029-2/007.jpg,https://oleks-netizen.github.io/product-images/L28029-2/008.jpg,https://oleks-netizen.github.io/product-images/L28029-2/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/003.jpg</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>L28029-3</t>
+          <t>dtsk-28mm-kоzh-029</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28029-3/001.jpg,https://oleks-netizen.github.io/product-images/L28029-3/003.jpg,https://oleks-netizen.github.io/product-images/L28029-3/004.jpg,https://oleks-netizen.github.io/product-images/L28029-3/005.jpg,https://oleks-netizen.github.io/product-images/L28029-3/006.jpg,https://oleks-netizen.github.io/product-images/L28029-3/007.jpg,https://oleks-netizen.github.io/product-images/L28029-3/008.jpg,https://oleks-netizen.github.io/product-images/L28029-3/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/003.jpg</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>L28029-4</t>
+          <t>dtsk-28mm-kоzh-030</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L28029-4/001.jpg,https://oleks-netizen.github.io/product-images/L28029-4/002.jpg,https://oleks-netizen.github.io/product-images/L28029-4/004.jpg,https://oleks-netizen.github.io/product-images/L28029-4/005.jpg,https://oleks-netizen.github.io/product-images/L28029-4/006.jpg,https://oleks-netizen.github.io/product-images/L28029-4/007.jpg,https://oleks-netizen.github.io/product-images/L28029-4/008.jpg,https://oleks-netizen.github.io/product-images/L28029-4/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/003.jpg</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>L501-041857</t>
+          <t>dtsk-28mm-kоzh-031</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L501-041857/001.jpg,https://oleks-netizen.github.io/product-images/L501-041857/002.jpg,https://oleks-netizen.github.io/product-images/L501-041857/003.jpg,https://oleks-netizen.github.io/product-images/L501-041857/004.jpg,https://oleks-netizen.github.io/product-images/L501-041857/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/004.jpg</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>L501-042014</t>
+          <t>dtsk-28mm-kоzh-032</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L501-042014/001.jpg,https://oleks-netizen.github.io/product-images/L501-042014/002.jpg,https://oleks-netizen.github.io/product-images/L501-042014/003.jpg,https://oleks-netizen.github.io/product-images/L501-042014/004.jpg,https://oleks-netizen.github.io/product-images/L501-042014/005.jpg,https://oleks-netizen.github.io/product-images/L501-042014/006.jpg,https://oleks-netizen.github.io/product-images/L501-042014/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/004.jpg</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>L501-042021</t>
+          <t>dtsk-28mm-kоzh-033</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L501-042021/001.jpg,https://oleks-netizen.github.io/product-images/L501-042021/002.jpg,https://oleks-netizen.github.io/product-images/L501-042021/003.jpg,https://oleks-netizen.github.io/product-images/L501-042021/004.jpg,https://oleks-netizen.github.io/product-images/L501-042021/005.jpg,https://oleks-netizen.github.io/product-images/L501-042021/006.jpg,https://oleks-netizen.github.io/product-images/L501-042021/007.jpg,https://oleks-netizen.github.io/product-images/L501-042021/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/004.jpg</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>L501-042038</t>
+          <t>dtsk-28mm-kоzh-034</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L501-042038/001.jpg,https://oleks-netizen.github.io/product-images/L501-042038/002.jpg,https://oleks-netizen.github.io/product-images/L501-042038/003.jpg,https://oleks-netizen.github.io/product-images/L501-042038/004.jpg,https://oleks-netizen.github.io/product-images/L501-042038/005.jpg,https://oleks-netizen.github.io/product-images/L501-042038/006.jpg,https://oleks-netizen.github.io/product-images/L501-042038/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/004.jpg</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>L87229-1</t>
+          <t>dtsk-28mm-kоzh-035</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L87229-1/001.jpg,https://oleks-netizen.github.io/product-images/L87229-1/002.jpg,https://oleks-netizen.github.io/product-images/L87229-1/003.jpg,https://oleks-netizen.github.io/product-images/L87229-1/004.jpg,https://oleks-netizen.github.io/product-images/L87229-1/005.jpg,https://oleks-netizen.github.io/product-images/L87229-1/006.jpg,https://oleks-netizen.github.io/product-images/L87229-1/007.jpg,https://oleks-netizen.github.io/product-images/L87229-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/004.jpg</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>L88003-32</t>
+          <t>dtsk-28mm-kоzh-036</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/L88003-32/001.jpg,https://oleks-netizen.github.io/product-images/L88003-32/003.jpg,https://oleks-netizen.github.io/product-images/L88003-32/004.jpg,https://oleks-netizen.github.io/product-images/L88003-32/005.jpg,https://oleks-netizen.github.io/product-images/L88003-32/006.jpg,https://oleks-netizen.github.io/product-images/L88003-32/007.jpg,https://oleks-netizen.github.io/product-images/L88003-32/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/004.jpg</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LC47208K-1</t>
+          <t>ekm-nwksh-001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47208K-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-001/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/005.jpg</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LC47208K-1X</t>
+          <t>ekm-nwksh-002</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47208K-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/006.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/007.jpg,https://oleks-netizen.github.io/product-images/LC47208K-1X/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-002/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/003.jpg</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LC47208K-92</t>
+          <t>ekm-nwksh-003</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47208K-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47208K-92/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-003/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/003.jpg</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LC47210-1</t>
+          <t>ekm-nwksh-004</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47210-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-1/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-004/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-004/002.jpg</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LC47210-1X</t>
+          <t>ekm-nwksh-005</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47210-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47210-1X/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-005/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/005.jpg</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LC47210-92</t>
+          <t>m-kozh33-wtrua-0025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47210-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47210-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/004.jpg</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LC47240W-1</t>
+          <t>m-kozh33-wtrua-0026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47240W-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/004.jpg</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LC47240W-1X</t>
+          <t>m-kozh33-wtrua-0027</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47240W-1X/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-1X/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/004.jpg</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LC47240W-92</t>
+          <t>m-kozh33-wtrua-0028</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47240W-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47240W-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/004.jpg</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LC47539-1</t>
+          <t>m-kozh33-wtrua-0029</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47539-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47539-1/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/004.jpg</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LC47539-92</t>
+          <t>m-kozh33-wtrua-0030</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47539-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47539-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/004.jpg</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LC47632F-1</t>
+          <t>m-kozh33-wtrua-0031</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47632F-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47632F-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/004.jpg</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LC47632F-92</t>
+          <t>m-kozh33-wtrua-0032</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47632F-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47632F-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/004.jpg</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LC47695-1</t>
+          <t>m-kozh33-wtrua-0033</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47695-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/007.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/008.jpg,https://oleks-netizen.github.io/product-images/LC47695-1/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/004.jpg</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>LC47832-1</t>
+          <t>m-kozh33-wtrua-0034</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47832-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/006.jpg,https://oleks-netizen.github.io/product-images/LC47832-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/005.jpg</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LC47832-92</t>
+          <t>m-kozh33-wtrua-0035</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47832-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47832-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/005.jpg</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LC47891-1</t>
+          <t>m-kozh38-wtrua-001</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47891-1/001.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/002.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/003.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/004.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/005.jpg,https://oleks-netizen.github.io/product-images/LC47891-1/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/004.jpg</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LC47891-92</t>
+          <t>m-kozh38-wtrua-0010</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47891-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47891-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/004.jpg</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>LC47991-1A</t>
+          <t>m-kozh38-wtrua-0012</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47991-1A/001.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/002.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/003.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/004.jpg,https://oleks-netizen.github.io/product-images/LC47991-1A/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/004.jpg</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LC47991-92</t>
+          <t>m-kozh38-wtrua-0013</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/LC47991-92/001.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/002.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/003.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/004.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/005.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/006.jpg,https://oleks-netizen.github.io/product-images/LC47991-92/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/004.jpg</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Lim-181GA</t>
+          <t>m-kozh38-wtrua-0014</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Lim-181GA/001.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/002.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/003.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/005.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/006.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/007.jpg,https://oleks-netizen.github.io/product-images/Lim-181GA/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/005.jpg</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>lim-22-115</t>
+          <t>m-kozh38-wtrua-0015</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lim-22-115/001.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/002.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/003.jpg,https://oleks-netizen.github.io/product-images/lim-22-115/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/004.jpg</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3541,282 +3541,282 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>lim-28-115</t>
+          <t>m-kozh38-wtrua-0016</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lim-28-115/001.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/002.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/003.jpg,https://oleks-netizen.github.io/product-images/lim-28-115/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/004.jpg</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lim-372RC</t>
+          <t>m-kozh38-wtrua-002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Lim-372RC/001.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/002.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/003.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/005.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/006.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/007.jpg,https://oleks-netizen.github.io/product-images/Lim-372RC/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/005.jpg</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PH601BR</t>
+          <t>m-kozh38-wtrua-0036</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/PH601BR/001.jpg,https://oleks-netizen.github.io/product-images/PH601BR/002.jpg,https://oleks-netizen.github.io/product-images/PH601BR/003.jpg,https://oleks-netizen.github.io/product-images/PH601BR/004.jpg,https://oleks-netizen.github.io/product-images/PH601BR/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/005.jpg</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PH601_BLK</t>
+          <t>m-kozh38-wtrua-0037</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/PH601_BLK/001.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/002.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/003.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/004.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/005.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/006.jpg,https://oleks-netizen.github.io/product-images/PH601_BLK/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/004.jpg</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PH602TAN</t>
+          <t>m-kozh38-wtrua-0038</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/PH602TAN/001.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/002.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/003.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/004.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/005.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/006.jpg,https://oleks-netizen.github.io/product-images/PH602TAN/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/005.jpg</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PH602_CROC-PLN_BRN</t>
+          <t>m-kozh38-wtrua-0039</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/001.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/002.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/003.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/004.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/005.jpg,https://oleks-netizen.github.io/product-images/PH602_CROC-PLN_BRN/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/005.jpg</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PH602_GRN</t>
+          <t>m-kozh38-wtrua-004</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/PH602_GRN/001.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/002.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/003.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/004.jpg,https://oleks-netizen.github.io/product-images/PH602_GRN/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/004.jpg</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RA-1046-3md</t>
+          <t>m-kozh38-wtrua-0040</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-1046-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/006.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/007.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/008.jpg,https://oleks-netizen.github.io/product-images/RA-1046-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/005.jpg</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RA-1342-3md</t>
+          <t>m-kozh38-wtrua-0041</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-1342-3md/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/005.jpg</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RA-1403-4lx</t>
+          <t>m-kozh38-wtrua-0042</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-1403-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RA-1403-4lx/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/005.jpg</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>RA-1501-3md</t>
+          <t>m-kozh38-wtrua-0043</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-1501-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/006.jpg,https://oleks-netizen.github.io/product-images/RA-1501-3md/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/005.jpg</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>RA-7122-3md</t>
+          <t>m-kozh38-wtrua-0044</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RA-7122-3md/001.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/002.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/003.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/004.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/005.jpg,https://oleks-netizen.github.io/product-images/RA-7122-3md/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/004.jpg</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>RAc-6690-4lx</t>
+          <t>m-kozh38-wtrua-0045</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RAc-6690-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RAc-6690-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/004.jpg</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RAg-1905-3md</t>
+          <t>m-kozh38-wtrua-0046</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RAg-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/003.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/007.jpg,https://oleks-netizen.github.io/product-images/RAg-1905-3md/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/004.jpg</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RB-2200RL-4lx</t>
+          <t>m-kozh38-wtrua-0047</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/008.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/009.jpg,https://oleks-netizen.github.io/product-images/RB-2200RL-4lx/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/005.jpg</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>RB-3960-4lx</t>
+          <t>m-kozh38-wtrua-0048</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB-3960-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/006.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/007.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/008.jpg,https://oleks-netizen.github.io/product-images/RB-3960-4lx/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/004.jpg</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RB-7122-3mdL</t>
+          <t>m-kozh38-wtrua-0049</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB-7122-3mdL/001.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/002.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/003.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/004.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/005.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/006.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/007.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/008.jpg,https://oleks-netizen.github.io/product-images/RB-7122-3mdL/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/004.jpg</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>RB-7340-3md</t>
+          <t>m-kozh38-wtrua-0050</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RB-7340-3md/001.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/002.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/003.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/004.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/006.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/007.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/008.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/009.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/010.jpg,https://oleks-netizen.github.io/product-images/RB-7340-3md/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/004.jpg</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RC-2200RL-4lx</t>
+          <t>m-kozh38-wtrua-0051</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RC-2200RL-4lx/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/004.jpg</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3826,72 +3826,72 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RC-60121-3md</t>
+          <t>m-kozh38-wtrua-0052</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RC-60121-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/002.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/006.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-60121-3md/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/004.jpg</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RC-7122-3mdL</t>
+          <t>m-kozh38-wtrua-0054</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RC-7122-3mdL/001.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/003.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/004.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/005.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/006.jpg,https://oleks-netizen.github.io/product-images/RC-7122-3mdL/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/005.jpg</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RC-7290-3md</t>
+          <t>m-kozh38-wtrua-0055</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RC-7290-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/006.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/008.jpg,https://oleks-netizen.github.io/product-images/RC-7290-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/007.jpg</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RC-7340-3md</t>
+          <t>m-kozh38-wtrua-0057</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RC-7340-3md/001.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/002.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/003.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/004.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/005.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/007.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/008.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/009.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/010.jpg,https://oleks-netizen.github.io/product-images/RC-7340-3md/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/006.jpg</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RCc-1905-3md</t>
+          <t>m-kozh38-wtrua-0058</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RCc-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCc-1905-3md/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/007.jpg</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3901,402 +3901,402 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RCC-3920-3md</t>
+          <t>m-kozh38-wtrua-0059</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RCC-3920-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCC-3920-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/004.jpg</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RCc-6600-3md</t>
+          <t>m-kozh38-wtrua-006</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RCc-6600-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCc-6600-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/005.jpg</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RCk-3420-3md</t>
+          <t>m-kozh38-wtrua-0060</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RCk-3420-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/005.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCk-3420-3md/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/005.jpg</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RCs-1905-3md</t>
+          <t>m-kozh38-wtrua-0061</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RCs-1905-3md/001.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/002.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/003.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/004.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/006.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/007.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/008.jpg,https://oleks-netizen.github.io/product-images/RCs-1905-3md/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/005.jpg</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RE-1342-3md</t>
+          <t>m-kozh38-wtrua-0063</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RE-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/005.jpg,https://oleks-netizen.github.io/product-images/RE-1342-3md/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/004.jpg</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RE-30272-3md</t>
+          <t>m-kozh38-wtrua-007</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RE-30272-3md/001.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/002.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/003.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/004.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/006.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/007.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/008.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/009.jpg,https://oleks-netizen.github.io/product-images/RE-30272-3md/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/005.jpg</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RK-1342-3md</t>
+          <t>m-kozh38-wtrua-008</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RK-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/005.jpg,https://oleks-netizen.github.io/product-images/RK-1342-3md/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/005.jpg</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RK-7122-3md</t>
+          <t>m-kozh38-wtrua-009</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RK-7122-3md/001.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/002.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/003.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/004.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/005.jpg,https://oleks-netizen.github.io/product-images/RK-7122-3md/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/003.jpg</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RYw-3027-4lx</t>
+          <t>m-kozh43-wtrua-0021</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RYw-3027-4lx/001.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/002.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/003.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/004.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/005.jpg,https://oleks-netizen.github.io/product-images/RYw-3027-4lx/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/006.jpg</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RА-3990-3md</t>
+          <t>m-kozh43-wtrua-0022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RА-3990-3md/001.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/002.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/004.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/005.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/006.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/007.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/008.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/009.jpg,https://oleks-netizen.github.io/product-images/RА-3990-3md/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/004.jpg</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RС-1342-3md</t>
+          <t>m-kozh43-wtrua-0023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/RС-1342-3md/001.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/002.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/003.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/004.jpg,https://oleks-netizen.github.io/product-images/RС-1342-3md/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/004.jpg</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SB1164BRN</t>
+          <t>m-kozh43-wtrua-0024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/SB1164BRN/001.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/002.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/004.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/005.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/006.jpg,https://oleks-netizen.github.io/product-images/SB1164BRN/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/005.jpg</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>T0138А</t>
+          <t>m-kozh43-wtrua-0064</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/T0138А/001.jpg,https://oleks-netizen.github.io/product-images/T0138А/002.jpg,https://oleks-netizen.github.io/product-images/T0138А/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/005.jpg</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TA-0042-4lx</t>
+          <t>m-kozh43-wtrua-0065</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TA-0042-4lx/001.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/002.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/004.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/005.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/006.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/007.jpg,https://oleks-netizen.github.io/product-images/TA-0042-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/005.jpg</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TA-5664-4lx</t>
+          <t>m-kozh43-wtrua-0066</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TA-5664-4lx/001.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/002.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/003.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/004.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/005.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/006.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/007.jpg,https://oleks-netizen.github.io/product-images/TA-5664-4lx/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/005.jpg</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TC4002 MH</t>
+          <t>m-zmsh38-wtrua-0001</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TC4002 MH/001.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/002.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/003.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/004.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/005.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/006.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/008.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/009.jpg,https://oleks-netizen.github.io/product-images/TC4002 MH/010.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/001.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/002.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/003.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/005.jpg</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TC4003_BU</t>
+          <t>mk-card-001</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TC4003_BU/001.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/002.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/003.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/004.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/005.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/006.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/008.jpg,https://oleks-netizen.github.io/product-images/TC4003_BU/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-card-001/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/003.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/004.jpg</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TC4004BR</t>
+          <t>mk-card-003</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TC4004BR/001.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/002.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/003.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/004.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/005.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/006.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/007.jpg,https://oleks-netizen.github.io/product-images/TC4004BR/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-card-003/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/003.jpg</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TC4004_BLK</t>
+          <t>nw-k-F6068</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TC4004_BLK/001.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/002.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/003.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/004.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/005.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/007.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/008.jpg,https://oleks-netizen.github.io/product-images/TC4004_BLK/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-F6068/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/005.jpg</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TC4004_BU</t>
+          <t>nwzh-15-0006</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TC4004_BU/001.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/002.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/003.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/004.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/005.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/006.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/007.jpg,https://oleks-netizen.github.io/product-images/TC4004_BU/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0006/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0006/003.jpg</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>tid3027</t>
+          <t>nwzh-15-0009</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tid3027/001.jpg,https://oleks-netizen.github.io/product-images/tid3027/002.jpg,https://oleks-netizen.github.io/product-images/tid3027/003.jpg,https://oleks-netizen.github.io/product-images/tid3027/004.jpg,https://oleks-netizen.github.io/product-images/tid3027/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0009/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0009/003.jpg</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TR34 BLK_RED</t>
+          <t>nwzh-15-0019</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TR34 BLK_RED/001.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/002.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/003.jpg,https://oleks-netizen.github.io/product-images/TR34 BLK_RED/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0019/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0019/003.jpg</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TW-Bella-black</t>
+          <t>nwzh-15-0020</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bella-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-black/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0020/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0020/002.jpg</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TW-Bella-dark-brown</t>
+          <t>nwzh-15-0026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-dark-brown/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0026/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0026/003.jpg</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TW-Bella-mokko</t>
+          <t>nwzh-15-0027</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bella-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/006.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-mokko/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0027/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0027/003.jpg</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TW-Bella-olive</t>
+          <t>nwzh-15-0033</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bella-olive/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-olive/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0033/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0033/003.jpg</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TW-Bella-red</t>
+          <t>pdr-pdt-004</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bella-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/004.jpg,https://oleks-netizen.github.io/product-images/TW-Bella-red/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-004/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/005.jpg</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4306,12 +4306,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TW-Bridget-white</t>
+          <t>pdr-pdt-005</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Bridget-white/001.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/002.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/003.jpg,https://oleks-netizen.github.io/product-images/TW-Bridget-white/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-005/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/005.jpg</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4321,27 +4321,27 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TW-Business-black</t>
+          <t>pdr-pdt-007</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Business-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-black/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-007/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/005.jpg</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TW-Business-dark-blue</t>
+          <t>pdr-pdt-008</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/004.jpg,https://oleks-netizen.github.io/product-images/TW-Business-dark-blue/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-008/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/005.jpg</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4351,312 +4351,312 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TW-Business-mars</t>
+          <t>pdr-pdt-009</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Business-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-Business-mars/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-009/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/005.jpg</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TW-CB-8-black</t>
+          <t>rmnd-30ua-002</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-black/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-002/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/004.jpg</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TW-CB-8-light-beige</t>
+          <t>rmnd-30ua-016</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-light-beige/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-016/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/004.jpg</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TW-CB-8-mars</t>
+          <t>rmnd-30ua-019</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mars/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-019/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/004.jpg</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TW-CB-8-mokko</t>
+          <t>rmnd-30ua-020</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-mokko/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-020/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/004.jpg</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TW-CB-8-pink</t>
+          <t>wtro-38ua-001</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-pink/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/002.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-pink/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-001/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/004.jpg</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TW-CB-8-red</t>
+          <t>wtro-38ua-002</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-CB-8-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-red/003.jpg,https://oleks-netizen.github.io/product-images/TW-CB-8-red/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-002/001.jpg</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TW-Classic-mokko</t>
+          <t>wtro-38ua-003</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Classic-mokko/001.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/002.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/003.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/005.jpg,https://oleks-netizen.github.io/product-images/TW-Classic-mokko/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-003/001.jpg</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TW-Explorer-S-mars</t>
+          <t>wtro-38ua-004</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Explorer-S-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Explorer-S-mars/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-004/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/004.jpg</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TW-Faith-mars</t>
+          <t>wtro-38ua-005</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Faith-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Faith-mars/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-005/001.jpg</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TW-Futsy-mars</t>
+          <t>wtro-38ua-006</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Futsy-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Futsy-mars/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-006/001.jpg</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TW-Holly-mars</t>
+          <t>wtro-38ua-007</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Holly-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/005.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/006.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/007.jpg,https://oleks-netizen.github.io/product-images/TW-Holly-mars/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-007/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-007/003.jpg</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TW-Jill-caramel</t>
+          <t>wtro-38ua-008</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Jill-caramel/001.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/002.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/003.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/004.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-caramel/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-008/001.jpg</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TW-Jill-red</t>
+          <t>wtro-38ua-009</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Jill-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-Jill-red/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-009/001.jpg</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TW-KL-5-mars</t>
+          <t>wtro-38ua-010</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-KL-5-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/004.jpg,https://oleks-netizen.github.io/product-images/TW-KL-5-mars/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-010/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-010/003.jpg</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TW-Moment-mars</t>
+          <t>wtro-38ua-011</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Moment-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Moment-mars/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-011/001.jpg</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TW-Nona-2-k</t>
+          <t>wtro-38ua-012</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-k/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/003.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-k/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-012/001.jpg</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TW-Nona-2-kon</t>
+          <t>wtro-38ua-013</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/003.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-kon/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-013/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/004.jpg</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TW-Nona-2-pink</t>
+          <t>wtro-38ua-014</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/001.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/002.jpg,https://oleks-netizen.github.io/product-images/TW-Nona-2-pink/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-014/001.jpg</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TW-OP-1-black</t>
+          <t>wtro-38ua-015</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-black/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-015/001.jpg</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TW-OP-1-dark-blue</t>
+          <t>wtro-38ua-016</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-dark-blue/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-016/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/004.jpg</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4666,27 +4666,27 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TW-OP-1-mars</t>
+          <t>wtro-38ua-017</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-OP-1-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-OP-1-mars/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-017/001.jpg</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TW-PM-2-mars</t>
+          <t>wtro-38ua-018</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-PM-2-mars/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-018/001.jpg</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4696,136 +4696,151 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>TW-PM-Classic-mars</t>
+          <t>wtro-38ua-019</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-mars/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-019/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/004.jpg</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TW-PM-Classic-red</t>
+          <t>wtro-38ua-020</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/001.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/002.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/004.jpg,https://oleks-netizen.github.io/product-images/TW-PM-Classic-red/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-020/001.jpg</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TW-Ruby-big-mars</t>
+          <t>wtro-38ua-021</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/001.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/002.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/003.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/005.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/006.jpg,https://oleks-netizen.github.io/product-images/TW-Ruby-big-mars/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-021/001.jpg</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>TW-Style-black</t>
+          <t>wtro-38ua-022</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Style-black/001.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/002.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/003.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/004.jpg,https://oleks-netizen.github.io/product-images/TW-Style-black/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-022/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/004.jpg</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TW-Style-kon</t>
+          <t>wtro-38ua-023</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Style-kon/001.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/002.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/004.jpg,https://oleks-netizen.github.io/product-images/TW-Style-kon/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-023/001.jpg</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TW-Vacation-vin</t>
+          <t>wtro-38ua-024</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/TW-Vacation-vin/001.jpg,https://oleks-netizen.github.io/product-images/TW-Vacation-vin/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-024/001.jpg</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>vc001A-orange</t>
+          <t>wtro-38ua-025</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/vc001A-orange/001.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/002.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/003.jpg,https://oleks-netizen.github.io/product-images/vc001A-orange/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-025/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/004.jpg</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>vc001a-red</t>
+          <t>wtro-38ua-026</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/vc001a-red/001.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/002.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/003.jpg,https://oleks-netizen.github.io/product-images/vc001a-red/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-026/001.jpg</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>VC2234black</t>
+          <t>wtro-38ua-027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/VC2234black/001.jpg,https://oleks-netizen.github.io/product-images/VC2234black/002.jpg,https://oleks-netizen.github.io/product-images/VC2234black/004.jpg,https://oleks-netizen.github.io/product-images/VC2234black/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-027/001.jpg</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>avt-4cm-ua-026</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026/002.jpg</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0026zh-1,5kz</t>
+          <t>0246zh-1kz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0026zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0246zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0246zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0246zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -451,12 +451,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0027zh-1,5kz</t>
+          <t>0247zh-1kz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0027zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0247zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0247zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0247zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0127zh-1kz</t>
+          <t>0248zh-1kz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0127zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0248zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0248zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0248zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,12 +481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0133zh-1kz</t>
+          <t>0251zh-1kz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0133zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0251zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0251zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0251zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,42 +496,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0134zh-1kz</t>
+          <t>0257zh-1kz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0134zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0134zh-1kz/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0257zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0257zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0257zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0135zh-1kz</t>
+          <t>0268zh-1kz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0135zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0268zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0268zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0268zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0136zh-1kz</t>
+          <t>0320rez-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0136zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0320rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0320rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0320rez-2/004.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0140zh-1kz</t>
+          <t>0321rez-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0140zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0321rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0321rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0321rez-2/004.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0142zh-1kz</t>
+          <t>0322rez-2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0142zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0322rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0322rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0322rez-2/004.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0145zh-1kz</t>
+          <t>0323rez-2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0145zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0323rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0323rez-2/003.jpg,https://oleks-netizen.github.io/product-images/0323rez-2/004.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,1287 +586,1287 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0154zh-1kz</t>
+          <t>0423zh-1kz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0154zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0423zh-1kz/001.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0181zh-1</t>
+          <t>0424zh-1kz</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0181zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0424zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0182zh-1</t>
+          <t>0425zh-1kz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0182zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/003.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0425zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0253zh-1kz</t>
+          <t>0431zh-1kz</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0253zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0431zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0255zh-1kz</t>
+          <t>0432zh-1kz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0255zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0432zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0260zh-1kz</t>
+          <t>0433zh-1kz</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0260zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0433zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0261zh-1kz</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0261zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0266zh-1kz</t>
+          <t>35k-rez-0334</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0266zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/35k-rez-0334/001.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0334/002.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0334/004.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0267zh-1kz</t>
+          <t>35k-rez-0336</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0267zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/35k-rez-0336/001.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0336/003.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0336/004.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0421zh-1kz</t>
+          <t>ek-zh-28kit-0010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0421zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0010/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0010/003.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0422zh-1kz</t>
+          <t>ek-zh-28kit-0013</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0422zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0013/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0013/003.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0426zh-1kz</t>
+          <t>ek-zh-28kit-0016</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0426zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0016/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0016/003.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0428zh-1kz</t>
+          <t>ek-zh-28kit-0018</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0428zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0018/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0018/003.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-001</t>
+          <t>ek-zh-28kit-003</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-003/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-003/003.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-002</t>
+          <t>ek-zh-28kit-006</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-002/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-006/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-006/003.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-003</t>
+          <t>ek-zh-28ua-0059</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-003/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0059/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0059/003.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-004</t>
+          <t>ek-zh-28ua-0060</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-004/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0060/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0060/002.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-005</t>
+          <t>ek-zh-28ua-0061</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0061/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0061/002.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-006</t>
+          <t>ek-zh-28ua-0062</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-006/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0062/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0062/003.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-007</t>
+          <t>ek-zh-28ua-0063</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-007/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0063/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0063/003.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-008</t>
+          <t>ek-zh-28ua-0064</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-008/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0064/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0064/003.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-009</t>
+          <t>ek-zh-28ua-0065</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0065/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0065/003.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-010</t>
+          <t>ek-zh-28ua-0066</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-010/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0066/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0066/003.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-011</t>
+          <t>ek-zh-33kit-0021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-011/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0021/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0021/003.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-012</t>
+          <t>ek-zh-33kit-0023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-012/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0023/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0023/003.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-013</t>
+          <t>ek-zh-33kit-0025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0025/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0025/003.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-014</t>
+          <t>ek-zh-33kit-0026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-014/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0026/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0026/003.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-015</t>
+          <t>ek-zh-33kit-0028</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-015/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0028/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0028/002.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-016</t>
+          <t>ek-zh-33kit-0031</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-016/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0031/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0031/002.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-017</t>
+          <t>ek-zh-33kit-0033</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0033/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0033/003.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-018</t>
+          <t>ek-zh-33ua-0057</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-018/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/003.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/004.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-019</t>
+          <t>ek-zh-33ua-0067</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-019/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0067/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0067/003.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-020</t>
+          <t>ek-zh-33ua-0068</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-020/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0068/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0068/003.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-021</t>
+          <t>ek-zh-38kit-0038</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0038/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0038/003.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-022</t>
+          <t>ek-zh-38kit-0043</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-022/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0043/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0043/003.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-023</t>
+          <t>ek-zh-38kit-0045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-023/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0045/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0045/003.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-024</t>
+          <t>ek-zh-38kit-0046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-024/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0046/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0046/003.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-025</t>
+          <t>ek-zh-38kit-0048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0048/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0048/003.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-026_131000315481</t>
+          <t>ek-zh-38kit-0051</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026_131000315481/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0051/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0051/003.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-027</t>
+          <t>ek-zh-38ua-0069</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-027/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0069/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0069/003.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-028</t>
+          <t>ek-zh-38ua-0070</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0070/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0070/003.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-029</t>
+          <t>ek-zh-38ua-0071</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-029/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0071/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0071/003.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-030</t>
+          <t>ek-zh-38ua-0072</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-030/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0072/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0072/003.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-031</t>
+          <t>ek-zh-38ua-0073</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-031/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0073/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0073/003.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-032</t>
+          <t>ek-zh-43ua-0058</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/003.jpg,https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/004.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-033</t>
+          <t>ekzh-27ua-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-033/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekzh-27ua-05/001.jpg,https://oleks-netizen.github.io/product-images/ekzh-27ua-05/003.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-034</t>
+          <t>ekzh-37ua-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-034/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekzh-37ua-06/001.jpg,https://oleks-netizen.github.io/product-images/ekzh-37ua-06/003.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-035</t>
+          <t>kkit-3zh-0005</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-035/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kkit-3zh-0005/001.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0005/003.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0005/004.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-036</t>
+          <t>kkit-3zh-0006</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kkit-3zh-0006/001.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0006/003.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0006/004.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-037</t>
+          <t>koz-zh3-kit-012</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-037/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-012/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-012/003.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-038</t>
+          <t>koz-zh3-kit-018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-038/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-018/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-018/003.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-039</t>
+          <t>koz-zh3-kit-023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-039/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-023/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-023/002.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-040</t>
+          <t>koz-zh3-kit-025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-025/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-025/002.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-041</t>
+          <t>koz-zh3-kit-027</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-041/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-027/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-027/002.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-042</t>
+          <t>koz-zh3-kit-028</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-042/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/003.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/004.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-043</t>
+          <t>koz-zh3-kit-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-043/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-05/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-05/003.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-044</t>
+          <t>koz-zh3-kit-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-09/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-09/003.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-045</t>
+          <t>kz-zh30-kit-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-045/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/002.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/004.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/005.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-046</t>
+          <t>kz-zh35-kit-010</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-046/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/004.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-047</t>
+          <t>kz-zh35-kit-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-047/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/004.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-048</t>
+          <t>kz-zh35-kit-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-05/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-05/003.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-049</t>
+          <t>kz-zh35-kit-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-049/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-07/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-07/003.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-050</t>
+          <t>kz-zh35-kit-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-050/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/002.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/004.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-051</t>
+          <t>kz-zh35-kit-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-051/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/004.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-052</t>
+          <t>new-30zh-k011</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k011/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k011/003.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-053</t>
+          <t>new-30zh-k014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-053/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k014/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k014/003.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-054</t>
+          <t>new-30zh-k015</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-054/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k015/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k015/003.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-055</t>
+          <t>new-30zh-k016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-055/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k016/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k016/003.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-056</t>
+          <t>new-30zh-k017</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k017/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k017/003.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-057</t>
+          <t>new-30zh-k018</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-057/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k018/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k018/003.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-058</t>
+          <t>new-30zh-k019</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-058/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k019/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k019/003.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-059</t>
+          <t>new-30zh-k020</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-059/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k020/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k020/003.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-060</t>
+          <t>new-30zh-k021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k021/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k021/003.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-061</t>
+          <t>new-30zh-k023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-061/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-30zh-k023/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/002.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/003.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/005.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-062</t>
+          <t>nw-2rez-0010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-062/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0010/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0010/003.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-063</t>
+          <t>nw-2rez-0017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-063/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0017/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0017/003.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-064</t>
+          <t>nw-2rez-0018</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0018/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0018/003.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-065</t>
+          <t>nw-2rez-0022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-065/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0022/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0022/003.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-066</t>
+          <t>nw-2rez-0028</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-066/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0028/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0028/003.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0028/004.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-067</t>
+          <t>nw-2rez-0029</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-067/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0029/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0029/002.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0029/004.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-068</t>
+          <t>nw-zh25k-0067</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0067/003.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-069</t>
+          <t>nw-zh25k-0072</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-069/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0072/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0072/003.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-070</t>
+          <t>nw-zh25k-0098</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-070/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0098/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0098/003.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>avt-4cm-ua-071</t>
+          <t>nw-zh25k-0123</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-071/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0123/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0123/003.jpg</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>det-15k-003</t>
+          <t>nw-zh25k-0136</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-15k-003/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0136/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0136/003.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0136/004.jpg</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>det-15k-007</t>
+          <t>nw-zh3k-0026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-15k-007/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-007/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0026/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0026/003.jpg</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1876,12 +1876,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>det-15k-008</t>
+          <t>nw-zh3k-0039</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-15k-008/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-008/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0039/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0039/003.jpg</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1891,12 +1891,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>det-15k-009</t>
+          <t>nw-zh3k-0052</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-15k-009/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-009/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0052/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0052/003.jpg</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1906,12 +1906,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>det-20k-014</t>
+          <t>nw-zh3k-0059</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-014/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-014/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0059/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0059/003.jpg</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1921,12 +1921,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>det-20k-015</t>
+          <t>nw-zh3k-0062</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-015/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-015/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0062/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0062/003.jpg</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1936,12 +1936,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>det-20k-016</t>
+          <t>nw-zh3k-0065</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-016/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-016/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0065/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0065/002.jpg</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1951,12 +1951,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>det-20k-019</t>
+          <t>nw-zh3k-0067</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-019/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-019/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0067/002.jpg</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1966,27 +1966,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>det-20k-020</t>
+          <t>nwk-30zh-0035</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-020/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-020/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwk-30zh-0035/001.jpg,https://oleks-netizen.github.io/product-images/nwk-30zh-0035/003.jpg,https://oleks-netizen.github.io/product-images/nwk-30zh-0035/004.jpg</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>det-20k-021</t>
+          <t>nwzh-15-0023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-021/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-021/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0023/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0023/003.jpg</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -1996,12 +1996,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>det-20k-022</t>
+          <t>nwzh-15-0028</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-20k-022/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-022/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0028/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0028/003.jpg</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2011,12 +2011,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>det-pd-013</t>
+          <t>nwzh-15-0032</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-013/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-013/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0032/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0032/003.jpg</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2026,12 +2026,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>det-pd-015</t>
+          <t>nwzh-25-0019</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-015/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-015/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0019/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0019/003.jpg</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2041,27 +2041,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>det-pd-020</t>
+          <t>nwzh-25-0020</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-020/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0020/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0020/003.jpg</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>det-pd-022</t>
+          <t>nwzh-25-0021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-022/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-022/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0021/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0021/003.jpg</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2071,12 +2071,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>det-pd-023</t>
+          <t>nwzh-25-0025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-023/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-023/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0025/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0025/003.jpg</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2086,12 +2086,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>det-pd-024</t>
+          <t>nwzh-25-0027</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-024/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-024/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0027/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0027/003.jpg</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2101,12 +2101,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>det-pd-027</t>
+          <t>nwzh-25-0029</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-027/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-027/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0029/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0029/003.jpg</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2116,207 +2116,207 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>det-pd-028</t>
+          <t>nwzh-25-0031</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-028/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0031/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0031/003.jpg</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>det-pd-029</t>
+          <t>nwzh-25-0033</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-029/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0033/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0033/003.jpg</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>det-pd-030</t>
+          <t>nwzh-25-0034</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-030/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0034/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0034/003.jpg</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>det-pd-031</t>
+          <t>nwzh-25-0035</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-031/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0035/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0035/003.jpg</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>det-pd-032</t>
+          <t>nwzh-25-0036</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-032/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0036/001.jpg</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>det-pd-033</t>
+          <t>nwzh-25-0037</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-033/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0037/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0037/003.jpg</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>det-pd-034</t>
+          <t>nwzh-25-0038</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-034/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0038/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0038/003.jpg</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>det-pd-035</t>
+          <t>nwzh-25-0044</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-035/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0044/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0044/003.jpg</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>det-pd-036</t>
+          <t>nwzh-25-0045</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-036/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0045/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0045/003.jpg</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>det-pd-037</t>
+          <t>nwzh-25-0046</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-037/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0046/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0046/003.jpg</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>det-pd-038</t>
+          <t>nwzh-25-0047</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-038/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0047/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0047/003.jpg</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>det-pd-039</t>
+          <t>nwzh-25-0048</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-039/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0048/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0048/003.jpg</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>det-pd-040</t>
+          <t>nwzh-25-0054</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-040/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0054/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0054/003.jpg</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>det-pd-041</t>
+          <t>nwzh-25-0059</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-041/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0059/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0059/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0059/004.jpg</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2326,102 +2326,102 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>det-pd-042</t>
+          <t>nwzh-25-0060</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-042/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-042/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0060/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0060/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0060/004.jpg</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>det-pd-043</t>
+          <t>nwzh-25-0063</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-043/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-043/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0063/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0063/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0063/004.jpg</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>det-pd-044</t>
+          <t>nwzh-30k-0046</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-044/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0046/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0046/003.jpg</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>det-pd-045</t>
+          <t>nwzh-30k-0051</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-045/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0051/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0051/003.jpg</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>det-pd-046</t>
+          <t>nwzh-30k-0052</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-046/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0052/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0052/003.jpg</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>det-pd-047</t>
+          <t>nwzh-30k-0054</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-047/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0054/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0054/003.jpg</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>det-pd-048</t>
+          <t>nwzh-30k-0067</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-048/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0067/002.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0067/003.jpg</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2431,27 +2431,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>det-pd-049</t>
+          <t>nwzh-30k-76</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-049/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-76/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-76/003.jpg</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>det-pd-050</t>
+          <t>rez-new-25kit-001</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-050/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-050/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-001/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-001/003.jpg</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2461,117 +2461,117 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>det-pd-051</t>
+          <t>rez-new-25kit-003</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-051/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-003/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-003/003.jpg</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>det-pd-052</t>
+          <t>rez-new-25kit-005</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-052/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-005/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-005/003.jpg</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>det-pd-053</t>
+          <t>rez-new-25kit-006</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-053/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-006/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-006/003.jpg</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>det-pd-054</t>
+          <t>rez-new-25kit-010</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-054/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-010/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-010/003.jpg</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>det-pd-055</t>
+          <t>rez-new-25kit-011</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-055/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-011/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-011/003.jpg</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>det-pd-056</t>
+          <t>rez-new-25kit-012</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-056/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-012/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-012/003.jpg</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>det-pd-057</t>
+          <t>rez-new-25kit-013</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-057/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-013/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-013/003.jpg</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>det-pd-058</t>
+          <t>rez-new-25kit-017</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-058/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-017/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-017/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-017/004.jpg</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2581,12 +2581,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>det-pd-059</t>
+          <t>rez-new-25kit-018</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/det-pd-059/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-018/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-018/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-018/004.jpg</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2596,42 +2596,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>dts-25rez-001</t>
+          <t>rez-new-25kit-019</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dts-25rez-001/001.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/002.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-019/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/005.jpg</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-006</t>
+          <t>rez-new-25kit-020</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-020/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/005.jpg</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-007</t>
+          <t>rez-new-25kit-021</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-021/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-021/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-021/004.jpg</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2641,12 +2641,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-008</t>
+          <t>rez-new-25kit-022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-022/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-022/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-022/004.jpg</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2656,12 +2656,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-009</t>
+          <t>rez-new-25kit-023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-023/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-023/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-023/004.jpg</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2671,12 +2671,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-010</t>
+          <t>rez-new-25kit-024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-024/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-024/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-024/004.jpg</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2686,12 +2686,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-011</t>
+          <t>rez-new-25kit-026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-026/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-026/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-026/004.jpg</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2701,12 +2701,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-012</t>
+          <t>rez-new-25kit-027</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-027/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-027/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-027/004.jpg</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2716,147 +2716,147 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dtsk-18mm-kz-013</t>
+          <t>rez-new-25kit-028</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-028/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/004.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/005.jpg</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-001</t>
+          <t>uzk-k25zh-kit005</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/003.jpg,https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/004.jpg</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-002</t>
+          <t>uzk-k30zh-kit016</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit016/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit016/003.jpg</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-003</t>
+          <t>uzk-k30zh-kit062</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit062/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit062/003.jpg</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-004</t>
+          <t>uzk-k30zh-kit063</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit063/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit063/003.jpg</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-005</t>
+          <t>uzk-k30zh-kit064</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit064/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit064/003.jpg</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-006</t>
+          <t>uzk-k30zh-kit065</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit065/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit065/003.jpg</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-007</t>
+          <t>uzk-k30zh-kit066</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit066/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit066/003.jpg</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-008</t>
+          <t>uzk-k30zh-ua-011</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-ua-011/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-ua-011/003.jpg</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-009</t>
+          <t>zhkz-18cm-041</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-18cm-041/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-041/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-041/004.jpg</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2866,147 +2866,147 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-014</t>
+          <t>zhkz-18cm-042</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-18cm-042/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-042/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-042/004.jpg</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-015</t>
+          <t>zhkz-1cm-001</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-001/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-001/003.jpg</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-017</t>
+          <t>zhkz-1cm-0014</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-0014/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-0014/003.jpg</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-018</t>
+          <t>zhkz-1cm-0015</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-0015/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-0015/003.jpg</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-019</t>
+          <t>zhkz-1cm-002</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-002/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-002/003.jpg</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-020</t>
+          <t>zhkz-1cm-003</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-003/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-003/003.jpg</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-021</t>
+          <t>zhkz-1cm-005</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-005/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-005/003.jpg</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-022</t>
+          <t>zhkz-1cm-006</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-006/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-006/003.jpg</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kz-037</t>
+          <t>zhkz-1cm-007</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-007/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-007/003.jpg</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-023</t>
+          <t>zhkz-23cm-031</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-031/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-031/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-031/004.jpg</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3016,27 +3016,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-024</t>
+          <t>zhkz-23cm-032</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-032/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/005.jpg</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-025</t>
+          <t>zhkz-23cm-043</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-043/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-043/003.jpg</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3046,27 +3046,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-026</t>
+          <t>zhkz-23cm-044</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-044/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-044/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-044/004.jpg</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-027</t>
+          <t>zhkz-23cm-045</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-045/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-045/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-045/004.jpg</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3076,12 +3076,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-028</t>
+          <t>zhkz-23cm-046</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-046/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-046/003.jpg</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3091,42 +3091,42 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-029</t>
+          <t>zhkz-25cm-001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-001/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/005.jpg</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-030</t>
+          <t>zhkz-25cm-002</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-002/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/005.jpg</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-031</t>
+          <t>zhkz-25cm-003</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-003/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-003/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-003/004.jpg</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3136,27 +3136,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-032</t>
+          <t>zhkz-25cm-004</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-004/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-004/003.jpg</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-033</t>
+          <t>zhkz-25cm-005</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-005/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-005/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-005/004.jpg</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3166,42 +3166,42 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-034</t>
+          <t>zhkz-25cm-006</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-006/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-006/003.jpg</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-035</t>
+          <t>zhkz-25cm-008</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-008/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-008/003.jpg</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>dtsk-28mm-kоzh-036</t>
+          <t>zhkz-28cm-033</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-033/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-033/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-033/004.jpg</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3211,42 +3211,42 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ekm-nwksh-001</t>
+          <t>zhkz-28cm-034</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-001/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-034/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/005.jpg</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ekm-nwksh-002</t>
+          <t>zhkz-28cm-047</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-002/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-047/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-047/003.jpg</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ekm-nwksh-003</t>
+          <t>zhkz-28cm-048</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-003/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-048/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-048/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-048/004.jpg</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3256,12 +3256,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ekm-nwksh-004</t>
+          <t>zhkz-28cm-049</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-004/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-004/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-049/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-049/003.jpg</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3271,27 +3271,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ekm-nwksh-005</t>
+          <t>zhkz-28cm-050</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-005/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-050/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-050/003.jpg</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0025</t>
+          <t>zhkz-28cm-051</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-051/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-051/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-051/004.jpg</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3301,12 +3301,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0026</t>
+          <t>zhkz-28cm-052</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-052/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-052/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-052/004.jpg</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3316,12 +3316,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0027</t>
+          <t>zhkz-30cm-009</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-009/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-009/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-009/004.jpg</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3331,12 +3331,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0028</t>
+          <t>zhkz-30cm-010</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-010/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-010/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-010/004.jpg</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3346,27 +3346,27 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0029</t>
+          <t>zhkz-30cm-012</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-012/001.jpg</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0030</t>
+          <t>zhkz-32cm-053</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-32cm-053/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-32cm-053/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-32cm-053/004.jpg</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3376,27 +3376,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0031</t>
+          <t>zhkz-33cm-025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-025/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/005.jpg</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0032</t>
+          <t>zhkz-33cm-026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-026/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-026/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-026/004.jpg</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3406,57 +3406,57 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0033</t>
+          <t>zhkz-33cm-027</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-027/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/005.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/006.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/007.jpg</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0034</t>
+          <t>zhkz-33cm-028</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-028/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-028/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-028/004.jpg</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>m-kozh33-wtrua-0035</t>
+          <t>zhkz-33cm-029</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-029/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/006.jpg</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-001</t>
+          <t>zhkz-33cm-030</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-030/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-030/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-030/004.jpg</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3466,42 +3466,42 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0010</t>
+          <t>zhkz-38cm-035</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-035/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/005.jpg</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0012</t>
+          <t>zhkz-38cm-036</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-036/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/005.jpg</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0013</t>
+          <t>zhkz-38cm-037</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-037/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/005.jpg</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3511,42 +3511,42 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0014</t>
+          <t>zhkz-38cm-038</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-038/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-038/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-038/004.jpg</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0015</t>
+          <t>zhkz-38cm-039</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-039/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-039/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-039/004.jpg</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0016</t>
+          <t>zhkz-38cm-040</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-040/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-040/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-040/004.jpg</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3556,42 +3556,42 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-002</t>
+          <t>zhkz-38cm-054</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-054/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-054/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-054/004.jpg</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0036</t>
+          <t>zhkz-38cm-055</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-055/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-055/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-055/004.jpg</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0037</t>
+          <t>zhkz-38cm-056</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-056/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-056/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-056/004.jpg</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3601,42 +3601,42 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0038</t>
+          <t>zhkz-38cm-057</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-057/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-057/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-057/004.jpg</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0039</t>
+          <t>zhkz-38cm-058</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-058/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-058/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-058/004.jpg</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-004</t>
+          <t>zhkz-38cm-059</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-059/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-059/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-059/004.jpg</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3646,72 +3646,72 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0040</t>
+          <t>zhkz-38cm-060</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-060/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-060/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-060/004.jpg</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0041</t>
+          <t>zhkz-38cm-061</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-061/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-061/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-061/004.jpg</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0042</t>
+          <t>zhkz-38cm-062</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-062/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-062/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-062/004.jpg</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0043</t>
+          <t>zhkz-38cm-063</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-063/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-063/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-063/004.jpg</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0044</t>
+          <t>zhkz-38cm-064</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-064/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-064/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-064/004.jpg</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3721,12 +3721,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0045</t>
+          <t>zhkz-38cm-065</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-065/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-065/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-065/004.jpg</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3736,12 +3736,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0046</t>
+          <t>zhkz-38cm-066</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-066/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-066/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-066/004.jpg</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3751,57 +3751,57 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0047</t>
+          <t>zhkz-38cm-067</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-067/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-067/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-067/004.jpg</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0048</t>
+          <t>zhkz-42cm-068</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-42cm-068/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-42cm-068/003.jpg</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0049</t>
+          <t>zhkz-42cm-069</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhkz-42cm-069/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-42cm-069/003.jpg</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0050</t>
+          <t>zhn-kz-kit13-031</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/004.jpg</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3811,12 +3811,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0051</t>
+          <t>zhn-kz-kit13-032</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/004.jpg</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3826,12 +3826,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0052</t>
+          <t>zhn-kz-kit13-033</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/004.jpg</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3841,72 +3841,72 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0054</t>
+          <t>zhn-kz-kit13-034</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/004.jpg</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0055</t>
+          <t>zhn-kz-kit13-035</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/004.jpg</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0057</t>
+          <t>zhn-kz-kit13-036</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/004.jpg</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0058</t>
+          <t>zhn-kz-kit13-037</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/004.jpg</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0059</t>
+          <t>zhn-kz-kit13-038</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/004.jpg</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3916,57 +3916,57 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-006</t>
+          <t>zhn-kz-kit13-039</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/004.jpg</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0060</t>
+          <t>zhn-kz-kit13-040</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/004.jpg</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0061</t>
+          <t>zhn-kz-kit13-041</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/004.jpg</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-0063</t>
+          <t>zhn-kz-kit13-042</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/004.jpg</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3976,72 +3976,72 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-007</t>
+          <t>zhn-kz-kit13-043</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/004.jpg</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-008</t>
+          <t>zhn-kz-kit13-044</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/004.jpg</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>m-kozh38-wtrua-009</t>
+          <t>zhn-kz-kit13-045</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/004.jpg</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0021</t>
+          <t>zhn-kz-kit13-059</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/004.jpg</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0022</t>
+          <t>zhn-kz-kit13-060</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/004.jpg</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4051,12 +4051,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0023</t>
+          <t>zhn-kz-kit13-061</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/004.jpg</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4066,102 +4066,102 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0024</t>
+          <t>zhn-kz-kit13-062</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/004.jpg</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0064</t>
+          <t>zhn-kz-kit13-063</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/004.jpg</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0065</t>
+          <t>zhn-kz-kit13-064</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/004.jpg</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>m-kozh43-wtrua-0066</t>
+          <t>zhn-kz-kit13-065</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/004.jpg</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>m-zmsh38-wtrua-0001</t>
+          <t>zhn-kz-kit13-066</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/001.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/002.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/003.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/004.jpg</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>mk-card-001</t>
+          <t>zhn-kz-kit13-067</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/mk-card-001/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/003.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/004.jpg</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>mk-card-003</t>
+          <t>zhn-kz-kit13-068</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/mk-card-003/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/004.jpg</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4171,207 +4171,207 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>nw-k-F6068</t>
+          <t>zhn-kz-kit13-069</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-k-F6068/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/004.jpg</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>nwzh-15-0006</t>
+          <t>zhn-kz-kit23-01</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0006/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/004.jpg</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>nwzh-15-0009</t>
+          <t>zhn-kz-kit23-010</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0009/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0009/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/004.jpg</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>nwzh-15-0019</t>
+          <t>zhn-kz-kit23-011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0019/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0019/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/004.jpg</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>nwzh-15-0020</t>
+          <t>zhn-kz-kit23-012</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0020/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0020/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/004.jpg</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>nwzh-15-0026</t>
+          <t>zhn-kz-kit23-013</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0026/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0026/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/004.jpg</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nwzh-15-0027</t>
+          <t>zhn-kz-kit23-014</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0027/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0027/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/004.jpg</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>nwzh-15-0033</t>
+          <t>zhn-kz-kit23-015</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0033/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0033/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/004.jpg</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>pdr-pdt-004</t>
+          <t>zhn-kz-kit23-02</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-004/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/004.jpg</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>pdr-pdt-005</t>
+          <t>zhn-kz-kit23-03</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-005/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/004.jpg</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>pdr-pdt-007</t>
+          <t>zhn-kz-kit23-04</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-007/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/004.jpg</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>pdr-pdt-008</t>
+          <t>zhn-kz-kit23-046</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-008/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/004.jpg</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>pdr-pdt-009</t>
+          <t>zhn-kz-kit23-047</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-009/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/004.jpg</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>rmnd-30ua-002</t>
+          <t>zhn-kz-kit23-048</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-002/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/004.jpg</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4381,12 +4381,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>rmnd-30ua-016</t>
+          <t>zhn-kz-kit23-049</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-016/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/004.jpg</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4396,12 +4396,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>rmnd-30ua-019</t>
+          <t>zhn-kz-kit23-05</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-019/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/004.jpg</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4411,12 +4411,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>rmnd-30ua-020</t>
+          <t>zhn-kz-kit23-050</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-020/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/004.jpg</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4426,12 +4426,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>wtro-38ua-001</t>
+          <t>zhn-kz-kit23-06</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-001/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/004.jpg</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4441,42 +4441,42 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>wtro-38ua-002</t>
+          <t>zhn-kz-kit23-07</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-002/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/004.jpg</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>wtro-38ua-003</t>
+          <t>zhn-kz-kit23-08</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-003/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/004.jpg</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>wtro-38ua-004</t>
+          <t>zhn-kz-kit23-09</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-004/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/004.jpg</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4486,132 +4486,132 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>wtro-38ua-005</t>
+          <t>zhn-kz-kit33-016</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-005/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/004.jpg</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>wtro-38ua-006</t>
+          <t>zhn-kz-kit33-017</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-006/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/004.jpg</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>wtro-38ua-007</t>
+          <t>zhn-kz-kit33-018</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-007/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-007/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/004.jpg</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>wtro-38ua-008</t>
+          <t>zhn-kz-kit33-019</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-008/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/004.jpg</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>wtro-38ua-009</t>
+          <t>zhn-kz-kit33-020</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-009/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/004.jpg</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>wtro-38ua-010</t>
+          <t>zhn-kz-kit33-021</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-010/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/004.jpg</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>wtro-38ua-011</t>
+          <t>zhn-kz-kit33-022</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-011/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/004.jpg</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>wtro-38ua-012</t>
+          <t>zhn-kz-kit33-023</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-012/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/004.jpg</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>wtro-38ua-013</t>
+          <t>zhn-kz-kit33-024</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-013/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/004.jpg</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4621,42 +4621,42 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>wtro-38ua-014</t>
+          <t>zhn-kz-kit33-025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-014/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/004.jpg</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>wtro-38ua-015</t>
+          <t>zhn-kz-kit33-026</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-015/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/004.jpg</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>wtro-38ua-016</t>
+          <t>zhn-kz-kit33-027</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-016/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/004.jpg</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4666,42 +4666,42 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>wtro-38ua-017</t>
+          <t>zhn-kz-kit33-028</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-017/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/004.jpg</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>wtro-38ua-018</t>
+          <t>zhn-kz-kit33-029</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-018/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/004.jpg</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>wtro-38ua-019</t>
+          <t>zhn-kz-kit33-030</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-019/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/004.jpg</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4711,42 +4711,42 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>wtro-38ua-020</t>
+          <t>zhn-kz-kit33-051</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-020/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/004.jpg</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>wtro-38ua-021</t>
+          <t>zhn-kz-kit33-052</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-021/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/004.jpg</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>wtro-38ua-022</t>
+          <t>zhn-kz-kit33-053</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-022/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/004.jpg</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4756,42 +4756,42 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>wtro-38ua-023</t>
+          <t>zhn-kz-kit33-054</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-023/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/004.jpg</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>wtro-38ua-024</t>
+          <t>zhn-kz-kit33-055</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-024/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/004.jpg</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>wtro-38ua-025</t>
+          <t>zhn-kz-kit33-056</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-025/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/004.jpg</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4801,46 +4801,31 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>wtro-38ua-026</t>
+          <t>zhn-kz-kit33-057</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-026/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/004.jpg</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>wtro-38ua-027</t>
+          <t>zhn-kz-kit33-058</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-027/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/004.jpg</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>avt-4cm-ua-026</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026/002.jpg</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C294"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0246zh-1kz</t>
+          <t>0026zh-1,5kz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0246zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0246zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0246zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0026zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0026zh-1,5kz/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -451,12 +451,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0247zh-1kz</t>
+          <t>0027zh-1,5kz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0247zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0247zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0247zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0027zh-1,5kz/001.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/002.jpg,https://oleks-netizen.github.io/product-images/0027zh-1,5kz/004.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0248zh-1kz</t>
+          <t>0127zh-1kz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0248zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0248zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0248zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0127zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0127zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,12 +481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0251zh-1kz</t>
+          <t>0133zh-1kz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0251zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0251zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0251zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0133zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0133zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,42 +496,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0257zh-1kz</t>
+          <t>0134zh-1kz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0257zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0257zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0257zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0134zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0134zh-1kz/003.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0268zh-1kz</t>
+          <t>0135zh-1kz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0268zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0268zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0268zh-1kz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0135zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0135zh-1kz/005.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0320rez-2</t>
+          <t>0136zh-1kz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0320rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0320rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0320rez-2/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0136zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0136zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0321rez-2</t>
+          <t>0140zh-1kz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0321rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0321rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0321rez-2/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0140zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0140zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0322rez-2</t>
+          <t>0142zh-1kz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0322rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0322rez-2/002.jpg,https://oleks-netizen.github.io/product-images/0322rez-2/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0142zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0142zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0323rez-2</t>
+          <t>0145zh-1kz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0323rez-2/001.jpg,https://oleks-netizen.github.io/product-images/0323rez-2/003.jpg,https://oleks-netizen.github.io/product-images/0323rez-2/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0145zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0145zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,1287 +586,1287 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0423zh-1kz</t>
+          <t>0154zh-1kz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0423zh-1kz/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0154zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0154zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0424zh-1kz</t>
+          <t>0181zh-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0424zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0424zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0181zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0181zh-1/004.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0425zh-1kz</t>
+          <t>0182zh-1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0425zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0425zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0182zh-1/001.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/002.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/003.jpg,https://oleks-netizen.github.io/product-images/0182zh-1/005.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0431zh-1kz</t>
+          <t>0253zh-1kz</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0431zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0431zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0253zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0253zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0432zh-1kz</t>
+          <t>0255zh-1kz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0432zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0432zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0255zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0255zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0433zh-1kz</t>
+          <t>0260zh-1kz</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/0433zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0433zh-1kz/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0260zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0260zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0261zh-1kz</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/001.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/002.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/003.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg,https://oleks-netizen.github.io/product-images/2/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0261zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0261zh-1kz/004.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>35k-rez-0334</t>
+          <t>0266zh-1kz</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/35k-rez-0334/001.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0334/002.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0334/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0266zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0266zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35k-rez-0336</t>
+          <t>0267zh-1kz</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/35k-rez-0336/001.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0336/003.jpg,https://oleks-netizen.github.io/product-images/35k-rez-0336/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0267zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0267zh-1kz/005.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-0010</t>
+          <t>0421zh-1kz</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0010/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0421zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0421zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-0013</t>
+          <t>0422zh-1kz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0013/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0013/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0422zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/004.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0422zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-0016</t>
+          <t>0426zh-1kz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0016/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0016/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0426zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0426zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-0018</t>
+          <t>0428zh-1kz</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-0018/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-0018/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0428zh-1kz/001.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/002.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/003.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/005.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/006.jpg,https://oleks-netizen.github.io/product-images/0428zh-1kz/007.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-003</t>
+          <t>avt-4cm-ua-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-003/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-001/005.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ek-zh-28kit-006</t>
+          <t>avt-4cm-ua-002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28kit-006/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28kit-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-002/001.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0059</t>
+          <t>avt-4cm-ua-003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0059/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0059/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-003/001.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0060</t>
+          <t>avt-4cm-ua-004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0060/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0060/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-004/001.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0061</t>
+          <t>avt-4cm-ua-005</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0061/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0061/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-005/005.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0062</t>
+          <t>avt-4cm-ua-006</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0062/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0062/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-006/001.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0063</t>
+          <t>avt-4cm-ua-007</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0063/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0063/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-007/001.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0064</t>
+          <t>avt-4cm-ua-008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0064/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0064/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-008/001.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0065</t>
+          <t>avt-4cm-ua-009</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0065/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0065/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-009/005.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ek-zh-28ua-0066</t>
+          <t>avt-4cm-ua-010</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-28ua-0066/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-28ua-0066/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-010/001.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0021</t>
+          <t>avt-4cm-ua-011</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0021/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0021/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-011/001.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0023</t>
+          <t>avt-4cm-ua-012</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0023/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0023/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-012/001.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0025</t>
+          <t>avt-4cm-ua-013</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0025/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0025/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-013/005.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0026</t>
+          <t>avt-4cm-ua-014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0026/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0026/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-014/001.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0028</t>
+          <t>avt-4cm-ua-015</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0028/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0028/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-015/001.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0031</t>
+          <t>avt-4cm-ua-016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0031/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0031/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-016/001.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ek-zh-33kit-0033</t>
+          <t>avt-4cm-ua-017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33kit-0033/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33kit-0033/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-017/005.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ek-zh-33ua-0057</t>
+          <t>avt-4cm-ua-018</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/003.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0057/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-018/001.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ek-zh-33ua-0067</t>
+          <t>avt-4cm-ua-019</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0067/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0067/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-019/001.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ek-zh-33ua-0068</t>
+          <t>avt-4cm-ua-020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-33ua-0068/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-33ua-0068/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-020/001.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0038</t>
+          <t>avt-4cm-ua-021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0038/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0038/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-021/005.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0043</t>
+          <t>avt-4cm-ua-022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0043/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0043/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-022/001.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0045</t>
+          <t>avt-4cm-ua-023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0045/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0045/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-023/001.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0046</t>
+          <t>avt-4cm-ua-024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0046/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0046/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-024/001.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0048</t>
+          <t>avt-4cm-ua-025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0048/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0048/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-025/005.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ek-zh-38kit-0051</t>
+          <t>avt-4cm-ua-026_131000315481</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38kit-0051/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38kit-0051/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026_131000315481/001.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ek-zh-38ua-0069</t>
+          <t>avt-4cm-ua-027</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0069/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0069/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-027/001.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ek-zh-38ua-0070</t>
+          <t>avt-4cm-ua-028</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0070/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0070/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-028/005.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ek-zh-38ua-0071</t>
+          <t>avt-4cm-ua-029</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0071/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0071/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-029/001.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ek-zh-38ua-0072</t>
+          <t>avt-4cm-ua-030</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0072/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0072/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-030/001.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ek-zh-38ua-0073</t>
+          <t>avt-4cm-ua-031</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-38ua-0073/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-38ua-0073/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-031/001.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ek-zh-43ua-0058</t>
+          <t>avt-4cm-ua-032</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/001.jpg,https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/003.jpg,https://oleks-netizen.github.io/product-images/ek-zh-43ua-0058/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-032/005.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ekzh-27ua-05</t>
+          <t>avt-4cm-ua-033</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekzh-27ua-05/001.jpg,https://oleks-netizen.github.io/product-images/ekzh-27ua-05/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-033/001.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ekzh-37ua-06</t>
+          <t>avt-4cm-ua-034</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ekzh-37ua-06/001.jpg,https://oleks-netizen.github.io/product-images/ekzh-37ua-06/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-034/001.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kkit-3zh-0005</t>
+          <t>avt-4cm-ua-035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kkit-3zh-0005/001.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0005/003.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0005/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-035/001.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kkit-3zh-0006</t>
+          <t>avt-4cm-ua-036</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kkit-3zh-0006/001.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0006/003.jpg,https://oleks-netizen.github.io/product-images/kkit-3zh-0006/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-036/005.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-012</t>
+          <t>avt-4cm-ua-037</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-012/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-012/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-037/001.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-018</t>
+          <t>avt-4cm-ua-038</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-018/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-018/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-038/001.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-023</t>
+          <t>avt-4cm-ua-039</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-023/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-023/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-039/001.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-025</t>
+          <t>avt-4cm-ua-040</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-025/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-025/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-040/005.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-027</t>
+          <t>avt-4cm-ua-041</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-027/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-027/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-041/001.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-028</t>
+          <t>avt-4cm-ua-042</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/003.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-028/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-042/001.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-05</t>
+          <t>avt-4cm-ua-043</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-05/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-05/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-043/001.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>koz-zh3-kit-09</t>
+          <t>avt-4cm-ua-044</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/koz-zh3-kit-09/001.jpg,https://oleks-netizen.github.io/product-images/koz-zh3-kit-09/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/004.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-044/005.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kz-zh30-kit-01</t>
+          <t>avt-4cm-ua-045</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/002.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/004.jpg,https://oleks-netizen.github.io/product-images/kz-zh30-kit-01/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-045/001.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-010</t>
+          <t>avt-4cm-ua-046</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-046/001.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-03</t>
+          <t>avt-4cm-ua-047</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-03/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-047/001.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-05</t>
+          <t>avt-4cm-ua-048</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-05/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-05/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-048/005.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-07</t>
+          <t>avt-4cm-ua-049</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-07/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-07/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-049/001.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-08</t>
+          <t>avt-4cm-ua-050</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/002.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-08/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-050/001.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kz-zh35-kit-09</t>
+          <t>avt-4cm-ua-051</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/001.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/003.jpg,https://oleks-netizen.github.io/product-images/kz-zh35-kit-09/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-051/001.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>new-30zh-k011</t>
+          <t>avt-4cm-ua-052</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k011/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k011/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-052/005.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>new-30zh-k014</t>
+          <t>avt-4cm-ua-053</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k014/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k014/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-053/001.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>new-30zh-k015</t>
+          <t>avt-4cm-ua-054</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k015/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k015/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-054/001.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>new-30zh-k016</t>
+          <t>avt-4cm-ua-055</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k016/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k016/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-055/001.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>new-30zh-k017</t>
+          <t>avt-4cm-ua-056</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k017/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k017/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-056/005.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>new-30zh-k018</t>
+          <t>avt-4cm-ua-057</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k018/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k018/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-057/001.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>new-30zh-k019</t>
+          <t>avt-4cm-ua-058</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k019/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k019/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-058/001.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>new-30zh-k020</t>
+          <t>avt-4cm-ua-059</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k020/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k020/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-059/001.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>new-30zh-k021</t>
+          <t>avt-4cm-ua-060</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k021/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k021/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-060/005.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>new-30zh-k023</t>
+          <t>avt-4cm-ua-061</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/new-30zh-k023/001.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/002.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/003.jpg,https://oleks-netizen.github.io/product-images/new-30zh-k023/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-061/001.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nw-2rez-0010</t>
+          <t>avt-4cm-ua-062</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0010/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-062/001.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>nw-2rez-0017</t>
+          <t>avt-4cm-ua-063</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0017/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0017/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-063/001.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nw-2rez-0018</t>
+          <t>avt-4cm-ua-064</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0018/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0018/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/003.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-064/005.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nw-2rez-0022</t>
+          <t>avt-4cm-ua-065</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0022/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0022/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-065/001.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>nw-2rez-0028</t>
+          <t>avt-4cm-ua-066</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0028/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0028/003.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0028/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-066/001.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nw-2rez-0029</t>
+          <t>avt-4cm-ua-067</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-2rez-0029/001.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0029/002.jpg,https://oleks-netizen.github.io/product-images/nw-2rez-0029/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-067/001.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nw-zh25k-0067</t>
+          <t>avt-4cm-ua-068</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0067/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/001.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/002.jpg,https://oleks-netizen.github.io/product-images/avt-4cm-ua-068/004.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nw-zh25k-0072</t>
+          <t>avt-4cm-ua-069</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0072/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0072/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-069/001.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nw-zh25k-0098</t>
+          <t>avt-4cm-ua-070</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0098/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0098/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-070/001.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nw-zh25k-0123</t>
+          <t>avt-4cm-ua-071</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0123/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0123/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-071/001.jpg</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nw-zh25k-0136</t>
+          <t>det-15k-003</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh25k-0136/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0136/003.jpg,https://oleks-netizen.github.io/product-images/nw-zh25k-0136/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-003/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-003/003.jpg</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>nw-zh3k-0026</t>
+          <t>det-15k-007</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0026/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0026/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-007/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-007/003.jpg</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1876,12 +1876,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nw-zh3k-0039</t>
+          <t>det-15k-008</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0039/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0039/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-008/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-008/003.jpg</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1891,12 +1891,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nw-zh3k-0052</t>
+          <t>det-15k-009</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0052/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0052/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-15k-009/001.jpg,https://oleks-netizen.github.io/product-images/det-15k-009/003.jpg</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1906,12 +1906,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nw-zh3k-0059</t>
+          <t>det-20k-014</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0059/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0059/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-014/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-014/003.jpg</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1921,12 +1921,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nw-zh3k-0062</t>
+          <t>det-20k-015</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0062/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0062/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-015/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-015/003.jpg</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1936,12 +1936,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nw-zh3k-0065</t>
+          <t>det-20k-016</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0065/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0065/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-016/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-016/003.jpg</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1951,12 +1951,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nw-zh3k-0067</t>
+          <t>det-20k-019</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nw-zh3k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nw-zh3k-0067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-019/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-019/003.jpg</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1966,27 +1966,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nwk-30zh-0035</t>
+          <t>det-20k-020</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwk-30zh-0035/001.jpg,https://oleks-netizen.github.io/product-images/nwk-30zh-0035/003.jpg,https://oleks-netizen.github.io/product-images/nwk-30zh-0035/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-020/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-020/003.jpg</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nwzh-15-0023</t>
+          <t>det-20k-021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0023/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0023/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-021/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-021/003.jpg</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -1996,12 +1996,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nwzh-15-0028</t>
+          <t>det-20k-022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0028/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0028/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-20k-022/001.jpg,https://oleks-netizen.github.io/product-images/det-20k-022/003.jpg</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2011,12 +2011,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nwzh-15-0032</t>
+          <t>det-pd-013</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0032/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0032/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-013/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-013/003.jpg</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2026,12 +2026,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nwzh-25-0019</t>
+          <t>det-pd-015</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0019/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0019/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-015/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-015/003.jpg</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2041,27 +2041,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nwzh-25-0020</t>
+          <t>det-pd-020</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0020/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0020/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-020/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-020/004.jpg</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nwzh-25-0021</t>
+          <t>det-pd-022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0021/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0021/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-022/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-022/003.jpg</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2071,12 +2071,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nwzh-25-0025</t>
+          <t>det-pd-023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0025/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0025/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-023/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-023/003.jpg</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2086,12 +2086,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nwzh-25-0027</t>
+          <t>det-pd-024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0027/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0027/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-024/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-024/003.jpg</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2101,12 +2101,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nwzh-25-0029</t>
+          <t>det-pd-027</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0029/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0029/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-027/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-027/003.jpg</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2116,207 +2116,207 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nwzh-25-0031</t>
+          <t>det-pd-028</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0031/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0031/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-028/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-028/003.jpg</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nwzh-25-0033</t>
+          <t>det-pd-029</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0033/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0033/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-029/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-029/004.jpg</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nwzh-25-0034</t>
+          <t>det-pd-030</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0034/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0034/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-030/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-030/004.jpg</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nwzh-25-0035</t>
+          <t>det-pd-031</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0035/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0035/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-031/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-031/004.jpg</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nwzh-25-0036</t>
+          <t>det-pd-032</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0036/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-032/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-032/003.jpg</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nwzh-25-0037</t>
+          <t>det-pd-033</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0037/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0037/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-033/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-033/004.jpg</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nwzh-25-0038</t>
+          <t>det-pd-034</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0038/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0038/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-034/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-034/003.jpg</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>nwzh-25-0044</t>
+          <t>det-pd-035</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0044/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0044/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-035/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-035/003.jpg</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>nwzh-25-0045</t>
+          <t>det-pd-036</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0045/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0045/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-036/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-036/004.jpg</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nwzh-25-0046</t>
+          <t>det-pd-037</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0046/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0046/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-037/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-037/004.jpg</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>nwzh-25-0047</t>
+          <t>det-pd-038</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0047/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0047/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-038/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-038/004.jpg</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>nwzh-25-0048</t>
+          <t>det-pd-039</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0048/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0048/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-039/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-039/004.jpg</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>nwzh-25-0054</t>
+          <t>det-pd-040</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0054/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0054/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-040/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-040/004.jpg</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>nwzh-25-0059</t>
+          <t>det-pd-041</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0059/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0059/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0059/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-041/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-041/004.jpg</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2326,102 +2326,102 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nwzh-25-0060</t>
+          <t>det-pd-042</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0060/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0060/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0060/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-042/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-042/003.jpg</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nwzh-25-0063</t>
+          <t>det-pd-043</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-25-0063/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0063/003.jpg,https://oleks-netizen.github.io/product-images/nwzh-25-0063/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-043/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-043/002.jpg</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>nwzh-30k-0046</t>
+          <t>det-pd-044</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0046/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0046/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-044/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-044/004.jpg</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>nwzh-30k-0051</t>
+          <t>det-pd-045</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0051/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0051/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-045/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-045/004.jpg</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>nwzh-30k-0052</t>
+          <t>det-pd-046</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0052/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0052/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-046/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-046/004.jpg</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>nwzh-30k-0054</t>
+          <t>det-pd-047</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0054/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0054/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-047/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-047/004.jpg</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>nwzh-30k-0067</t>
+          <t>det-pd-048</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-0067/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0067/002.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-0067/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-048/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-048/004.jpg</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2431,27 +2431,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>nwzh-30k-76</t>
+          <t>det-pd-049</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/nwzh-30k-76/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-30k-76/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-049/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-049/004.jpg</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rez-new-25kit-001</t>
+          <t>det-pd-050</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-001/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-001/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-050/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-050/003.jpg</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2461,117 +2461,117 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rez-new-25kit-003</t>
+          <t>det-pd-051</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-003/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-051/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-051/004.jpg</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rez-new-25kit-005</t>
+          <t>det-pd-052</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-005/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-005/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-052/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-052/004.jpg</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rez-new-25kit-006</t>
+          <t>det-pd-053</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-006/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-053/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-053/004.jpg</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rez-new-25kit-010</t>
+          <t>det-pd-054</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-010/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-054/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-054/004.jpg</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rez-new-25kit-011</t>
+          <t>det-pd-055</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-011/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-011/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-055/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-055/004.jpg</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rez-new-25kit-012</t>
+          <t>det-pd-056</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-012/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-012/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-056/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-056/003.jpg</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rez-new-25kit-013</t>
+          <t>det-pd-057</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-013/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-013/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-057/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-057/004.jpg</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rez-new-25kit-017</t>
+          <t>det-pd-058</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-017/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-017/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-017/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-058/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/003.jpg,https://oleks-netizen.github.io/product-images/det-pd-058/004.jpg</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2581,12 +2581,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rez-new-25kit-018</t>
+          <t>det-pd-059</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-018/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-018/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-018/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/det-pd-059/001.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/002.jpg,https://oleks-netizen.github.io/product-images/det-pd-059/003.jpg</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2596,42 +2596,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rez-new-25kit-019</t>
+          <t>dts-25rez-001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-019/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-019/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dts-25rez-001/001.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/002.jpg,https://oleks-netizen.github.io/product-images/dts-25rez-001/004.jpg</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rez-new-25kit-020</t>
+          <t>dtsk-18mm-kz-006</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-020/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-020/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-006/004.jpg</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rez-new-25kit-021</t>
+          <t>dtsk-18mm-kz-007</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-021/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-021/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-021/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-007/004.jpg</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2641,12 +2641,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rez-new-25kit-022</t>
+          <t>dtsk-18mm-kz-008</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-022/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-022/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-022/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-008/004.jpg</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2656,12 +2656,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rez-new-25kit-023</t>
+          <t>dtsk-18mm-kz-009</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-023/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-023/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-023/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-009/004.jpg</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2671,12 +2671,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rez-new-25kit-024</t>
+          <t>dtsk-18mm-kz-010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-024/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-024/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-024/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-010/004.jpg</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2686,12 +2686,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rez-new-25kit-026</t>
+          <t>dtsk-18mm-kz-011</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-026/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-026/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-026/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-011/004.jpg</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2701,12 +2701,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rez-new-25kit-027</t>
+          <t>dtsk-18mm-kz-012</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-027/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-027/002.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-027/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-012/004.jpg</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2716,147 +2716,147 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rez-new-25kit-028</t>
+          <t>dtsk-18mm-kz-013</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/rez-new-25kit-028/001.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/003.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/004.jpg,https://oleks-netizen.github.io/product-images/rez-new-25kit-028/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-18mm-kz-013/004.jpg</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>uzk-k25zh-kit005</t>
+          <t>dtsk-28mm-kz-001</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/003.jpg,https://oleks-netizen.github.io/product-images/uzk-k25zh-kit005/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-001/005.jpg</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit016</t>
+          <t>dtsk-28mm-kz-002</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit016/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit016/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-002/005.jpg</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit062</t>
+          <t>dtsk-28mm-kz-003</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit062/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit062/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-003/005.jpg</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit063</t>
+          <t>dtsk-28mm-kz-004</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit063/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit063/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-004/005.jpg</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit064</t>
+          <t>dtsk-28mm-kz-005</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit064/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit064/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-005/005.jpg</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit065</t>
+          <t>dtsk-28mm-kz-006</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit065/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit065/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-006/005.jpg</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>uzk-k30zh-kit066</t>
+          <t>dtsk-28mm-kz-007</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-kit066/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-kit066/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-007/004.jpg</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>uzk-k30zh-ua-011</t>
+          <t>dtsk-28mm-kz-008</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/uzk-k30zh-ua-011/001.jpg,https://oleks-netizen.github.io/product-images/uzk-k30zh-ua-011/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-008/004.jpg</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>zhkz-18cm-041</t>
+          <t>dtsk-28mm-kz-009</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-18cm-041/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-041/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-041/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-009/004.jpg</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2866,147 +2866,147 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>zhkz-18cm-042</t>
+          <t>dtsk-28mm-kz-014</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-18cm-042/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-042/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-18cm-042/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-014/005.jpg</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>zhkz-1cm-001</t>
+          <t>dtsk-28mm-kz-015</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-001/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-001/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-015/005.jpg</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>zhkz-1cm-0014</t>
+          <t>dtsk-28mm-kz-017</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-0014/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-0014/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-017/005.jpg</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>zhkz-1cm-0015</t>
+          <t>dtsk-28mm-kz-018</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-0015/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-0015/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-018/004.jpg</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>zhkz-1cm-002</t>
+          <t>dtsk-28mm-kz-019</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-002/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-002/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-019/005.jpg</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>zhkz-1cm-003</t>
+          <t>dtsk-28mm-kz-020</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-003/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-003/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-020/005.jpg</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>zhkz-1cm-005</t>
+          <t>dtsk-28mm-kz-021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-005/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-005/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-021/005.jpg</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>zhkz-1cm-006</t>
+          <t>dtsk-28mm-kz-022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-006/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/004.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-022/005.jpg</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>zhkz-1cm-007</t>
+          <t>dtsk-28mm-kz-037</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-1cm-007/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-1cm-007/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kz-037/004.jpg</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>zhkz-23cm-031</t>
+          <t>dtsk-28mm-kоzh-023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-031/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-031/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-031/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-023/004.jpg</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3016,27 +3016,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>zhkz-23cm-032</t>
+          <t>dtsk-28mm-kоzh-024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-032/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-032/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-024/003.jpg</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>zhkz-23cm-043</t>
+          <t>dtsk-28mm-kоzh-025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-043/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-043/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-025/003.jpg</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3046,27 +3046,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>zhkz-23cm-044</t>
+          <t>dtsk-28mm-kоzh-026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-044/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-044/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-044/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-026/003.jpg</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>zhkz-23cm-045</t>
+          <t>dtsk-28mm-kоzh-027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-045/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-045/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-045/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-027/004.jpg</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3076,12 +3076,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>zhkz-23cm-046</t>
+          <t>dtsk-28mm-kоzh-028</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-23cm-046/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-23cm-046/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-028/003.jpg</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3091,42 +3091,42 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>zhkz-25cm-001</t>
+          <t>dtsk-28mm-kоzh-029</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-001/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-029/003.jpg</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>zhkz-25cm-002</t>
+          <t>dtsk-28mm-kоzh-030</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-002/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-002/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-030/003.jpg</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>zhkz-25cm-003</t>
+          <t>dtsk-28mm-kоzh-031</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-003/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-003/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-003/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-031/004.jpg</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3136,27 +3136,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>zhkz-25cm-004</t>
+          <t>dtsk-28mm-kоzh-032</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-004/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-004/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-032/004.jpg</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>zhkz-25cm-005</t>
+          <t>dtsk-28mm-kоzh-033</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-005/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-005/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-005/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-033/004.jpg</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3166,42 +3166,42 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>zhkz-25cm-006</t>
+          <t>dtsk-28mm-kоzh-034</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-006/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-034/004.jpg</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>zhkz-25cm-008</t>
+          <t>dtsk-28mm-kоzh-035</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-25cm-008/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-25cm-008/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/003.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-035/004.jpg</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>zhkz-28cm-033</t>
+          <t>dtsk-28mm-kоzh-036</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-033/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-033/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-033/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/001.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/002.jpg,https://oleks-netizen.github.io/product-images/dtsk-28mm-kоzh-036/004.jpg</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3211,42 +3211,42 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>zhkz-28cm-034</t>
+          <t>ekm-nwksh-001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-034/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-034/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-001/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-001/005.jpg</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>zhkz-28cm-047</t>
+          <t>ekm-nwksh-002</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-047/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-047/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-002/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-002/003.jpg</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>zhkz-28cm-048</t>
+          <t>ekm-nwksh-003</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-048/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-048/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-048/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-003/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/002.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-003/003.jpg</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3256,12 +3256,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>zhkz-28cm-049</t>
+          <t>ekm-nwksh-004</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-049/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-049/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-004/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-004/002.jpg</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3271,27 +3271,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>zhkz-28cm-050</t>
+          <t>ekm-nwksh-005</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-050/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-050/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ekm-nwksh-005/001.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/003.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/004.jpg,https://oleks-netizen.github.io/product-images/ekm-nwksh-005/005.jpg</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>zhkz-28cm-051</t>
+          <t>m-kozh33-wtrua-0025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-051/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-051/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-051/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0025/004.jpg</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3301,12 +3301,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>zhkz-28cm-052</t>
+          <t>m-kozh33-wtrua-0026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-28cm-052/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-052/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-28cm-052/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0026/004.jpg</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3316,12 +3316,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>zhkz-30cm-009</t>
+          <t>m-kozh33-wtrua-0027</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-009/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-009/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-009/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0027/004.jpg</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3331,12 +3331,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>zhkz-30cm-010</t>
+          <t>m-kozh33-wtrua-0028</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-010/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-010/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-30cm-010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0028/004.jpg</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3346,27 +3346,27 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>zhkz-30cm-012</t>
+          <t>m-kozh33-wtrua-0029</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-30cm-012/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0029/004.jpg</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>zhkz-32cm-053</t>
+          <t>m-kozh33-wtrua-0030</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-32cm-053/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-32cm-053/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-32cm-053/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0030/004.jpg</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3376,27 +3376,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>zhkz-33cm-025</t>
+          <t>m-kozh33-wtrua-0031</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-025/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-025/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0031/004.jpg</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>zhkz-33cm-026</t>
+          <t>m-kozh33-wtrua-0032</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-026/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-026/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-026/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0032/004.jpg</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3406,57 +3406,57 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>zhkz-33cm-027</t>
+          <t>m-kozh33-wtrua-0033</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-027/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/005.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/006.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-027/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0033/004.jpg</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>zhkz-33cm-028</t>
+          <t>m-kozh33-wtrua-0034</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-028/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-028/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-028/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0034/005.jpg</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>zhkz-33cm-029</t>
+          <t>m-kozh33-wtrua-0035</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-029/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-029/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh33-wtrua-0035/005.jpg</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>zhkz-33cm-030</t>
+          <t>m-kozh38-wtrua-001</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-33cm-030/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-030/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-33cm-030/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-001/004.jpg</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3466,42 +3466,42 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>zhkz-38cm-035</t>
+          <t>m-kozh38-wtrua-0010</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-035/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-035/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0010/004.jpg</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>zhkz-38cm-036</t>
+          <t>m-kozh38-wtrua-0012</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-036/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/004.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-036/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0012/004.jpg</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>zhkz-38cm-037</t>
+          <t>m-kozh38-wtrua-0013</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-037/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-037/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0013/004.jpg</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3511,42 +3511,42 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>zhkz-38cm-038</t>
+          <t>m-kozh38-wtrua-0014</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-038/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-038/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-038/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0014/005.jpg</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>zhkz-38cm-039</t>
+          <t>m-kozh38-wtrua-0015</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-039/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-039/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-039/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0015/004.jpg</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>zhkz-38cm-040</t>
+          <t>m-kozh38-wtrua-0016</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-040/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-040/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-040/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0016/004.jpg</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3556,42 +3556,42 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>zhkz-38cm-054</t>
+          <t>m-kozh38-wtrua-002</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-054/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-054/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-054/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-002/005.jpg</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>zhkz-38cm-055</t>
+          <t>m-kozh38-wtrua-0036</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-055/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-055/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-055/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0036/005.jpg</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>zhkz-38cm-056</t>
+          <t>m-kozh38-wtrua-0037</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-056/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-056/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-056/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0037/004.jpg</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3601,42 +3601,42 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>zhkz-38cm-057</t>
+          <t>m-kozh38-wtrua-0038</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-057/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-057/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-057/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0038/005.jpg</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>zhkz-38cm-058</t>
+          <t>m-kozh38-wtrua-0039</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-058/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-058/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-058/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0039/005.jpg</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>zhkz-38cm-059</t>
+          <t>m-kozh38-wtrua-004</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-059/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-059/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-059/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-004/004.jpg</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3646,72 +3646,72 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>zhkz-38cm-060</t>
+          <t>m-kozh38-wtrua-0040</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-060/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-060/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-060/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0040/005.jpg</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>zhkz-38cm-061</t>
+          <t>m-kozh38-wtrua-0041</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-061/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-061/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-061/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0041/005.jpg</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>zhkz-38cm-062</t>
+          <t>m-kozh38-wtrua-0042</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-062/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-062/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-062/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0042/005.jpg</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>zhkz-38cm-063</t>
+          <t>m-kozh38-wtrua-0043</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-063/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-063/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-063/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0043/005.jpg</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>zhkz-38cm-064</t>
+          <t>m-kozh38-wtrua-0044</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-064/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-064/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-064/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0044/004.jpg</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3721,12 +3721,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>zhkz-38cm-065</t>
+          <t>m-kozh38-wtrua-0045</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-065/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-065/002.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-065/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0045/004.jpg</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3736,12 +3736,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>zhkz-38cm-066</t>
+          <t>m-kozh38-wtrua-0046</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-066/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-066/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-066/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0046/004.jpg</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3751,57 +3751,57 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>zhkz-38cm-067</t>
+          <t>m-kozh38-wtrua-0047</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-38cm-067/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-067/003.jpg,https://oleks-netizen.github.io/product-images/zhkz-38cm-067/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0047/005.jpg</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>zhkz-42cm-068</t>
+          <t>m-kozh38-wtrua-0048</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-42cm-068/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-42cm-068/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0048/004.jpg</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>zhkz-42cm-069</t>
+          <t>m-kozh38-wtrua-0049</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhkz-42cm-069/001.jpg,https://oleks-netizen.github.io/product-images/zhkz-42cm-069/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0049/004.jpg</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-031</t>
+          <t>m-kozh38-wtrua-0050</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-031/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0050/004.jpg</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3811,12 +3811,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-032</t>
+          <t>m-kozh38-wtrua-0051</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-032/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0051/004.jpg</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3826,12 +3826,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-033</t>
+          <t>m-kozh38-wtrua-0052</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-033/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0052/004.jpg</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3841,72 +3841,72 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-034</t>
+          <t>m-kozh38-wtrua-0054</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-034/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0054/005.jpg</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-035</t>
+          <t>m-kozh38-wtrua-0055</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-035/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0055/007.jpg</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-036</t>
+          <t>m-kozh38-wtrua-0057</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-036/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0057/006.jpg</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-037</t>
+          <t>m-kozh38-wtrua-0058</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-037/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/006.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0058/007.jpg</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-038</t>
+          <t>m-kozh38-wtrua-0059</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-038/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0059/004.jpg</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3916,57 +3916,57 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-039</t>
+          <t>m-kozh38-wtrua-006</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-039/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-006/005.jpg</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-040</t>
+          <t>m-kozh38-wtrua-0060</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-040/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0060/005.jpg</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-041</t>
+          <t>m-kozh38-wtrua-0061</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-041/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0061/005.jpg</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-042</t>
+          <t>m-kozh38-wtrua-0063</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-042/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-0063/004.jpg</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3976,72 +3976,72 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-043</t>
+          <t>m-kozh38-wtrua-007</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-043/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-007/005.jpg</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-044</t>
+          <t>m-kozh38-wtrua-008</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-044/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-008/005.jpg</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-045</t>
+          <t>m-kozh38-wtrua-009</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-045/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh38-wtrua-009/003.jpg</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-059</t>
+          <t>m-kozh43-wtrua-0021</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-059/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0021/006.jpg</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-060</t>
+          <t>m-kozh43-wtrua-0022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-060/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0022/004.jpg</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4051,12 +4051,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-061</t>
+          <t>m-kozh43-wtrua-0023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-061/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0023/004.jpg</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4066,102 +4066,102 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-062</t>
+          <t>m-kozh43-wtrua-0024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-062/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/004.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0024/005.jpg</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-063</t>
+          <t>m-kozh43-wtrua-0064</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-063/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0064/005.jpg</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-064</t>
+          <t>m-kozh43-wtrua-0065</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-064/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0065/005.jpg</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-065</t>
+          <t>m-kozh43-wtrua-0066</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-065/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/001.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/002.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/003.jpg,https://oleks-netizen.github.io/product-images/m-kozh43-wtrua-0066/005.jpg</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-066</t>
+          <t>m-zmsh38-wtrua-0001</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-066/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/001.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/002.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/003.jpg,https://oleks-netizen.github.io/product-images/m-zmsh38-wtrua-0001/005.jpg</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-067</t>
+          <t>mk-card-001</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-067/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-card-001/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/003.jpg,https://oleks-netizen.github.io/product-images/mk-card-001/004.jpg</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-068</t>
+          <t>mk-card-003</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-068/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-card-003/001.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/002.jpg,https://oleks-netizen.github.io/product-images/mk-card-003/003.jpg</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4171,207 +4171,207 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>zhn-kz-kit13-069</t>
+          <t>nw-k-F6068</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit13-069/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-F6068/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-F6068/005.jpg</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-01</t>
+          <t>nwzh-15-0006</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-01/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0006/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0006/003.jpg</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-010</t>
+          <t>nwzh-15-0009</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0009/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0009/003.jpg</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-011</t>
+          <t>nwzh-15-0019</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-011/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0019/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0019/003.jpg</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-012</t>
+          <t>nwzh-15-0020</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-012/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0020/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0020/002.jpg</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-013</t>
+          <t>nwzh-15-0026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-013/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0026/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0026/003.jpg</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-014</t>
+          <t>nwzh-15-0027</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-014/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0027/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0027/003.jpg</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-015</t>
+          <t>nwzh-15-0033</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-015/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwzh-15-0033/001.jpg,https://oleks-netizen.github.io/product-images/nwzh-15-0033/003.jpg</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-02</t>
+          <t>pdr-pdt-004</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-02/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-004/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-004/005.jpg</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-03</t>
+          <t>pdr-pdt-005</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-03/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-005/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-005/005.jpg</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-04</t>
+          <t>pdr-pdt-007</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-04/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-007/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/003.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-007/005.jpg</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-046</t>
+          <t>pdr-pdt-008</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-046/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-008/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-008/005.jpg</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-047</t>
+          <t>pdr-pdt-009</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-047/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/pdr-pdt-009/001.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/002.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/004.jpg,https://oleks-netizen.github.io/product-images/pdr-pdt-009/005.jpg</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-048</t>
+          <t>rmnd-30ua-002</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-048/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-002/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-002/004.jpg</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4381,12 +4381,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-049</t>
+          <t>rmnd-30ua-016</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-049/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-016/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-016/004.jpg</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4396,12 +4396,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-05</t>
+          <t>rmnd-30ua-019</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-05/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-019/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-019/004.jpg</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4411,12 +4411,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-050</t>
+          <t>rmnd-30ua-020</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-050/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/rmnd-30ua-020/001.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/003.jpg,https://oleks-netizen.github.io/product-images/rmnd-30ua-020/004.jpg</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4426,12 +4426,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-06</t>
+          <t>wtro-38ua-001</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-06/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-001/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-001/004.jpg</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4441,42 +4441,42 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-07</t>
+          <t>wtro-38ua-002</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-07/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-002/001.jpg</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-08</t>
+          <t>wtro-38ua-003</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-08/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-003/001.jpg</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>zhn-kz-kit23-09</t>
+          <t>wtro-38ua-004</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit23-09/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-004/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-004/004.jpg</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4486,132 +4486,132 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-016</t>
+          <t>wtro-38ua-005</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-016/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-005/001.jpg</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-017</t>
+          <t>wtro-38ua-006</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-017/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-006/001.jpg</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-018</t>
+          <t>wtro-38ua-007</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-018/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-007/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-007/003.jpg</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-019</t>
+          <t>wtro-38ua-008</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-019/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-008/001.jpg</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-020</t>
+          <t>wtro-38ua-009</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-020/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-009/001.jpg</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-021</t>
+          <t>wtro-38ua-010</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-021/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-010/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-010/003.jpg</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-022</t>
+          <t>wtro-38ua-011</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-022/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-011/001.jpg</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-023</t>
+          <t>wtro-38ua-012</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-023/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-012/001.jpg</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-024</t>
+          <t>wtro-38ua-013</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-024/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-013/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-013/004.jpg</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4621,42 +4621,42 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-025</t>
+          <t>wtro-38ua-014</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-025/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-014/001.jpg</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-026</t>
+          <t>wtro-38ua-015</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-026/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-015/001.jpg</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-027</t>
+          <t>wtro-38ua-016</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-027/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-016/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-016/004.jpg</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4666,42 +4666,42 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-028</t>
+          <t>wtro-38ua-017</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-028/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-017/001.jpg</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-029</t>
+          <t>wtro-38ua-018</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-029/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-018/001.jpg</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-030</t>
+          <t>wtro-38ua-019</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-030/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-019/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/002.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-019/004.jpg</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4711,42 +4711,42 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-051</t>
+          <t>wtro-38ua-020</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-051/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-020/001.jpg</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-052</t>
+          <t>wtro-38ua-021</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-052/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-021/001.jpg</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-053</t>
+          <t>wtro-38ua-022</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-053/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-022/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-022/004.jpg</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4756,42 +4756,42 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-054</t>
+          <t>wtro-38ua-023</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-054/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-023/001.jpg</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-055</t>
+          <t>wtro-38ua-024</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-055/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-024/001.jpg</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-056</t>
+          <t>wtro-38ua-025</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-056/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-025/001.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/003.jpg,https://oleks-netizen.github.io/product-images/wtro-38ua-025/004.jpg</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4801,31 +4801,46 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-057</t>
+          <t>wtro-38ua-026</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/002.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-057/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-026/001.jpg</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>zhn-kz-kit33-058</t>
+          <t>wtro-38ua-027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/001.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/003.jpg,https://oleks-netizen.github.io/product-images/zhn-kz-kit33-058/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/wtro-38ua-027/001.jpg</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>avt-4cm-ua-026</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/avt-4cm-ua-026/002.jpg</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,87 +436,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>WELL-10210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11614/001.jpg,https://oleks-netizen.github.io/product-images/11614/002.jpg,https://oleks-netizen.github.io/product-images/11614/003.jpg,https://oleks-netizen.github.io/product-images/11614/005.jpg,https://oleks-netizen.github.io/product-images/11614/006.jpg,https://oleks-netizen.github.io/product-images/11614/007.jpg,https://oleks-netizen.github.io/product-images/11614/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10210/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10210/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10210/003.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>WELL-10300</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11615/001.jpg,https://oleks-netizen.github.io/product-images/11615/002.jpg,https://oleks-netizen.github.io/product-images/11615/004.jpg,https://oleks-netizen.github.io/product-images/11615/005.jpg,https://oleks-netizen.github.io/product-images/11615/006.jpg,https://oleks-netizen.github.io/product-images/11615/007.jpg,https://oleks-netizen.github.io/product-images/11615/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10300/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10300/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10300/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10300/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10300/005.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>WELL-10301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11616/001.jpg,https://oleks-netizen.github.io/product-images/11616/002.jpg,https://oleks-netizen.github.io/product-images/11616/003.jpg,https://oleks-netizen.github.io/product-images/11616/004.jpg,https://oleks-netizen.github.io/product-images/11616/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10301/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10301/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10301/003.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>WELL-10304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/55000/001.jpg,https://oleks-netizen.github.io/product-images/55000/002.jpg,https://oleks-netizen.github.io/product-images/55000/003.jpg,https://oleks-netizen.github.io/product-images/55000/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10304/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10304/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10304/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10304/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10304/005.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>80460410</t>
+          <t>WELL-10305</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460410/001.jpg,https://oleks-netizen.github.io/product-images/80460410/002.jpg,https://oleks-netizen.github.io/product-images/80460410/003.jpg,https://oleks-netizen.github.io/product-images/80460410/004.jpg,https://oleks-netizen.github.io/product-images/80460410/005.jpg,https://oleks-netizen.github.io/product-images/80460410/006.jpg,https://oleks-netizen.github.io/product-images/80460410/007.jpg,https://oleks-netizen.github.io/product-images/80460410/008.jpg,https://oleks-netizen.github.io/product-images/80460410/010.jpg,https://oleks-netizen.github.io/product-images/80460410/011.jpg,https://oleks-netizen.github.io/product-images/80460410/012.jpg,https://oleks-netizen.github.io/product-images/80460410/013.jpg,https://oleks-netizen.github.io/product-images/80460410/014.jpg,https://oleks-netizen.github.io/product-images/80460410/015.jpg,https://oleks-netizen.github.io/product-images/80460410/016.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10305/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10305/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10305/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10305/004.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BN-BK1-red</t>
+          <t>WELL-10309</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK1-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK1-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK1-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-BK1-red/005.jpg,https://oleks-netizen.github.io/product-images/BN-BK1-red/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10309/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10309/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10309/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10309/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10309/005.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,72 +526,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BN-BK10-malachite</t>
+          <t>WELL-10400</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK10-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK10-malachite/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10400/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10400/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10400/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10400/004.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BN-BK11-g</t>
+          <t>WELL-10404</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK11-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK11-g/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10404/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10404/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10404/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10404/005.jpg,https://oleks-netizen.github.io/product-images/WELL-10404/006.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BN-BK12-o</t>
+          <t>WELL-10405</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK12-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK12-o/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10405/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10405/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10405/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10405/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10405/005.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BN-BK13-beige</t>
+          <t>WELL-10409</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK13-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK13-beige/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10409/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10409/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10409/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10409/005.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BN-BK15-choko</t>
+          <t>WELL-10410</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-choko/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10410/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10410/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10410/003.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,12 +601,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BN-BK15-g</t>
+          <t>WELL-10411</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-g/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10411/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10411/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10411/004.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,57 +616,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BN-BK15-k</t>
+          <t>WELL-10503</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-k/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10503/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10503/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10503/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10503/004.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BN-BK15-light-beige</t>
+          <t>WELL-10505</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-light-beige/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10505/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10505/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10505/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10505/005.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BN-BK15-malachite</t>
+          <t>WELL-10524</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-malachite/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10524/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10524/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10524/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10524/004.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BN-BK15-red</t>
+          <t>WELL-10528</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK15-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-BK15-red/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10528/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10528/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10528/003.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,132 +676,132 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BN-BK16-choko</t>
+          <t>WELL-10529</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK16-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK16-choko/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10529/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10529/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10529/003.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BN-BK17-g</t>
+          <t>WELL-10601</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK17-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK17-g/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10601/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10601/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10601/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10601/004.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BN-BK18-g</t>
+          <t>WELL-10604</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK18-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK18-g/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10604/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10604/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10604/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10604/004.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BN-BK2</t>
+          <t>WELL-10701</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/003.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/005.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/006.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/007.jpg,https://oleks-netizen.github.io/product-images/BN-BK2/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10701/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10701/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10701/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10701/004.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BN-BK2-3-red</t>
+          <t>WELL-10703</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2-3-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-3-red/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10703/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10703/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10703/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10703/005.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BN-BK2-4-light</t>
+          <t>WELL-10704</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2-4-light/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-4-light/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10704/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10704/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10704/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10704/005.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BN-BK2-4-pink-peach</t>
+          <t>WELL-10705</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2-4-pink-peach/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-4-pink-peach/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10705/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10705/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10705/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10705/005.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BN-BK2-4-shadow</t>
+          <t>WELL-10724</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2-4-shadow/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-4-shadow/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10724/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10724/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10724/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10724/005.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BN-BK2-5-tiffany</t>
+          <t>WELL-10728</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK2-5-tiffany/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-5-tiffany/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK2-5-tiffany/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10728/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10728/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10728/003.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -811,102 +811,102 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BN-BK3</t>
+          <t>WELL-10729</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK3/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/002.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/004.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/005.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/006.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/007.jpg,https://oleks-netizen.github.io/product-images/BN-BK3/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10729/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10729/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10729/004.jpg,https://oleks-netizen.github.io/product-images/WELL-10729/005.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BN-BK4-blue-ylw</t>
+          <t>WELL-10801</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-blue-ylw/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-blue-ylw/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10801/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10801/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10801/003.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BN-BK4-choko</t>
+          <t>WELL-10804</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-choko/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10804/003.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BN-BK4-k</t>
+          <t>WELL-10805</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-k/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10805/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10805/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10805/003.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BN-BK4-malachite</t>
+          <t>WELL-10807</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-malachite/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10807/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10807/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10807/003.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BN-BK4-navy-blue</t>
+          <t>WELL-10822</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-navy-blue/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10822/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10822/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10822/003.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BN-BK4-vin</t>
+          <t>WELL-10824</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK4-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK4-vin/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10824/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10824/003.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -916,132 +916,132 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BN-BK5-choko</t>
+          <t>WELL-10825</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK5-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK5-choko/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10825/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10825/002.jpg,https://oleks-netizen.github.io/product-images/WELL-10825/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10825/004.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BN-BK6-navy-blue</t>
+          <t>WELL-10829</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK6-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK6-navy-blue/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-10829/001.jpg,https://oleks-netizen.github.io/product-images/WELL-10829/003.jpg,https://oleks-netizen.github.io/product-images/WELL-10829/004.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BN-BK7-iz</t>
+          <t>WELL-11000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK7-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK7-iz/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11000/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11000/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11000/003.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BN-BK8-k</t>
+          <t>WELL-11002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK8-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK8-k/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11002/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11002/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11002/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11002/005.jpg,https://oleks-netizen.github.io/product-images/WELL-11002/006.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BN-BK9-coral</t>
+          <t>WELL-11004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BK9-coral/001.jpg,https://oleks-netizen.github.io/product-images/BN-BK9-coral/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11004/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11004/004.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BN-GC-32-1-g</t>
+          <t>WELL-11006</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-1-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-1-g/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11006/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11006/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11006/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11006/005.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BN-GC-32-1-vin</t>
+          <t>WELL-11009</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-1-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-1-vin/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11009/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11009/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11009/003.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BN-GC-32-choko</t>
+          <t>WELL-11019</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-choko/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11019/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11019/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11019/003.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BN-GC-32-g</t>
+          <t>WELL-11100</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-g/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11100/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11100/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11100/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11100/005.jpg,https://oleks-netizen.github.io/product-images/WELL-11100/006.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1051,147 +1051,147 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BN-GC-32-k</t>
+          <t>WELL-11102</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-k/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11102/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11102/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11102/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11102/005.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BN-GC-32-malachite</t>
+          <t>WELL-11104</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-malachite/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-malachite/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-malachite/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-malachite/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-malachite/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11104/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11104/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11104/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11104/005.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BN-GC-32-navy-blue</t>
+          <t>WELL-11105</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-navy-blue/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11105/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11105/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11105/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11105/005.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BN-GC-32-vin</t>
+          <t>WELL-11109</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-GC-32-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-vin/003.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-GC-32-vin/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11109/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11109/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11109/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11109/005.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BN-SB-8-k</t>
+          <t>WELL-11119</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-k/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11119/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11119/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11119/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11119/005.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BN-SB-8-navy-blue</t>
+          <t>WELL-11204</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-navy-blue/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11204/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11204/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11204/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11204/005.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BN-SB-8-nn</t>
+          <t>WELL-11205</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-nn/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-nn/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-nn/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11205/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11205/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11205/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11205/005.jpg,https://oleks-netizen.github.io/product-images/WELL-11205/006.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BN-SB-8-o</t>
+          <t>WELL-11303</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-o/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-o/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-o/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11303/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11303/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11303/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11303/005.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BN-SB-8-red</t>
+          <t>WELL-11304</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-red/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11304/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11304/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11304/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11304/005.jpg,https://oleks-netizen.github.io/product-images/WELL-11304/006.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BN-SB-8-vin</t>
+          <t>WELL-11404</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-8-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-8-vin/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11404/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11404/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11404/003.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1201,57 +1201,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-choko</t>
+          <t>WELL-11406</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-choko/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11406/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11406/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11406/004.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-g</t>
+          <t>WELL-11409</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-g/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11409/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11409/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11409/003.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-iz</t>
+          <t>WELL-11419</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-iz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11419/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11419/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11419/003.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-k</t>
+          <t>WELL-11501</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-k/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11501/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11501/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11501/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11501/004.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1261,27 +1261,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-navy-blue</t>
+          <t>WELL-11502</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-navy-blue/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11502/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11502/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11502/004.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BN-SB-9-2-A4-vin-kr</t>
+          <t>WELL-11503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-2-A4-vin-kr/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11503/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11503/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11503/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11503/005.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1291,57 +1291,57 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-choko</t>
+          <t>WELL-11504</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-choko/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11504/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11504/002.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-g</t>
+          <t>WELL-11601</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-g/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11601/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11601/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11601/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11601/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11601/005.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-iz</t>
+          <t>WELL-11608</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-iz/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11608/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11608/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11608/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11608/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11608/005.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-k</t>
+          <t>WELL-11609</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-k/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11609/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11609/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11609/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11609/004.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1351,27 +1351,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-navy-blue</t>
+          <t>WELL-11701</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-navy-blue/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11701/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11701/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11701/003.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BN-SB-9-3-A5-vin-kr</t>
+          <t>WELL-11702</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-vin-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-vin-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-vin-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-3-A5-vin-kr/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11702/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11702/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11702/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11702/004.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1381,496 +1381,3241 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-choko</t>
+          <t>WELL-11704</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-choko/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11704/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11704/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11704/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11704/004.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-g</t>
+          <t>WELL-11709</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-g/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11709/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11709/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11709/003.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-k</t>
+          <t>WELL-11800</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-k/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11800/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11800/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11800/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11800/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11800/005.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-light-beige</t>
+          <t>WELL-11804</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-light-beige/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11804/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11804/004.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-navy-blue</t>
+          <t>WELL-11902</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-navy-blue/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11902/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11902/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11902/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11902/004.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BN-SB-9-4-red</t>
+          <t>WELL-11904</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/005.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/006.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/007.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-4-red/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11904/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11904/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11904/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11904/004.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BN-SB-9-soft-k-kr</t>
+          <t>WELL-11905</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-SB-9-soft-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-soft-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-soft-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-soft-k-kr/004.jpg,https://oleks-netizen.github.io/product-images/BN-SB-9-soft-k-kr/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11905/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11905/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11905/003.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S32008-1</t>
+          <t>WELL-11909</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32008-1/001.jpg,https://oleks-netizen.github.io/product-images/S32008-1/002.jpg,https://oleks-netizen.github.io/product-images/S32008-1/003.jpg,https://oleks-netizen.github.io/product-images/S32008-1/004.jpg,https://oleks-netizen.github.io/product-images/S32008-1/005.jpg,https://oleks-netizen.github.io/product-images/S32008-1/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11909/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11909/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11909/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11909/004.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S32008-2</t>
+          <t>WELL-12000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32008-2/001.jpg,https://oleks-netizen.github.io/product-images/S32008-2/002.jpg,https://oleks-netizen.github.io/product-images/S32008-2/003.jpg,https://oleks-netizen.github.io/product-images/S32008-2/004.jpg,https://oleks-netizen.github.io/product-images/S32008-2/005.jpg,https://oleks-netizen.github.io/product-images/S32008-2/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12000/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12000/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12000/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12000/004.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S32008-4</t>
+          <t>WELL-12004</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32008-4/001.jpg,https://oleks-netizen.github.io/product-images/S32008-4/002.jpg,https://oleks-netizen.github.io/product-images/S32008-4/003.jpg,https://oleks-netizen.github.io/product-images/S32008-4/004.jpg,https://oleks-netizen.github.io/product-images/S32008-4/005.jpg,https://oleks-netizen.github.io/product-images/S32008-4/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12004/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12004/004.jpg,https://oleks-netizen.github.io/product-images/WELL-12004/005.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S32008-5</t>
+          <t>WELL-12005</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32008-5/001.jpg,https://oleks-netizen.github.io/product-images/S32008-5/002.jpg,https://oleks-netizen.github.io/product-images/S32008-5/003.jpg,https://oleks-netizen.github.io/product-images/S32008-5/004.jpg,https://oleks-netizen.github.io/product-images/S32008-5/005.jpg,https://oleks-netizen.github.io/product-images/S32008-5/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12005/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12005/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12005/003.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S32008-6</t>
+          <t>WELL-12009</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32008-6/001.jpg,https://oleks-netizen.github.io/product-images/S32008-6/002.jpg,https://oleks-netizen.github.io/product-images/S32008-6/004.jpg,https://oleks-netizen.github.io/product-images/S32008-6/005.jpg,https://oleks-netizen.github.io/product-images/S32008-6/006.jpg,https://oleks-netizen.github.io/product-images/S32008-6/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12009/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12009/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12009/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12009/004.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S32101-1</t>
+          <t>WELL-12124</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32101-1/001.jpg,https://oleks-netizen.github.io/product-images/S32101-1/002.jpg,https://oleks-netizen.github.io/product-images/S32101-1/004.jpg,https://oleks-netizen.github.io/product-images/S32101-1/005.jpg,https://oleks-netizen.github.io/product-images/S32101-1/006.jpg,https://oleks-netizen.github.io/product-images/S32101-1/007.jpg,https://oleks-netizen.github.io/product-images/S32101-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12124/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12124/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12124/003.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S32101-5</t>
+          <t>WELL-12128</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32101-5/001.jpg,https://oleks-netizen.github.io/product-images/S32101-5/002.jpg,https://oleks-netizen.github.io/product-images/S32101-5/003.jpg,https://oleks-netizen.github.io/product-images/S32101-5/004.jpg,https://oleks-netizen.github.io/product-images/S32101-5/005.jpg,https://oleks-netizen.github.io/product-images/S32101-5/006.jpg,https://oleks-netizen.github.io/product-images/S32101-5/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12128/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12128/002.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S32103-1</t>
+          <t>WELL-12129</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32103-1/001.jpg,https://oleks-netizen.github.io/product-images/S32103-1/002.jpg,https://oleks-netizen.github.io/product-images/S32103-1/003.jpg,https://oleks-netizen.github.io/product-images/S32103-1/004.jpg,https://oleks-netizen.github.io/product-images/S32103-1/005.jpg,https://oleks-netizen.github.io/product-images/S32103-1/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12129/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12129/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12129/003.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S32103-2</t>
+          <t>WELL-12205</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32103-2/001.jpg,https://oleks-netizen.github.io/product-images/S32103-2/002.jpg,https://oleks-netizen.github.io/product-images/S32103-2/003.jpg,https://oleks-netizen.github.io/product-images/S32103-2/004.jpg,https://oleks-netizen.github.io/product-images/S32103-2/005.jpg,https://oleks-netizen.github.io/product-images/S32103-2/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12205/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12205/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12205/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12205/004.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S32103-4</t>
+          <t>WELL-12208</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32103-4/001.jpg,https://oleks-netizen.github.io/product-images/S32103-4/002.jpg,https://oleks-netizen.github.io/product-images/S32103-4/003.jpg,https://oleks-netizen.github.io/product-images/S32103-4/004.jpg,https://oleks-netizen.github.io/product-images/S32103-4/005.jpg,https://oleks-netizen.github.io/product-images/S32103-4/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12208/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12208/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12208/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12208/004.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S32103-5</t>
+          <t>WELL-12209</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32103-5/001.jpg,https://oleks-netizen.github.io/product-images/S32103-5/002.jpg,https://oleks-netizen.github.io/product-images/S32103-5/003.jpg,https://oleks-netizen.github.io/product-images/S32103-5/004.jpg,https://oleks-netizen.github.io/product-images/S32103-5/005.jpg,https://oleks-netizen.github.io/product-images/S32103-5/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12209/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12209/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12209/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12209/004.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S32106-1</t>
+          <t>WELL-12304</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32106-1/001.jpg,https://oleks-netizen.github.io/product-images/S32106-1/002.jpg,https://oleks-netizen.github.io/product-images/S32106-1/004.jpg,https://oleks-netizen.github.io/product-images/S32106-1/005.jpg,https://oleks-netizen.github.io/product-images/S32106-1/006.jpg,https://oleks-netizen.github.io/product-images/S32106-1/007.jpg,https://oleks-netizen.github.io/product-images/S32106-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12304/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12304/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12304/003.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S32106-2</t>
+          <t>WELL-12305</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32106-2/001.jpg,https://oleks-netizen.github.io/product-images/S32106-2/002.jpg,https://oleks-netizen.github.io/product-images/S32106-2/004.jpg,https://oleks-netizen.github.io/product-images/S32106-2/005.jpg,https://oleks-netizen.github.io/product-images/S32106-2/006.jpg,https://oleks-netizen.github.io/product-images/S32106-2/007.jpg,https://oleks-netizen.github.io/product-images/S32106-2/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12305/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12305/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12305/003.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S32106-3</t>
+          <t>WELL-12309</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32106-3/001.jpg,https://oleks-netizen.github.io/product-images/S32106-3/002.jpg,https://oleks-netizen.github.io/product-images/S32106-3/004.jpg,https://oleks-netizen.github.io/product-images/S32106-3/005.jpg,https://oleks-netizen.github.io/product-images/S32106-3/006.jpg,https://oleks-netizen.github.io/product-images/S32106-3/007.jpg,https://oleks-netizen.github.io/product-images/S32106-3/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12309/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12309/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12309/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12309/004.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S32106-4</t>
+          <t>WELL-12404</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32106-4/001.jpg,https://oleks-netizen.github.io/product-images/S32106-4/002.jpg,https://oleks-netizen.github.io/product-images/S32106-4/004.jpg,https://oleks-netizen.github.io/product-images/S32106-4/005.jpg,https://oleks-netizen.github.io/product-images/S32106-4/006.jpg,https://oleks-netizen.github.io/product-images/S32106-4/007.jpg,https://oleks-netizen.github.io/product-images/S32106-4/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12404/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12404/002.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S32106-5</t>
+          <t>WELL-12405</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32106-5/001.jpg,https://oleks-netizen.github.io/product-images/S32106-5/002.jpg,https://oleks-netizen.github.io/product-images/S32106-5/004.jpg,https://oleks-netizen.github.io/product-images/S32106-5/005.jpg,https://oleks-netizen.github.io/product-images/S32106-5/006.jpg,https://oleks-netizen.github.io/product-images/S32106-5/007.jpg,https://oleks-netizen.github.io/product-images/S32106-5/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12405/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12405/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12405/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12405/004.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S32110-1</t>
+          <t>WELL-12409</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32110-1/001.jpg,https://oleks-netizen.github.io/product-images/S32110-1/003.jpg,https://oleks-netizen.github.io/product-images/S32110-1/004.jpg,https://oleks-netizen.github.io/product-images/S32110-1/005.jpg,https://oleks-netizen.github.io/product-images/S32110-1/006.jpg,https://oleks-netizen.github.io/product-images/S32110-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12409/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12409/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12409/003.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S32110-2</t>
+          <t>WELL-12504</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32110-2/001.jpg,https://oleks-netizen.github.io/product-images/S32110-2/002.jpg,https://oleks-netizen.github.io/product-images/S32110-2/003.jpg,https://oleks-netizen.github.io/product-images/S32110-2/004.jpg,https://oleks-netizen.github.io/product-images/S32110-2/005.jpg,https://oleks-netizen.github.io/product-images/S32110-2/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12504/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12504/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12504/003.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S32110-3</t>
+          <t>WELL-12505</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32110-3/001.jpg,https://oleks-netizen.github.io/product-images/S32110-3/002.jpg,https://oleks-netizen.github.io/product-images/S32110-3/003.jpg,https://oleks-netizen.github.io/product-images/S32110-3/004.jpg,https://oleks-netizen.github.io/product-images/S32110-3/005.jpg,https://oleks-netizen.github.io/product-images/S32110-3/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12505/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12505/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12505/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12505/004.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S32110-4</t>
+          <t>WELL-12507</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32110-4/001.jpg,https://oleks-netizen.github.io/product-images/S32110-4/002.jpg,https://oleks-netizen.github.io/product-images/S32110-4/003.jpg,https://oleks-netizen.github.io/product-images/S32110-4/004.jpg,https://oleks-netizen.github.io/product-images/S32110-4/005.jpg,https://oleks-netizen.github.io/product-images/S32110-4/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12507/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12507/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12507/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12507/004.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S32110-5</t>
+          <t>WELL-12509</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32110-5/001.jpg,https://oleks-netizen.github.io/product-images/S32110-5/002.jpg,https://oleks-netizen.github.io/product-images/S32110-5/003.jpg,https://oleks-netizen.github.io/product-images/S32110-5/004.jpg,https://oleks-netizen.github.io/product-images/S32110-5/005.jpg,https://oleks-netizen.github.io/product-images/S32110-5/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12509/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12509/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12509/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12509/004.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S32112-1</t>
+          <t>WELL-12602</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32112-1/001.jpg,https://oleks-netizen.github.io/product-images/S32112-1/002.jpg,https://oleks-netizen.github.io/product-images/S32112-1/004.jpg,https://oleks-netizen.github.io/product-images/S32112-1/005.jpg,https://oleks-netizen.github.io/product-images/S32112-1/006.jpg,https://oleks-netizen.github.io/product-images/S32112-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12602/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12602/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12602/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12602/004.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S32112-2</t>
+          <t>WELL-12607</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32112-2/001.jpg,https://oleks-netizen.github.io/product-images/S32112-2/002.jpg,https://oleks-netizen.github.io/product-images/S32112-2/004.jpg,https://oleks-netizen.github.io/product-images/S32112-2/005.jpg,https://oleks-netizen.github.io/product-images/S32112-2/006.jpg,https://oleks-netizen.github.io/product-images/S32112-2/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12607/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12607/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12607/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12607/004.jpg,https://oleks-netizen.github.io/product-images/WELL-12607/005.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S32112-3</t>
+          <t>WELL-12609</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32112-3/001.jpg,https://oleks-netizen.github.io/product-images/S32112-3/002.jpg,https://oleks-netizen.github.io/product-images/S32112-3/004.jpg,https://oleks-netizen.github.io/product-images/S32112-3/005.jpg,https://oleks-netizen.github.io/product-images/S32112-3/006.jpg,https://oleks-netizen.github.io/product-images/S32112-3/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12609/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12609/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12609/003.jpg</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S32112-4</t>
+          <t>WELL-12704</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32112-4/001.jpg,https://oleks-netizen.github.io/product-images/S32112-4/002.jpg,https://oleks-netizen.github.io/product-images/S32112-4/004.jpg,https://oleks-netizen.github.io/product-images/S32112-4/005.jpg,https://oleks-netizen.github.io/product-images/S32112-4/006.jpg,https://oleks-netizen.github.io/product-images/S32112-4/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12704/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12704/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12704/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12704/004.jpg</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S32112-5</t>
+          <t>WELL-12708</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/S32112-5/001.jpg,https://oleks-netizen.github.io/product-images/S32112-5/002.jpg,https://oleks-netizen.github.io/product-images/S32112-5/004.jpg,https://oleks-netizen.github.io/product-images/S32112-5/005.jpg,https://oleks-netizen.github.io/product-images/S32112-5/006.jpg,https://oleks-netizen.github.io/product-images/S32112-5/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12708/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12708/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12708/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12708/004.jpg</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WELL-12709</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12709/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12709/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12709/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12709/004.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WELL-12801</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12801/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12801/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12801/003.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>WELL-12802</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12802/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12802/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12802/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12802/004.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>WELL-12804</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12804/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12804/004.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WELL-12805</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12805/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12805/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12805/003.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WELL-12807</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12807/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12807/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12807/003.jpg,https://oleks-netizen.github.io/product-images/WELL-12807/004.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WELL-12809</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12809/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12809/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12809/003.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WELL-13004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13004/003.jpg,https://oleks-netizen.github.io/product-images/WELL-13004/004.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>WELL-13102</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13102/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13102/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13102/003.jpg,https://oleks-netizen.github.io/product-images/WELL-13102/004.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WELL-13104</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13104/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13104/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13104/003.jpg,https://oleks-netizen.github.io/product-images/WELL-13104/004.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>WELL-13109</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13109/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13109/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13109/003.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WELL-13555</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13555/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13555/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13555/003.jpg,https://oleks-netizen.github.io/product-images/WELL-13555/004.jpg,https://oleks-netizen.github.io/product-images/WELL-13555/005.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>WELL-13559</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13559/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13559/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13559/003.jpg,https://oleks-netizen.github.io/product-images/WELL-13559/004.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>WELL-13604</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13604/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13604/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13604/003.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>WELL-13606</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13606/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13606/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13606/003.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>WELL-13609</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13609/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13609/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13609/003.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>WELL-13803</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13803/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13803/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13803/003.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>WELL-13804</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13804/003.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>WELL-13809</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-13809/001.jpg,https://oleks-netizen.github.io/product-images/WELL-13809/002.jpg,https://oleks-netizen.github.io/product-images/WELL-13809/003.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WELL-14003</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14003/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14003/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14003/003.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WELL-14004</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14004/003.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>WELL-14009</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14009/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14009/002.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>WELL-14103</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14103/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14103/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14103/003.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>WELL-14104</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14104/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14104/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14104/003.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WELL-14202</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14202/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14202/002.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>WELL-14209</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14209/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14209/002.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>WELL-14254</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14254/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14254/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14254/003.jpg,https://oleks-netizen.github.io/product-images/WELL-14254/004.jpg,https://oleks-netizen.github.io/product-images/WELL-14254/005.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WELL-14300</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-14300/001.jpg,https://oleks-netizen.github.io/product-images/WELL-14300/002.jpg,https://oleks-netizen.github.io/product-images/WELL-14300/003.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>WELL-15002</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15002/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15002/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15002/003.jpg</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>WELL-15004</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15004/002.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WELL-15005</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15005/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15005/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15005/003.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>WELL-15007</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15007/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15007/002.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>WELL-15009</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15009/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15009/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15009/003.jpg</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>WELL-15154</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15154/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15154/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15154/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15154/004.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>WELL-15155</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15155/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15155/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15155/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15155/004.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>WELL-15157</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15157/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15157/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15157/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15157/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15157/005.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WELL-15159</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15159/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15159/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15159/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15159/004.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>WELL-15252</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15252/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15252/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15252/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15252/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15252/005.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>WELL-15254</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15254/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15254/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15254/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15254/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15254/005.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WELL-15255</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15255/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15255/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15255/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15255/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15255/005.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>WELL-15257</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15257/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15257/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15257/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15257/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15257/005.jpg</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>WELL-15259</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15259/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15259/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15259/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15259/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15259/005.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>WELL-15304</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15304/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15304/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15304/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15304/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15304/005.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>WELL-15305</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15305/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15305/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15305/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15305/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15305/005.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>WELL-15308</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15308/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15308/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15308/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15308/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15308/005.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>WELL-15309</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15309/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15309/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15309/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15309/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15309/005.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>WELL-15454</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15454/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15454/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15454/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15454/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15454/005.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>WELL-15455</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15455/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15455/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15455/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15455/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15455/005.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>WELL-15504</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15504/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15504/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15504/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15504/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15504/005.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>WELL-15505</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15505/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15505/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15505/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15505/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15505/005.jpg,https://oleks-netizen.github.io/product-images/WELL-15505/006.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>WELL-15507</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15507/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15507/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15507/003.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>WELL-15509</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15509/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15509/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15509/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15509/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15509/005.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>WELL-15654</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15654/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15654/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15654/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15654/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15654/005.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>WELL-15655</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15655/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15655/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15655/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15655/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15655/005.jpg</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>WELL-15657</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15657/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15657/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15657/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15657/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15657/005.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>WELL-15659</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15659/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15659/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15659/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15659/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15659/005.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WELL-15702</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15702/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15702/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15702/003.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>WELL-15704</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15704/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15704/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15704/003.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>WELL-15705</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15705/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15705/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15705/003.jpg</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>WELL-15707</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15707/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15707/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15707/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15707/004.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>WELL-15709</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15709/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15709/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15709/003.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>WELL-15802</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15802/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15802/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15802/003.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>WELL-15804</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15804/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15804/004.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>WELL-15805</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15805/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15805/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15805/003.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>WELL-15809</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15809/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15809/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15809/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15809/004.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>WELL-15955</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-15955/001.jpg,https://oleks-netizen.github.io/product-images/WELL-15955/002.jpg,https://oleks-netizen.github.io/product-images/WELL-15955/003.jpg,https://oleks-netizen.github.io/product-images/WELL-15955/004.jpg,https://oleks-netizen.github.io/product-images/WELL-15955/005.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>WELL-44201</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44201/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44201/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44201/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44201/004.jpg,https://oleks-netizen.github.io/product-images/WELL-44201/005.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>WELL-44205</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44205/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44205/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44205/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44205/004.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>WELL-44206</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44206/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44206/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44206/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44206/004.jpg</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>WELL-44208</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44208/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44208/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44208/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44208/004.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>WELL-44209</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44209/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44209/002.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>WELL-44210</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44210/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44210/002.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>WELL-44213</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44213/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44213/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44213/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44213/004.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>WELL-44312</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44312/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44312/002.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>WELL-44415</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44415/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44415/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44415/003.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>WELL-44419</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44419/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44419/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44419/003.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>WELL-44425</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44425/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44425/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44425/003.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>WELL-44429</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44429/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44429/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44429/003.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>WELL-44444</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44444/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44444/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44444/003.jpg</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>WELL-44601</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44601/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44601/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44601/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44601/004.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>WELL-44603</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44603/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44603/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44603/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44603/004.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>WELL-44606</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44606/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44606/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44606/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44606/004.jpg,https://oleks-netizen.github.io/product-images/WELL-44606/005.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>WELL-44607</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44607/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44607/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44607/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44607/004.jpg,https://oleks-netizen.github.io/product-images/WELL-44607/005.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>WELL-44608</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-44608/001.jpg,https://oleks-netizen.github.io/product-images/WELL-44608/002.jpg,https://oleks-netizen.github.io/product-images/WELL-44608/003.jpg,https://oleks-netizen.github.io/product-images/WELL-44608/004.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>WELL-45352</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45352/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45352/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45352/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45352/004.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>WELL-45505</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45505/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45505/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45505/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45505/004.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>WELL-45508</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45508/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45508/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45508/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45508/004.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>WELL-45510</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45510/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45510/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45510/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45510/004.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>WELL-45601</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45601/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45601/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45601/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45601/004.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>WELL-45602</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45602/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45602/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45602/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45602/004.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>WELL-45603</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-45603/001.jpg,https://oleks-netizen.github.io/product-images/WELL-45603/002.jpg,https://oleks-netizen.github.io/product-images/WELL-45603/003.jpg,https://oleks-netizen.github.io/product-images/WELL-45603/004.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>WELL-46109</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46109/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46109/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46109/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46109/004.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>WELL-46110</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46110/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46110/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46110/003.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>WELL-46111</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46111/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46111/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46111/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46111/004.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>WELL-46113</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46113/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46113/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46113/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46113/004.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>WELL-46202</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46202/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46202/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46202/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46202/004.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>WELL-46407</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46407/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46407/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46407/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46407/004.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>WELL-46427</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46427/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46427/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46427/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46427/004.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>WELL-46500</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46500/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46500/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46500/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46500/004.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>WELL-46501</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46501/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46501/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46501/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46501/004.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>WELL-46504</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46504/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46504/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46504/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46504/004.jpg,https://oleks-netizen.github.io/product-images/WELL-46504/005.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>WELL-46507</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46507/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46507/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46507/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46507/004.jpg,https://oleks-netizen.github.io/product-images/WELL-46507/005.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>WELL-46601</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46601/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46601/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46601/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46601/004.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>WELL-46707</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46707/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46707/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46707/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46707/004.jpg,https://oleks-netizen.github.io/product-images/WELL-46707/005.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>WELL-46708</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46708/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46708/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46708/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46708/004.jpg,https://oleks-netizen.github.io/product-images/WELL-46708/005.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>WELL-46711</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46711/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46711/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46711/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46711/004.jpg,https://oleks-netizen.github.io/product-images/WELL-46711/005.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>WELL-46900</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46900/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46900/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46900/003.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>WELL-46904</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46904/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46904/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46904/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46904/004.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>WELL-46908</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46908/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46908/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46908/003.jpg,https://oleks-netizen.github.io/product-images/WELL-46908/004.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>WELL-46909</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46909/001.jpg,https://oleks-netizen.github.io/product-images/WELL-46909/002.jpg,https://oleks-netizen.github.io/product-images/WELL-46909/003.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>WELL-47208</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47208/001.jpg,https://oleks-netizen.github.io/product-images/WELL-47208/002.jpg,https://oleks-netizen.github.io/product-images/WELL-47208/003.jpg,https://oleks-netizen.github.io/product-images/WELL-47208/004.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>WELL-47400</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47400/001.jpg,https://oleks-netizen.github.io/product-images/WELL-47400/002.jpg,https://oleks-netizen.github.io/product-images/WELL-47400/003.jpg,https://oleks-netizen.github.io/product-images/WELL-47400/004.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>WELL-47401</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47401/001.jpg,https://oleks-netizen.github.io/product-images/WELL-47401/002.jpg,https://oleks-netizen.github.io/product-images/WELL-47401/003.jpg,https://oleks-netizen.github.io/product-images/WELL-47401/004.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>WELL-47404</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47404/001.jpg,https://oleks-netizen.github.io/product-images/WELL-47404/002.jpg,https://oleks-netizen.github.io/product-images/WELL-47404/003.jpg,https://oleks-netizen.github.io/product-images/WELL-47404/004.jpg,https://oleks-netizen.github.io/product-images/WELL-47404/005.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>WELL-47409</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47409/001.jpg,https://oleks-netizen.github.io/product-images/WELL-47409/002.jpg,https://oleks-netizen.github.io/product-images/WELL-47409/003.jpg,https://oleks-netizen.github.io/product-images/WELL-47409/004.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>WELL-55354</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-55354/001.jpg,https://oleks-netizen.github.io/product-images/WELL-55354/002.jpg,https://oleks-netizen.github.io/product-images/WELL-55354/003.jpg,https://oleks-netizen.github.io/product-images/WELL-55354/004.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>WELL-56300</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56300/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56300/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56300/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56300/004.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>WELL-56304</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56304/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56304/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56304/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56304/004.jpg,https://oleks-netizen.github.io/product-images/WELL-56304/005.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>WELL-56310</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56310/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56310/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56310/003.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>WELL-56500</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56500/001.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>WELL-56600</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56600/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56600/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56600/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56600/004.jpg,https://oleks-netizen.github.io/product-images/WELL-56600/005.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>WELL-56604</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56604/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56604/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56604/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56604/004.jpg,https://oleks-netizen.github.io/product-images/WELL-56604/005.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>WELL-56605</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56605/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56605/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56605/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56605/004.jpg,https://oleks-netizen.github.io/product-images/WELL-56605/005.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>WELL-56609</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56609/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56609/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56609/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56609/004.jpg,https://oleks-netizen.github.io/product-images/WELL-56609/005.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>WELL-56630</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56630/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56630/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56630/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56630/004.jpg</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>WELL-56631</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56631/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56631/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56631/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56631/004.jpg</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>WELL-56902</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56902/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56902/002.jpg,https://oleks-netizen.github.io/product-images/WELL-56902/003.jpg,https://oleks-netizen.github.io/product-images/WELL-56902/004.jpg</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>WELL-56907</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-56907/001.jpg,https://oleks-netizen.github.io/product-images/WELL-56907/002.jpg</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>WELL-57806</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-57806/001.jpg,https://oleks-netizen.github.io/product-images/WELL-57806/002.jpg,https://oleks-netizen.github.io/product-images/WELL-57806/003.jpg,https://oleks-netizen.github.io/product-images/WELL-57806/004.jpg</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>WELL-57808</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-57808/001.jpg,https://oleks-netizen.github.io/product-images/WELL-57808/002.jpg,https://oleks-netizen.github.io/product-images/WELL-57808/003.jpg,https://oleks-netizen.github.io/product-images/WELL-57808/004.jpg</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>WELL-57809</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-57809/001.jpg,https://oleks-netizen.github.io/product-images/WELL-57809/002.jpg,https://oleks-netizen.github.io/product-images/WELL-57809/003.jpg,https://oleks-netizen.github.io/product-images/WELL-57809/004.jpg</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>WELL-58001</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58001/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58001/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58001/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58001/004.jpg</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>WELL-58004</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58004/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58004/004.jpg</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>WELL-58010</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58010/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58010/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58010/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58010/004.jpg</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>WELL-58013</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58013/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58013/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58013/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58013/004.jpg</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>WELL-58411</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58411/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58411/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58411/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58411/004.jpg,https://oleks-netizen.github.io/product-images/WELL-58411/005.jpg</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>WELL-58412</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58412/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58412/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58412/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58412/004.jpg</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>WELL-58501</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-58501/001.jpg,https://oleks-netizen.github.io/product-images/WELL-58501/002.jpg,https://oleks-netizen.github.io/product-images/WELL-58501/003.jpg,https://oleks-netizen.github.io/product-images/WELL-58501/004.jpg</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>WELL-60003</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60003/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60003/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60003/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60003/004.jpg</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>WELL-60004</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60004/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60004/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60004/004.jpg</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>WELL-60009</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60009/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60009/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60009/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60009/004.jpg</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>WELL-60303</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60303/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60303/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60303/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60303/004.jpg,https://oleks-netizen.github.io/product-images/WELL-60303/005.jpg</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>WELL-60305</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60305/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60305/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60305/003.jpg</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>WELL-60403</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60403/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60403/002.jpg</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>WELL-60408</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60408/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60408/002.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>WELL-60411</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60411/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60411/002.jpg</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>WELL-60413</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60413/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60413/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60413/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60413/004.jpg</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>WELL-60500</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60500/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60500/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60500/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60500/004.jpg</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>WELL-60501</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60501/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60501/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60501/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60501/004.jpg</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>WELL-60509</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60509/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60509/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60509/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60509/004.jpg</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>WELL-60510</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60510/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60510/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60510/003.jpg</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>WELL-60604</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60604/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60604/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60604/003.jpg</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>WELL-60609</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60609/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60609/002.jpg</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>WELL-60610</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60610/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60610/002.jpg</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>WELL-60654</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60654/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60654/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60654/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60654/004.jpg</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>WELL-60711</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60711/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60711/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60711/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60711/004.jpg</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>WELL-60805</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60805/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60805/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60805/003.jpg</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>WELL-60806</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60806/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60806/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60806/003.jpg</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>WELL-60814</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60814/001.jpg</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>WELL-60824</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60824/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60824/002.jpg</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>WELL-60902</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60902/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60902/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60902/003.jpg</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>WELL-60903</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60903/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60903/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60903/003.jpg</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>WELL-60905</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60905/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60905/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60905/003.jpg,https://oleks-netizen.github.io/product-images/WELL-60905/004.jpg</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>WELL-60907</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60907/001.jpg,https://oleks-netizen.github.io/product-images/WELL-60907/002.jpg,https://oleks-netizen.github.io/product-images/WELL-60907/003.jpg</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>WELL-61001</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61001/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61001/002.jpg</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>WELL-61004</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61004/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61004/002.jpg</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>WELL-61006</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61006/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61006/002.jpg</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>WELL-61007</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61007/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61007/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61007/003.jpg,https://oleks-netizen.github.io/product-images/WELL-61007/004.jpg,https://oleks-netizen.github.io/product-images/WELL-61007/005.jpg</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>WELL-61010</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61010/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61010/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61010/003.jpg</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>WELL-61024</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61024/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61024/002.jpg</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>WELL-61030</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61030/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61030/002.jpg</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>WELL-61035</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61035/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61035/002.jpg</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>WELL-61036</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61036/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61036/002.jpg</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>WELL-61301</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61301/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61301/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61301/003.jpg</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>WELL-61302</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61302/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61302/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61302/003.jpg</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>WELL-61303</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61303/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61303/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61303/003.jpg</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>WELL-61400</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61400/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61400/002.jpg</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>WELL-61503</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61503/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61503/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61503/003.jpg,https://oleks-netizen.github.io/product-images/WELL-61503/004.jpg</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>WELL-61602</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61602/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61602/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61602/003.jpg,https://oleks-netizen.github.io/product-images/WELL-61602/004.jpg,https://oleks-netizen.github.io/product-images/WELL-61602/005.jpg</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>WELL-61610</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61610/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61610/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61610/003.jpg,https://oleks-netizen.github.io/product-images/WELL-61610/004.jpg</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>WELL-61614</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61614/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61614/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61614/003.jpg</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>WELL-61804</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61804/001.jpg,https://oleks-netizen.github.io/product-images/WELL-61804/002.jpg,https://oleks-netizen.github.io/product-images/WELL-61804/003.jpg</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>WELL-62200</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-62200/001.jpg,https://oleks-netizen.github.io/product-images/WELL-62200/002.jpg,https://oleks-netizen.github.io/product-images/WELL-62200/003.jpg,https://oleks-netizen.github.io/product-images/WELL-62200/004.jpg</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10110001</t>
+          <t>0121tk-4t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110001/001.jpg,https://oleks-netizen.github.io/product-images/10110001/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0121tk-4t/001.jpg,https://oleks-netizen.github.io/product-images/0121tk-4t/002.jpg,https://oleks-netizen.github.io/product-images/0121tk-4t/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10110013</t>
+          <t>nwm-4zmsh-0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110013/001.jpg,https://oleks-netizen.github.io/product-images/10110013/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwm-4zmsh-0001/001.jpg,https://oleks-netizen.github.io/product-images/nwm-4zmsh-0001/003.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10110020</t>
+          <t>nwm-4zmsh-0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110020/001.jpg,https://oleks-netizen.github.io/product-images/10110020/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwm-4zmsh-0003/001.jpg,https://oleks-netizen.github.io/product-images/nwm-4zmsh-0003/003.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,57 +481,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10110030</t>
+          <t>roza-ua-33k-001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110030/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-001/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-001/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-001/004.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10110066</t>
+          <t>roza-ua-33k-001-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110066/001.jpg,https://oleks-netizen.github.io/product-images/10110066/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-001-1/001.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10110067</t>
+          <t>roza-ua-33k-001-2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110067/001.jpg,https://oleks-netizen.github.io/product-images/10110067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-001-2/001.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10110068</t>
+          <t>roza-ua-33k-001-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10110068/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-001-3/001.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,147 +541,147 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10211001</t>
+          <t>roza-ua-33k-002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211001/001.jpg,https://oleks-netizen.github.io/product-images/10211001/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-002/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-002/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-002/004.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10211013</t>
+          <t>roza-ua-33k-002-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211013/001.jpg,https://oleks-netizen.github.io/product-images/10211013/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-002-1/001.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10211020</t>
+          <t>roza-ua-33k-002-2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211020/001.jpg,https://oleks-netizen.github.io/product-images/10211020/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-002-2/001.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10211030</t>
+          <t>roza-ua-33k-002-3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211030/001.jpg,https://oleks-netizen.github.io/product-images/10211030/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-002-3/001.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10211066</t>
+          <t>roza-ua-33k-003</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211066/001.jpg,https://oleks-netizen.github.io/product-images/10211066/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-003/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-003/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-003/004.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10211067</t>
+          <t>roza-ua-33k-003-1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211067/001.jpg,https://oleks-netizen.github.io/product-images/10211067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-003-1/001.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10211068</t>
+          <t>roza-ua-33k-003-2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/10211068/001.jpg,https://oleks-netizen.github.io/product-images/10211068/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-003-2/001.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>roza-ua-33k-003-3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1203/001.jpg,https://oleks-netizen.github.io/product-images/1203/003.jpg,https://oleks-netizen.github.io/product-images/1203/004.jpg,https://oleks-netizen.github.io/product-images/1203/005.jpg,https://oleks-netizen.github.io/product-images/1203/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-003-3/001.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1FB9368-2be-beige</t>
+          <t>roza-ua-33k-004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FB9368-2be-beige/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-004/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-004/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-004/004.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1FB9368-2bl-black</t>
+          <t>roza-ua-33k-004-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FB9368-2bl-black/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-004-1/001.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,12 +691,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1FB9368-2br-brown</t>
+          <t>roza-ua-33k-004-2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FB9368-2br-brown/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-004-2/001.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,12 +706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1FB9368-2co-brown</t>
+          <t>roza-ua-33k-004-3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FB9368-2co-brown/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-004-3/001.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,87 +721,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1FB9368-2t-taupe</t>
+          <t>roza-ua-33k-005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FB9368-2t-taupe/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-005/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-005/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-005/004.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1FP2206-2be-beige</t>
+          <t>roza-ua-33k-005-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP2206-2be-beige/001.jpg,https://oleks-netizen.github.io/product-images/1FP2206-2be-beige/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-005-1/001.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1FP2206-2bl-black</t>
+          <t>roza-ua-33k-005-2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP2206-2bl-black/001.jpg,https://oleks-netizen.github.io/product-images/1FP2206-2bl-black/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-005-2/001.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1FP2206-2br-brown</t>
+          <t>roza-ua-33k-005-3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP2206-2br-brown/001.jpg,https://oleks-netizen.github.io/product-images/1FP2206-2br-brown/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-005-3/001.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1FP2206-2t-taupe</t>
+          <t>roza-ua-33k-006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP2206-2t-taupe/001.jpg,https://oleks-netizen.github.io/product-images/1FP2206-2t-taupe/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-006/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-006/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-006/004.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1FP9295br-brown</t>
+          <t>roza-ua-33k-006-1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9295br-brown/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-006-1/001.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -811,72 +811,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1FP9298bl-black</t>
+          <t>roza-ua-33k-006-2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9298bl-black/001.jpg,https://oleks-netizen.github.io/product-images/1FP9298bl-black/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-006-2/001.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1FP9298gold-black</t>
+          <t>roza-ua-33k-006-3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9298gold-black/001.jpg,https://oleks-netizen.github.io/product-images/1FP9298gold-black/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-006-3/001.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1FP9298or-orange</t>
+          <t>roza-ua-33k-007</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9298or-orange/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-007/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-007/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-007/004.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1FP9298w-white</t>
+          <t>roza-ua-33k-007-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9298w-white/001.jpg,https://oleks-netizen.github.io/product-images/1FP9298w-white/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-007-1/001.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1FP9325-2bl-black</t>
+          <t>roza-ua-33k-007-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9325-2bl-black/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-007-2/001.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -886,12 +886,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1FP9325-2br-brown</t>
+          <t>roza-ua-33k-007-3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1FP9325-2br-brown/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-007-3/001.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -901,72 +901,72 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30111013</t>
+          <t>roza-ua-33k-008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111013/001.jpg,https://oleks-netizen.github.io/product-images/30111013/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-008/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-008/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-008/004.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30111030</t>
+          <t>roza-ua-33k-008-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111030/001.jpg,https://oleks-netizen.github.io/product-images/30111030/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-008-1/001.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>30111066</t>
+          <t>roza-ua-33k-008-2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111066/001.jpg,https://oleks-netizen.github.io/product-images/30111066/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-008-2/001.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>30111067</t>
+          <t>roza-ua-33k-008-3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111067/001.jpg,https://oleks-netizen.github.io/product-images/30111067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-008-3/001.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30111068</t>
+          <t>roza-ua-33k-009</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111068/001.jpg,https://oleks-netizen.github.io/product-images/30111068/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-009/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-33k-009/003.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -976,147 +976,147 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>303110013</t>
+          <t>roza-ua-33k-009-1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110013/001.jpg,https://oleks-netizen.github.io/product-images/303110013/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-009-1/001.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>303110020</t>
+          <t>roza-ua-33k-009-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110020/001.jpg,https://oleks-netizen.github.io/product-images/303110020/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-009-2/001.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>303110030</t>
+          <t>roza-ua-33k-009-3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110030/001.jpg,https://oleks-netizen.github.io/product-images/303110030/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-33k-009-3/001.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>303110066</t>
+          <t>ssch-kit-0011</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110066/001.jpg,https://oleks-netizen.github.io/product-images/303110066/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0011/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0011/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0011/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0011/005.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>303110067</t>
+          <t>ssch-kit-0012</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110067/001.jpg,https://oleks-netizen.github.io/product-images/303110067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0012/001.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>303110068</t>
+          <t>ssch-kit-0013</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/303110068/001.jpg,https://oleks-netizen.github.io/product-images/303110068/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0013/001.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30411001</t>
+          <t>ssch-kit-0014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411001/001.jpg,https://oleks-netizen.github.io/product-images/30411001/002.jpg,https://oleks-netizen.github.io/product-images/30411001/004.jpg,https://oleks-netizen.github.io/product-images/30411001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0014/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/010.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0014/011.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30411013</t>
+          <t>ssch-kit-0015</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411013/001.jpg,https://oleks-netizen.github.io/product-images/30411013/002.jpg,https://oleks-netizen.github.io/product-images/30411013/004.jpg,https://oleks-netizen.github.io/product-images/30411013/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0015/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0015/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0015/004.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30411020</t>
+          <t>ssch-kit-0016</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411020/001.jpg,https://oleks-netizen.github.io/product-images/30411020/002.jpg,https://oleks-netizen.github.io/product-images/30411020/003.jpg,https://oleks-netizen.github.io/product-images/30411020/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0016/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0016/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0016/004.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30411030</t>
+          <t>ssch-kit-0017</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411030/001.jpg,https://oleks-netizen.github.io/product-images/30411030/002.jpg,https://oleks-netizen.github.io/product-images/30411030/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0017/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0017/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0017/004.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1126,12 +1126,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>30411066</t>
+          <t>ssch-kit-0018</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411066/001.jpg,https://oleks-netizen.github.io/product-images/30411066/002.jpg,https://oleks-netizen.github.io/product-images/30411066/003.jpg,https://oleks-netizen.github.io/product-images/30411066/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0018/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0018/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0018/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0018/005.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1141,12 +1141,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30411067</t>
+          <t>ssch-kit-0019</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411067/001.jpg,https://oleks-netizen.github.io/product-images/30411067/002.jpg,https://oleks-netizen.github.io/product-images/30411067/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0019/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0019/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0019/004.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1156,147 +1156,147 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30411068</t>
+          <t>ssch-kit-0020</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30411068/001.jpg,https://oleks-netizen.github.io/product-images/30411068/002.jpg,https://oleks-netizen.github.io/product-images/30411068/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0020/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0020/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0020/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0020/005.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BN-CB-6-violet-flo</t>
+          <t>ssch-kit-0026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-6-violet-flo/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-6-violet-flo/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-6-violet-flo/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0026/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0026/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0026/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0026/005.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BN-CB-8-vin</t>
+          <t>ssch-kit-0029</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-CB-8-vin/001.jpg,https://oleks-netizen.github.io/product-images/BN-CB-8-vin/002.jpg,https://oleks-netizen.github.io/product-images/BN-CB-8-vin/004.jpg,https://oleks-netizen.github.io/product-images/BN-CB-8-vin/005.jpg,https://oleks-netizen.github.io/product-images/BN-CB-8-vin/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0029/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0029/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0029/004.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BV38015-2803</t>
+          <t>ssch-kit-0035</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BV38015-2803/001.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/002.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/003.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/004.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/005.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/006.jpg,https://oleks-netizen.github.io/product-images/BV38015-2803/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0035/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0035/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0035/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0035/005.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C54 TEAL</t>
+          <t>ssch-kit-0036</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/C54 TEAL/001.jpg,https://oleks-netizen.github.io/product-images/C54 TEAL/002.jpg,https://oleks-netizen.github.io/product-images/C54 TEAL/004.jpg,https://oleks-netizen.github.io/product-images/C54 TEAL/005.jpg,https://oleks-netizen.github.io/product-images/C54 TEAL/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0036/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0036/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0036/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0036/005.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CV1ZK-019bo-bordo</t>
+          <t>ssch-kit-0038</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/CV1ZK-019bo-bordo/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0038/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0038/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0038/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0038/004.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D102 BRANDY</t>
+          <t>ssch-kit-0039</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/D102 BRANDY/001.jpg,https://oleks-netizen.github.io/product-images/D102 BRANDY/002.jpg,https://oleks-netizen.github.io/product-images/D102 BRANDY/003.jpg,https://oleks-netizen.github.io/product-images/D102 BRANDY/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0039/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0039/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0039/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0039/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0039/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0039/007.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>K43 BLACK</t>
+          <t>ssch-kit-004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/K43 BLACK/001.jpg,https://oleks-netizen.github.io/product-images/K43 BLACK/002.jpg,https://oleks-netizen.github.io/product-images/K43 BLACK/003.jpg,https://oleks-netizen.github.io/product-images/K43 BLACK/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-004/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-004/007.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>K47 BLK</t>
+          <t>ssch-kit-0042</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/K47 BLK/001.jpg,https://oleks-netizen.github.io/product-images/K47 BLK/002.jpg,https://oleks-netizen.github.io/product-images/K47 BLK/003.jpg,https://oleks-netizen.github.io/product-images/K47 BLK/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0042/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0042/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0042/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0042/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0042/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0042/007.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WELL-11403</t>
+          <t>ssch-kit-0043</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11403/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11403/002.jpg,https://oleks-netizen.github.io/product-images/WELL-11403/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11403/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0043/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0043/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0043/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0043/005.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1306,166 +1306,6196 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WELL-12204</t>
+          <t>ssch-kit-0045</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-12204/001.jpg,https://oleks-netizen.github.io/product-images/WELL-12204/002.jpg,https://oleks-netizen.github.io/product-images/WELL-12204/004.jpg,https://oleks-netizen.github.io/product-images/WELL-12204/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0045/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/010.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0045/011.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WELL-67212</t>
+          <t>ssch-kit-0046</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-67212/001.jpg,https://oleks-netizen.github.io/product-images/WELL-67212/002.jpg,https://oleks-netizen.github.io/product-images/WELL-67212/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0046/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/009.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/010.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0046/011.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WELL-69925</t>
+          <t>ssch-kit-0048</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-69925/001.jpg,https://oleks-netizen.github.io/product-images/WELL-69925/003.jpg,https://oleks-netizen.github.io/product-images/WELL-69925/004.jpg,https://oleks-netizen.github.io/product-images/WELL-69925/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0048/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0048/009.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WELL-K68551</t>
+          <t>ssch-kit-005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K68551/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K68551/003.jpg,https://oleks-netizen.github.io/product-images/WELL-K68551/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-005/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-005/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-005/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-005/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-005/006.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WELL-K69956</t>
+          <t>ssch-kit-0051</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K69956/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K69956/003.jpg,https://oleks-netizen.github.io/product-images/WELL-K69956/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0051/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0051/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0051/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0051/005.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WELL-K72259</t>
+          <t>ssch-kit-0053</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K72259/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K72259/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0053/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0053/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0053/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0053/005.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WELL-K72653</t>
+          <t>ssch-kit-0054</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K72653/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K72653/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0054/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0054/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0054/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0054/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0054/005.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WELL-K72658</t>
+          <t>ssch-kit-0055</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K72658/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K72658/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0055/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0055/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0055/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0055/004.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WELL-K72660</t>
+          <t>ssch-kit-0056</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K72660/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K72660/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0056/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0056/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0056/003.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WELL-K75057</t>
+          <t>ssch-kit-0057</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-K75057/001.jpg,https://oleks-netizen.github.io/product-images/WELL-K75057/003.jpg,https://oleks-netizen.github.io/product-images/WELL-K75057/004.jpg,https://oleks-netizen.github.io/product-images/WELL-K75057/005.jpg,https://oleks-netizen.github.io/product-images/WELL-K75057/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0057/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0057/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0057/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0057/004.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>30111020</t>
+          <t>ssch-kit-0058</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30111020/002.jpg,https://oleks-netizen.github.io/product-images/30111020/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0058/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0058/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0058/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0058/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0058/006.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ssch-kit-0059</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0059/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0059/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0059/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0059/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0059/005.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ssch-kit-006</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-006/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/009.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-006/010.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ssch-kit-0060</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0060/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0060/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0060/004.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ssch-kit-0061</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0061/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0061/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0061/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0061/005.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ssch-kit-0062</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0062/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0062/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0062/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0062/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0062/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0062/007.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ssch-kit-0063</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0063/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0063/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0063/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0063/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0063/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0063/007.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ssch-kit-0064</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0064/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0064/008.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ssch-kit-0065</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0065/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0065/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0065/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0065/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0065/006.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ssch-kit-0066</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0066/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0066/003.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ssch-kit-0067</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0067/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0067/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0067/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0067/005.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ssch-kit-0068</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0068/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0068/003.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ssch-kit-0069</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0069/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0069/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0069/004.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ssch-kit-007</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-007/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-007/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-007/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-007/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-007/006.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ssch-kit-0070</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0070/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0070/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0070/004.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ssch-kit-0071</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0071/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0071/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0071/004.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ssch-kit-0072</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0072/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0072/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0072/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0072/005.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ssch-kit-0073</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0073/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0073/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0073/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0073/005.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ssch-kit-0074</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0074/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0074/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0074/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0074/005.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ssch-kit-0075</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0075/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/008.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/009.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0075/011.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ssch-kit-0076</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0076/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0076/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0076/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0076/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0076/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0076/007.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ssch-kit-0077</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0077/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0077/008.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ssch-kit-0078</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0078/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0078/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0078/003.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ssch-kit-0079</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0079/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0079/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0079/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0079/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0079/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0079/007.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ssch-kit-0080</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0080/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0080/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0080/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0080/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0080/006.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ssch-kit-0081</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0081/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0081/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0081/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0081/005.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ssch-kit-0082</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0082/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0082/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0082/004.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ssch-kit-0083</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0083/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0083/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0083/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0083/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0083/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0083/007.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ssch-kit-0084</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0084/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0084/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0084/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0084/005.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ssch-kit-0085</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0085/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0085/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0085/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0085/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0085/006.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ssch-kit-0086</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0086/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0086/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0086/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0086/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0086/006.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ssch-kit-0087</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0087/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0087/007.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ssch-kit-0088</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0088/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0088/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0088/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0088/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0088/006.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ssch-kit-0089</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0089/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0089/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0089/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0089/005.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ssch-kit-009</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-009/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-009/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-009/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-009/005.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ssch-kit-0090</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0090/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0090/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0090/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0090/005.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ssch-kit-0091</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0091/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0091/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0091/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0091/005.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ssch-kit-0092</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0092/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0092/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0092/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0092/005.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ssch-kit-0093</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0093/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0093/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0093/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0093/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0093/006.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ssch-kit-0094</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0094/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0094/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0094/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0094/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0094/006.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ssch-kit-0095</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0095/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0095/008.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ssch-kit-0096</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0096/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0096/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0096/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0096/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0096/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0096/007.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ssch-kit-0097</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0097/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0097/008.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ssch-kit-0098</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0098/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0098/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0098/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0098/005.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ssch-kit-0099</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0099/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0099/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0099/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0099/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0099/006.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ssch-kit-0100</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0100/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0100/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0100/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0100/005.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ssch-kit-0101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0101/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0101/008.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ssch-kit-0102</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0102/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0102/008.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ssch-kit-0103</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0103/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/007.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0103/008.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ssch-kit-0104</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0104/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0104/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0104/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0104/005.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ssch-kit-0105</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0105/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0105/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0105/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0105/005.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ssch-kit-0106</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0106/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0106/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0106/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0106/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0106/006.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ssch-kit-0107</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0107/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0107/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0107/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0107/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0107/006.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ssch-kit-0108</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0108/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0108/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0108/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0108/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0108/006.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ssch-kit-0109</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0109/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0109/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0109/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0109/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0109/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0109/007.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ssch-kit-0111</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0111/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0111/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0111/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0111/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0111/006.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0111/007.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ssch-kit-0112</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0112/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0112/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0112/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0112/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0112/006.jpg</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ssch-kit-0113</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0113/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0113/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0113/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0113/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0113/006.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ssch-kit-0114</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0114/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0114/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0114/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0114/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0114/006.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ssch-kit-0115</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0115/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0115/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0115/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0115/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0115/006.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ssch-kit-0116</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0116/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0116/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0116/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0116/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0116/006.jpg</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ssch-kit-0117</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0117/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0117/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0117/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0117/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0117/006.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ssch-kit-0118</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0118/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0118/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0118/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0118/005.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ssch-kit-0119</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0119/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0119/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0119/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0119/005.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ssch-kit-0120</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0120/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0120/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0120/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0120/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0120/006.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ssch-kit-0121</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0121/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0121/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0121/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0121/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0121/006.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ssch-kit-0122</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0122/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0122/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0122/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0122/005.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ssch-kit-0123</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0123/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0123/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0123/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0123/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0123/006.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ssch-kit-0124</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0124/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0124/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0124/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0124/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0124/006.jpg</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ssch-kit-0125</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0125/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0125/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0125/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0125/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0125/006.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ssch-kit-0126</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0126/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0126/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0126/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0126/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0126/006.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ssch-kit-0127</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0127/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0127/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0127/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0127/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0127/006.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ssch-kit-0128</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0128/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0128/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0128/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0128/005.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ssch-kit-0129</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0129/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0129/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0129/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0129/005.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ssch-kit-0130</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0130/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0130/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0130/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0130/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0130/006.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ssch-kit-0131</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0131/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0131/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0131/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0131/005.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ssch-kit-0132</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0132/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0132/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0132/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0132/005.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ssch-kit-0133</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0133/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0133/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0133/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0133/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0133/006.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ssch-kit-0134</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0134/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0134/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0134/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0134/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0134/006.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ssch-kit-0136</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0136/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0136/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0136/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0136/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0136/006.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ssch-kit-0137</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0137/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0137/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0137/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0137/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0137/006.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ssch-kit-0138</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0138/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0138/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0138/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0138/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0138/006.jpg</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ssch-kit-0139</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0139/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0139/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0139/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0139/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0139/006.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ssch-kit-0140</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0140/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0140/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0140/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0140/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0140/006.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ssch-kit-0141</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0141/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0141/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0141/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0141/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0141/006.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ssch-kit-0142</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0142/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0142/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0142/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0142/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0142/006.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ssch-kit-0143</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0143/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0143/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0143/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0143/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0143/006.jpg</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ssch-kit-0144</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0144/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0144/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0144/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0144/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0144/006.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ssch-kit-0145</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0145/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0145/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0145/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0145/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0145/006.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ssch-kit-0146</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0146/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0146/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0146/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0146/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0146/006.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ssch-kit-0147</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0147/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0147/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0147/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0147/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0147/006.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ssch-kit-0148</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0148/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0148/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0148/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0148/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0148/006.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ssch-kit-0149</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0149/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0149/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0149/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0149/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0149/006.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ssch-kit-0150</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0150/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0150/003.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0150/004.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0150/005.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0150/006.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ssch-kit-0151</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ssch-kit-0151/001.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0151/002.jpg,https://oleks-netizen.github.io/product-images/ssch-kit-0151/003.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>tk-38kit-0013</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-38kit-0013/001.jpg,https://oleks-netizen.github.io/product-images/tk-38kit-0013/003.jpg,https://oleks-netizen.github.io/product-images/tk-38kit-0013/004.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>tk-4-nw-001</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-001/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-001/003.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-001/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-001/005.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-001/006.jpg</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>tk-4-nw-002</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-002/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-002/002.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-002/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-002/005.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-002/006.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>tk-4-nw-003</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-003/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-003/003.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-003/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-003/005.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-003/006.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>tk-4-nw-004</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-004/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-004/003.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-004/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-004/005.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-004/006.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>tk-4-nw-005</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-005/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-005/003.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-005/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-005/005.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>tk-4-nw-006</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-4-nw-006/001.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-006/003.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-006/004.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-006/005.jpg,https://oleks-netizen.github.io/product-images/tk-4-nw-006/006.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>tk-40kit-0012</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tk-40kit-0012/001.jpg,https://oleks-netizen.github.io/product-images/tk-40kit-0012/003.jpg,https://oleks-netizen.github.io/product-images/tk-40kit-0012/004.jpg,https://oleks-netizen.github.io/product-images/tk-40kit-0012/005.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>tkn-38-tkt-0010</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/001.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/002.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/003.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/004.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/006.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0010/007.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>tkn-38-tkt-0011</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/001.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/002.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/003.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/005.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/006.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0011/007.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>tkn-38-tkt-0012</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-38-tkt-0012/001.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0012/002.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0012/004.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-0012/005.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>tkn-38-tkt-009</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-38-tkt-009/001.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-009/003.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-009/004.jpg,https://oleks-netizen.github.io/product-images/tkn-38-tkt-009/005.jpg</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>tkn-40-tkt-004</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-40-tkt-004/001.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-004/002.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-004/004.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-004/005.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-004/006.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>tkn-40-tkt-006</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-40-tkt-006/001.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-006/002.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-006/003.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-006/005.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-006/006.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>tkn-40-tkt-008</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-40-tkt-008/001.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-008/002.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-008/003.jpg,https://oleks-netizen.github.io/product-images/tkn-40-tkt-008/005.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-001</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/008.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/009.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-001/010.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0010</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0010/007.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0011</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0011/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0011/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0011/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0011/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0011/006.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0012</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0012/007.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0013</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0013/007.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0014</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0014/008.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0015</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0015/008.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0016</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/008.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0016/009.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0017</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0017/008.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0018</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0018/008.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0019</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0019/008.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0020</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0020/008.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0021</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0021/008.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0022</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0022/008.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0023</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0023/008.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0024</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0024/008.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0025</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0025/008.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-0026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/004.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-0026/008.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>tkn-dvst-38k-005</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/001.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/002.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/003.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/005.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/006.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/007.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/008.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/009.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/010.jpg,https://oleks-netizen.github.io/product-images/tkn-dvst-38k-005/011.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tkst-3K-007</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-007/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-007/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-007/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-007/005.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-007/006.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>tkst-3K-008</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-008/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-008/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-008/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-008/005.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-008/006.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>tkst-3K-009</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-009/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-009/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-009/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-009/005.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-009/006.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>tkst-3K-010</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-010/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-010/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-010/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-010/005.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-010/006.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>tkst-3K-011</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-011/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-011/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-011/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-011/005.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-011/006.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>tkst-3K-012</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-012/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-012/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-012/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-012/005.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>tkst-3K-013</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-013/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-013/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-013/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-013/005.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>tkst-3K-014</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/tkst-3K-014/001.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-014/002.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-014/004.jpg,https://oleks-netizen.github.io/product-images/tkst-3K-014/005.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0103</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0103/001.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-33k-0103/002.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-33k-0103/004.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0103-1</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0103-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0103-2</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0103-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0104</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0104/001.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-33k-0104/002.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-33k-0104/004.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0104-1</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0104-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>wtro-kit-33k-0104-2</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-33k-0104-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0215</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215/001.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215/003.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215/004.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0215-1</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0215-2</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0215-3</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0215-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216/001.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216/003.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216/004.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0216-1</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0216-2</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0216-3</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0216-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0217</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217/001.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217/002.jpg,https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217/004.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0217-1</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0217-2</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>wtro-kit-38k-0217-3</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-kit-38k-0217-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0067</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067/004.jpg</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0067-1</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0067-2</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0067-3</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0067-4</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0067-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0068</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068/004.jpg</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0068-1</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0068-2</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0068-3</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0068-4</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0068-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0069</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069/004.jpg</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0069-1</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0069-2</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0069-3</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0069-4</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0069-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0070</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070/004.jpg</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0070-1</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0070-2</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0070-3</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0070-4</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0070-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0071</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071/004.jpg</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0071-1</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0071-2</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0071-3</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0071-4</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0071-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0072</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072/004.jpg</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0072-1</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0072-2</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0072-3</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0072-4</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0072-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0073</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073/004.jpg</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0073-1</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0073-3</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0073-4</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0073-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0074</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074/004.jpg</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0074-</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074-/001.jpg</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0074-1</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0074-2</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0074-3</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0074-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0075</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075/004.jpg</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0075-1</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0075-2</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0075-3</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0075-4</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0075-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0076</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076/004.jpg</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0076-1</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0076-2</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0076-3</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0076-4</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0076-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0077</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077/004.jpg</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0077-1</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0077-2</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0077-3</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0077-4</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0077-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0078</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078/004.jpg</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0078-1</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0078-2</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0078-3</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0078-4</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0078-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0079</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079/004.jpg</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0079-1</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0079-2</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0079-3</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0079-4</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0079-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0080</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080/004.jpg</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0080-2</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0080-3</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0080-4</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0080-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0081</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081/004.jpg</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0081-1</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0081-2</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0081-3</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0081-4</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0081-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0082</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082/004.jpg</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0082-1</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0082-2</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0082-3</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0082-4</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0082-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0083</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083/004.jpg</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0083-1</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0083-2</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0083-3</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0083-4</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0083-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0084</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084/004.jpg</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0084-1</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0084-2</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0084-3</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0084-4</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0084-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0105</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105/004.jpg</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0105-1</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0105-2</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0105-3</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0105-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0106</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106/004.jpg</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0106-1</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0106-2</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0106-3</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0106-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0107</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107/004.jpg</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0107-1</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0107-2</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0107-3</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0107-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0108</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108/004.jpg</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0108-1</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0108-2</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0108-3</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0108-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0109</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109/004.jpg</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0109-1</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0109-2</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0109-3</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0109-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0110</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0110/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0110/003.jpg</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0110-1</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0110-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0110-2</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0110-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0110-3</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0110-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0111</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111/004.jpg</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0111-1</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0111-2</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0111-3</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0111-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0112</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112/004.jpg</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0112-1</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0112-2</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0112-3</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0112-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0113</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113/004.jpg</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0113-1</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0113-2</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0113-3</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0113-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0114</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114/004.jpg</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0114-1</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0114-2</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>wtro-tur-33k-0114-3</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-33k-0114-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0018-2</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0018-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0018-3</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0018-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0100-1</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0100-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0100-2</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0100-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0101-1</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0101-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0101-2</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0101-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0102-1</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0102-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0102-2</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0102-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0115</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115/004.jpg</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0115-1</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0115-2</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0115-3</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0115-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0116</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116/004.jpg</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0116-1</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0116-2</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0116-3</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0116-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0117</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117/004.jpg</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0117-1</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0117-2</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0117-3</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0117-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0118</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118/004.jpg</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0118-1</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0118-2</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0118-3</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0118-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0119</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119/004.jpg</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0119-1</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0119-2</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0119-3</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0119-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0120</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120/004.jpg</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0120-1</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0120-2</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0120-3</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0120-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0121</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121/004.jpg</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0121-1</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0121-2</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0121-3</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0121-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0122</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122/004.jpg</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0122-1</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0122-2</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0122-3</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0122-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0200</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200/004.jpg</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0200-1</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0200-2</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0200-3</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0200-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0201</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201/004.jpg</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0201-1</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0201-2</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0201-3</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0201-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0202</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202/004.jpg</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0202-1</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0202-2</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0202-3</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0202-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0203</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203/004.jpg</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0203-1</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0203-2</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0203-3</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0203-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0204</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204/004.jpg</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0204-1</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0204-2</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0204-3</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0204-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0205</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205/004.jpg</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0205-1</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0205-2</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0205-3</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0205-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0206</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206/004.jpg</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0206-1</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0206-2</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0206-3</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0206-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0207</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207/004.jpg</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0207-1</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0207-2</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0207-3</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0207-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0208</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208/004.jpg</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0208-1</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0208-2</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0208-3</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0208-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0209</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209/004.jpg</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0209-1</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0209-2</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0209-3</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0209-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0210</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210/004.jpg</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0210-1</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0210-2</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>wtro-ua-33k-0210-3</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-33k-0210-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0211</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211/004.jpg</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0211-1</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0211-2</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0211-3</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0211-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0212</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212/004.jpg</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0212-1</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0212-2</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0212-3</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0212-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0213</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213/004.jpg</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0213-1</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0213-2</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0213-3</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0213-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0214</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214/004.jpg</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0214-1</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0214-2</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0214-3</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0214-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0218</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218/004.jpg</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0218-1</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0218-2</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0218-3</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0218-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0219</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219/004.jpg</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0219-1</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0219-2</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0219-3</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0219-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0220</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220/004.jpg</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0220-1</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0220-2</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0220-3</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0220-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0221</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221/004.jpg</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0221-1</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0221-2</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0221-3</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0221-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0222</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222/004.jpg</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0222-1</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0222-2</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0222-3</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0222-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,207 +436,207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11405217622222</t>
+          <t>0060zh-4k-tur</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11405217622222/001.jpg,https://oleks-netizen.github.io/product-images/11405217622222/002.jpg,https://oleks-netizen.github.io/product-images/11405217622222/003.jpg,https://oleks-netizen.github.io/product-images/11405217622222/004.jpg,https://oleks-netizen.github.io/product-images/11405217622222/005.jpg,https://oleks-netizen.github.io/product-images/11405217622222/006.jpg,https://oleks-netizen.github.io/product-images/11405217622222/007.jpg,https://oleks-netizen.github.io/product-images/11405217622222/008.jpg,https://oleks-netizen.github.io/product-images/11405217622222/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0060zh-4k-tur/001.jpg,https://oleks-netizen.github.io/product-images/0060zh-4k-tur/002.jpg,https://oleks-netizen.github.io/product-images/0060zh-4k-tur/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11405217632222</t>
+          <t>0359m-4kozh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11405217632222/001.jpg,https://oleks-netizen.github.io/product-images/11405217632222/002.jpg,https://oleks-netizen.github.io/product-images/11405217632222/003.jpg,https://oleks-netizen.github.io/product-images/11405217632222/004.jpg,https://oleks-netizen.github.io/product-images/11405217632222/005.jpg,https://oleks-netizen.github.io/product-images/11405217632222/006.jpg,https://oleks-netizen.github.io/product-images/11405217632222/007.jpg,https://oleks-netizen.github.io/product-images/11405217632222/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0359m-4kozh/001.jpg,https://oleks-netizen.github.io/product-images/0359m-4kozh/002.jpg,https://oleks-netizen.github.io/product-images/0359m-4kozh/004.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11405217642222</t>
+          <t>0360m-4kozh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11405217642222/001.jpg,https://oleks-netizen.github.io/product-images/11405217642222/002.jpg,https://oleks-netizen.github.io/product-images/11405217642222/003.jpg,https://oleks-netizen.github.io/product-images/11405217642222/004.jpg,https://oleks-netizen.github.io/product-images/11405217642222/005.jpg,https://oleks-netizen.github.io/product-images/11405217642222/006.jpg,https://oleks-netizen.github.io/product-images/11405217642222/007.jpg,https://oleks-netizen.github.io/product-images/11405217642222/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0360m-4kozh/001.jpg,https://oleks-netizen.github.io/product-images/0360m-4kozh/002.jpg,https://oleks-netizen.github.io/product-images/0360m-4kozh/004.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11406217652222</t>
+          <t>0363m-4kozh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11406217652222/001.jpg,https://oleks-netizen.github.io/product-images/11406217652222/002.jpg,https://oleks-netizen.github.io/product-images/11406217652222/003.jpg,https://oleks-netizen.github.io/product-images/11406217652222/004.jpg,https://oleks-netizen.github.io/product-images/11406217652222/005.jpg,https://oleks-netizen.github.io/product-images/11406217652222/006.jpg,https://oleks-netizen.github.io/product-images/11406217652222/007.jpg,https://oleks-netizen.github.io/product-images/11406217652222/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/0363m-4kozh/001.jpg,https://oleks-netizen.github.io/product-images/0363m-4kozh/002.jpg,https://oleks-netizen.github.io/product-images/0363m-4kozh/004.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11406217662222</t>
+          <t>jns-nw4k-rus-035</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11406217662222/001.jpg,https://oleks-netizen.github.io/product-images/11406217662222/002.jpg,https://oleks-netizen.github.io/product-images/11406217662222/003.jpg,https://oleks-netizen.github.io/product-images/11406217662222/004.jpg,https://oleks-netizen.github.io/product-images/11406217662222/005.jpg,https://oleks-netizen.github.io/product-images/11406217662222/006.jpg,https://oleks-netizen.github.io/product-images/11406217662222/007.jpg,https://oleks-netizen.github.io/product-images/11406217662222/008.jpg,https://oleks-netizen.github.io/product-images/11406217662222/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-rus-035/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-rus-035/003.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11406217672222</t>
+          <t>jns-nw4k-rus-037</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11406217672222/001.jpg,https://oleks-netizen.github.io/product-images/11406217672222/002.jpg,https://oleks-netizen.github.io/product-images/11406217672222/003.jpg,https://oleks-netizen.github.io/product-images/11406217672222/004.jpg,https://oleks-netizen.github.io/product-images/11406217672222/005.jpg,https://oleks-netizen.github.io/product-images/11406217672222/006.jpg,https://oleks-netizen.github.io/product-images/11406217672222/007.jpg,https://oleks-netizen.github.io/product-images/11406217672222/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-rus-037/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-rus-037/003.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11407217682222</t>
+          <t>jns-nw4k-rus-038</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11407217682222/001.jpg,https://oleks-netizen.github.io/product-images/11407217682222/002.jpg,https://oleks-netizen.github.io/product-images/11407217682222/003.jpg,https://oleks-netizen.github.io/product-images/11407217682222/004.jpg,https://oleks-netizen.github.io/product-images/11407217682222/005.jpg,https://oleks-netizen.github.io/product-images/11407217682222/006.jpg,https://oleks-netizen.github.io/product-images/11407217682222/007.jpg,https://oleks-netizen.github.io/product-images/11407217682222/008.jpg,https://oleks-netizen.github.io/product-images/11407217682222/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-rus-038/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-rus-038/003.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11407217692222</t>
+          <t>jns-nw4k-ua-003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11407217692222/001.jpg,https://oleks-netizen.github.io/product-images/11407217692222/002.jpg,https://oleks-netizen.github.io/product-images/11407217692222/003.jpg,https://oleks-netizen.github.io/product-images/11407217692222/004.jpg,https://oleks-netizen.github.io/product-images/11407217692222/005.jpg,https://oleks-netizen.github.io/product-images/11407217692222/006.jpg,https://oleks-netizen.github.io/product-images/11407217692222/007.jpg,https://oleks-netizen.github.io/product-images/11407217692222/008.jpg,https://oleks-netizen.github.io/product-images/11407217692222/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-003/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-003/003.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11407217702222</t>
+          <t>jns-nw4k-ua-004</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/11407217702222/001.jpg,https://oleks-netizen.github.io/product-images/11407217702222/002.jpg,https://oleks-netizen.github.io/product-images/11407217702222/003.jpg,https://oleks-netizen.github.io/product-images/11407217702222/004.jpg,https://oleks-netizen.github.io/product-images/11407217702222/005.jpg,https://oleks-netizen.github.io/product-images/11407217702222/006.jpg,https://oleks-netizen.github.io/product-images/11407217702222/007.jpg,https://oleks-netizen.github.io/product-images/11407217702222/008.jpg,https://oleks-netizen.github.io/product-images/11407217702222/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-004/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-004/003.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18sm-ua-085-1</t>
+          <t>jns-nw4k-ua-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18sm-ua-085-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-010/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-010/003.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18sm-ua-085-2</t>
+          <t>jns-nw4k-ua-017</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18sm-ua-085-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-017/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-017/003.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18sm-ua-085-3</t>
+          <t>jns-nw4k-ua-018</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18sm-ua-085-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-018/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-018/003.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28sm-zmshua-132-4</t>
+          <t>jns-nw4k-ua-020</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/28sm-zmshua-132-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-020/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-020/003.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BN-OP-36-g</t>
+          <t>jns-nw4k-ua-025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-36-g/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-g/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-025/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-025/003.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,1617 +646,1617 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BN-OP-36-iz</t>
+          <t>jns-nw4k-ua-032</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-36-iz/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/004.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/005.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/006.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/007.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/008.jpg,https://oleks-netizen.github.io/product-images/BN-OP-36-iz/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/jns-nw4k-ua-032/001.jpg,https://oleks-netizen.github.io/product-images/jns-nw4k-ua-032/003.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BN-OP-37-choko</t>
+          <t>kbra-lmn-kozh-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-37-choko/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-choko/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-choko/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-choko/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/001.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/002.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/003.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/004.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/005.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/006.jpg,https://oleks-netizen.github.io/product-images/kbra-lmn-kozh-01/008.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BN-OP-37-k-kr</t>
+          <t>kobura-lmn-001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-OP-37-k-kr/001.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-k-kr/002.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-k-kr/003.jpg,https://oleks-netizen.github.io/product-images/BN-OP-37-k-kr/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kobura-lmn-001/001.jpg,https://oleks-netizen.github.io/product-images/kobura-lmn-001/002.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BN-PM-7-vin-kr-ls</t>
+          <t>kobura-lmn-002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-PM-7-vin-kr-ls/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-7-vin-kr-ls/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-7-vin-kr-ls/003.jpg,https://oleks-netizen.github.io/product-images/BN-PM-7-vin-kr-ls/004.jpg,https://oleks-netizen.github.io/product-images/BN-PM-7-vin-kr-ls/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kobura-lmn-002/001.jpg,https://oleks-netizen.github.io/product-images/kobura-lmn-002/002.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HF514 CROC PLN BRN</t>
+          <t>kobura-lmn-003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/HF514 CROC PLN BRN/001.jpg,https://oleks-netizen.github.io/product-images/HF514 CROC PLN BRN/002.jpg,https://oleks-netizen.github.io/product-images/HF514 CROC PLN BRN/004.jpg,https://oleks-netizen.github.io/product-images/HF514 CROC PLN BRN/005.jpg,https://oleks-netizen.github.io/product-images/HF514 CROC PLN BRN/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kobura-lmn-003/001.jpg,https://oleks-netizen.github.io/product-images/kobura-lmn-003/002.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0016-1</t>
+          <t>kobura-lmn-004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0016-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kobura-lmn-004/001.jpg,https://oleks-netizen.github.io/product-images/kobura-lmn-004/002.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0016-2</t>
+          <t>kobura-lmn-005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0016-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/kobura-lmn-005/001.jpg,https://oleks-netizen.github.io/product-images/kobura-lmn-005/002.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0017-1</t>
+          <t>lmn-mk38ua-012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0017-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-012/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-012/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-012/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-012/005.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0017-2</t>
+          <t>lmn-mk38ua-013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0017-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-013/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-013/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-013/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-013/005.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0018-1</t>
+          <t>lmn-mk38ua-014</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0018-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-014/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-014/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-014/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-014/005.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0018-2</t>
+          <t>lmn-mk38ua-015</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0018-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-015/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-015/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-015/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-015/005.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0019-1</t>
+          <t>lmn-mk38ua-016</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0019-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-016/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-016/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-016/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-016/005.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0019-2</t>
+          <t>lmn-mk38ua-017</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0019-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-017/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-017/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-017/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-017/005.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0020-1</t>
+          <t>lmn-mk38ua-018</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0020-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-018/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-018/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-018/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-018/005.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0020-2</t>
+          <t>lmn-mk38ua-020</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0020-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-020/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-020/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-020/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-020/005.jpg</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0021-1</t>
+          <t>lmn-mk38ua-021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0021-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-021/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-021/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-021/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-021/005.jpg</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0021-2</t>
+          <t>lmn-mk38ua-022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0021-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-022/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-022/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-022/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-022/005.jpg</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0022-1</t>
+          <t>lmn-mk38ua-023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0022-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-023/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-023/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-023/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-023/005.jpg</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lmn-tur-35k-0022-2</t>
+          <t>lmn-mk38ua-024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-35k-0022-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-024/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-024/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-024/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-024/005.jpg</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0010-1</t>
+          <t>lmn-mk38ua-025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0010-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-025/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-025/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-025/004.jpg</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0010-2</t>
+          <t>lmn-mk38ua-026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0010-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-026/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-026/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-026/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-026/005.jpg</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0011-1</t>
+          <t>lmn-mk38ua-027</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0011-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk38ua-027/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-027/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-027/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk38ua-027/005.jpg</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0011-2</t>
+          <t>lmn-mk43ua-028</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0011-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk43ua-028/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-028/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-028/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-028/005.jpg</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0012-1</t>
+          <t>lmn-mk43ua-029</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0012-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk43ua-029/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-029/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-029/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-029/005.jpg</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0012-2</t>
+          <t>lmn-mk43ua-030</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0012-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk43ua-030/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-030/002.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-030/004.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-030/005.jpg</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0013-1</t>
+          <t>lmn-mk43ua-032</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0013-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk43ua-032/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-032/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-032/004.jpg</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0013-2</t>
+          <t>lmn-mk43ua-033</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0013-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-mk43ua-033/001.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-033/003.jpg,https://oleks-netizen.github.io/product-images/lmn-mk43ua-033/004.jpg</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0014-1</t>
+          <t>lmn-tur-40k-001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0014-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-001/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-001/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-001/004.jpg</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0014-2</t>
+          <t>lmn-tur-40k-002</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0014-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-002/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-002/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-002/004.jpg</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0015-1</t>
+          <t>lmn-tur-40k-003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0015-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-003/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-003/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-003/004.jpg</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-0015-2</t>
+          <t>lmn-tur-40k-004</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-0015-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-004/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-004/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-004/004.jpg</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-008-1</t>
+          <t>lmn-tur-40k-005</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-008-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-005/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-005/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-005/004.jpg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-008-2</t>
+          <t>lmn-tur-40k-006</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-008-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-006/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-006/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-006/004.jpg</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-009-1</t>
+          <t>lmn-tur-40k-007</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-009-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-007/001.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-007/002.jpg,https://oleks-netizen.github.io/product-images/lmn-tur-40k-007/004.jpg</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>lmn-tur-40k-009-2</t>
+          <t>m-45kozh-0388</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/lmn-tur-40k-009-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-45kozh-0388/001.jpg,https://oleks-netizen.github.io/product-images/m-45kozh-0388/003.jpg,https://oleks-netizen.github.io/product-images/m-45kozh-0388/004.jpg</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ua-23cmk-001-1</t>
+          <t>m-45kozh-0389</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-001-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/m-45kozh-0389/001.jpg,https://oleks-netizen.github.io/product-images/m-45kozh-0389/003.jpg,https://oleks-netizen.github.io/product-images/m-45kozh-0389/004.jpg</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ua-23cmk-001-2</t>
+          <t>mk-35tur-003</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-001-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-35tur-003/001.jpg,https://oleks-netizen.github.io/product-images/mk-35tur-003/003.jpg</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ua-23cmk-001-3</t>
+          <t>mk-40tur-0012</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-001-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0012/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0012/003.jpg</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ua-23cmk-001-4</t>
+          <t>mk-40tur-0013</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-001-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0013/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0013/003.jpg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ua-23cmk-002-1</t>
+          <t>mk-40tur-0014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-002-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0014/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0014/003.jpg</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ua-23cmk-002-2</t>
+          <t>mk-40tur-0015</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-002-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0015/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0015/003.jpg</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ua-23cmk-002-3</t>
+          <t>mk-40tur-0016</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-002-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0016/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0016/003.jpg</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ua-23cmk-002-4</t>
+          <t>mk-40tur-0017</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-002-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0017/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0017/003.jpg</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ua-23cmk-003-1</t>
+          <t>mk-40tur-0018</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-003-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0018/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0018/003.jpg</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ua-23cmk-003-2</t>
+          <t>mk-40tur-0019</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-003-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0019/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0019/003.jpg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ua-23cmk-003-3</t>
+          <t>mk-40tur-0020</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-003-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-40tur-0020/001.jpg,https://oleks-netizen.github.io/product-images/mk-40tur-0020/003.jpg</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ua-23cmk-003-4</t>
+          <t>mk-45tur-0024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-003-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-45tur-0024/001.jpg,https://oleks-netizen.github.io/product-images/mk-45tur-0024/003.jpg</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ua-23cmk-004-1</t>
+          <t>mk-45tur-0029</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-004-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-45tur-0029/001.jpg,https://oleks-netizen.github.io/product-images/mk-45tur-0029/003.jpg</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ua-23cmk-004-2</t>
+          <t>mk-45tur-0030</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-004-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mk-45tur-0030/001.jpg,https://oleks-netizen.github.io/product-images/mk-45tur-0030/003.jpg</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ua-23cmk-004-3</t>
+          <t>mnk40rus-014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-004-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk40rus-014/001.jpg,https://oleks-netizen.github.io/product-images/mnk40rus-014/003.jpg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ua-23cmk-004-4</t>
+          <t>mnk40ua-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-004-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk40ua-01/001.jpg,https://oleks-netizen.github.io/product-images/mnk40ua-01/003.jpg</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ua-23cmk-005-1</t>
+          <t>mnk40ua-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-005-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk40ua-02/001.jpg,https://oleks-netizen.github.io/product-images/mnk40ua-02/003.jpg</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ua-23cmk-005-2</t>
+          <t>mnk40ua-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-005-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk40ua-03/001.jpg,https://oleks-netizen.github.io/product-images/mnk40ua-03/003.jpg</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ua-23cmk-005-3</t>
+          <t>mnk40ua-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-005-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk40ua-06/001.jpg,https://oleks-netizen.github.io/product-images/mnk40ua-06/003.jpg</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ua-23cmk-005-4</t>
+          <t>mnk45ua-010</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-005-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk45ua-010/001.jpg,https://oleks-netizen.github.io/product-images/mnk45ua-010/003.jpg</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ua-23cmk-006-1</t>
+          <t>mnk45ua-011</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-006-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk45ua-011/001.jpg,https://oleks-netizen.github.io/product-images/mnk45ua-011/003.jpg</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ua-23cmk-006-2</t>
+          <t>mnk45ua-013</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-006-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnk45ua-013/001.jpg,https://oleks-netizen.github.io/product-images/mnk45ua-013/003.jpg</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ua-23cmk-006-3</t>
+          <t>mnw-40tur-017</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-006-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnw-40tur-017/001.jpg,https://oleks-netizen.github.io/product-images/mnw-40tur-017/003.jpg</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ua-23cmk-006-4</t>
+          <t>mnw-45tur-021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-006-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnw-45tur-021/001.jpg,https://oleks-netizen.github.io/product-images/mnw-45tur-021/003.jpg</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ua-23cmk-007-1</t>
+          <t>mnw-45tur-022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-007-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnw-45tur-022/001.jpg,https://oleks-netizen.github.io/product-images/mnw-45tur-022/003.jpg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ua-23cmk-007-2</t>
+          <t>mnw-45tur-023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-007-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnw-45tur-023/001.jpg,https://oleks-netizen.github.io/product-images/mnw-45tur-023/003.jpg</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ua-23cmk-007-3</t>
+          <t>mnwb-40tur-010</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-007-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnwb-40tur-010/001.jpg,https://oleks-netizen.github.io/product-images/mnwb-40tur-010/003.jpg</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ua-23cmk-007-4</t>
+          <t>mnwb-40tur-011</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-007-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/mnwb-40tur-011/001.jpg,https://oleks-netizen.github.io/product-images/mnwb-40tur-011/003.jpg</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ua-23cmk-008-1</t>
+          <t>new-m-40k-020</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-008-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-020/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-020/002.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-020/004.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-020/005.jpg</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ua-23cmk-008-2</t>
+          <t>new-m-40k-021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-008-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-021/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-021/002.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-021/003.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-021/005.jpg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ua-23cmk-008-3</t>
+          <t>new-m-40k-023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-008-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-023/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-023/003.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-023/004.jpg</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ua-23cmk-008-4</t>
+          <t>new-m-40k-027</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-008-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-027/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-027/003.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-027/004.jpg</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ua-23cmk-009-1</t>
+          <t>new-m-40k-032</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-009-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-032/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-032/003.jpg</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ua-23cmk-009-2</t>
+          <t>new-m-40k-034</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-009-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-034/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-034/002.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-034/004.jpg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ua-23cmk-009-3</t>
+          <t>new-m-40k-035</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-009-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-035/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-035/003.jpg</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ua-23cmk-009-4</t>
+          <t>new-m-40k-038</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-23cmk-009-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-038/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-038/003.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-038/004.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-038/005.jpg</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ua-33cmk-0010-1</t>
+          <t>new-m-40k-040</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0010-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-040/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-040/002.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-040/004.jpg</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ua-33cmk-0010-2</t>
+          <t>new-m-40k-041</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0010-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-041/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-041/002.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-041/004.jpg</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ua-33cmk-0010-3</t>
+          <t>new-m-40k-042</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0010-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/new-m-40k-042/001.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-042/003.jpg,https://oleks-netizen.github.io/product-images/new-m-40k-042/004.jpg</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ua-33cmk-0010-4</t>
+          <t>nw-bel-m4k-0014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0010-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-bel-m4k-0014/001.jpg,https://oleks-netizen.github.io/product-images/nw-bel-m4k-0014/003.jpg,https://oleks-netizen.github.io/product-images/nw-bel-m4k-0014/004.jpg</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ua-33cmk-0011-1</t>
+          <t>nw-k-208-00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0011-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-208-00/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-208-00/002.jpg,https://oleks-netizen.github.io/product-images/nw-k-208-00/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-208-00/004.jpg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ua-33cmk-0011-2</t>
+          <t>nw-k-800-2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0011-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-800-2/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-800-2/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-800-2/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-800-2/005.jpg</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ua-33cmk-0011-3</t>
+          <t>nw-k-8916-13-1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0011-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-8916-13-1/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-13-1/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-13-1/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-13-1/005.jpg</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ua-33cmk-0011-4</t>
+          <t>nw-k-8916-14-1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0011-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-8916-14-1/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-14-1/002.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-14-1/004.jpg</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ua-33cmk-0012-1</t>
+          <t>nw-k-8916-15-1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0012-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-8916-15-1/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-15-1/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-15-1/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-8916-15-1/005.jpg</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ua-33cmk-0012-2</t>
+          <t>nw-k-F30010</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0012-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-F30010/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-F30010/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-F30010/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-F30010/005.jpg,https://oleks-netizen.github.io/product-images/nw-k-F30010/006.jpg</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ua-33cmk-0012-3</t>
+          <t>nw-k-F9903-2W</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0012-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-k-F9903-2W/001.jpg,https://oleks-netizen.github.io/product-images/nw-k-F9903-2W/003.jpg,https://oleks-netizen.github.io/product-images/nw-k-F9903-2W/004.jpg,https://oleks-netizen.github.io/product-images/nw-k-F9903-2W/005.jpg</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ua-33cmk-0012-4</t>
+          <t>nw-rus-m4k-0030</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0012-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0030/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0030/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0030/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0030/005.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0030/006.jpg</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ua-33cmk-0013-1</t>
+          <t>nw-rus-m4k-0033</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0013-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0033/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0033/003.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0033/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0033/005.jpg</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ua-33cmk-0013-2</t>
+          <t>nw-rus-m4k-0039</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0013-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0039/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0039/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0039/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0039/005.jpg</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ua-33cmk-0013-3</t>
+          <t>nw-rus-m4k-0041</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0013-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0041/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0041/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0041/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0041/005.jpg</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ua-33cmk-0013-4</t>
+          <t>nw-rus-m4k-0044</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0013-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0044/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0044/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0044/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0044/005.jpg</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ua-33cmk-0014-1</t>
+          <t>nw-rus-m4k-0046</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0014-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0046/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0046/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0046/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0046/005.jpg</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ua-33cmk-0014-2</t>
+          <t>nw-rus-m4k-0047</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0014-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0047/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0047/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0047/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0047/005.jpg</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ua-33cmk-0014-3</t>
+          <t>nw-rus-m4k-0050</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0014-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-rus-m4k-0050/001.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0050/002.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0050/004.jpg,https://oleks-netizen.github.io/product-images/nw-rus-m4k-0050/005.jpg</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ua-33cmk-0014-4</t>
+          <t>nw-tur-40k-0024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0014-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-40k-0024/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-40k-0024/003.jpg</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ua-33cmk-0015-1</t>
+          <t>nw-tur-40k-0025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0015-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-40k-0025/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-40k-0025/003.jpg</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ua-33cmk-0015-2</t>
+          <t>nw-tur-40k-0026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0015-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-40k-0026/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-40k-0026/003.jpg</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ua-33cmk-0015-3</t>
+          <t>nw-tur-m4k-0008</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0015-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-m4k-0008/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0008/003.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0008/004.jpg</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ua-33cmk-0015-4</t>
+          <t>nw-tur-m4k-0009</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33cmk-0015-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-m4k-0009/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0009/003.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0009/004.jpg</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ua-33mkr-0012-1</t>
+          <t>nw-tur-m4k-0011</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0012-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-m4k-0011/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0011/003.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0011/004.jpg</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ua-33mkr-0012-2</t>
+          <t>nw-tur-m4k-0012</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0012-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-m4k-0012/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0012/002.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0012/004.jpg</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ua-33mkr-0012-3</t>
+          <t>nw-tur-m4k-0013</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0012-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-tur-m4k-0013/001.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0013/003.jpg,https://oleks-netizen.github.io/product-images/nw-tur-m4k-0013/004.jpg</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ua-33mkr-0012-4</t>
+          <t>nw-ua-m4k-005</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0012-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-ua-m4k-005/001.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-005/003.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-005/004.jpg</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ua-33mkr-0014-1</t>
+          <t>nw-ua-m4k-006</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-ua-m4k-006/001.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-006/003.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-006/004.jpg</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ua-33mkr-0014-2</t>
+          <t>nw-ua-m4k-007</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-ua-m4k-007/001.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-007/003.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-007/004.jpg</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ua-33mkr-0014-3</t>
+          <t>nw-ua-m4k-008</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-ua-m4k-008/001.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-008/003.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-008/004.jpg</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ua-33mkr-0014-4</t>
+          <t>nw-ua-m4k-025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nw-ua-m4k-025/001.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-025/003.jpg,https://oleks-netizen.github.io/product-images/nw-ua-m4k-025/004.jpg</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ua-33mkr-0015-1</t>
+          <t>nwkit-m4k-001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0015-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwkit-m4k-001/001.jpg,https://oleks-netizen.github.io/product-images/nwkit-m4k-001/003.jpg</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ua-33mkr-0015-2</t>
+          <t>nwkit-m4k-002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0015-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwkit-m4k-002/001.jpg,https://oleks-netizen.github.io/product-images/nwkit-m4k-002/003.jpg</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ua-33mkr-0015-3</t>
+          <t>nwkit-m4k-003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0015-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/nwkit-m4k-003/001.jpg,https://oleks-netizen.github.io/product-images/nwkit-m4k-003/003.jpg</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ua-33mkr-0015-4</t>
+          <t>roza-ua-38k-010</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0015-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-010/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-010/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-010/004.jpg</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ua-33mkr-009-1</t>
+          <t>roza-ua-38k-010-1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-009-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-010-1/001.jpg</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2266,12 +2266,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ua-33mkr-009-2</t>
+          <t>roza-ua-38k-010-2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-009-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-010-2/001.jpg</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2281,12 +2281,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ua-33mkr-009-3</t>
+          <t>roza-ua-38k-010-3</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-009-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-010-3/001.jpg</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2296,27 +2296,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ua-33mkr-009-4</t>
+          <t>roza-ua-38k-011</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-009-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-011/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-011/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-011/004.jpg</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ua-38mkr-0016-1</t>
+          <t>roza-ua-38k-011-1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0016-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-011-1/001.jpg</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2326,12 +2326,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ua-38mkr-0016-2</t>
+          <t>roza-ua-38k-011-2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0016-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-011-2/001.jpg</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2341,12 +2341,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ua-38mkr-0016-3</t>
+          <t>roza-ua-38k-011-3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0016-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-011-3/001.jpg</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2356,27 +2356,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ua-38mkr-0016-4</t>
+          <t>roza-ua-38k-012</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0016-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-012/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-012/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-012/004.jpg</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ua-38mkr-0017-1</t>
+          <t>roza-ua-38k-012-1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0017-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-012-1/001.jpg</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2386,12 +2386,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ua-38mkr-0017-2</t>
+          <t>roza-ua-38k-012-2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0017-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-012-2/001.jpg</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2401,12 +2401,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ua-38mkr-0017-3</t>
+          <t>roza-ua-38k-012-3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0017-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-012-3/001.jpg</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2416,27 +2416,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ua-38mkr-0018-1</t>
+          <t>roza-ua-38k-013</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0018-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-013/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-013/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-013/004.jpg</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ua-38mkr-0018-2</t>
+          <t>roza-ua-38k-013-1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0018-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-013-1/001.jpg</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2446,12 +2446,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ua-38mkr-0018-3</t>
+          <t>roza-ua-38k-013-2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0018-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-013-2/001.jpg</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2461,12 +2461,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ua-38mkr-0018-4</t>
+          <t>roza-ua-38k-013-3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0018-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-013-3/001.jpg</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2476,27 +2476,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ua-38mkr-0019-1</t>
+          <t>roza-ua-38k-014</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0019-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-014/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-014/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-014/004.jpg</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ua-38mkr-0019-2</t>
+          <t>roza-ua-38k-014-1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0019-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-014-1/001.jpg</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2506,12 +2506,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ua-38mkr-0019-3</t>
+          <t>roza-ua-38k-014-2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0019-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-014-2/001.jpg</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2521,12 +2521,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ua-38mkr-0019-4</t>
+          <t>roza-ua-38k-014-3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0019-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-014-3/001.jpg</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2536,27 +2536,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ua-38mkr-0020-1</t>
+          <t>roza-ua-38k-015</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0020-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-015/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-015/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-015/004.jpg</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ua-38mkr-0020-2</t>
+          <t>roza-ua-38k-015-1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0020-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-015-1/001.jpg</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2566,12 +2566,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ua-38mkr-0020-3</t>
+          <t>roza-ua-38k-015-2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0020-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-015-2/001.jpg</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2581,12 +2581,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ua-38mkr-0020-4</t>
+          <t>roza-ua-38k-015-3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0020-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-015-3/001.jpg</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2596,27 +2596,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0028-1</t>
+          <t>roza-ua-38k-016</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0028-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-016/001.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-016/002.jpg,https://oleks-netizen.github.io/product-images/roza-ua-38k-016/004.jpg</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0028-2</t>
+          <t>roza-ua-38k-016-1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0028-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-016-1/001.jpg</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2626,12 +2626,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0028-3</t>
+          <t>roza-ua-38k-016-2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0028-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-016-2/001.jpg</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2641,12 +2641,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0028-4</t>
+          <t>roza-ua-38k-016-3</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0028-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/roza-ua-38k-016-3/001.jpg</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2656,342 +2656,342 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0029-1</t>
+          <t>sbros-lmn-001</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0029-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/sbros-lmn-001/001.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-001/002.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-001/004.jpg</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0029-2</t>
+          <t>sbros-lmn-002</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0029-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/sbros-lmn-002/001.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-002/002.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-002/004.jpg</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0029-3</t>
+          <t>sbros-lmn-003</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0029-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/sbros-lmn-003/001.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-003/002.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-003/004.jpg</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0029-4</t>
+          <t>sbros-lmn-004</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0029-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/sbros-lmn-004/001.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-004/002.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-004/004.jpg</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0030-1</t>
+          <t>sbros-lmn-005</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0030-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/sbros-lmn-005/001.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-005/002.jpg,https://oleks-netizen.github.io/product-images/sbros-lmn-005/004.jpg</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0030-2</t>
+          <t>tkn-48tkt-006</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0030-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tkn-48tkt-006/001.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-006/002.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-006/003.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-006/004.jpg</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0030-3</t>
+          <t>tkn-48tkt-007</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0030-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tkn-48tkt-007/001.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/002.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/003.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/004.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/005.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/006.jpg,https://oleks-netizen.github.io/product-images/tkn-48tkt-007/007.jpg</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0030-4</t>
+          <t>tktcl-police-001</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0030-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tktcl-police-001/001.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/002.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/003.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/005.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/006.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/007.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/008.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/009.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/010.jpg,https://oleks-netizen.github.io/product-images/tktcl-police-001/011.jpg</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0031-1</t>
+          <t>tur-avtmt-35k-0011</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0031-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-avtmt-35k-0011/001.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-0011/002.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-0011/004.jpg</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0031-2</t>
+          <t>tur-avtmt-35k-002</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0031-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-avtmt-35k-002/001.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-002/002.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-002/004.jpg</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0031-3</t>
+          <t>tur-avtmt-35k-003</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0031-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-avtmt-35k-003/001.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-003/002.jpg,https://oleks-netizen.github.io/product-images/tur-avtmt-35k-003/004.jpg</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0031-4</t>
+          <t>tur-m-35k-01</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0031-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-m-35k-01/001.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/002.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/004.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/005.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/006.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/007.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/008.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/009.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-01/010.jpg</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0032-1</t>
+          <t>tur-m-35k-02</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0032-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-m-35k-02/001.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/002.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/004.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/005.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/006.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/007.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/008.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/009.jpg,https://oleks-netizen.github.io/product-images/tur-m-35k-02/010.jpg</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0032-2</t>
+          <t>tur-m-40k-08</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0032-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-m-40k-08/001.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/002.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/003.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/004.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/006.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/007.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/008.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/009.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-08/010.jpg</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0032-3</t>
+          <t>tur-m-40k-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0032-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-m-40k-09/001.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/002.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/004.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/005.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/006.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/007.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/008.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/009.jpg,https://oleks-netizen.github.io/product-images/tur-m-40k-09/010.jpg</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0032-4</t>
+          <t>tur-mkr-40k-003</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0032-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-mkr-40k-003/001.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-003/002.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-003/004.jpg</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0033-1</t>
+          <t>tur-mkr-40k-004</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0033-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-mkr-40k-004/001.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-004/003.jpg</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0033-2</t>
+          <t>tur-mkr-40k-006</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0033-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-mkr-40k-006/001.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-006/003.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-006/004.jpg</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0033-3</t>
+          <t>tur-mkr-40k-007</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0033-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-mkr-40k-007/001.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-007/003.jpg</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0033-4</t>
+          <t>tur-mkr-40k-008</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0033-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/tur-mkr-40k-008/001.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-008/003.jpg,https://oleks-netizen.github.io/product-images/tur-mkr-40k-008/004.jpg</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0034-1</t>
+          <t>twnmth-new-0002</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0034-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/twnmth-new-0002/001.jpg,https://oleks-netizen.github.io/product-images/twnmth-new-0002/003.jpg,https://oleks-netizen.github.io/product-images/twnmth-new-0002/004.jpg</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0034-2</t>
+          <t>ua-33mkr-itl-0057</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0034-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057/001.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057/002.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057/004.jpg</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0034-3</t>
+          <t>ua-33mkr-itl-0057-1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0034-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057-1/001.jpg</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3001,12 +3001,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0034-4</t>
+          <t>ua-33mkr-itl-0057-2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0034-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057-2/001.jpg</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3016,12 +3016,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0035-1</t>
+          <t>ua-33mkr-itl-0057-3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0035-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0057-3/001.jpg</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3031,27 +3031,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0035-2</t>
+          <t>ua-33mkr-itl-0058</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0035-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058/001.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058/003.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058/004.jpg</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0035-3</t>
+          <t>ua-33mkr-itl-0058-1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0035-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058-1/001.jpg</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3061,12 +3061,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0035-4</t>
+          <t>ua-33mkr-itl-0058-2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0035-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058-2/001.jpg</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3076,12 +3076,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0036-1</t>
+          <t>ua-33mkr-itl-0058-3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0036-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0058-3/001.jpg</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3091,27 +3091,27 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0036-2</t>
+          <t>ua-33mkr-itl-0059</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0036-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059/001.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059/003.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059/004.jpg</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0036-3</t>
+          <t>ua-33mkr-itl-0059-1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0036-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059-1/001.jpg</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3121,12 +3121,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ua-38mkr-itl-0036-4</t>
+          <t>ua-33mkr-itl-0059-2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0036-4/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059-2/001.jpg</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3136,31 +3136,5161 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Weatro uzk-k15zh-ua-03</t>
+          <t>ua-33mkr-itl-0059-3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/Weatro uzk-k15zh-ua-03/001.jpg,https://oleks-netizen.github.io/product-images/Weatro uzk-k15zh-ua-03/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0059-3/001.jpg</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>zh3k-6336</t>
+          <t>ua-33mkr-itl-0060</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/zh3k-6336/001.jpg,https://oleks-netizen.github.io/product-images/zh3k-6336/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060/001.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060/003.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060/004.jpg</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0060-1</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0060-2</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0060-3</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0060-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0061</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061/001.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061/002.jpg,https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061/004.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0061-1</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0061-2</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ua-33mkr-itl-0061-3</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-itl-0061-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0021</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0021/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0021/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0021/004.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0022</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0022/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0022/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0022/004.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0023</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0023/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0023/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0023/004.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0024</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0024/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0024/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0024/004.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0025</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0025/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0025/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0025/004.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0026/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0026/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0026/004.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ua-38mkr-0027</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-0027/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0027/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-0027/004.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0037</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037/004.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0037-1</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0037-2</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0037-3</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0037-4</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0037-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0038</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038/004.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0038-1</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0038-2</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0038-3</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0038-4</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0038-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0039</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039/004.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0039-1</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0039-2</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0039-3</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0039-4</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0039-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0040</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040/004.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0040-1</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0040-2</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0040-3</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0040-4</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0040-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0041</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041/004.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0041-1</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0041-2</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0041-3</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0041-4</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0041-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0042</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042/004.jpg</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0042-1</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0042-2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0042-3</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0042-4</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0042-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0043</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043/004.jpg</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0043-1</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0043-2</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0043-3</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0043-4</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0043-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0044</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044/004.jpg</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0044-1</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0044-2</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0044-3</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0044-4</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0044-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0045</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045/004.jpg</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0045-1</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0045-2</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0045-3</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0045-4</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0045-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0046</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046/004.jpg</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0046-1</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0046-2</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0046-3</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0046-4</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0046-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0047</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047/004.jpg</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0047-1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0047-2</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0047-3</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0047-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0048</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048/004.jpg</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0048-1</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0048-2</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0048-3</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0048-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0049</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049/004.jpg</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0049-1</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0049-2</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0049-3</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0049-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0050</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050/004.jpg</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0050-1</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0050-2</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0050-3</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0050-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0051</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051/004.jpg</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0051-1</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0051-2</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0051-3</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0051-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052/004.jpg</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052-1</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052-2</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052-6</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052-6/001.jpg</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052-7</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052-7/001.jpg</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0052-8</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0052-8/001.jpg</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0053</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053/004.jpg</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0053-1</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0053-2</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0053-3</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0053-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0054</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054/003.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054/004.jpg</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0054-1</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0054-2</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0054-3</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0054-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0055</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055/004.jpg</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0055-1</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0055-2</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0055-3</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0055-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0056</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056/001.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056/002.jpg,https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056/004.jpg</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0056-1</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0056-2</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ua-38mkr-itl-0056-3</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-38mkr-itl-0056-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-01</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-01/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-01/003.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-01/004.jpg</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-01-1</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-01-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-01-2</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-01-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-010</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-010/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-010/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-010/004.jpg</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-010-1</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-010-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-010-2</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-010-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-02</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-02/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-02/003.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-02/004.jpg</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-02-1</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-02-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-02-2</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-02-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-03</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-03/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-03/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-03/004.jpg</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-03-1</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-03-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-03-2</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-03-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-04</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-04/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-04/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-04/004.jpg</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-04-1</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-04-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-04-2</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-04-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-05</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-05/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-05/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-05/004.jpg</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-05-1</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-05-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-05-2</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-05-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-06</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-06/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-06/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-06/004.jpg</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-06-1</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-06-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-06-2</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-06-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-07</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-07/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-07/002.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-07/004.jpg</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-07-1</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-07-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-07-2</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-07-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-08</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-08/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-08/003.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-08/004.jpg</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-08-1</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-08-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-08-2</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-08-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-09</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-09/001.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-09/003.jpg,https://oleks-netizen.github.io/product-images/ua-avtmt-35k-09/004.jpg</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-09-1</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-09-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>ua-avtmt-35k-09-2</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-09-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>wtro-1-208B</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-1-208B/001.jpg,https://oleks-netizen.github.io/product-images/wtro-1-208B/002.jpg,https://oleks-netizen.github.io/product-images/wtro-1-208B/003.jpg,https://oleks-netizen.github.io/product-images/wtro-1-208B/004.jpg,https://oleks-netizen.github.io/product-images/wtro-1-208B/005.jpg,https://oleks-netizen.github.io/product-images/wtro-1-208B/007.jpg</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>wtro-163-25F</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-163-25F/001.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/002.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/003.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/005.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/006.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/007.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/008.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/009.jpg,https://oleks-netizen.github.io/product-images/wtro-163-25F/010.jpg</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>wtro-165-13-2</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-165-13-2/001.jpg,https://oleks-netizen.github.io/product-images/wtro-165-13-2/002.jpg,https://oleks-netizen.github.io/product-images/wtro-165-13-2/003.jpg,https://oleks-netizen.github.io/product-images/wtro-165-13-2/004.jpg,https://oleks-netizen.github.io/product-images/wtro-165-13-2/005.jpg,https://oleks-netizen.github.io/product-images/wtro-165-13-2/006.jpg</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>wtro-168-24B</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-168-24B/001.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24B/002.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24B/003.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24B/005.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24B/006.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24B/007.jpg</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>wtro-168-24C</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-168-24C/001.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24C/002.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24C/003.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24C/004.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24C/006.jpg</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>wtro-168-24F</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-168-24F/001.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24F/002.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24F/003.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24F/004.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24F/005.jpg,https://oleks-netizen.github.io/product-images/wtro-168-24F/007.jpg</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>wtro-168-58</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-168-58/001.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/002.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/003.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/005.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/006.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/007.jpg,https://oleks-netizen.github.io/product-images/wtro-168-58/008.jpg</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>wtro-508</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-508/001.jpg,https://oleks-netizen.github.io/product-images/wtro-508/002.jpg,https://oleks-netizen.github.io/product-images/wtro-508/004.jpg,https://oleks-netizen.github.io/product-images/wtro-508/005.jpg,https://oleks-netizen.github.io/product-images/wtro-508/006.jpg</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>wtro-nw-105-3-015</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/003.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/005.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/006.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/007.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/008.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-105-3-015/009.jpg</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>wtro-nw-163-100-013</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/004.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/005.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/006.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-100-013/007.jpg</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>wtro-nw-163-33-03</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-163-33-03/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-33-03/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-33-03/004.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-33-03/005.jpg</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>wtro-nw-163-34-012</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/004.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/005.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/006.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-163-34-012/007.jpg</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>wtro-nw-168-17-05</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/003.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/004.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/006.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-17-05/007.jpg</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>wtro-nw-168-40-01</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-168-40-01/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-40-01/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-40-01/003.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-40-01/005.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-168-40-01/006.jpg</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>wtro-nw-208K-09</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-nw-208K-09/001.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-208K-09/002.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-208K-09/004.jpg,https://oleks-netizen.github.io/product-images/wtro-nw-208K-09/005.jpg</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0051</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051/004.jpg</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0051-1</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0051-2</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0051-3</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0051-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0052</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052/004.jpg</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0052-1</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0052-2</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0052-3</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0052-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0053</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053/004.jpg</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0053-1</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0053-2</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0053-3</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0053-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0054</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054/004.jpg</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0054-1</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0054-2</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0054-3</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0054-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0055</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055/004.jpg</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0055-1</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0055-2</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0055-3</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0055-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0056</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056/004.jpg</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0056-1</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0056-2</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0056-3</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0056-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0057</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057/004.jpg</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0057-1</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0057-2</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0057-3</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0057-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0058</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058/004.jpg</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0058-1</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0058-2</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0058-3</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0058-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0059</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059/004.jpg</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0059-1</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0059-2</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0059-3</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0059-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0060</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060/004.jpg</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0060-1</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0060-2</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0060-3</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0060-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0061</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061/004.jpg</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0061-1</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0061-2</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0061-3</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0061-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0062</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062/004.jpg</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0062-1</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0062-2</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0062-3</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0062-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0063</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063/004.jpg</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0063-1</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0063-2</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0063-3</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0063-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0064</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064/004.jpg</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0064-1</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0064-2</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0064-3</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0064-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0065</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065/004.jpg</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0065-1</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0065-2</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0065-3</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0065-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0066</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066/004.jpg</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0066-1</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0066-2</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0066-3</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0066-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0086</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086/004.jpg</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0086-1</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0086-2</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0086-3</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0086-4</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0086-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0087</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087/004.jpg</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0087-1</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0087-2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0087-3</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0087-4</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0087-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0088</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088/004.jpg</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0088-1</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0088-2</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0088-3</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0088-4</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0088-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0089</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089/004.jpg</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0089-1</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0089-2</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0089-3</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0089-4</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0089-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0090</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090/004.jpg</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0090-1</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0090-2</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0090-3</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0090-4</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0090-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0091</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091/004.jpg</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0091-1</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0091-2</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0091-3</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0091-4</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0091-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0092</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092/004.jpg</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0092-1</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0092-2</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0092-3</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0092-4</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0092-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0093</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093/004.jpg</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0093-1</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0093-2</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0093-3</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0093-4</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0093-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0094</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094/004.jpg</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0094-1</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0094-2</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0094-3</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0094-4</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0094-4/001.jpg</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0123</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123/004.jpg</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0123-1</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0123-2</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0123-3</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0123-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0124</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124/004.jpg</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0124-1</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0124-2</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0124-3</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0124-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0125</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125/004.jpg</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0125-1</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0125-2</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>wtro-tur-38k-0125-3</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-38k-0125-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0044</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044/004.jpg</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0044-1</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0044-2</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0044-3</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0044-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0045</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045/004.jpg</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0045-1</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0045-2</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0045-3</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0045-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0046</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046/004.jpg</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0046-1</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0046-2</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0046-3</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0046-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0047</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047/004.jpg</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0047-1</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0047-2</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0047-3</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0047-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0048</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048/002.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048/004.jpg</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0048-1</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0048-2</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0048-3</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0048-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0049</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049/004.jpg</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0049-1</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0049-2</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0049-3</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0049-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0050</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050/001.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050/003.jpg,https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050/004.jpg</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0050-1</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0050-2</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>wtro-tur-43k-0050-3</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-tur-43k-0050-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0033</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033/004.jpg</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0033-1</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0033-2</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0033-3</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0033-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0034</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034/004.jpg</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0034-1</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0034-2</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0034-3</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0034-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0035</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035/004.jpg</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0035-1</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0035-2</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0035-3</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0035-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0036</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036/004.jpg</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0036-1</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0036-2</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0036-3</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0036-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0037-1</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0037-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0037-2</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0037-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0037-3</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0037-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0038-1</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0038-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0038-2</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0038-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0038-3</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0038-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0039</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039/004.jpg</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0039-1</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0039-2</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0039-3</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0039-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0040</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040/004.jpg</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0040-1</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0040-2</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0040-3</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0040-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0041</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041/004.jpg</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0041-1</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0041-2</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0041-3</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0041-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0042</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042/003.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042/004.jpg</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0042-1</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0042-2</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0042-3</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0042-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0043</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043/001.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043/002.jpg,https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043/004.jpg</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0043-1</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0043-2</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043-2/001.jpg</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>wtro-ua-38k-0043-3</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/wtro-ua-38k-0043-3/001.jpg</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>125V1FX92-BLACK</t>
+          <t>1065618885</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1FX92-BLACK/001.jpg,https://oleks-netizen.github.io/product-images/125V1FX92-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/001.jpg,https://oleks-netizen.github.io/product-images/1065618885/002.jpg,https://oleks-netizen.github.io/product-images/1065618885/003.jpg,https://oleks-netizen.github.io/product-images/1065618885/004.jpg,https://oleks-netizen.github.io/product-images/1065618885/006.jpg,https://oleks-netizen.github.io/product-images/1065618885/007.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>125V1GENAV37-BLACK</t>
+          <t>30311066</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1GENAV37-BLACK/001.jpg,https://oleks-netizen.github.io/product-images/125V1GENAV37-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311066/001.jpg,https://oleks-netizen.github.io/product-images/30311066/002.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150V1GENAV36-BLACK</t>
+          <t>30311067</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150V1GENAV36-BLACK/001.jpg,https://oleks-netizen.github.io/product-images/150V1GENAV36-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311067/001.jpg,https://oleks-netizen.github.io/product-images/30311067/002.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,12 +481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>150VFX85-BLACK</t>
+          <t>30311068</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150VFX85-BLACK/001.jpg,https://oleks-netizen.github.io/product-images/150VFX85-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311068/001.jpg,https://oleks-netizen.github.io/product-images/30311068/002.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,27 +496,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>31111120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18010/001.jpg,https://oleks-netizen.github.io/product-images/18010/002.jpg,https://oleks-netizen.github.io/product-images/18010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/31111120/001.jpg,https://oleks-netizen.github.io/product-images/31111120/003.jpg,https://oleks-netizen.github.io/product-images/31111120/004.jpg,https://oleks-netizen.github.io/product-images/31111120/005.jpg,https://oleks-netizen.github.io/product-images/31111120/006.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>31211120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18240/001.jpg,https://oleks-netizen.github.io/product-images/18240/002.jpg,https://oleks-netizen.github.io/product-images/18240/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/31211120/001.jpg,https://oleks-netizen.github.io/product-images/31211120/002.jpg,https://oleks-netizen.github.io/product-images/31211120/003.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,166 +526,391 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BN-BELT-3-RAVEN</t>
+          <t>50223060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/001.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/002.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223060/001.jpg,https://oleks-netizen.github.io/product-images/50223060/002.jpg,https://oleks-netizen.github.io/product-images/50223060/003.jpg,https://oleks-netizen.github.io/product-images/50223060/004.jpg,https://oleks-netizen.github.io/product-images/50223060/005.jpg,https://oleks-netizen.github.io/product-images/50223060/007.jpg,https://oleks-netizen.github.io/product-images/50223060/008.jpg,https://oleks-netizen.github.io/product-images/50223060/009.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BN-BELT-8-RAVEN</t>
+          <t>50223161</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/001.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/002.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223161/001.jpg,https://oleks-netizen.github.io/product-images/50223161/002.jpg,https://oleks-netizen.github.io/product-images/50223161/003.jpg,https://oleks-netizen.github.io/product-images/50223161/005.jpg,https://oleks-netizen.github.io/product-images/50223161/006.jpg,https://oleks-netizen.github.io/product-images/50223161/007.jpg,https://oleks-netizen.github.io/product-images/50223161/008.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>50223401</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/001.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/002.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/003.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/004.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/005.jpg,https://oleks-netizen.github.io/product-images/BS70106-01/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223401/001.jpg,https://oleks-netizen.github.io/product-images/50223401/002.jpg,https://oleks-netizen.github.io/product-images/50223401/003.jpg,https://oleks-netizen.github.io/product-images/50223401/004.jpg,https://oleks-netizen.github.io/product-images/50223401/005.jpg,https://oleks-netizen.github.io/product-images/50223401/007.jpg,https://oleks-netizen.github.io/product-images/50223401/008.jpg,https://oleks-netizen.github.io/product-images/50223401/009.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>50223406</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/001.jpg,https://oleks-netizen.github.io/product-images/NEW-ALN-010/002.jpg,https://oleks-netizen.github.io/product-images/NEW-ALN-010/003.jpg,https://oleks-netizen.github.io/product-images/NEW-ALN-010/004.jpg,https://oleks-netizen.github.io/product-images/NEW-ALN-010/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223406/001.jpg,https://oleks-netizen.github.io/product-images/50223406/003.jpg,https://oleks-netizen.github.io/product-images/50223406/004.jpg,https://oleks-netizen.github.io/product-images/50223406/005.jpg,https://oleks-netizen.github.io/product-images/50223406/006.jpg,https://oleks-netizen.github.io/product-images/50223406/007.jpg,https://oleks-netizen.github.io/product-images/50223406/008.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0014</t>
+          <t>51411101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0014/001.jpg,https://oleks-netizen.github.io/product-images/NW-TUR-35K-0014/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411101/001.jpg,https://oleks-netizen.github.io/product-images/51411101/002.jpg,https://oleks-netizen.github.io/product-images/51411101/003.jpg,https://oleks-netizen.github.io/product-images/51411101/004.jpg,https://oleks-netizen.github.io/product-images/51411101/006.jpg,https://oleks-netizen.github.io/product-images/51411101/007.jpg,https://oleks-netizen.github.io/product-images/51411101/008.jpg,https://oleks-netizen.github.io/product-images/51411101/009.jpg,https://oleks-netizen.github.io/product-images/51411101/010.jpg,https://oleks-netizen.github.io/product-images/51411101/011.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0016</t>
+          <t>53400066</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0016/001.jpg,https://oleks-netizen.github.io/product-images/NW-TUR-35K-0016/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400066/001.jpg,https://oleks-netizen.github.io/product-images/53400066/002.jpg,https://oleks-netizen.github.io/product-images/53400066/004.jpg,https://oleks-netizen.github.io/product-images/53400066/005.jpg,https://oleks-netizen.github.io/product-images/53400066/006.jpg,https://oleks-netizen.github.io/product-images/53400066/007.jpg,https://oleks-netizen.github.io/product-images/53400066/008.jpg,https://oleks-netizen.github.io/product-images/53400066/009.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NWKZ-38MM-KIT-006</t>
+          <t>53400067</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/001.jpg,https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/002.jpg,https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400067/001.jpg,https://oleks-netizen.github.io/product-images/53400067/002.jpg,https://oleks-netizen.github.io/product-images/53400067/003.jpg,https://oleks-netizen.github.io/product-images/53400067/004.jpg,https://oleks-netizen.github.io/product-images/53400067/005.jpg,https://oleks-netizen.github.io/product-images/53400067/007.jpg,https://oleks-netizen.github.io/product-images/53400067/008.jpg,https://oleks-netizen.github.io/product-images/53400067/009.jpg,https://oleks-netizen.github.io/product-images/53400067/010.jpg,https://oleks-netizen.github.io/product-images/53400067/011.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V1125FX01-BLACK</t>
+          <t>54650001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1125FX01-BLACK/001.jpg,https://oleks-netizen.github.io/product-images/V1125FX01-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/54650001/001.jpg,https://oleks-netizen.github.io/product-images/54650001/002.jpg,https://oleks-netizen.github.io/product-images/54650001/003.jpg,https://oleks-netizen.github.io/product-images/54650001/004.jpg,https://oleks-netizen.github.io/product-images/54650001/005.jpg,https://oleks-netizen.github.io/product-images/54650001/006.jpg,https://oleks-netizen.github.io/product-images/54650001/007.jpg,https://oleks-netizen.github.io/product-images/54650001/008.jpg,https://oleks-netizen.github.io/product-images/54650001/010.jpg,https://oleks-netizen.github.io/product-images/54650001/011.jpg,https://oleks-netizen.github.io/product-images/54650001/012.jpg,https://oleks-netizen.github.io/product-images/54650001/013.jpg,https://oleks-netizen.github.io/product-images/54650001/014.jpg,https://oleks-netizen.github.io/product-images/54650001/015.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X2</t>
+          <t>80460406</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/001.jpg,https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/002.jpg,https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460406/001.jpg,https://oleks-netizen.github.io/product-images/80460406/002.jpg,https://oleks-netizen.github.io/product-images/80460406/003.jpg,https://oleks-netizen.github.io/product-images/80460406/004.jpg,https://oleks-netizen.github.io/product-images/80460406/005.jpg,https://oleks-netizen.github.io/product-images/80460406/006.jpg,https://oleks-netizen.github.io/product-images/80460406/007.jpg,https://oleks-netizen.github.io/product-images/80460406/008.jpg,https://oleks-netizen.github.io/product-images/80460406/010.jpg,https://oleks-netizen.github.io/product-images/80460406/011.jpg,https://oleks-netizen.github.io/product-images/80460406/012.jpg,https://oleks-netizen.github.io/product-images/80460406/013.jpg,https://oleks-netizen.github.io/product-images/80460406/014.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X3</t>
+          <t>80460419</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/001.jpg,https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/002.jpg,https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460419/001.jpg,https://oleks-netizen.github.io/product-images/80460419/002.jpg,https://oleks-netizen.github.io/product-images/80460419/003.jpg,https://oleks-netizen.github.io/product-images/80460419/004.jpg,https://oleks-netizen.github.io/product-images/80460419/005.jpg,https://oleks-netizen.github.io/product-images/80460419/006.jpg,https://oleks-netizen.github.io/product-images/80460419/007.jpg,https://oleks-netizen.github.io/product-images/80460419/008.jpg,https://oleks-netizen.github.io/product-images/80460419/009.jpg,https://oleks-netizen.github.io/product-images/80460419/010.jpg,https://oleks-netizen.github.io/product-images/80460419/011.jpg,https://oleks-netizen.github.io/product-images/80460419/012.jpg,https://oleks-netizen.github.io/product-images/80460419/014.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BN-BELT-3-FLINT</t>
+          <t>BN-PM-12-light-beige</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/002.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/003.jpg,https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/004.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BN-PM-12-navy-blue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/003.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BN-PM-12-red</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/004.jpg</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/001.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/002.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/003.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/005.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/006.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/007.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/008.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/009.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/008.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/001.jpg,https://oleks-netizen.github.io/product-images/L340-037744/003.jpg,https://oleks-netizen.github.io/product-images/L340-037744/004.jpg,https://oleks-netizen.github.io/product-images/L340-037744/005.jpg,https://oleks-netizen.github.io/product-images/L340-037744/006.jpg,https://oleks-netizen.github.io/product-images/L340-037744/007.jpg,https://oleks-netizen.github.io/product-images/L340-037744/008.jpg,https://oleks-netizen.github.io/product-images/L340-037744/009.jpg,https://oleks-netizen.github.io/product-images/L340-037744/010.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ua-33mkr-0014-1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-1/001.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WELL-11705</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11705/001.jpg,https://oleks-netizen.github.io/product-images/WELL-11705/003.jpg,https://oleks-netizen.github.io/product-images/WELL-11705/004.jpg,https://oleks-netizen.github.io/product-images/WELL-11705/005.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/articles_summary.xlsx
+++ b/articles_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,57 +436,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1065618885</t>
+          <t>1102060033-96492</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/1065618885/001.jpg,https://oleks-netizen.github.io/product-images/1065618885/002.jpg,https://oleks-netizen.github.io/product-images/1065618885/003.jpg,https://oleks-netizen.github.io/product-images/1065618885/004.jpg,https://oleks-netizen.github.io/product-images/1065618885/006.jpg,https://oleks-netizen.github.io/product-images/1065618885/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1102060033-96492/001.jpg,https://oleks-netizen.github.io/product-images/1102060033-96492/002.jpg,https://oleks-netizen.github.io/product-images/1102060033-96492/004.jpg</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30311066</t>
+          <t>463110</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30311066/001.jpg,https://oleks-netizen.github.io/product-images/30311066/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/463110/001.jpg,https://oleks-netizen.github.io/product-images/463110/002.jpg,https://oleks-netizen.github.io/product-images/463110/003.jpg,https://oleks-netizen.github.io/product-images/463110/004.jpg,https://oleks-netizen.github.io/product-images/463110/005.jpg,https://oleks-netizen.github.io/product-images/463110/007.jpg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30311067</t>
+          <t>463120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30311067/001.jpg,https://oleks-netizen.github.io/product-images/30311067/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/463120/001.jpg,https://oleks-netizen.github.io/product-images/463120/002.jpg,https://oleks-netizen.github.io/product-images/463120/004.jpg,https://oleks-netizen.github.io/product-images/463120/005.jpg,https://oleks-netizen.github.io/product-images/463120/006.jpg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30311068</t>
+          <t>463610</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/30311068/001.jpg,https://oleks-netizen.github.io/product-images/30311068/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/463610/001.jpg,https://oleks-netizen.github.io/product-images/463610/002.jpg</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,57 +496,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>31111120</t>
+          <t>5241701</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/31111120/001.jpg,https://oleks-netizen.github.io/product-images/31111120/003.jpg,https://oleks-netizen.github.io/product-images/31111120/004.jpg,https://oleks-netizen.github.io/product-images/31111120/005.jpg,https://oleks-netizen.github.io/product-images/31111120/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5241701/001.jpg,https://oleks-netizen.github.io/product-images/5241701/002.jpg,https://oleks-netizen.github.io/product-images/5241701/004.jpg,https://oleks-netizen.github.io/product-images/5241701/005.jpg,https://oleks-netizen.github.io/product-images/5241701/006.jpg,https://oleks-netizen.github.io/product-images/5241701/007.jpg,https://oleks-netizen.github.io/product-images/5241701/008.jpg,https://oleks-netizen.github.io/product-images/5241701/009.jpg,https://oleks-netizen.github.io/product-images/5241701/010.jpg,https://oleks-netizen.github.io/product-images/5241701/011.jpg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31211120</t>
+          <t>5241801</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/31211120/001.jpg,https://oleks-netizen.github.io/product-images/31211120/002.jpg,https://oleks-netizen.github.io/product-images/31211120/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5241801/001.jpg,https://oleks-netizen.github.io/product-images/5241801/003.jpg,https://oleks-netizen.github.io/product-images/5241801/004.jpg,https://oleks-netizen.github.io/product-images/5241801/005.jpg,https://oleks-netizen.github.io/product-images/5241801/006.jpg,https://oleks-netizen.github.io/product-images/5241801/007.jpg,https://oleks-netizen.github.io/product-images/5241801/008.jpg,https://oleks-netizen.github.io/product-images/5241801/009.jpg,https://oleks-netizen.github.io/product-images/5241801/010.jpg,https://oleks-netizen.github.io/product-images/5241801/011.jpg</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50223060</t>
+          <t>5246801W</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/50223060/001.jpg,https://oleks-netizen.github.io/product-images/50223060/002.jpg,https://oleks-netizen.github.io/product-images/50223060/003.jpg,https://oleks-netizen.github.io/product-images/50223060/004.jpg,https://oleks-netizen.github.io/product-images/50223060/005.jpg,https://oleks-netizen.github.io/product-images/50223060/007.jpg,https://oleks-netizen.github.io/product-images/50223060/008.jpg,https://oleks-netizen.github.io/product-images/50223060/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/5246801W/001.jpg,https://oleks-netizen.github.io/product-images/5246801W/002.jpg,https://oleks-netizen.github.io/product-images/5246801W/003.jpg,https://oleks-netizen.github.io/product-images/5246801W/004.jpg,https://oleks-netizen.github.io/product-images/5246801W/006.jpg,https://oleks-netizen.github.io/product-images/5246801W/007.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>50223161</t>
+          <t>bx3101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/50223161/001.jpg,https://oleks-netizen.github.io/product-images/50223161/002.jpg,https://oleks-netizen.github.io/product-images/50223161/003.jpg,https://oleks-netizen.github.io/product-images/50223161/005.jpg,https://oleks-netizen.github.io/product-images/50223161/006.jpg,https://oleks-netizen.github.io/product-images/50223161/007.jpg,https://oleks-netizen.github.io/product-images/50223161/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/bx3101/001.jpg,https://oleks-netizen.github.io/product-images/bx3101/002.jpg,https://oleks-netizen.github.io/product-images/bx3101/003.jpg,https://oleks-netizen.github.io/product-images/bx3101/004.jpg,https://oleks-netizen.github.io/product-images/bx3101/005.jpg,https://oleks-netizen.github.io/product-images/bx3101/007.jpg,https://oleks-netizen.github.io/product-images/bx3101/008.jpg</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,222 +556,222 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>50223401</t>
+          <t>bx3101br</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/50223401/001.jpg,https://oleks-netizen.github.io/product-images/50223401/002.jpg,https://oleks-netizen.github.io/product-images/50223401/003.jpg,https://oleks-netizen.github.io/product-images/50223401/004.jpg,https://oleks-netizen.github.io/product-images/50223401/005.jpg,https://oleks-netizen.github.io/product-images/50223401/007.jpg,https://oleks-netizen.github.io/product-images/50223401/008.jpg,https://oleks-netizen.github.io/product-images/50223401/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/bx3101br/001.jpg,https://oleks-netizen.github.io/product-images/bx3101br/002.jpg,https://oleks-netizen.github.io/product-images/bx3101br/003.jpg,https://oleks-netizen.github.io/product-images/bx3101br/004.jpg,https://oleks-netizen.github.io/product-images/bx3101br/006.jpg,https://oleks-netizen.github.io/product-images/bx3101br/007.jpg</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>50223406</t>
+          <t>FA-0910-4lx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/50223406/001.jpg,https://oleks-netizen.github.io/product-images/50223406/003.jpg,https://oleks-netizen.github.io/product-images/50223406/004.jpg,https://oleks-netizen.github.io/product-images/50223406/005.jpg,https://oleks-netizen.github.io/product-images/50223406/006.jpg,https://oleks-netizen.github.io/product-images/50223406/007.jpg,https://oleks-netizen.github.io/product-images/50223406/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0910-4lx/001.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/002.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/004.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/005.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/006.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/007.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/008.jpg,https://oleks-netizen.github.io/product-images/FA-0910-4lx/009.jpg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51411101</t>
+          <t>FA-5402-4lx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51411101/001.jpg,https://oleks-netizen.github.io/product-images/51411101/002.jpg,https://oleks-netizen.github.io/product-images/51411101/003.jpg,https://oleks-netizen.github.io/product-images/51411101/004.jpg,https://oleks-netizen.github.io/product-images/51411101/006.jpg,https://oleks-netizen.github.io/product-images/51411101/007.jpg,https://oleks-netizen.github.io/product-images/51411101/008.jpg,https://oleks-netizen.github.io/product-images/51411101/009.jpg,https://oleks-netizen.github.io/product-images/51411101/010.jpg,https://oleks-netizen.github.io/product-images/51411101/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-5402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/FA-5402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/FA-5402-4lx/003.jpg,https://oleks-netizen.github.io/product-images/FA-5402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/FA-5402-4lx/005.jpg</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>53400066</t>
+          <t>FC-5402-4lx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400066/001.jpg,https://oleks-netizen.github.io/product-images/53400066/002.jpg,https://oleks-netizen.github.io/product-images/53400066/004.jpg,https://oleks-netizen.github.io/product-images/53400066/005.jpg,https://oleks-netizen.github.io/product-images/53400066/006.jpg,https://oleks-netizen.github.io/product-images/53400066/007.jpg,https://oleks-netizen.github.io/product-images/53400066/008.jpg,https://oleks-netizen.github.io/product-images/53400066/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FC-5402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/FC-5402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/FC-5402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/FC-5402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/FC-5402-4lx/006.jpg</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>53400067</t>
+          <t>fz375235_taup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/53400067/001.jpg,https://oleks-netizen.github.io/product-images/53400067/002.jpg,https://oleks-netizen.github.io/product-images/53400067/003.jpg,https://oleks-netizen.github.io/product-images/53400067/004.jpg,https://oleks-netizen.github.io/product-images/53400067/005.jpg,https://oleks-netizen.github.io/product-images/53400067/007.jpg,https://oleks-netizen.github.io/product-images/53400067/008.jpg,https://oleks-netizen.github.io/product-images/53400067/009.jpg,https://oleks-netizen.github.io/product-images/53400067/010.jpg,https://oleks-netizen.github.io/product-images/53400067/011.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/fz375235_taup/001.jpg,https://oleks-netizen.github.io/product-images/fz375235_taup/002.jpg,https://oleks-netizen.github.io/product-images/fz375235_taup/003.jpg,https://oleks-netizen.github.io/product-images/fz375235_taup/004.jpg</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>54650001</t>
+          <t>fz376023_chok</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/54650001/001.jpg,https://oleks-netizen.github.io/product-images/54650001/002.jpg,https://oleks-netizen.github.io/product-images/54650001/003.jpg,https://oleks-netizen.github.io/product-images/54650001/004.jpg,https://oleks-netizen.github.io/product-images/54650001/005.jpg,https://oleks-netizen.github.io/product-images/54650001/006.jpg,https://oleks-netizen.github.io/product-images/54650001/007.jpg,https://oleks-netizen.github.io/product-images/54650001/008.jpg,https://oleks-netizen.github.io/product-images/54650001/010.jpg,https://oleks-netizen.github.io/product-images/54650001/011.jpg,https://oleks-netizen.github.io/product-images/54650001/012.jpg,https://oleks-netizen.github.io/product-images/54650001/013.jpg,https://oleks-netizen.github.io/product-images/54650001/014.jpg,https://oleks-netizen.github.io/product-images/54650001/015.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/fz376023_chok/001.jpg,https://oleks-netizen.github.io/product-images/fz376023_chok/002.jpg,https://oleks-netizen.github.io/product-images/fz376023_chok/004.jpg,https://oleks-netizen.github.io/product-images/fz376023_chok/005.jpg,https://oleks-netizen.github.io/product-images/fz376023_chok/006.jpg</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>80460406</t>
+          <t>fz378839_chok</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460406/001.jpg,https://oleks-netizen.github.io/product-images/80460406/002.jpg,https://oleks-netizen.github.io/product-images/80460406/003.jpg,https://oleks-netizen.github.io/product-images/80460406/004.jpg,https://oleks-netizen.github.io/product-images/80460406/005.jpg,https://oleks-netizen.github.io/product-images/80460406/006.jpg,https://oleks-netizen.github.io/product-images/80460406/007.jpg,https://oleks-netizen.github.io/product-images/80460406/008.jpg,https://oleks-netizen.github.io/product-images/80460406/010.jpg,https://oleks-netizen.github.io/product-images/80460406/011.jpg,https://oleks-netizen.github.io/product-images/80460406/012.jpg,https://oleks-netizen.github.io/product-images/80460406/013.jpg,https://oleks-netizen.github.io/product-images/80460406/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/fz378839_chok/001.jpg,https://oleks-netizen.github.io/product-images/fz378839_chok/002.jpg,https://oleks-netizen.github.io/product-images/fz378839_chok/004.jpg,https://oleks-netizen.github.io/product-images/fz378839_chok/005.jpg,https://oleks-netizen.github.io/product-images/fz378839_chok/006.jpg</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>80460419</t>
+          <t>fz379037_dtaup</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/80460419/001.jpg,https://oleks-netizen.github.io/product-images/80460419/002.jpg,https://oleks-netizen.github.io/product-images/80460419/003.jpg,https://oleks-netizen.github.io/product-images/80460419/004.jpg,https://oleks-netizen.github.io/product-images/80460419/005.jpg,https://oleks-netizen.github.io/product-images/80460419/006.jpg,https://oleks-netizen.github.io/product-images/80460419/007.jpg,https://oleks-netizen.github.io/product-images/80460419/008.jpg,https://oleks-netizen.github.io/product-images/80460419/009.jpg,https://oleks-netizen.github.io/product-images/80460419/010.jpg,https://oleks-netizen.github.io/product-images/80460419/011.jpg,https://oleks-netizen.github.io/product-images/80460419/012.jpg,https://oleks-netizen.github.io/product-images/80460419/014.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/fz379037_dtaup/001.jpg,https://oleks-netizen.github.io/product-images/fz379037_dtaup/002.jpg,https://oleks-netizen.github.io/product-images/fz379037_dtaup/003.jpg,https://oleks-netizen.github.io/product-images/fz379037_dtaup/005.jpg,https://oleks-netizen.github.io/product-images/fz379037_dtaup/006.jpg</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BN-PM-12-light-beige</t>
+          <t>GA-5402-4lx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GA-5402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-5402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GA-5402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-5402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-5402-4lx/006.jpg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BN-PM-12-navy-blue</t>
+          <t>GA-7310-4lx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GA-7310-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-7310-4lx/010.jpg</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BN-PM-12-red</t>
+          <t>GA-9552-4lx</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/001.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/002.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/003.jpg,https://oleks-netizen.github.io/product-images/BN-PM-12-red/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GA-9552-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/010.jpg,https://oleks-netizen.github.io/product-images/GA-9552-4lx/011.jpg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DRS17009-1</t>
+          <t>GC-5402-4lx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17009-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GC-5402-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-5402-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GC-5402-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-5402-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-5402-4lx/006.jpg</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DRS17012-1</t>
+          <t>GC-9552-4lx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17012-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GC-9552-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/008.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/009.jpg,https://oleks-netizen.github.io/product-images/GC-9552-4lx/010.jpg</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DRS17015-1</t>
+          <t>GSE-5565-4lx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17015-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GSE-5565-4lx/001.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/002.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/003.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/004.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/005.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/006.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/007.jpg,https://oleks-netizen.github.io/product-images/GSE-5565-4lx/008.jpg</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DRS17038-1</t>
+          <t>GX-7280-3md</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17038-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GX-7280-3md/001.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/002.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/003.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/004.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/005.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/006.jpg,https://oleks-netizen.github.io/product-images/GX-7280-3md/007.jpg</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -781,136 +781,811 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DRS17082-1</t>
+          <t>HB03334Beige</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17082-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/HB03334Beige/001.jpg,https://oleks-netizen.github.io/product-images/HB03334Beige/002.jpg,https://oleks-netizen.github.io/product-images/HB03334Beige/003.jpg,https://oleks-netizen.github.io/product-images/HB03334Beige/004.jpg,https://oleks-netizen.github.io/product-images/HB03334Beige/006.jpg</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DRS17083-1</t>
+          <t>HB15295B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/002.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17083-1/007.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/HB15295B/001.jpg,https://oleks-netizen.github.io/product-images/HB15295B/002.jpg,https://oleks-netizen.github.io/product-images/HB15295B/003.jpg,https://oleks-netizen.github.io/product-images/HB15295B/004.jpg,https://oleks-netizen.github.io/product-images/HB15295B/005.jpg,https://oleks-netizen.github.io/product-images/HB15295B/007.jpg</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DRS17203-1-26</t>
+          <t>ht-st1-ga1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/001.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/002.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/003.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/005.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/006.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/007.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/008.jpg,https://oleks-netizen.github.io/product-images/DRS17203-1-26/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ht-st1-ga1/001.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga1/002.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga1/003.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga1/004.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga1/005.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga1/006.jpg</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DRS17306-1</t>
+          <t>ht-st1-ga2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17306-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ht-st1-ga2/001.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga2/002.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga2/003.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga2/004.jpg,https://oleks-netizen.github.io/product-images/ht-st1-ga2/005.jpg</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DRS17708-1</t>
+          <t>ht-st1-rb1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17708-1/008.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ht-st1-rb1/001.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb1/002.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb1/003.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb1/004.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb1/005.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb1/006.jpg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DRS17927-1</t>
+          <t>ht-st1-rb2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/001.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/003.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/004.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/005.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/006.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/007.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/008.jpg,https://oleks-netizen.github.io/product-images/DRS17927-1/009.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ht-st1-rb2/001.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb2/002.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb2/003.jpg,https://oleks-netizen.github.io/product-images/ht-st1-rb2/004.jpg,https://oleks-netizen.github.io/product-images/ht-